--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6396</v>
+        <v>6386</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6504</v>
+        <v>6363</v>
       </c>
       <c r="M9" s="3" t="n">
         <v>1621555</v>
@@ -1053,7 +1053,7 @@
         <v>8919</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9105</v>
+        <v>9110</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8722</v>
+        <v>8640</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>154006</v>
@@ -1117,7 +1117,7 @@
         <v>17837</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>1622</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>3243</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1252</v>
+        <v>970</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>1617248</v>
@@ -2396,7 +2396,7 @@
         <v>1622</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3405</v>
+        <v>3399</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>6486</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>12972</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
@@ -2739,10 +2739,10 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3458</v>
+        <v>3289</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3832</v>
+        <v>3243</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>10589</v>
+        <v>9707</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>40</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9669</v>
+        <v>9682</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3131,16 +3131,16 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9707</v>
+        <v>10582</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>10683</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10808</v>
+        <v>10800</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>6486</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
@@ -3500,7 +3500,7 @@
         <v>1784</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>15097</v>
+        <v>14266</v>
       </c>
       <c r="M57" s="3" t="n">
         <v>31406</v>
@@ -3920,7 +3920,7 @@
         <v>15945</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
@@ -3943,18 +3943,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3781</v>
+        <v>5533</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>38</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4490</v>
+        <v>4539</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3975,13 +3975,13 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>5525</v>
+        <v>1649</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10586</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>5017</v>
+        <v>5084</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>6</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4853</v>
+        <v>4368</v>
       </c>
       <c r="M59" s="3" t="n">
         <v>11594</v>
@@ -4048,7 +4048,7 @@
         <v>4728</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
@@ -8347,10 +8347,10 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8530,23 +8530,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D143" s="3" t="n">
-        <v>2919</v>
-      </c>
-      <c r="E143" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>2919</v>
-      </c>
+      <c r="D143" s="3" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr"/>
+      <c r="F143" s="2" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
@@ -8636,7 +8626,7 @@
         <v>4054</v>
       </c>
       <c r="O144" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
@@ -8929,10 +8919,10 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16378</v>
+        <v>16374</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8962,7 +8952,7 @@
         <v>32431</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
@@ -9026,7 +9016,7 @@
         <v>77835</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
@@ -9080,7 +9070,7 @@
         <v>210802</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
@@ -9388,7 +9378,7 @@
         <v>6486</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
@@ -9679,7 +9669,7 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1947</v>
+        <v>1941</v>
       </c>
       <c r="M162" s="3" t="n">
         <v>30939</v>
@@ -9688,7 +9678,7 @@
         <v>1622</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
@@ -9775,7 +9765,7 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3733</v>
+        <v>3783</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
@@ -9786,7 +9776,7 @@
         <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3662</v>
+        <v>3664</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9816,7 +9806,7 @@
         <v>6486</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
@@ -9880,7 +9870,7 @@
         <v>324</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
@@ -10008,7 +9998,7 @@
         <v>1406</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
@@ -10532,7 +10522,7 @@
         <v>32431</v>
       </c>
       <c r="O177" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
@@ -10576,13 +10566,13 @@
         <v>19459</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19621</v>
+        <v>33980</v>
       </c>
       <c r="N178" s="3" t="n">
         <v>38917</v>
       </c>
       <c r="O178" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
@@ -10996,7 +10986,7 @@
         <v>324</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
@@ -11436,7 +11426,7 @@
         <v>324</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
@@ -11663,7 +11653,7 @@
         <v>16216</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="O198" s="2" t="n">
         <v>13</v>
@@ -13402,7 +13392,7 @@
         <v>324</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
@@ -13466,7 +13456,7 @@
         <v>324</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
@@ -13520,7 +13510,7 @@
         <v>1622</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
@@ -14078,12 +14068,18 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L241" s="3" t="inlineStr"/>
-      <c r="M241" s="3" t="inlineStr"/>
+      <c r="L241" s="3" t="n">
+        <v>26383</v>
+      </c>
+      <c r="M241" s="3" t="n">
+        <v>26383</v>
+      </c>
       <c r="N241" s="3" t="n">
         <v>32431</v>
       </c>
-      <c r="O241" s="2" t="inlineStr"/>
+      <c r="O241" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -14137,7 +14133,7 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>40779</v>
+        <v>40193</v>
       </c>
       <c r="M242" s="3" t="n">
         <v>60082</v>
@@ -14146,7 +14142,7 @@
         <v>77835</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
@@ -14197,7 +14193,7 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>20458</v>
+        <v>20388</v>
       </c>
       <c r="M243" s="3" t="n">
         <v>32431103</v>
@@ -14206,7 +14202,7 @@
         <v>32431</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
@@ -14363,7 +14359,7 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2648</v>
+        <v>2445</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>16216</v>
@@ -14372,7 +14368,7 @@
         <v>3271</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
@@ -15029,10 +15025,10 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15062,7 +15058,7 @@
         <v>649</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>266</v>
+        <v>361</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
@@ -15149,18 +15145,18 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>2726</v>
+        <v>2643</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>1953</v>
+        <v>2039</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -15181,7 +15177,7 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2643</v>
+        <v>2659</v>
       </c>
       <c r="M260" s="3" t="n">
         <v>3765</v>
@@ -15190,7 +15186,7 @@
         <v>3243</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
@@ -15372,7 +15368,7 @@
         <v>1622</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
@@ -15552,13 +15548,13 @@
         <v>9882</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9882</v>
+        <v>12972</v>
       </c>
       <c r="N266" s="3" t="n">
         <v>12972</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
@@ -16202,7 +16198,7 @@
         <v>1622</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
@@ -16637,7 +16633,7 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10478</v>
+        <v>10477</v>
       </c>
       <c r="M285" s="3" t="n">
         <v>16216</v>
@@ -16793,7 +16789,7 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6679</v>
+        <v>7072</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
@@ -16801,10 +16797,10 @@
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6811</v>
+        <v>6819</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16821,16 +16817,16 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7072</v>
+        <v>7266</v>
       </c>
       <c r="M288" s="3" t="n">
         <v>8036</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7422</v>
+        <v>7449</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
@@ -16977,18 +16973,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>1951</v>
+        <v>2531</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>1951</v>
+        <v>2241</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -17009,7 +17005,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>2531</v>
+        <v>3888</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5189</v>
@@ -17018,7 +17014,7 @@
         <v>3243</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
@@ -17049,10 +17045,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4455</v>
+        <v>4503</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17210,7 +17206,7 @@
         <v>7398</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
@@ -17291,11 +17287,11 @@
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G296" s="3" t="n">
         <v>32431</v>
@@ -17328,7 +17324,7 @@
         <v>40539</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
@@ -17392,7 +17388,7 @@
         <v>81078</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
@@ -17639,16 +17635,16 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>34215</v>
+        <v>33980</v>
       </c>
       <c r="M301" s="3" t="n">
         <v>34215</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>17463</v>
+        <v>17067</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
@@ -17712,7 +17708,7 @@
         <v>2270</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
@@ -17743,10 +17739,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4256</v>
+        <v>4298</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17767,7 +17763,7 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4391</v>
+        <v>4378</v>
       </c>
       <c r="M303" s="3" t="n">
         <v>16214</v>
@@ -17776,7 +17772,7 @@
         <v>4719</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
@@ -18508,7 +18504,7 @@
         <v>32431</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
@@ -18572,7 +18568,7 @@
         <v>77835</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
@@ -18626,7 +18622,7 @@
         <v>210802</v>
       </c>
       <c r="O317" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
@@ -18712,23 +18708,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D319" s="3" t="n">
-        <v>1378</v>
-      </c>
-      <c r="E319" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="F319" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G319" s="3" t="n">
-        <v>1378</v>
-      </c>
+      <c r="D319" s="3" t="inlineStr"/>
+      <c r="E319" s="2" t="inlineStr"/>
+      <c r="F319" s="2" t="inlineStr"/>
+      <c r="G319" s="3" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I319" s="2" t="n">
@@ -18937,7 +18923,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>522</v>
+        <v>378</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1067</v>
@@ -19098,7 +19084,7 @@
         <v>17</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>1801</v>
+        <v>1765</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19119,7 +19105,7 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>2329</v>
+        <v>2319</v>
       </c>
       <c r="M325" s="3" t="n">
         <v>16105</v>
@@ -19128,7 +19114,7 @@
         <v>2517</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
@@ -19247,16 +19233,16 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>3738</v>
+        <v>2912</v>
       </c>
       <c r="M327" s="3" t="n">
         <v>11351</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>3631</v>
+        <v>3123</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
@@ -19279,18 +19265,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22630</v>
+        <v>26211</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>20821</v>
+        <v>21066</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19311,16 +19297,16 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>26211</v>
+        <v>24659</v>
       </c>
       <c r="M328" s="3" t="n">
         <v>33422</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>22090</v>
+        <v>22510</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
@@ -19375,16 +19361,16 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>6697</v>
+        <v>6668</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9329</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8035</v>
+        <v>7993</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
@@ -19439,7 +19425,7 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6584</v>
+        <v>6407</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8873</v>
@@ -19448,7 +19434,7 @@
         <v>6770</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
@@ -19535,18 +19521,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1148</v>
+        <v>970</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1240</v>
+        <v>1217</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19567,16 +19553,16 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>970</v>
+        <v>1067</v>
       </c>
       <c r="M332" s="3" t="n">
         <v>16216</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1262</v>
+        <v>1164</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
@@ -19759,7 +19745,7 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>4946</v>
@@ -20143,7 +20129,7 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2450</v>
@@ -20216,7 +20202,7 @@
         <v>478</v>
       </c>
       <c r="O342" s="2" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
@@ -20311,10 +20297,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1841</v>
+        <v>1802</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20335,7 +20321,7 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>1622</v>
+        <v>1746</v>
       </c>
       <c r="M344" s="3" t="n">
         <v>3882</v>
@@ -20344,7 +20330,7 @@
         <v>3243</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
@@ -20408,7 +20394,7 @@
         <v>4054</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
@@ -20510,7 +20496,7 @@
         <v>6486</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
@@ -20554,12 +20540,18 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L348" s="3" t="inlineStr"/>
-      <c r="M348" s="3" t="inlineStr"/>
+      <c r="L348" s="3" t="n">
+        <v>9729</v>
+      </c>
+      <c r="M348" s="3" t="n">
+        <v>9729</v>
+      </c>
       <c r="N348" s="3" t="n">
         <v>12972</v>
       </c>
-      <c r="O348" s="2" t="inlineStr"/>
+      <c r="O348" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
           <t>2026-07-16</t>
@@ -20701,10 +20693,10 @@
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16512</v>
+        <v>16503</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20728,13 +20720,13 @@
         <v>16216</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>48543</v>
+        <v>32431</v>
       </c>
       <c r="N351" s="3" t="n">
         <v>32431</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
@@ -20916,7 +20908,7 @@
         <v>18161</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
@@ -20938,13 +20930,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D355" s="3" t="inlineStr"/>
-      <c r="E355" s="2" t="inlineStr"/>
-      <c r="F355" s="2" t="inlineStr"/>
-      <c r="G355" s="3" t="inlineStr"/>
+      <c r="D355" s="3" t="n">
+        <v>9081</v>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G355" s="3" t="n">
+        <v>9081</v>
+      </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I355" s="2" t="n">
@@ -20970,7 +20972,7 @@
         <v>18161</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3638</v>
+        <v>3679</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
         <v>3248</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6496</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>6496</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>99277</v>
+        <v>99272</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>36</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24360</v>
+        <v>24359</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24360</v>
+        <v>24359</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24360</v>
+        <v>24359</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24360</v>
+        <v>24359</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>48720</v>
+        <v>48718</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>74353</v>
+        <v>74350</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>87696</v>
+        <v>87692</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -926,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>146160</v>
+        <v>146153</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>146160</v>
+        <v>146153</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>259840</v>
+        <v>259828</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -980,20 +980,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>365400</v>
+        <v>365383</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>365400</v>
+        <v>365383</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>730800</v>
+        <v>730765</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1012,18 +1012,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6114</v>
+        <v>5893</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6377</v>
+        <v>6340</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5824</v>
+        <v>6210</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8932</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1076,18 +1076,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7764</v>
+        <v>8345</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9106</v>
+        <v>9100</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1108,20 +1108,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8705</v>
+        <v>8638</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>154238</v>
+        <v>154230</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17864</v>
+        <v>17863</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1140,18 +1140,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14291</v>
+        <v>14424</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>27</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14783</v>
+        <v>14787</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1175,17 +1175,17 @@
         <v>14291</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>43603</v>
+        <v>43601</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35728</v>
+        <v>35726</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1226,20 +1226,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>24565</v>
+        <v>24563</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1280,20 +1280,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>96496</v>
+        <v>96492</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>96496</v>
+        <v>96492</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1334,20 +1334,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>35203</v>
+        <v>35202</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>65790</v>
+        <v>65787</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5522</v>
+        <v>5521</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1442,20 +1442,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14738</v>
+        <v>14737</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>65790</v>
+        <v>65787</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5522</v>
+        <v>5521</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
         <v>812</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1624</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1527,13 +1527,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="n">
+        <v>1624</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1624</v>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -1553,17 +1563,17 @@
         <v>1624</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>233871</v>
+        <v>233859</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3248</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1617,7 @@
         <v>3248</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>276080</v>
+        <v>276067</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6496</v>
@@ -1617,7 +1627,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1661,17 +1671,17 @@
         <v>5846</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11693</v>
+        <v>11692</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1712,20 +1722,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11368</v>
+        <v>11367</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37953</v>
+        <v>37951</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1766,20 +1776,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21924</v>
+        <v>21923</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>143350</v>
+        <v>143344</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1808,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1819,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1830,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>330218</v>
+        <v>330202</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81200</v>
+        <v>81196</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1908,7 @@
         <v>2527</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>325</v>
@@ -1908,7 +1918,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -1935,10 +1945,10 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1678</v>
+        <v>1693</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1959,10 +1969,10 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1533</v>
+        <v>1455</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1619</v>
@@ -1972,7 +1982,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2036,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2053,10 +2063,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1141</v>
+        <v>1148</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2080,7 +2090,7 @@
         <v>1340</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1619687</v>
+        <v>1619609</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1624</v>
@@ -2090,7 +2100,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2109,18 +2119,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1650</v>
+        <v>1624</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1715</v>
+        <v>1712</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2144,17 +2154,17 @@
         <v>1624</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3248</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2191,7 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3248</v>
@@ -2208,17 +2218,17 @@
         <v>3248</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17497</v>
+        <v>17496</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2272,17 @@
         <v>650</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1299</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2346,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2355,18 +2365,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1270</v>
+        <v>1509</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1145</v>
+        <v>1205</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2387,20 +2397,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1509</v>
+        <v>1517</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>649600</v>
+        <v>649569</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1624</v>
+        <v>1660</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2419,18 +2429,18 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2954</v>
+        <v>2290</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2451,20 +2461,20 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2956</v>
+        <v>2969</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13156</v>
+        <v>13155</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3248</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2491,10 +2501,10 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3411</v>
+        <v>3410</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2515,20 +2525,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3787</v>
+        <v>3686</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21708</v>
+        <v>21707</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2551,11 +2561,11 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6496</v>
@@ -2582,17 +2592,17 @@
         <v>6496</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>31390</v>
+        <v>31389</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2652,7 +2662,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2722,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2762,17 +2772,17 @@
         <v>3248</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>324800</v>
+        <v>324784</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2836,7 @@
         <v>1626</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>148672</v>
+        <v>148665</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3248</v>
@@ -2836,7 +2846,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2887,20 +2897,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>7608</v>
+        <v>4833</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17866</v>
+        <v>17865</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -2927,10 +2937,10 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6623</v>
+        <v>6628</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2954,17 +2964,17 @@
         <v>6496</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15537</v>
+        <v>15536</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3014,17 +3024,17 @@
         <v>3816</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6290</v>
+        <v>6289</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3053,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6412</v>
+        <v>6411</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3074,17 +3084,17 @@
         <v>6496</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>9127</v>
+        <v>9126</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>5671</v>
+        <v>7051</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3113,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9996</v>
+        <v>9995</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -3111,10 +3121,10 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9824</v>
+        <v>9857</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3131,20 +3141,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9707</v>
+        <v>9701</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>10699</v>
+        <v>10698</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11277</v>
+        <v>11395</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3198,7 +3208,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3252,7 +3262,7 @@
         <v>3248</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>6496</v>
@@ -3262,7 +3272,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3326,7 @@
         <v>796</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>6032</v>
+        <v>6031</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>812</v>
@@ -3326,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3345,18 +3355,18 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>973</v>
+        <v>580</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>973</v>
+        <v>776</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3390,7 +3400,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3454,7 +3464,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3501,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>1946</v>
+        <v>969</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4258</v>
@@ -3504,7 +3514,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3551,10 +3561,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>3881</v>
+        <v>3880</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4481</v>
+        <v>4480</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1624</v>
@@ -3564,7 +3574,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3624,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3633,11 +3643,11 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>692</v>
+        <v>177</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
@@ -3668,17 +3678,17 @@
         <v>680</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4952</v>
+        <v>4951</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>812</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3732,7 @@
         <v>1851</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11597</v>
+        <v>11596</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1624</v>
@@ -3732,7 +3742,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3783,20 +3793,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>4872</v>
+        <v>3493</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>31413</v>
+        <v>31412</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3248</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3836,7 @@
         <v>13</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>9041</v>
+        <v>9040</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3850,17 +3860,17 @@
         <v>11142</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>11709</v>
+        <v>11708</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>10264</v>
+        <v>10263</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3879,18 +3889,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>13966</v>
+        <v>13100</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>14103</v>
+        <v>14158</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3911,20 +3921,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>13780</v>
+        <v>13316</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>31454</v>
+        <v>31452</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>15400</v>
+        <v>15398</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3943,18 +3953,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3596</v>
+        <v>3883</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4495</v>
+        <v>4521</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3975,20 +3985,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>4799</v>
+        <v>3691</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10601</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4874</v>
+        <v>4942</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4039,20 +4049,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4153</v>
+        <v>3469</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11612</v>
+        <v>11611</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>4653</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4102,11 +4112,11 @@
         <v>2923</v>
       </c>
       <c r="O60" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4170,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4213,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>10069</v>
+        <v>10068</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4252,17 +4262,17 @@
         <v>7308</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4315,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4351,20 +4361,20 @@
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4405,20 +4415,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>51968</v>
+        <v>51966</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4462,17 +4472,17 @@
         <v>9094</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4515,12 +4525,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22736</v>
+        <v>22735</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4580,11 +4590,11 @@
         <v>1624</v>
       </c>
       <c r="O69" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4634,11 +4644,11 @@
         <v>3248</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4702,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4736,17 +4746,17 @@
         <v>2598</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1523380</v>
+        <v>1523308</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11693</v>
+        <v>11692</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4800,7 @@
         <v>4880</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7677</v>
+        <v>7676</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>9744</v>
@@ -4800,7 +4810,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4844,17 +4854,17 @@
         <v>8932</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21516</v>
+        <v>21515</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17864</v>
+        <v>17863</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4895,20 +4905,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17864</v>
+        <v>17863</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27774</v>
+        <v>27772</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -4959,20 +4969,20 @@
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>253</v>
+        <v>192</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6545</v>
+        <v>6544</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5029,14 +5039,14 @@
         <v>5325</v>
       </c>
       <c r="N77" s="3" t="n">
-        <v>1190</v>
+        <v>650</v>
       </c>
       <c r="O77" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5104,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5158,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5206,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5237,20 +5247,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23753</v>
+        <v>23751</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23753</v>
+        <v>23751</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5293,12 +5303,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20787</v>
+        <v>20786</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5348,7 +5358,7 @@
         <v>408</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1623838</v>
+        <v>1623760</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>812</v>
@@ -5358,7 +5368,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5418,7 @@
         <v>778</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35501</v>
+        <v>35499</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1624</v>
@@ -5418,7 +5428,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5475,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="n">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>3238</v>
@@ -5478,7 +5488,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5538,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5567,12 +5577,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5615,14 +5625,14 @@
         <v>4851</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5661,12 +5671,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17864</v>
+        <v>17863</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5726,7 @@
         <v>508</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>88261</v>
+        <v>88257</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>812</v>
@@ -5726,7 +5736,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5796,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5846,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5890,7 @@
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5919,12 +5929,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5973,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6007,12 +6017,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17864</v>
+        <v>17863</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6076,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6130,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6167,14 +6177,14 @@
         <v>5315</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10069</v>
+        <v>10068</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6221,14 +6231,14 @@
         <v>7308</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6271,12 +6281,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6317,20 +6327,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18450</v>
+        <v>18449</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18450</v>
+        <v>18449</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6373,12 +6383,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>51968</v>
+        <v>51966</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6442,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6490,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6523,12 +6533,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>10069</v>
+        <v>10068</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6575,14 +6585,14 @@
         <v>7308</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6625,12 +6635,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6673,12 +6683,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6721,12 +6731,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>51968</v>
+        <v>51966</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6767,20 +6777,20 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>75662</v>
+        <v>75659</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>75662</v>
+        <v>75659</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>81200</v>
+        <v>81196</v>
       </c>
       <c r="O111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6809,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>89320</v>
+        <v>89316</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6810,7 +6820,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>89320</v>
+        <v>89316</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6831,20 +6841,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>89320</v>
+        <v>89316</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>99704</v>
+        <v>99699</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>113680</v>
+        <v>113675</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6885,20 +6895,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>113680</v>
+        <v>113675</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>113680</v>
+        <v>113675</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>146160</v>
+        <v>146153</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6927,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6928,7 +6938,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6949,20 +6959,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6991,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -6992,7 +7002,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7013,20 +7023,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>194880</v>
+        <v>194871</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7067,20 +7077,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>219240</v>
+        <v>219230</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>292320</v>
+        <v>292306</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>259840</v>
+        <v>259828</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7127,14 +7137,14 @@
         <v>2327</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7188,7 @@
         <v>3894</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>6006</v>
+        <v>6005</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>4060</v>
@@ -7188,7 +7198,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7246,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7280,17 +7290,17 @@
         <v>7308</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7343,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23386</v>
+        <v>23384</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7379,20 +7389,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19527</v>
+        <v>19526</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7433,20 +7443,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>32480003</v>
+        <v>32478450</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7493,14 +7503,14 @@
         <v>2241</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7554,7 +7564,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7618,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7655,14 +7665,14 @@
         <v>12201</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7705,12 +7715,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23386</v>
+        <v>23384</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7763,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7816,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7836,7 +7846,7 @@
         <v>2</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>4170</v>
+        <v>4169</v>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
@@ -7870,7 +7880,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7917,14 +7927,14 @@
         <v>6496</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -7971,14 +7981,14 @@
         <v>16329</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8031,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8067,20 +8077,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21924</v>
+        <v>21923</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21924</v>
+        <v>21923</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>48720</v>
+        <v>48718</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8110,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8131,20 +8141,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>73080</v>
+        <v>73077</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8185,20 +8195,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8221,11 +8231,11 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G138" s="3" t="n">
         <v>6496</v>
@@ -8252,17 +8262,17 @@
         <v>6496</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>13085</v>
+        <v>13084</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8326,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8367,20 +8377,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5302</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8454,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8508,7 +8518,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8572,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8613,10 +8623,10 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>11024</v>
+        <v>11023</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>4060</v>
@@ -8626,7 +8636,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8684,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8738,7 @@
         <v>4547</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>54920</v>
+        <v>54918</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6496</v>
@@ -8738,7 +8748,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8791,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8830,17 +8840,17 @@
         <v>9744</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17796</v>
+        <v>17795</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8883,12 +8893,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8907,18 +8917,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16395</v>
+        <v>16391</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8939,20 +8949,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8981,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8989,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9003,20 +9013,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>86299</v>
+        <v>86295</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>77952</v>
+        <v>77948</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9057,20 +9067,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>105560</v>
+        <v>105555</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>105560</v>
+        <v>105555</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>211120</v>
+        <v>211110</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9144,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9208,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9258,7 @@
         <v>838</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15912</v>
+        <v>15911</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1624</v>
@@ -9258,7 +9268,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9314,11 +9324,11 @@
         <v>3248</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9388,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9432,7 @@
         <v>812</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19853</v>
+        <v>19852</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1624</v>
@@ -9432,7 +9442,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9486,7 @@
         <v>1624</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19694</v>
+        <v>19693</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3248</v>
@@ -9486,7 +9496,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9540,17 +9550,17 @@
         <v>3248</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6556</v>
+        <v>6793</v>
       </c>
       <c r="N160" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9614,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9668,7 @@
         <v>1843</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30986</v>
+        <v>30984</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1624</v>
@@ -9668,7 +9678,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9722,17 +9732,17 @@
         <v>3108</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3898</v>
+        <v>3897</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3531</v>
+        <v>3248</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9751,18 +9761,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3777</v>
+        <v>3714</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3700</v>
+        <v>3709</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9783,20 +9793,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3779</v>
+        <v>3688</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N164" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9860,7 @@
         <v>162</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>5043</v>
+        <v>5042</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>325</v>
@@ -9860,7 +9870,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9911,10 +9921,10 @@
         </is>
       </c>
       <c r="L166" s="3" t="n">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="M166" s="3" t="n">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="N166" s="3" t="n">
         <v>650</v>
@@ -9924,7 +9934,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -9984,11 +9994,11 @@
         <v>1299</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10062,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10116,7 @@
         <v>339</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>325</v>
@@ -10116,7 +10126,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10157,20 +10167,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>97440</v>
+        <v>97435</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>97440</v>
+        <v>97435</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10213,12 +10223,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10255,20 +10265,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10328,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10372,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10402,17 +10412,17 @@
         <v>7308</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14585</v>
+        <v>14584</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10449,20 +10459,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11693</v>
+        <v>11692</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11693</v>
+        <v>11692</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23386</v>
+        <v>23384</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10499,20 +10509,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16321</v>
+        <v>16320</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10549,20 +10559,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>34031</v>
+        <v>19649</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10610,7 +10620,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10674,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10717,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10759,14 +10769,14 @@
         <v>9744</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10819,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10855,20 +10865,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21924</v>
+        <v>21923</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21924</v>
+        <v>21923</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>43848</v>
+        <v>43846</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10909,20 +10919,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>29232</v>
+        <v>29231</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>58464</v>
+        <v>58461</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -10966,17 +10976,17 @@
         <v>162</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11020,17 +11030,17 @@
         <v>162</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11084,7 @@
         <v>162</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>105661</v>
+        <v>105656</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>325</v>
@@ -11084,7 +11094,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11142,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11186,17 +11196,17 @@
         <v>162</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29953</v>
+        <v>29952</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11250,17 +11260,17 @@
         <v>162</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>160342</v>
+        <v>160335</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11314,7 @@
         <v>162</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>325</v>
@@ -11314,7 +11324,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11372,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11406,17 +11416,17 @@
         <v>162</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11480,7 @@
         <v>162</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>162238</v>
+        <v>162230</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>325</v>
@@ -11480,7 +11490,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11524,17 +11534,17 @@
         <v>162</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11592,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11646,7 @@
         <v>875</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>612</v>
@@ -11646,7 +11656,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11675,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -11676,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -11697,20 +11707,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>21148</v>
+        <v>21147</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>21148</v>
+        <v>21147</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11764,7 +11774,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11818,7 +11828,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11862,17 +11872,17 @@
         <v>6496</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>8104</v>
+        <v>8103</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11913,10 +11923,10 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>283502</v>
+        <v>283488</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>14291</v>
@@ -11926,7 +11936,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11967,20 +11977,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>16047</v>
+        <v>16046</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16471</v>
+        <v>16470</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -11999,7 +12009,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>21792</v>
+        <v>21791</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -12010,7 +12020,7 @@
         <v>2</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>21290</v>
+        <v>21289</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -12031,20 +12041,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>23407</v>
+        <v>23406</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>50099</v>
+        <v>50096</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12087,12 +12097,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23386</v>
+        <v>23384</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12156,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12210,7 +12220,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12251,20 +12261,20 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>2087</v>
+        <v>1832</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>3082</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12328,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12372,7 +12382,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12419,14 +12429,14 @@
         <v>7308</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12469,12 +12479,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23386</v>
+        <v>23384</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12515,20 +12525,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12575,14 +12585,14 @@
         <v>2805</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O215" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12626,7 +12636,7 @@
         <v>2111</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>12195</v>
+        <v>12194</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4222</v>
@@ -12636,7 +12646,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12677,20 +12687,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15990</v>
+        <v>15989</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>21953</v>
+        <v>21952</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12754,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12791,14 +12801,14 @@
         <v>7308</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14616</v>
+        <v>14615</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12851,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12887,20 +12897,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -12927,10 +12937,10 @@
         </is>
       </c>
       <c r="F222" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>1302</v>
+        <v>1306</v>
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
@@ -12964,7 +12974,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13024,11 +13034,11 @@
         <v>3248</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13065,7 @@
         </is>
       </c>
       <c r="F224" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G224" s="3" t="n">
         <v>3248</v>
@@ -13082,17 +13092,17 @@
         <v>3248</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7391</v>
+        <v>7390</v>
       </c>
       <c r="N224" s="3" t="n">
         <v>6496</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13156,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13165,7 +13175,7 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
@@ -13176,7 +13186,7 @@
         <v>1</v>
       </c>
       <c r="G226" s="3" t="n">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
@@ -13210,7 +13220,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13284,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13328,17 +13338,17 @@
         <v>162</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13382,17 +13392,17 @@
         <v>162</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13411,18 +13421,18 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>162</v>
+        <v>627</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>162</v>
+        <v>317</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13446,17 +13456,17 @@
         <v>162</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N230" s="3" t="n">
-        <v>325</v>
+        <v>518</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1125</v>
+        <v>1135</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13510,7 @@
         <v>812</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1624</v>
@@ -13510,7 +13520,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13564,17 +13574,17 @@
         <v>1624</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3289</v>
+        <v>3288</v>
       </c>
       <c r="N232" s="3" t="n">
         <v>3248</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13638,7 +13648,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13702,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13721,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -13722,7 +13732,7 @@
         <v>1</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>3656</v>
+        <v>3655</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -13746,7 +13756,7 @@
         <v>4042</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4377</v>
+        <v>4376</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3248</v>
@@ -13756,7 +13766,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13820,7 +13830,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13878,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13912,7 +13922,7 @@
         <v>8932</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11321</v>
+        <v>11320</v>
       </c>
       <c r="N238" s="3" t="n">
         <v>6496</v>
@@ -13922,7 +13932,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13975,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14017,14 +14027,14 @@
         <v>10757</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14053,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14054,7 +14064,7 @@
         <v>11</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19437</v>
+        <v>19436</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14075,20 +14085,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>23218</v>
+        <v>19411</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>35715</v>
+        <v>35713</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14117,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14118,7 +14128,7 @@
         <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14139,20 +14149,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>40840</v>
+        <v>40838</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>60172</v>
+        <v>60170</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>77952</v>
+        <v>77948</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14181,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>20946</v>
+        <v>20945</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14179,10 +14189,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>19643</v>
+        <v>19516</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14199,20 +14209,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>20488</v>
+        <v>18440</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>32480003</v>
+        <v>32478450</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14255,12 +14265,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14324,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14365,10 +14375,10 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2449</v>
+        <v>2351</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N246" s="3" t="n">
         <v>3131</v>
@@ -14378,7 +14388,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14419,20 +14429,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15948</v>
+        <v>15947</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23944</v>
+        <v>23943</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>18189</v>
+        <v>18188</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14489,14 +14499,14 @@
         <v>9094</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>18189</v>
+        <v>18188</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14546,7 @@
         <v>812</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9535</v>
+        <v>9534</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1624</v>
@@ -14546,7 +14556,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14596,7 +14606,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14650,17 +14660,17 @@
         <v>162</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>99861</v>
+        <v>99857</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14701,10 +14711,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>51747</v>
+        <v>51745</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>51747</v>
+        <v>51745</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6496</v>
@@ -14714,7 +14724,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14755,7 +14765,7 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>6839</v>
+        <v>6838</v>
       </c>
       <c r="M253" s="3" t="n">
         <v>7743</v>
@@ -14768,7 +14778,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14808,7 @@
         <v>2</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>6679</v>
+        <v>6678</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -14822,17 +14832,17 @@
         <v>8073</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>194880</v>
+        <v>194871</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14889,14 +14899,14 @@
         <v>1624</v>
       </c>
       <c r="N255" s="3" t="n">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="O255" s="2" t="n">
         <v>1706</v>
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -14950,7 +14960,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15014,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15027,14 +15037,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15064,11 +15074,11 @@
         <v>650</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15122,17 +15132,17 @@
         <v>1361</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21961</v>
+        <v>21960</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1624</v>
       </c>
       <c r="O259" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15196,7 +15206,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15270,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15279,7 +15289,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6498</v>
+        <v>6497</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15287,10 +15297,10 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6524</v>
+        <v>6525</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15314,17 +15324,17 @@
         <v>6496</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O262" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15374,11 +15384,11 @@
         <v>1624</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15442,7 +15452,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15461,7 +15471,7 @@
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -15472,7 +15482,7 @@
         <v>1</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -15500,7 +15510,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15554,17 +15564,17 @@
         <v>6496</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>12992</v>
+        <v>9896</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15615,20 +15625,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2473</v>
+        <v>2134</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19974</v>
+        <v>19973</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2912</v>
+        <v>650</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15657,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15655,10 +15665,10 @@
         </is>
       </c>
       <c r="F268" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15679,10 +15689,10 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8445</v>
+        <v>8444</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14629</v>
+        <v>14628</v>
       </c>
       <c r="N268" s="3" t="n">
         <v>14291</v>
@@ -15692,7 +15702,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15735,12 +15745,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15781,20 +15791,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>25572</v>
+        <v>25570</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25572</v>
+        <v>25570</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15813,18 +15823,18 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>34132</v>
+        <v>20786</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F271" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>27459</v>
+        <v>25234</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15845,20 +15855,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>20787</v>
+        <v>21579</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>53383</v>
+        <v>53380</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O271" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15922,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -15956,17 +15966,17 @@
         <v>162</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21508</v>
+        <v>21507</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16020,17 +16030,17 @@
         <v>162</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>32587</v>
+        <v>32586</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16084,7 +16094,7 @@
         <v>162</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16321</v>
+        <v>16320</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>325</v>
@@ -16094,7 +16104,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16124,7 +16134,7 @@
         <v>3</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>4691</v>
+        <v>4690</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16148,17 +16158,17 @@
         <v>162</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>162397</v>
+        <v>162389</v>
       </c>
       <c r="N276" s="3" t="n">
-        <v>15121</v>
+        <v>15120</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16204,11 +16214,11 @@
         <v>1624</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16268,11 +16278,11 @@
         <v>6496</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16336,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16370,17 +16380,17 @@
         <v>6496</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8838</v>
+        <v>8837</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16428,7 +16438,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16471,12 +16481,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16519,12 +16529,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16543,7 +16553,7 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>20787</v>
+        <v>20786</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -16554,7 +16564,7 @@
         <v>1</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>20787</v>
+        <v>20786</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -16575,20 +16585,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>37027</v>
+        <v>37025</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>37027</v>
+        <v>37025</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16607,18 +16617,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9721</v>
+        <v>9705</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>10376</v>
+        <v>10233</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16639,20 +16649,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>9057</v>
+        <v>10185</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10692</v>
+        <v>11577</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16716,7 +16726,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16735,18 +16745,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5351</v>
+        <v>4852</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5104</v>
+        <v>5085</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16766,17 +16776,17 @@
         <v>5825</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5928</v>
+        <v>5927</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>4714</v>
+        <v>4529</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16795,18 +16805,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6598</v>
+        <v>6984</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6893</v>
+        <v>6899</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16823,20 +16833,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6985</v>
+        <v>6793</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8049</v>
+        <v>8048</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7448</v>
+        <v>7464</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16863,10 +16873,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9417</v>
+        <v>9441</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16883,20 +16893,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9710</v>
+        <v>9703</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11805</v>
+        <v>11804</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10192</v>
+        <v>10091</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16970,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16989,7 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2620</v>
+        <v>2619</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -17011,7 +17021,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3894</v>
+        <v>3881</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5197</v>
@@ -17024,7 +17034,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17088,7 +17098,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17118,7 +17128,7 @@
         <v>2</v>
       </c>
       <c r="G293" s="3" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -17152,7 +17162,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17179,10 +17189,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6612</v>
+        <v>6696</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17203,20 +17213,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6309</v>
+        <v>6212</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>19386</v>
+        <v>19385</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6715</v>
+        <v>6773</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17257,20 +17267,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>52785</v>
+        <v>52782</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>717387</v>
+        <v>717353</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17299,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17300,7 +17310,7 @@
         <v>11</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17321,20 +17331,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>70610</v>
+        <v>70607</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>40600</v>
+        <v>40598</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17363,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>64960</v>
+        <v>64957</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17364,7 +17374,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>64960</v>
+        <v>64957</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17385,20 +17395,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>64960</v>
+        <v>64957</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>81200</v>
+        <v>81196</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17427,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17428,7 +17438,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17449,20 +17459,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>129920</v>
+        <v>129914</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>129923</v>
+        <v>129917</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>162400</v>
+        <v>162392</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17491,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>259840</v>
+        <v>259828</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17492,7 +17502,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>259840</v>
+        <v>259828</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17513,20 +17523,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>259840</v>
+        <v>259828</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>262343</v>
+        <v>262330</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>324800</v>
+        <v>324784</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17555,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>454720</v>
+        <v>454698</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17553,10 +17563,10 @@
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>454720</v>
+        <v>454698</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17577,20 +17587,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>454720</v>
+        <v>454698</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>975227</v>
+        <v>975180</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>649600</v>
+        <v>649569</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17609,7 +17619,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>16992</v>
+        <v>16991</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17617,10 +17627,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>19815</v>
+        <v>18670</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17641,20 +17651,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>29128</v>
+        <v>29127</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>34266</v>
+        <v>34265</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>17093</v>
+        <v>17092</v>
       </c>
       <c r="O301" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17694,7 @@
         <v>9</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17705,20 +17715,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1954</v>
+        <v>1941</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4926</v>
+        <v>4925</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17775,14 +17785,14 @@
         <v>16238</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4726</v>
+        <v>4708</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17801,18 +17811,18 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1460</v>
+        <v>1137</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1812</v>
+        <v>1716</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17833,20 +17843,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1137</v>
+        <v>2598</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>11368</v>
+        <v>16239</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17897,7 +17907,7 @@
         </is>
       </c>
       <c r="L305" s="3" t="n">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="M305" s="3" t="n">
         <v>1501</v>
@@ -17910,7 +17920,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -17929,18 +17939,18 @@
         </is>
       </c>
       <c r="D306" s="3" t="n">
-        <v>10064</v>
+        <v>14073</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>2638</v>
+        <v>4925</v>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
@@ -17964,17 +17974,17 @@
         <v>162</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N306" s="3" t="n">
-        <v>325</v>
+        <v>2364</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17007</v>
+        <v>16667</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18028,7 +18038,7 @@
         <v>1400</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>1546</v>
@@ -18038,7 +18048,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18092,17 +18102,17 @@
         <v>2111</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1299200</v>
+        <v>1299138</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>4060</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18156,7 @@
         <v>4547</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32837</v>
+        <v>32836</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6496</v>
@@ -18156,7 +18166,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18193,7 @@
         </is>
       </c>
       <c r="F310" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G310" s="3" t="n">
         <v>1624</v>
@@ -18220,7 +18230,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18271,7 +18281,7 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>4973</v>
+        <v>4972</v>
       </c>
       <c r="M311" s="3" t="n">
         <v>6197</v>
@@ -18284,7 +18294,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18327,12 +18337,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18386,17 +18396,17 @@
         <v>9744</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26851</v>
+        <v>26850</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>43</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18437,20 +18447,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15888</v>
+        <v>15887</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15888</v>
+        <v>15887</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18469,18 +18479,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>16301</v>
+        <v>16298</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18501,20 +18511,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18533,7 +18543,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18544,7 +18554,7 @@
         <v>5</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18565,20 +18575,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38976</v>
+        <v>38974</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>77952</v>
+        <v>77948</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18619,20 +18629,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>105560</v>
+        <v>105555</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>105560</v>
+        <v>105555</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>211120</v>
+        <v>211110</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18696,7 +18706,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18750,7 @@
         <v>1309</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>16130</v>
+        <v>16129</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>325</v>
@@ -18750,7 +18760,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18801,20 +18811,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>2243</v>
+        <v>2239</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>10090</v>
+        <v>10089</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18878,7 @@
         <v>3735</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>6040</v>
+        <v>6039</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>325</v>
@@ -18878,7 +18888,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18952,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -18993,20 +19003,20 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>2522</v>
+        <v>2329</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16943</v>
+        <v>16942</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19070,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19083,14 +19093,14 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>1934</v>
+        <v>1990</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19114,17 +19124,17 @@
         <v>2038</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>16130</v>
+        <v>16129</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2465</v>
+        <v>2387</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19175,20 +19185,20 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="M326" s="3" t="n">
         <v>3084</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="O326" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19207,18 +19217,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>4666</v>
+        <v>11367</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>3761</v>
+        <v>4521</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19242,17 +19252,17 @@
         <v>1137</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>11368</v>
+        <v>4614</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>3386</v>
+        <v>6413</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19271,18 +19281,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22807</v>
+        <v>23196</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>21472</v>
+        <v>21607</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19303,20 +19313,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>23288</v>
+        <v>22806</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>33472</v>
+        <v>33471</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>22176</v>
+        <v>21705</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19335,18 +19345,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7839</v>
+        <v>3881</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7484</v>
+        <v>7417</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19367,20 +19377,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7743</v>
+        <v>7176</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9343</v>
+        <v>9342</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7865</v>
+        <v>7519</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19399,18 +19409,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6306</v>
+        <v>6460</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>6196</v>
+        <v>6175</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19431,20 +19441,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6460</v>
+        <v>6463</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8887</v>
+        <v>8886</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6743</v>
+        <v>6785</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19505,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1455</v>
+        <v>1444</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3248</v>
@@ -19508,7 +19518,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19527,18 +19537,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1069</v>
+        <v>1319</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19562,17 +19572,17 @@
         <v>1069</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1169</v>
+        <v>1254</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19626,7 +19636,7 @@
         <v>227</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>4960</v>
+        <v>4959</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>325</v>
@@ -19636,7 +19646,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19690,7 +19700,7 @@
         <v>455</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>507</v>
@@ -19700,7 +19710,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19729,7 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
@@ -19751,20 +19761,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1872</v>
+        <v>1822</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>4953</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2274</v>
+        <v>2501</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19787,14 +19797,14 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>359</v>
+        <v>331</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19815,7 +19825,7 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="M336" s="3" t="n">
         <v>2975</v>
@@ -19824,11 +19834,11 @@
         <v>325</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19851,11 +19861,11 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G337" s="3" t="n">
         <v>163</v>
@@ -19882,17 +19892,17 @@
         <v>162</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15901</v>
+        <v>15900</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19956,7 +19966,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -19986,7 +19996,7 @@
         <v>12</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -20016,11 +20026,11 @@
         <v>513</v>
       </c>
       <c r="O339" s="2" t="n">
-        <v>463</v>
+        <v>416</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20081,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>1069</v>
+        <v>853</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3248</v>
@@ -20080,11 +20090,11 @@
         <v>325</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20111,10 +20121,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20148,7 +20158,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20167,18 +20177,18 @@
         </is>
       </c>
       <c r="D342" s="3" t="n">
-        <v>437</v>
+        <v>320</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F342" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G342" s="3" t="n">
-        <v>437</v>
+        <v>378</v>
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
@@ -20199,20 +20209,20 @@
         </is>
       </c>
       <c r="L342" s="3" t="n">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="N342" s="3" t="n">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="O342" s="2" t="n">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20263,7 +20273,7 @@
         </is>
       </c>
       <c r="L343" s="3" t="n">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="M343" s="3" t="n">
         <v>758</v>
@@ -20272,11 +20282,11 @@
         <v>502</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20316,7 @@
         <v>6</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20336,11 +20346,11 @@
         <v>3248</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20363,11 +20373,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2111</v>
@@ -20394,17 +20404,17 @@
         <v>2111</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1624000</v>
+        <v>1623922</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>4060</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20452,7 +20462,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20506,7 +20516,7 @@
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20553,14 +20563,14 @@
         <v>9744</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12992</v>
+        <v>12991</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20583,11 +20593,11 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G349" s="3" t="n">
         <v>9744</v>
@@ -20614,17 +20624,17 @@
         <v>9744</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19488</v>
+        <v>19487</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20667,12 +20677,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25984</v>
+        <v>25983</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20691,18 +20701,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16240</v>
+        <v>16449</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16384</v>
+        <v>16387</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20723,20 +20733,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16240</v>
+        <v>16239</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38833</v>
+        <v>32478</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>32480</v>
+        <v>32478</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20755,18 +20765,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>46606</v>
+        <v>46585</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>47323</v>
+        <v>47418</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20786,21 +20796,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="n">
-        <v>48446</v>
-      </c>
-      <c r="M352" s="3" t="n">
-        <v>48543</v>
-      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+      <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>77952</v>
-      </c>
-      <c r="O352" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>77948</v>
+      </c>
+      <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20819,7 +20823,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>194206</v>
+        <v>194197</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20830,7 +20834,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>194206</v>
+        <v>194197</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20851,20 +20855,20 @@
         </is>
       </c>
       <c r="L353" s="3" t="n">
-        <v>242635</v>
+        <v>242637</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>242635</v>
+        <v>242637</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>213626</v>
+        <v>213616</v>
       </c>
       <c r="O353" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20918,17 +20922,17 @@
         <v>9094</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>19447</v>
+        <v>19446</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>18189</v>
+        <v>18188</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -20982,17 +20986,17 @@
         <v>9094</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>22362</v>
+        <v>22361</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>18189</v>
+        <v>18188</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -21022,7 +21026,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>162.400016</v>
+        <v>162.39225</v>
       </c>
     </row>
     <row r="2">
@@ -21033,7 +21037,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 18 Jul 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 19 Jul 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21045,7 +21049,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3705</v>
+        <v>3659</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3250</v>
+        <v>4603</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>99331</v>
+        <v>99318</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>35</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24373</v>
+        <v>24370</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24373</v>
+        <v>24370</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24373</v>
+        <v>24370</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24373</v>
+        <v>24370</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>48746</v>
+        <v>48740</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>74394</v>
+        <v>74384</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>87744</v>
+        <v>87733</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -926,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>146239</v>
+        <v>146221</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>146239</v>
+        <v>146221</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>259981</v>
+        <v>259949</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -980,20 +980,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>365599</v>
+        <v>365553</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>365599</v>
+        <v>365553</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>731197</v>
+        <v>731106</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6019</v>
+        <v>6018</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6335</v>
+        <v>6333</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1044,20 +1044,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6020</v>
+        <v>5802</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8937</v>
+        <v>8936</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1076,18 +1076,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7772</v>
+        <v>8430</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>52</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9100</v>
+        <v>9077</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1108,20 +1108,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>7765</v>
+        <v>7753</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>154322</v>
+        <v>154302</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17874</v>
+        <v>17871</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1140,18 +1140,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14432</v>
+        <v>14297</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14836</v>
+        <v>14813</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1172,20 +1172,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14299</v>
+        <v>14297</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>43626</v>
+        <v>43621</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35747</v>
+        <v>35743</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1226,20 +1226,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>24578</v>
+        <v>24575</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1280,20 +1280,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>96549</v>
+        <v>96537</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>96549</v>
+        <v>96537</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1334,20 +1334,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1388,20 +1388,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>35223</v>
+        <v>35218</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>65826</v>
+        <v>65817</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5525</v>
+        <v>5524</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1442,20 +1442,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14746</v>
+        <v>14744</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>65826</v>
+        <v>65817</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5525</v>
+        <v>5524</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1499,7 +1499,7 @@
         <v>812</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1625</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1563,17 +1563,17 @@
         <v>1625</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>233998</v>
+        <v>233969</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>113</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1614,20 +1614,20 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>276230</v>
+        <v>276196</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1668,20 +1668,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5850</v>
+        <v>5849</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11699</v>
+        <v>11698</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1722,20 +1722,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11374</v>
+        <v>11373</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37973</v>
+        <v>37969</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1776,20 +1776,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21936</v>
+        <v>21933</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>143428</v>
+        <v>143411</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1808,18 +1808,18 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1840,20 +1840,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>330397</v>
+        <v>330356</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81244</v>
+        <v>81234</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>2266</v>
+        <v>2422</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2528</v>
+        <v>2522</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>325</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1456</v>
+        <v>1446</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1620</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2026,17 +2026,17 @@
         <v>1300</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1134</v>
+        <v>1148</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2087,20 +2087,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1341</v>
+        <v>1300</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1620567</v>
+        <v>1620366</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1625</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2123,14 +2123,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>28</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1687</v>
+        <v>1675</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2154,17 +2154,17 @@
         <v>1625</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O28" s="2" t="n">
         <v>85</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2215,20 +2215,20 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17506</v>
+        <v>17504</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>61</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
         <v>650</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1300</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2336,17 +2336,17 @@
         <v>2437</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11854</v>
+        <v>11852</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>52</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2365,18 +2365,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1510</v>
+        <v>812</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1206</v>
+        <v>1150</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2397,20 +2397,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1518</v>
+        <v>1163</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>649953</v>
+        <v>649872</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1661</v>
+        <v>1625</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>193</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
         <v>12</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2464,17 +2464,17 @@
         <v>2970</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13163</v>
+        <v>13162</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2493,18 +2493,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3542</v>
+        <v>3761</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3418</v>
+        <v>3431</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2525,20 +2525,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3688</v>
+        <v>3628</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21720</v>
+        <v>21717</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>67</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>19</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2589,20 +2589,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>31407</v>
+        <v>31403</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2715,14 +2715,14 @@
         <v>4270</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>8</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3296</v>
+        <v>3295</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2769,20 +2769,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>324976</v>
+        <v>324936</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2833,20 +2833,20 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>148753</v>
+        <v>148735</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>49</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
         <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2897,20 +2897,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4836</v>
+        <v>4835</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17875</v>
+        <v>17873</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -2929,18 +2929,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6615</v>
+        <v>6610</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2961,20 +2961,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15545</v>
+        <v>15543</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
         <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>3818</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6293</v>
+        <v>6292</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>2275</v>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6415</v>
+        <v>6414</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3081,10 +3081,10 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>9132</v>
+        <v>9131</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>4062</v>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3113,18 +3113,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9954</v>
+        <v>9220</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9928</v>
+        <v>9949</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3141,20 +3141,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9610</v>
+        <v>9607</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>10705</v>
+        <v>10703</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11301</v>
+        <v>11090</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
         <v>1625</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8958</v>
+        <v>8957</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>42</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3259,20 +3259,20 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
         <v>796</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>6035</v>
+        <v>6034</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>812</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3387,10 +3387,10 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2691</v>
+        <v>2690</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1625</v>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3451,20 +3451,20 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O49" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr"/>
-      <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="3" t="inlineStr"/>
+      <c r="D50" s="3" t="n">
+        <v>1457</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>1457</v>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -3501,20 +3511,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>970</v>
+        <v>2197</v>
       </c>
       <c r="M50" s="3" t="n">
         <v>4260</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>812</v>
+        <v>1604</v>
       </c>
       <c r="O50" s="2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3543,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3544,7 +3554,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3561,10 +3571,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4483</v>
+        <v>4482</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1625</v>
@@ -3574,7 +3584,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3611,20 +3621,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3698,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3742,7 @@
         <v>1852</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11603</v>
+        <v>11602</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1625</v>
@@ -3742,7 +3752,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3793,20 +3803,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>31430</v>
+        <v>31426</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3835,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>10206</v>
+        <v>10205</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3836,7 +3846,7 @@
         <v>11</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>9828</v>
+        <v>9827</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3857,20 +3867,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>11148</v>
+        <v>11147</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>11715</v>
+        <v>11714</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>11226</v>
+        <v>6499</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3889,18 +3899,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>12624</v>
+        <v>11647</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>14362</v>
+        <v>14329</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3921,20 +3931,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9717</v>
+        <v>9693</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>31471</v>
+        <v>31467</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>15362</v>
+        <v>14582</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3963,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3752</v>
+        <v>3751</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3961,10 +3971,10 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4499</v>
+        <v>4564</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3985,20 +3995,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3885</v>
+        <v>3865</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10607</v>
+        <v>10606</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4605</v>
+        <v>4333</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4017,18 +4027,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>4857</v>
+        <v>3348</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3473</v>
+        <v>3466</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4049,20 +4059,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>3461</v>
+        <v>2616</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11618</v>
+        <v>11616</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>4784</v>
+        <v>4478</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4116,17 @@
         <v>1142</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4157,20 +4167,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3557</v>
+        <v>3556</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4223,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>10074</v>
+        <v>10073</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4259,20 +4269,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4315,12 +4325,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4361,20 +4371,20 @@
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4415,20 +4425,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>51996</v>
+        <v>51990</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4469,20 +4479,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4535,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22748</v>
+        <v>22746</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4587,14 +4597,14 @@
         <v>3805</v>
       </c>
       <c r="N69" s="3" t="n">
-        <v>1766</v>
+        <v>1625</v>
       </c>
       <c r="O69" s="2" t="n">
         <v>83</v>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4641,14 +4651,14 @@
         <v>5175</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>38</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4689,20 +4699,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5167</v>
+        <v>5166</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4743,20 +4753,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1524208</v>
+        <v>1524019</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11699</v>
+        <v>11698</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4797,20 +4807,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4883</v>
+        <v>4882</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7681</v>
+        <v>7680</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4851,20 +4861,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8937</v>
+        <v>8936</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21528</v>
+        <v>21525</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17874</v>
+        <v>17871</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4905,20 +4915,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17874</v>
+        <v>17871</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27789</v>
+        <v>27785</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O75" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4982,7 @@
         <v>192</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6548</v>
+        <v>6547</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>325</v>
@@ -4982,7 +4992,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5046,7 @@
         <v>1219</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5328</v>
+        <v>5327</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>650</v>
@@ -5046,7 +5056,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5114,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5145,20 +5155,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5850</v>
+        <v>5849</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5850</v>
+        <v>5849</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5201,12 +5211,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5247,20 +5257,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23766</v>
+        <v>23763</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23766</v>
+        <v>23763</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5303,12 +5313,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20798</v>
+        <v>20796</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5358,7 +5368,7 @@
         <v>408</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1624720</v>
+        <v>1624519</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>812</v>
@@ -5368,7 +5378,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5428,7 @@
         <v>975</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35520</v>
+        <v>35516</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1625</v>
@@ -5428,7 +5438,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5481,14 +5491,14 @@
         <v>3240</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5525,20 +5535,20 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>5047</v>
+        <v>5046</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5577,12 +5587,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5619,20 +5629,20 @@
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="n">
-        <v>4854</v>
+        <v>4853</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>4854</v>
+        <v>4853</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5671,12 +5681,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17874</v>
+        <v>17871</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5736,7 @@
         <v>509</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>88309</v>
+        <v>88298</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>812</v>
@@ -5736,7 +5746,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5796,7 @@
         <v>845</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5401</v>
+        <v>5400</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1625</v>
@@ -5796,7 +5806,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5833,20 +5843,20 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5895,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5929,12 +5939,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5983,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6017,12 +6027,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17874</v>
+        <v>17871</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6069,14 +6079,14 @@
         <v>3180</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6123,14 +6133,14 @@
         <v>2112</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6177,14 +6187,14 @@
         <v>5318</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10074</v>
+        <v>10073</v>
       </c>
       <c r="O99" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6225,20 +6235,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6281,12 +6291,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6327,20 +6337,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18460</v>
+        <v>18458</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18460</v>
+        <v>18458</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6383,12 +6393,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>51996</v>
+        <v>51990</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6435,14 +6445,14 @@
         <v>2762</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="O104" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6485,12 +6495,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6543,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>10074</v>
+        <v>10073</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6579,20 +6589,20 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6635,12 +6645,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6683,12 +6693,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6731,12 +6741,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>51996</v>
+        <v>51990</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6777,20 +6787,20 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>75703</v>
+        <v>75694</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>75703</v>
+        <v>75694</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>81244</v>
+        <v>81234</v>
       </c>
       <c r="O111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6819,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>89369</v>
+        <v>89357</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6820,7 +6830,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>89369</v>
+        <v>89357</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6841,20 +6851,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>89369</v>
+        <v>89357</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>99758</v>
+        <v>99746</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>113742</v>
+        <v>113728</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6895,20 +6905,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>113742</v>
+        <v>113728</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>113742</v>
+        <v>113728</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>146239</v>
+        <v>146221</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6927,7 +6937,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6938,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6959,20 +6969,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -6991,7 +7001,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -7002,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7023,20 +7033,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>194986</v>
+        <v>194962</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7077,20 +7087,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>219359</v>
+        <v>219332</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>292479</v>
+        <v>292443</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>259981</v>
+        <v>259949</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7154,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7188,7 +7198,7 @@
         <v>3896</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>6009</v>
+        <v>6008</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>4062</v>
@@ -7198,7 +7208,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7241,12 +7251,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7287,20 +7297,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7343,12 +7353,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23398</v>
+        <v>23395</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7389,20 +7399,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19538</v>
+        <v>19535</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7443,20 +7453,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>32497645</v>
+        <v>32493620</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7520,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7551,10 +7561,10 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5835</v>
+        <v>5834</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>4062</v>
@@ -7564,7 +7574,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7605,20 +7615,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6636</v>
+        <v>6635</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6636</v>
+        <v>6635</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7659,20 +7669,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>12208</v>
+        <v>12206</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7715,12 +7725,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23398</v>
+        <v>23395</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7763,12 +7773,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7821,12 @@
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="3" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7857,20 +7867,20 @@
         </is>
       </c>
       <c r="L131" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M131" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7911,20 +7921,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -7965,20 +7975,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16338</v>
+        <v>16336</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8021,12 +8031,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8067,20 +8077,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21936</v>
+        <v>21933</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21936</v>
+        <v>21933</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>48746</v>
+        <v>48740</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8109,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8110,7 +8120,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8131,20 +8141,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>73120</v>
+        <v>73111</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8185,20 +8195,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8217,18 +8227,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8249,20 +8259,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>13092</v>
+        <v>13090</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8326,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8380,7 +8390,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8454,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8471,10 +8481,10 @@
         </is>
       </c>
       <c r="F142" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>1472</v>
+        <v>1552</v>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
@@ -8508,7 +8518,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8549,20 +8559,20 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8626,7 @@
         <v>2138</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>11030</v>
+        <v>11028</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>4062</v>
@@ -8626,7 +8636,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8669,12 +8679,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8693,7 +8703,7 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -8704,7 +8714,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -8725,20 +8735,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>54950</v>
+        <v>54943</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8781,12 +8791,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8827,20 +8837,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17805</v>
+        <v>17803</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8883,12 +8893,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8907,18 +8917,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
         <v>43</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16408</v>
+        <v>16406</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8939,20 +8949,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -8971,18 +8981,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
         <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9003,20 +9013,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>86346</v>
+        <v>86336</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>77994</v>
+        <v>77985</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9057,20 +9067,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>105617</v>
+        <v>105604</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>105617</v>
+        <v>105604</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>211235</v>
+        <v>211209</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9124,7 +9134,7 @@
         <v>162</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10630</v>
+        <v>10629</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>325</v>
@@ -9134,7 +9144,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9208,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9258,7 @@
         <v>838</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15921</v>
+        <v>15919</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1625</v>
@@ -9258,7 +9268,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9308,17 +9318,17 @@
         <v>1625</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>3328</v>
+        <v>3327</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9337,7 +9347,7 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -9348,7 +9358,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -9365,20 +9375,20 @@
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9422,7 +9432,7 @@
         <v>812</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19864</v>
+        <v>19862</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1625</v>
@@ -9432,7 +9442,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9476,17 +9486,17 @@
         <v>1625</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19705</v>
+        <v>19703</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9505,7 +9515,7 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
@@ -9516,7 +9526,7 @@
         <v>3</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
@@ -9537,20 +9547,20 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6797</v>
+        <v>6796</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9614,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9623,18 +9633,18 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1767</v>
+        <v>1777</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9655,20 +9665,20 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1844</v>
+        <v>1787</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>31003</v>
+        <v>30999</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>1625</v>
+        <v>2029</v>
       </c>
       <c r="O162" s="2" t="n">
         <v>32</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9698,7 +9708,7 @@
         <v>7</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9722,17 +9732,17 @@
         <v>3110</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3900</v>
+        <v>3899</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9751,18 +9761,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4225</v>
+        <v>3776</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3715</v>
+        <v>3716</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9783,20 +9793,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3770</v>
+        <v>3586</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9823,10 +9833,10 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9860,7 +9870,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9887,10 +9897,10 @@
         </is>
       </c>
       <c r="F166" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G166" s="3" t="n">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
@@ -9924,7 +9934,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9953,7 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -9978,7 +9988,7 @@
         <v>1461</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9987</v>
+        <v>9985</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1300</v>
@@ -9988,7 +9998,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10052,7 @@
         <v>1625</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5541</v>
+        <v>5540</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>325</v>
@@ -10052,7 +10062,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10116,7 @@
         <v>340</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>325</v>
@@ -10116,7 +10126,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10157,20 +10167,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>97493</v>
+        <v>97481</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>97493</v>
+        <v>97481</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10213,12 +10223,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10278,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10328,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10357,12 +10367,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10399,20 +10409,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14593</v>
+        <v>14591</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10449,20 +10459,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11699</v>
+        <v>11698</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11699</v>
+        <v>11698</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23398</v>
+        <v>23395</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10499,20 +10509,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16330</v>
+        <v>16328</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10549,20 +10559,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19661</v>
+        <v>19659</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O178" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10605,12 +10615,12 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10651,20 +10661,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10707,12 +10717,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10753,20 +10763,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10819,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10855,20 +10865,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21936</v>
+        <v>21933</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21936</v>
+        <v>21933</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>43872</v>
+        <v>43866</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10909,20 +10919,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>29248</v>
+        <v>29244</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>58496</v>
+        <v>58489</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10976,7 @@
         <v>162</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>325</v>
@@ -10976,7 +10986,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11030,7 @@
         <v>162</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>325</v>
@@ -11030,7 +11040,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11084,7 @@
         <v>162</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>105718</v>
+        <v>105705</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>325</v>
@@ -11084,7 +11094,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11142,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11196,7 @@
         <v>162</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29969</v>
+        <v>29966</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>325</v>
@@ -11196,7 +11206,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11215,18 +11225,18 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>656</v>
+        <v>853</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>656</v>
+        <v>755</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -11250,17 +11260,17 @@
         <v>162</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>160430</v>
+        <v>160410</v>
       </c>
       <c r="N191" s="3" t="n">
-        <v>325</v>
+        <v>937</v>
       </c>
       <c r="O191" s="2" t="n">
         <v>512</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11314,7 @@
         <v>162</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>325</v>
@@ -11314,7 +11324,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11372,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11416,7 @@
         <v>162</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>325</v>
@@ -11416,7 +11426,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11480,7 @@
         <v>162</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>162326</v>
+        <v>162306</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>325</v>
@@ -11480,7 +11490,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11524,7 +11534,7 @@
         <v>162</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>325</v>
@@ -11534,7 +11544,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11592,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11646,7 @@
         <v>876</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>640</v>
@@ -11646,7 +11656,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11665,7 +11675,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -11676,7 +11686,7 @@
         <v>1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -11697,20 +11707,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>21159</v>
+        <v>21157</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>21159</v>
+        <v>21157</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11751,20 +11761,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="M200" s="3" t="n">
         <v>6478</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11805,20 +11815,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>11070</v>
+        <v>11069</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7799</v>
+        <v>7798</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11859,20 +11869,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>8108</v>
+        <v>8107</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11913,20 +11923,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8449</v>
+        <v>8448</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>283656</v>
+        <v>283621</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14299</v>
+        <v>14297</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11967,20 +11977,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>16055</v>
+        <v>16053</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16480</v>
+        <v>16478</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -11999,7 +12009,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>21804</v>
+        <v>21802</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -12010,7 +12020,7 @@
         <v>2</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>21301</v>
+        <v>21299</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -12031,20 +12041,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>23419</v>
+        <v>23269</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>50126</v>
+        <v>50120</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O205" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12087,12 +12097,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23398</v>
+        <v>23395</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12146,7 +12156,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12173,10 +12183,10 @@
         </is>
       </c>
       <c r="F208" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G208" s="3" t="n">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
@@ -12210,7 +12220,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12274,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12308,17 +12318,17 @@
         <v>2112</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4594</v>
+        <v>4593</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4225</v>
+        <v>4224</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12362,17 +12372,17 @@
         <v>4062</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12413,20 +12423,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12469,12 +12479,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23398</v>
+        <v>23395</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12515,20 +12525,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12592,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12626,17 +12636,17 @@
         <v>2112</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>12201</v>
+        <v>12200</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4225</v>
+        <v>4224</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12677,20 +12687,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15999</v>
+        <v>15997</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>21965</v>
+        <v>21962</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12734,17 +12744,17 @@
         <v>4062</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>7899</v>
+        <v>7898</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12785,20 +12795,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7312</v>
+        <v>7311</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14624</v>
+        <v>14622</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12841,12 +12851,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12887,20 +12897,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -12964,7 +12974,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13021,14 +13031,14 @@
         <v>4158</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13047,7 +13057,7 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -13058,7 +13068,7 @@
         <v>1</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -13079,20 +13089,20 @@
         </is>
       </c>
       <c r="L224" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7395</v>
+        <v>7394</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13146,7 +13156,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13197,20 +13207,20 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3131</v>
+        <v>1940</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>3570</v>
+        <v>3569</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13229,7 +13239,7 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -13240,7 +13250,7 @@
         <v>1</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -13261,20 +13271,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M227" s="3" t="n">
         <v>3885</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13338,7 @@
         <v>162</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>325</v>
@@ -13338,7 +13348,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13382,7 +13392,7 @@
         <v>162</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>325</v>
@@ -13392,7 +13402,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13446,7 +13456,7 @@
         <v>162</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>689</v>
@@ -13456,7 +13466,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13510,7 @@
         <v>812</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1625</v>
@@ -13510,7 +13520,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13567,14 +13577,14 @@
         <v>3290</v>
       </c>
       <c r="N232" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>55</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13603,7 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
@@ -13604,7 +13614,7 @@
         <v>1</v>
       </c>
       <c r="G233" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
@@ -13625,20 +13635,20 @@
         </is>
       </c>
       <c r="L233" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7403</v>
+        <v>7402</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13702,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13721,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -13722,7 +13732,7 @@
         <v>1</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>3658</v>
+        <v>3657</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -13749,14 +13759,14 @@
         <v>4379</v>
       </c>
       <c r="N235" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O235" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13785,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>5135</v>
+        <v>5134</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -13786,7 +13796,7 @@
         <v>1</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>5135</v>
+        <v>5134</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -13810,17 +13820,17 @@
         <v>5149</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6701</v>
+        <v>6700</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>5648</v>
+        <v>4062</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13863,12 +13873,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13909,20 +13919,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8937</v>
+        <v>8936</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11327</v>
+        <v>11326</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -13965,12 +13975,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14011,20 +14021,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10763</v>
+        <v>10762</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10763</v>
+        <v>10762</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14043,7 +14053,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>20392</v>
+        <v>20390</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14054,7 +14064,7 @@
         <v>11</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19447</v>
+        <v>19445</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14075,20 +14085,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>19422</v>
+        <v>19420</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>35734</v>
+        <v>35730</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14107,7 +14117,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14118,7 +14128,7 @@
         <v>1</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14139,20 +14149,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>39038</v>
+        <v>39033</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>60205</v>
+        <v>60198</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>77994</v>
+        <v>77985</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14171,18 +14181,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>18451</v>
+        <v>18335</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>19397</v>
+        <v>19333</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14199,20 +14209,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>20392</v>
+        <v>18846</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>32497645</v>
+        <v>32493620</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14255,12 +14265,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14314,7 @@
         <v>650</v>
       </c>
       <c r="M245" s="3" t="n">
-        <v>2527</v>
+        <v>2526</v>
       </c>
       <c r="N245" s="3" t="n">
         <v>325</v>
@@ -14314,7 +14324,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14344,7 +14354,7 @@
         <v>9</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2838</v>
+        <v>2837</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14365,20 +14375,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2353</v>
+        <v>2232</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2985</v>
+        <v>3022</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14419,20 +14429,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15956</v>
+        <v>15954</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23957</v>
+        <v>23954</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>18199</v>
+        <v>18196</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14473,20 +14483,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>18199</v>
+        <v>18196</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14526,7 +14536,7 @@
         <v>812</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9540</v>
+        <v>9539</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1625</v>
@@ -14536,7 +14546,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14596,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14640,7 @@
         <v>162</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>99916</v>
+        <v>99903</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>325</v>
@@ -14640,7 +14650,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14681,20 +14691,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>51775</v>
+        <v>51769</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>51775</v>
+        <v>51769</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14738,17 +14748,17 @@
         <v>6842</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>7747</v>
+        <v>7746</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7799</v>
+        <v>7798</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14767,7 +14777,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>6865</v>
+        <v>6864</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -14799,20 +14809,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>8077</v>
+        <v>8076</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>194986</v>
+        <v>194962</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14886,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14940,7 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -14974,7 +14984,7 @@
         <v>299</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>8124</v>
+        <v>8123</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>325</v>
@@ -14984,7 +14994,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15007,14 +15017,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
         <v>54</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15038,17 +15048,17 @@
         <v>325</v>
       </c>
       <c r="M258" s="3" t="n">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N258" s="3" t="n">
         <v>650</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15102,7 +15112,7 @@
         <v>970</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21973</v>
+        <v>21971</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1625</v>
@@ -15112,7 +15122,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15131,7 +15141,7 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -15163,20 +15173,20 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2665</v>
+        <v>2664</v>
       </c>
       <c r="M260" s="3" t="n">
         <v>3773</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O260" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15195,7 +15205,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>4022</v>
+        <v>4021</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15206,7 +15216,7 @@
         <v>2</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3636</v>
+        <v>3635</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15227,20 +15237,20 @@
         </is>
       </c>
       <c r="L261" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7208</v>
+        <v>7207</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15259,7 +15269,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6501</v>
+        <v>6500</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15270,7 +15280,7 @@
         <v>17</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6533</v>
+        <v>6532</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15291,20 +15301,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O262" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15348,7 +15358,7 @@
         <v>812</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10851</v>
+        <v>10850</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1625</v>
@@ -15358,7 +15368,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15415,14 +15425,14 @@
         <v>1657</v>
       </c>
       <c r="N264" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O264" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15475,12 +15485,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15498,23 +15508,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D266" s="3" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G266" s="3" t="n">
-        <v>6500</v>
-      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="3" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
@@ -15531,20 +15531,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9902</v>
+        <v>9901</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15563,7 +15563,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>6</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15595,10 +15595,10 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2039</v>
+        <v>1743</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19984</v>
+        <v>19982</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>650</v>
@@ -15608,7 +15608,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15627,7 +15627,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8449</v>
+        <v>8448</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8449</v>
+        <v>8448</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15659,20 +15659,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8449</v>
+        <v>8448</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14637</v>
+        <v>14635</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14299</v>
+        <v>14297</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15715,12 +15715,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15761,20 +15761,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>25585</v>
+        <v>25582</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25585</v>
+        <v>25582</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15793,7 +15793,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>20798</v>
+        <v>20796</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>25249</v>
+        <v>25246</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15825,20 +15825,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24534</v>
+        <v>24531</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>53412</v>
+        <v>53405</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15882,17 +15882,17 @@
         <v>162</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>9972</v>
+        <v>9971</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>325</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -15936,7 +15936,7 @@
         <v>162</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21520</v>
+        <v>21517</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>325</v>
@@ -15946,7 +15946,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16000,7 +16000,7 @@
         <v>162</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>32605</v>
+        <v>32601</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>325</v>
@@ -16010,7 +16010,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16064,7 +16064,7 @@
         <v>162</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16330</v>
+        <v>16328</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>325</v>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16093,7 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>13755</v>
+        <v>13753</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -16128,17 +16128,17 @@
         <v>162</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>162485</v>
+        <v>162465</v>
       </c>
       <c r="N276" s="3" t="n">
-        <v>15129</v>
+        <v>15127</v>
       </c>
       <c r="O276" s="2" t="n">
         <v>278</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="D278" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>1</v>
       </c>
       <c r="G278" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
@@ -16239,20 +16239,20 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>8766</v>
+        <v>8765</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16293,20 +16293,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>10167</v>
+        <v>10166</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7799</v>
+        <v>7798</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16347,20 +16347,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8843</v>
+        <v>8842</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10399</v>
+        <v>10398</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16403,12 +16403,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14299</v>
+        <v>14297</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16451,12 +16451,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16499,12 +16499,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16523,7 +16523,7 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>20798</v>
+        <v>20796</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -16534,7 +16534,7 @@
         <v>1</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>20798</v>
+        <v>20796</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -16555,20 +16555,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>37047</v>
+        <v>37043</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>37047</v>
+        <v>37043</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16587,18 +16587,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9710</v>
+        <v>10180</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>10248</v>
+        <v>10242</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16619,20 +16619,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10185</v>
+        <v>10180</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>11584</v>
+        <v>11506</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16696,7 +16696,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16726,7 @@
         <v>13</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5100</v>
+        <v>5099</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16743,20 +16743,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5825</v>
+        <v>5046</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5931</v>
+        <v>5930</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>4709</v>
+        <v>5665</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16775,18 +16775,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6797</v>
+        <v>7036</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6911</v>
+        <v>6984</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16803,20 +16803,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6987</v>
+        <v>8044</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8053</v>
+        <v>8052</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7348</v>
+        <v>7387</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16835,18 +16835,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9709</v>
+        <v>9703</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9459</v>
+        <v>9469</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16863,20 +16863,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9705</v>
+        <v>9722</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11811</v>
+        <v>11810</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10370</v>
+        <v>10456</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16895,7 @@
         </is>
       </c>
       <c r="D290" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>2525</v>
       </c>
       <c r="M290" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="N290" s="3" t="n">
         <v>1625</v>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -16994,17 +16994,17 @@
         <v>3883</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>5200</v>
+        <v>5199</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>3739</v>
+        <v>3738</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>4320</v>
+        <v>4148</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17055,20 +17055,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4095</v>
+        <v>4314</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5687</v>
+        <v>5686</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17132,7 +17132,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17151,18 +17151,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5825</v>
+        <v>6169</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6629</v>
+        <v>6649</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17183,20 +17183,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>5148</v>
+        <v>6312</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>19396</v>
+        <v>19394</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6917</v>
+        <v>6871</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17237,20 +17237,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>52814</v>
+        <v>52807</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>717777</v>
+        <v>717688</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17269,7 +17269,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17280,7 +17280,7 @@
         <v>12</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17301,20 +17301,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>70648</v>
+        <v>70640</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>40622</v>
+        <v>40617</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17333,7 +17333,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>64995</v>
+        <v>64987</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>64995</v>
+        <v>64987</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17365,20 +17365,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>64995</v>
+        <v>64987</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>81244</v>
+        <v>81234</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17397,18 +17397,18 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17429,20 +17429,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>129991</v>
+        <v>129974</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>129994</v>
+        <v>129978</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>162488</v>
+        <v>162468</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>259981</v>
+        <v>259949</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>259981</v>
+        <v>259949</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17493,20 +17493,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>259981</v>
+        <v>259949</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>262485</v>
+        <v>262453</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>324976</v>
+        <v>324936</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17525,7 +17525,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>454967</v>
+        <v>454911</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>3</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>454967</v>
+        <v>454911</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17557,20 +17557,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>454967</v>
+        <v>454911</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>975756</v>
+        <v>975636</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>649953</v>
+        <v>649872</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>17001</v>
+        <v>16999</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>9</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>18681</v>
+        <v>18678</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17621,20 +17621,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>29144</v>
+        <v>29140</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>34285</v>
+        <v>34281</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>17102</v>
+        <v>17100</v>
       </c>
       <c r="O301" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1684</v>
+        <v>1753</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1942</v>
+        <v>1137</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4928</v>
@@ -17698,7 +17698,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17717,7 +17717,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4334</v>
+        <v>4333</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17725,10 +17725,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4354</v>
+        <v>4351</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17749,20 +17749,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4272</v>
+        <v>4271</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>16247</v>
+        <v>16245</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4766</v>
+        <v>325</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17781,18 +17781,18 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1137</v>
+        <v>2518</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1642</v>
+        <v>1767</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17816,17 +17816,17 @@
         <v>2523</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2275</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17853,10 +17853,10 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G305" s="3" t="n">
-        <v>652</v>
+        <v>616</v>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -17944,17 +17944,17 @@
         <v>162</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>2091</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>16812</v>
+        <v>17029</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18005,10 +18005,10 @@
         </is>
       </c>
       <c r="L307" s="3" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>1547</v>
@@ -18018,7 +18018,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18072,7 +18072,7 @@
         <v>2112</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1299906</v>
+        <v>1299745</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>4062</v>
@@ -18082,7 +18082,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18123,20 +18123,20 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32855</v>
+        <v>32851</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18190,17 +18190,17 @@
         <v>1625</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6191</v>
+        <v>6190</v>
       </c>
       <c r="N310" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O310" s="2" t="n">
         <v>61</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18219,7 +18219,7 @@
         </is>
       </c>
       <c r="D311" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>1</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
@@ -18254,17 +18254,17 @@
         <v>4975</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6201</v>
+        <v>6200</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18307,12 +18307,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18363,20 +18363,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26866</v>
+        <v>26862</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18417,20 +18417,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15896</v>
+        <v>15894</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15896</v>
+        <v>15894</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>27</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>16310</v>
+        <v>16308</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18481,20 +18481,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>4</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18545,20 +18545,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38997</v>
+        <v>38992</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>77994</v>
+        <v>77985</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18599,20 +18599,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>105617</v>
+        <v>105604</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>105617</v>
+        <v>105604</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>211235</v>
+        <v>211209</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18639,10 +18639,10 @@
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>837</v>
+        <v>883</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18717,10 +18717,10 @@
         </is>
       </c>
       <c r="L319" s="3" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>16138</v>
+        <v>16136</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>325</v>
@@ -18730,7 +18730,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
         <v>14</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18781,20 +18781,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>2234</v>
+        <v>1137</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>10095</v>
+        <v>10094</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2275</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18848,7 +18848,7 @@
         <v>3737</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>6043</v>
+        <v>6042</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>325</v>
@@ -18858,7 +18858,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18909,7 +18909,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>379</v>
+        <v>484</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1069</v>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -18952,7 +18952,7 @@
         <v>7</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>3095</v>
+        <v>3094</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18976,17 +18976,17 @@
         <v>2523</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16952</v>
+        <v>16950</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="O323" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19030,7 +19030,7 @@
         <v>325</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5746</v>
+        <v>5745</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>325</v>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19067,10 +19067,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2017</v>
+        <v>2047</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19091,20 +19091,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>2038</v>
+        <v>1932</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>16138</v>
+        <v>16136</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="O325" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19131,10 +19131,10 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2327</v>
+        <v>2268</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19155,20 +19155,20 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>3086</v>
+        <v>2465</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2275</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19187,18 +19187,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>11374</v>
+        <v>2876</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>4524</v>
+        <v>4594</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19219,20 +19219,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1137</v>
+        <v>3745</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>4616</v>
+        <v>4370</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>6417</v>
+        <v>5114</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19251,18 +19251,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22724</v>
+        <v>21121</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>21821</v>
+        <v>21833</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19283,20 +19283,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>21123</v>
+        <v>22323</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>33490</v>
+        <v>33486</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>23325</v>
+        <v>25659</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19315,7 +19315,7 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7180</v>
+        <v>7179</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
@@ -19323,10 +19323,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7410</v>
+        <v>7372</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19347,20 +19347,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7283</v>
+        <v>7282</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9348</v>
+        <v>9347</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7544</v>
+        <v>7569</v>
       </c>
       <c r="O329" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19379,7 +19379,7 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5731</v>
+        <v>5730</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>6172</v>
+        <v>6151</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19411,20 +19411,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6139</v>
+        <v>5199</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8891</v>
+        <v>8890</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6825</v>
+        <v>7084</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19478,7 +19478,7 @@
         <v>1435</v>
       </c>
       <c r="M331" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="N331" s="3" t="n">
         <v>325</v>
@@ -19488,7 +19488,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19539,10 +19539,10 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1254</v>
@@ -19552,7 +19552,7 @@
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19616,7 +19616,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19635,18 +19635,18 @@
         </is>
       </c>
       <c r="D334" s="3" t="n">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>2439</v>
+        <v>2218</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19670,17 +19670,17 @@
         <v>455</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="O334" s="2" t="n">
         <v>37</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19731,20 +19731,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1815</v>
+        <v>1812</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>4956</v>
+        <v>4955</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2502</v>
+        <v>2275</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19767,14 +19767,14 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>162</v>
       </c>
       <c r="M336" s="3" t="n">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="N336" s="3" t="n">
         <v>325</v>
@@ -19808,7 +19808,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19835,7 +19835,7 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G337" s="3" t="n">
         <v>163</v>
@@ -19862,7 +19862,7 @@
         <v>162</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15909</v>
+        <v>15907</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>325</v>
@@ -19872,7 +19872,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19936,7 +19936,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -19963,7 +19963,7 @@
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G339" s="3" t="n">
         <v>478</v>
@@ -19990,7 +19990,7 @@
         <v>453</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4839</v>
+        <v>4838</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>325</v>
@@ -20000,7 +20000,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20018,23 +20018,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D340" s="3" t="n">
-        <v>1063</v>
-      </c>
-      <c r="E340" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-21</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G340" s="3" t="n">
-        <v>1063</v>
-      </c>
+      <c r="D340" s="3" t="inlineStr"/>
+      <c r="E340" s="2" t="inlineStr"/>
+      <c r="F340" s="2" t="inlineStr"/>
+      <c r="G340" s="3" t="inlineStr"/>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I340" s="2" t="n">
@@ -20054,7 +20044,7 @@
         <v>1069</v>
       </c>
       <c r="M340" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="N340" s="3" t="n">
         <v>325</v>
@@ -20064,7 +20054,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20118,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20182,7 +20172,7 @@
         <v>320</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>351</v>
@@ -20192,7 +20182,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20246,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20279,14 +20269,14 @@
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1714</v>
+        <v>1704</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20310,17 +20300,17 @@
         <v>1625</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>17479</v>
+        <v>17477</v>
       </c>
       <c r="N344" s="3" t="n">
-        <v>3250</v>
+        <v>3249</v>
       </c>
       <c r="O344" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20374,17 +20364,17 @@
         <v>2112</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1624882</v>
+        <v>1624681</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>4062</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20427,12 +20417,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4875</v>
+        <v>4874</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20451,7 +20441,7 @@
         </is>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -20462,7 +20452,7 @@
         <v>1</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
@@ -20483,20 +20473,20 @@
         </is>
       </c>
       <c r="L347" s="3" t="n">
-        <v>4550</v>
+        <v>4549</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>7286</v>
+        <v>8153</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6500</v>
+        <v>6499</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20537,20 +20527,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12999</v>
+        <v>12997</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20569,7 +20559,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20580,7 +20570,7 @@
         <v>4</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20601,20 +20591,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9749</v>
+        <v>9748</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19499</v>
+        <v>19496</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20657,12 +20647,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25998</v>
+        <v>25995</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20681,18 +20671,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16360</v>
+        <v>16348</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20713,20 +20703,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16249</v>
+        <v>16247</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38862</v>
+        <v>38857</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>32498</v>
+        <v>32494</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20745,7 +20735,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>47585</v>
+        <v>47579</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20756,7 +20746,7 @@
         <v>5</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>47474</v>
+        <v>47468</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20776,15 +20766,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="inlineStr"/>
-      <c r="M352" s="3" t="inlineStr"/>
+      <c r="L352" s="3" t="n">
+        <v>53216</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>96932</v>
+      </c>
       <c r="N352" s="3" t="n">
-        <v>77994</v>
-      </c>
-      <c r="O352" s="2" t="inlineStr"/>
+        <v>77985</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20803,7 +20799,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>194312</v>
+        <v>194287</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20814,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>194312</v>
+        <v>194287</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20835,20 +20831,20 @@
         </is>
       </c>
       <c r="L353" s="3" t="n">
-        <v>223464</v>
+        <v>213546</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>223464</v>
+        <v>213546</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>213742</v>
+        <v>213715</v>
       </c>
       <c r="O353" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20867,7 +20863,7 @@
         </is>
       </c>
       <c r="D354" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
@@ -20878,7 +20874,7 @@
         <v>1</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
@@ -20899,20 +20895,20 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>19458</v>
+        <v>19456</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>18199</v>
+        <v>18196</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -20931,7 +20927,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20942,7 +20938,7 @@
         <v>1</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20963,20 +20959,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>9099</v>
+        <v>9098</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>22375</v>
+        <v>22372</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>18199</v>
+        <v>18196</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -21006,7 +21002,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>162.488226</v>
+        <v>162.468102</v>
       </c>
     </row>
     <row r="2">
@@ -21017,7 +21013,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Mon, 20 Jul 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Tue, 21 Jul 2026 00:02:32 +0000)</t>
         </is>
       </c>
     </row>
@@ -21029,7 +21025,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3276</v>
+        <v>3930</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3762</v>
+        <v>3771</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3883</v>
+        <v>3882</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>181</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -660,20 +660,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>100146</v>
+        <v>100138</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -724,20 +724,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24573</v>
+        <v>24571</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24573</v>
+        <v>24571</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24573</v>
+        <v>24571</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24573</v>
+        <v>24571</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>49147</v>
+        <v>49143</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -852,20 +852,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>75005</v>
+        <v>74999</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>88464</v>
+        <v>88457</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>147440</v>
+        <v>147429</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>147440</v>
+        <v>147429</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>262116</v>
+        <v>262095</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>368601</v>
+        <v>368572</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>368601</v>
+        <v>368572</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>737202</v>
+        <v>737144</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6299</v>
+        <v>6163</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>38</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6314</v>
+        <v>6307</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,10 +1034,10 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6307</v>
+        <v>6259</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>9010</v>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8398</v>
+        <v>8928</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9084</v>
+        <v>9072</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8350</v>
+        <v>9702</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>155589</v>
+        <v>155577</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>18020</v>
+        <v>18019</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1130,18 +1130,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14937</v>
+        <v>14916</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>43985</v>
+        <v>43981</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>36041</v>
+        <v>36038</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>26477</v>
+        <v>26475</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>97342</v>
+        <v>97334</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>97342</v>
+        <v>97334</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1378,10 +1378,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>35512</v>
+        <v>35509</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>66366</v>
+        <v>66361</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5570</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14867</v>
+        <v>14866</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>66366</v>
+        <v>66361</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5570</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
         <v>819</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1638</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
         <v>1638</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>235919</v>
+        <v>235901</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3276</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1607,17 +1607,17 @@
         <v>3276</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>278499</v>
+        <v>278476</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1658,20 +1658,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11795</v>
+        <v>11794</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1712,20 +1712,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11468</v>
+        <v>11467</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>38285</v>
+        <v>38282</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1766,20 +1766,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>22116</v>
+        <v>22114</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>144606</v>
+        <v>144595</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1830,20 +1830,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>333110</v>
+        <v>333084</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81911</v>
+        <v>81905</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2543</v>
+        <v>2503</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>328</v>
@@ -1898,7 +1898,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1708</v>
+        <v>1677</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1952,17 +1952,17 @@
         <v>1365</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>328</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2621</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
@@ -2067,20 +2067,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1358</v>
+        <v>1165</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1633875</v>
+        <v>1633746</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1638</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2131,20 +2131,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2606</v>
+        <v>1843</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3276</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
@@ -2198,17 +2198,17 @@
         <v>3276</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17650</v>
+        <v>17649</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>60</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2252,17 +2252,17 @@
         <v>655</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>381</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>2457</v>
@@ -2316,17 +2316,17 @@
         <v>2457</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11951</v>
+        <v>11950</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2380,17 +2380,17 @@
         <v>1173</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>655291</v>
+        <v>655239</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1638</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13271</v>
+        <v>13270</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3276</v>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3629</v>
+        <v>3804</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3457</v>
+        <v>3473</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2505,20 +2505,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3784</v>
+        <v>3276</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21898</v>
+        <v>21896</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2569,20 +2569,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>31665</v>
+        <v>31663</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2638,11 +2638,11 @@
         <v>1638</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2742,17 +2742,17 @@
         <v>3276</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>327645</v>
+        <v>327619</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2771,18 +2771,18 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2370</v>
+        <v>2126</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2803,20 +2803,20 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>1640</v>
+        <v>2893</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>149975</v>
+        <v>149963</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3276</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2835,18 +2835,18 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>3276</v>
+        <v>4875</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>3276</v>
+        <v>4076</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2867,20 +2867,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4875</v>
+        <v>7674</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18022</v>
+        <v>18021</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6614</v>
+        <v>6618</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2931,20 +2931,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15673</v>
+        <v>15672</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O41" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
         <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -2994,17 +2994,17 @@
         <v>3997</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6345</v>
+        <v>6344</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>4235</v>
+        <v>4234</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6468</v>
+        <v>6467</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3051,20 +3051,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>9207</v>
+        <v>9206</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3083,18 +3083,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9780</v>
+        <v>9704</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10057</v>
+        <v>10047</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3111,20 +3111,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9706</v>
+        <v>9219</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>10244</v>
+        <v>10243</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10655</v>
+        <v>10662</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
         <v>1638</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9032</v>
+        <v>9031</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3276</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3232,17 +3232,17 @@
         <v>3276</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1063</v>
+        <v>754</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2713</v>
@@ -3366,11 +3366,11 @@
         <v>1638</v>
       </c>
       <c r="O48" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
         <v>3276</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3276</v>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3914</v>
+        <v>3913</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3547,14 +3547,14 @@
         <v>4520</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>4304</v>
+        <v>4303</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3591,10 +3591,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3276</v>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3709,20 +3709,20 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1868</v>
+        <v>1455</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11699</v>
+        <v>11698</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1638</v>
       </c>
       <c r="O54" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3580</v>
+        <v>3579</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>31688</v>
+        <v>31686</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3276</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>8778</v>
+        <v>8777</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3837,20 +3837,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>9706</v>
+        <v>8734</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>11812</v>
+        <v>11811</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>9654</v>
+        <v>9653</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3869,18 +3869,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>11453</v>
+        <v>10967</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>14530</v>
+        <v>14406</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3901,20 +3901,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>11648</v>
+        <v>11257</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>31729</v>
+        <v>31727</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O57" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3706</v>
+        <v>3558</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4590</v>
+        <v>4656</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3965,20 +3965,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3411</v>
+        <v>4012</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10694</v>
+        <v>10693</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3942</v>
+        <v>3894</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3594</v>
+        <v>3638</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4413</v>
+        <v>4411</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11713</v>
+        <v>11712</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>3378</v>
@@ -4042,7 +4042,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4193,12 +4193,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4216,13 +4216,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr"/>
-      <c r="E63" s="2" t="inlineStr"/>
-      <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
+      <c r="D63" s="3" t="n">
+        <v>7371</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>7371</v>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -4239,20 +4249,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>7372</v>
+        <v>18492</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4295,12 +4305,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4341,20 +4351,20 @@
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4395,20 +4405,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>52423</v>
+        <v>52419</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4449,20 +4459,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4505,12 +4515,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22935</v>
+        <v>22933</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4574,7 @@
         <v>328</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3837</v>
+        <v>3836</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1638</v>
@@ -4574,7 +4584,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4628,7 @@
         <v>655</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5218</v>
+        <v>5217</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3276</v>
@@ -4628,7 +4638,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4672,17 +4682,17 @@
         <v>1391</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5210</v>
+        <v>5209</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4726,17 +4736,17 @@
         <v>2621</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1536725</v>
+        <v>1536604</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11795</v>
+        <v>11794</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4777,10 +4787,10 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4923</v>
+        <v>4922</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7744</v>
+        <v>7743</v>
       </c>
       <c r="N73" s="3" t="n">
         <v>9829</v>
@@ -4790,7 +4800,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4844,17 @@
         <v>9010</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21705</v>
+        <v>21703</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>18020</v>
+        <v>18019</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4885,20 +4895,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>18020</v>
+        <v>18019</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>28017</v>
+        <v>28015</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4917,18 +4927,18 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>193</v>
+        <v>256</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4949,7 +4959,7 @@
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>193</v>
+        <v>300</v>
       </c>
       <c r="M76" s="3" t="n">
         <v>6602</v>
@@ -4958,11 +4968,11 @@
         <v>328</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5016,7 +5026,7 @@
         <v>1229</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5372</v>
+        <v>5371</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>655</v>
@@ -5026,7 +5036,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5089,12 @@
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="3" t="n">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5125,10 +5135,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5898</v>
+        <v>5897</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2621</v>
@@ -5138,7 +5148,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5196,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5227,20 +5237,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23961</v>
+        <v>23959</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23961</v>
+        <v>23959</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5293,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20969</v>
+        <v>20968</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5335,20 +5345,20 @@
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1638063</v>
+        <v>1637933</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>819</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5408,7 @@
         <v>983</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35812</v>
+        <v>35809</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1638</v>
@@ -5408,7 +5418,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5458,7 +5468,7 @@
         <v>2333</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3267</v>
+        <v>3266</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3276</v>
@@ -5468,7 +5478,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5508,17 +5518,17 @@
         <v>5088</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5557,12 +5567,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5605,14 +5615,14 @@
         <v>4893</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5651,12 +5661,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>18020</v>
+        <v>18019</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5706,7 +5716,7 @@
         <v>513</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>89034</v>
+        <v>89027</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>819</v>
@@ -5716,7 +5726,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5786,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5813,10 +5823,10 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3276</v>
@@ -5826,7 +5836,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5875,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5919,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5963,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -5997,12 +6007,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>18020</v>
+        <v>18019</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6066,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6120,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6151,20 +6161,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4887</v>
+        <v>4886</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5362</v>
+        <v>5361</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6215,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6261,12 +6271,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6307,20 +6317,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18612</v>
+        <v>18610</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18612</v>
+        <v>18610</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6363,12 +6373,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>52423</v>
+        <v>52419</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6432,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6480,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6513,12 +6523,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>10157</v>
+        <v>10156</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6559,20 +6569,20 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6615,12 +6625,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6673,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6721,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>52423</v>
+        <v>52419</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6757,20 +6767,20 @@
         </is>
       </c>
       <c r="L111" s="3" t="n">
-        <v>76325</v>
+        <v>76319</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>76325</v>
+        <v>76319</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>81911</v>
+        <v>81905</v>
       </c>
       <c r="O111" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6799,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>90102</v>
+        <v>90095</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6800,7 +6810,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>90102</v>
+        <v>90095</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6821,20 +6831,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>90102</v>
+        <v>90095</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>100577</v>
+        <v>100569</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>114676</v>
+        <v>114667</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6875,20 +6885,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>114676</v>
+        <v>114667</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>114676</v>
+        <v>114667</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>147440</v>
+        <v>147429</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6907,7 +6917,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6918,7 +6928,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6939,20 +6949,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6981,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -6982,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7003,20 +7013,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>196587</v>
+        <v>196572</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7057,20 +7067,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>221161</v>
+        <v>221143</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>294881</v>
+        <v>262095</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>262116</v>
+        <v>262095</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7114,17 +7124,17 @@
         <v>1746</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2348</v>
+        <v>2347</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7171,14 +7181,14 @@
         <v>6058</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7221,12 +7231,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7267,20 +7277,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7323,12 +7333,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23590</v>
+        <v>23589</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7369,20 +7379,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19698</v>
+        <v>19696</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7433,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>32764530</v>
+        <v>32761937</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7477,20 +7487,20 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>2261</v>
+        <v>1843</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>2261</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O124" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7534,17 +7544,17 @@
         <v>2316</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5883</v>
+        <v>5882</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7585,20 +7595,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6691</v>
+        <v>6690</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6691</v>
+        <v>6690</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7639,20 +7649,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>12308</v>
+        <v>12307</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7695,12 +7705,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23590</v>
+        <v>23589</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7743,12 +7753,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7806,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7843,14 +7853,14 @@
         <v>3276</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7891,20 +7901,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -7948,17 +7958,17 @@
         <v>9829</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16472</v>
+        <v>16471</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8001,12 +8011,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8047,20 +8057,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>22116</v>
+        <v>22114</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>22116</v>
+        <v>22114</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>49147</v>
+        <v>49143</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8089,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8090,7 +8100,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8111,20 +8121,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>73720</v>
+        <v>73714</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8165,20 +8175,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8197,7 +8207,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8208,7 +8218,7 @@
         <v>19</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8229,20 +8239,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>13199</v>
+        <v>13198</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8306,7 @@
         <v>1098</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="N139" s="3" t="n">
         <v>1204</v>
@@ -8306,7 +8316,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8333,10 +8343,10 @@
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8360,7 +8370,7 @@
         <v>590</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5349</v>
+        <v>5348</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>637</v>
@@ -8370,7 +8380,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8444,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8488,7 +8498,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8542,7 @@
         <v>2146</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3276</v>
@@ -8542,7 +8552,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8596,17 +8606,17 @@
         <v>2156</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>11120</v>
+        <v>11119</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>52</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8649,12 +8659,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8718,17 @@
         <v>4587</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>55402</v>
+        <v>55397</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8761,12 +8771,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8810,17 +8820,17 @@
         <v>9829</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17952</v>
+        <v>17950</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8873,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8887,18 +8897,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>16543</v>
+        <v>16538</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8919,20 +8929,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8961,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8962,7 +8972,7 @@
         <v>13</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -8983,20 +8993,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>87055</v>
+        <v>87048</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>78635</v>
+        <v>78629</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9037,20 +9047,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>106485</v>
+        <v>106476</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>106485</v>
+        <v>106476</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>212969</v>
+        <v>212953</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9114,7 @@
         <v>164</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10717</v>
+        <v>10716</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>328</v>
@@ -9114,7 +9124,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9188,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9225,20 +9235,20 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>845</v>
+        <v>819</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>16051</v>
+        <v>16050</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1638</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9308,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9348,17 +9358,17 @@
         <v>3276</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9412,7 @@
         <v>819</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>20027</v>
+        <v>20026</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1638</v>
@@ -9412,7 +9422,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9466,7 @@
         <v>1638</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19867</v>
+        <v>19865</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3276</v>
@@ -9466,7 +9476,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9520,17 +9530,17 @@
         <v>3276</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6853</v>
+        <v>6852</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9594,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9638,17 +9648,17 @@
         <v>1802</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>31257</v>
+        <v>31255</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="O162" s="2" t="n">
         <v>32</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9667,7 +9677,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9699,10 +9709,10 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3932</v>
+        <v>3931</v>
       </c>
       <c r="N163" s="3" t="n">
         <v>3886</v>
@@ -9712,7 +9722,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9731,18 +9741,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3747</v>
+        <v>3895</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3747</v>
+        <v>3762</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9763,20 +9773,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3879</v>
+        <v>4094</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9830,17 +9840,17 @@
         <v>193</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>5087</v>
+        <v>5086</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>328</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9904,7 +9914,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9968,7 @@
         <v>1458</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>10069</v>
+        <v>10068</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1615</v>
@@ -9968,7 +9978,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10032,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10073,20 +10083,20 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>342</v>
+        <v>485</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>328</v>
       </c>
       <c r="O169" s="2" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10127,20 +10137,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>98294</v>
+        <v>98286</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>98294</v>
+        <v>98286</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10183,12 +10193,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10225,20 +10235,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10281,14 +10291,14 @@
         <v>4033</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10327,12 +10337,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10369,20 +10379,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14713</v>
+        <v>14712</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O175" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10419,20 +10429,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11795</v>
+        <v>11794</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11795</v>
+        <v>11794</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23590</v>
+        <v>23589</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10469,20 +10479,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16464</v>
+        <v>16463</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10519,20 +10529,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19823</v>
+        <v>19821</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10590,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10621,20 +10631,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10677,12 +10687,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10729,14 +10739,14 @@
         <v>9829</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10779,12 +10789,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10825,20 +10835,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>22116</v>
+        <v>22114</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>22116</v>
+        <v>22114</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>44232</v>
+        <v>44229</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10879,20 +10889,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>29488</v>
+        <v>29486</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>58976</v>
+        <v>58971</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10946,7 @@
         <v>164</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>328</v>
@@ -10946,7 +10956,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -10990,7 +11000,7 @@
         <v>164</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>328</v>
@@ -11000,7 +11010,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11044,7 +11054,7 @@
         <v>164</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>106586</v>
+        <v>106578</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>328</v>
@@ -11054,7 +11064,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11112,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11146,7 +11156,7 @@
         <v>164</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>30215</v>
+        <v>30213</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>328</v>
@@ -11156,7 +11166,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11210,7 +11220,7 @@
         <v>164</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>161747</v>
+        <v>161734</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>945</v>
@@ -11220,7 +11230,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11264,7 +11274,7 @@
         <v>164</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>328</v>
@@ -11274,7 +11284,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11332,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11366,7 +11376,7 @@
         <v>164</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>328</v>
@@ -11376,7 +11386,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11430,17 +11440,17 @@
         <v>164</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>163659</v>
+        <v>163646</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>328</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11494,7 @@
         <v>164</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>328</v>
@@ -11494,7 +11504,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11552,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11561,18 +11571,18 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>536</v>
+        <v>932</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F198" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>536</v>
+        <v>734</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11596,17 +11606,17 @@
         <v>932</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>328</v>
+        <v>1024</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11625,7 +11635,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -11636,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -11657,20 +11667,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>21333</v>
+        <v>21331</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11688,13 +11698,23 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr"/>
-      <c r="E200" s="2" t="inlineStr"/>
-      <c r="F200" s="2" t="inlineStr"/>
-      <c r="G200" s="3" t="inlineStr"/>
+      <c r="D200" s="3" t="n">
+        <v>4587</v>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>4587</v>
+      </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I200" s="2" t="n">
@@ -11714,17 +11734,17 @@
         <v>4587</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6532</v>
+        <v>6531</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11768,7 +11788,7 @@
         <v>5242</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>11161</v>
+        <v>11160</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7863</v>
@@ -11778,7 +11798,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11819,20 +11839,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10721</v>
+        <v>10720</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11873,20 +11893,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>285985</v>
+        <v>285963</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11927,20 +11947,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>16187</v>
+        <v>16186</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16615</v>
+        <v>16614</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -11959,7 +11979,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>21983</v>
+        <v>21982</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -11970,7 +11990,7 @@
         <v>1</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>21983</v>
+        <v>21982</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -11991,20 +12011,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>22427</v>
+        <v>22426</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>50538</v>
+        <v>50534</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12047,12 +12067,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23590</v>
+        <v>23589</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12113,7 @@
         </is>
       </c>
       <c r="L207" s="3" t="n">
-        <v>586</v>
+        <v>532</v>
       </c>
       <c r="M207" s="3" t="n">
         <v>1638</v>
@@ -12102,11 +12122,11 @@
         <v>328</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12157,7 +12177,7 @@
         </is>
       </c>
       <c r="L208" s="3" t="n">
-        <v>631</v>
+        <v>531</v>
       </c>
       <c r="M208" s="3" t="n">
         <v>1638</v>
@@ -12170,7 +12190,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12217,14 +12237,14 @@
         <v>3109</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O209" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12298,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12319,20 +12339,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12373,20 +12393,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12429,12 +12449,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23590</v>
+        <v>23589</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12475,20 +12495,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12535,14 +12555,14 @@
         <v>2829</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O215" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12606,7 @@
         <v>2130</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>12301</v>
+        <v>12300</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4259</v>
@@ -12596,7 +12616,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12637,20 +12657,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>16130</v>
+        <v>16129</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>22146</v>
+        <v>22144</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12691,20 +12711,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="M218" s="3" t="n">
         <v>7963</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12745,20 +12765,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7372</v>
+        <v>7371</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14744</v>
+        <v>14743</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12801,12 +12821,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12847,20 +12867,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12911,7 +12931,7 @@
         </is>
       </c>
       <c r="L222" s="3" t="n">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="M222" s="3" t="n">
         <v>2942</v>
@@ -12924,7 +12944,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -12988,7 +13008,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13032,17 +13052,17 @@
         <v>3276</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7456</v>
+        <v>7455</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13096,7 +13116,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13156,11 +13176,11 @@
         <v>3276</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13217,14 +13237,14 @@
         <v>3917</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13298,7 @@
         <v>164</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>328</v>
@@ -13288,7 +13308,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13332,7 +13352,7 @@
         <v>164</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>328</v>
@@ -13342,7 +13362,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13396,17 +13416,17 @@
         <v>164</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N230" s="3" t="n">
-        <v>695</v>
+        <v>328</v>
       </c>
       <c r="O230" s="2" t="n">
         <v>1129</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13470,7 @@
         <v>819</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1638</v>
@@ -13460,7 +13480,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13524,7 +13544,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13578,17 +13598,17 @@
         <v>3276</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7464</v>
+        <v>7463</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13649,7 @@
         </is>
       </c>
       <c r="L234" s="3" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="M234" s="3" t="n">
         <v>424</v>
@@ -13638,11 +13658,11 @@
         <v>328</v>
       </c>
       <c r="O234" s="2" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13661,7 +13681,7 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
@@ -13672,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="G235" s="3" t="n">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
@@ -13693,7 +13713,7 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>4078</v>
+        <v>4077</v>
       </c>
       <c r="M235" s="3" t="n">
         <v>4415</v>
@@ -13706,7 +13726,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13725,7 +13745,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -13736,7 +13756,7 @@
         <v>1</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -13757,20 +13777,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>5192</v>
+        <v>5191</v>
       </c>
       <c r="M236" s="3" t="n">
         <v>6756</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13813,12 +13833,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13836,13 +13856,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D238" s="3" t="inlineStr"/>
-      <c r="E238" s="2" t="inlineStr"/>
-      <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="3" t="inlineStr"/>
+      <c r="D238" s="3" t="n">
+        <v>4587</v>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" s="3" t="n">
+        <v>4587</v>
+      </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I238" s="2" t="n">
@@ -13862,17 +13892,17 @@
         <v>9010</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11420</v>
+        <v>11419</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13915,12 +13945,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13961,20 +13991,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10852</v>
+        <v>10851</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10852</v>
+        <v>10851</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -13993,7 +14023,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>19582</v>
+        <v>19580</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14001,10 +14031,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19709</v>
+        <v>19440</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14025,20 +14055,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>21839</v>
+        <v>21837</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>36028</v>
+        <v>36025</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14057,7 +14087,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14068,7 +14098,7 @@
         <v>1</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14089,20 +14119,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>39358</v>
+        <v>39355</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>60700</v>
+        <v>60695</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>78635</v>
+        <v>78629</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14121,18 +14151,18 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>17550</v>
+        <v>16381</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F243" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18977</v>
+        <v>18648</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14149,20 +14179,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>16500</v>
+        <v>19000</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>32764530</v>
+        <v>32761937</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14205,12 +14235,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14264,7 +14294,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14318,7 +14348,7 @@
         <v>2369</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="N246" s="3" t="n">
         <v>2475</v>
@@ -14328,7 +14358,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14369,20 +14399,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>16087</v>
+        <v>16086</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>24154</v>
+        <v>24152</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>18348</v>
+        <v>18347</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14423,20 +14453,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>18348</v>
+        <v>18347</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14506,7 @@
         <v>819</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9618</v>
+        <v>9617</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1638</v>
@@ -14486,7 +14516,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14566,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14585,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>32411</v>
+        <v>32408</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -14566,7 +14596,7 @@
         <v>1</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>32411</v>
+        <v>32408</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -14590,17 +14620,17 @@
         <v>164</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>100736</v>
+        <v>100728</v>
       </c>
       <c r="N251" s="3" t="n">
-        <v>35651</v>
+        <v>35648</v>
       </c>
       <c r="O251" s="2" t="n">
         <v>137</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14641,20 +14671,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>52200</v>
+        <v>4587</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>52200</v>
+        <v>52196</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O252" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14695,10 +14725,10 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>6899</v>
+        <v>6898</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>7811</v>
+        <v>7810</v>
       </c>
       <c r="N253" s="3" t="n">
         <v>7863</v>
@@ -14708,7 +14738,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14757,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>6922</v>
+        <v>6921</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -14738,7 +14768,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>6922</v>
+        <v>6921</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -14759,20 +14789,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>8144</v>
+        <v>8143</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>196587</v>
+        <v>196572</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14836,7 +14866,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14894,7 +14924,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14968,7 @@
         <v>301</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>8191</v>
+        <v>8190</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>328</v>
@@ -14948,7 +14978,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -14971,14 +15001,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>389</v>
+        <v>437</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15008,11 +15038,11 @@
         <v>655</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15066,7 +15096,7 @@
         <v>1358</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>22154</v>
+        <v>22152</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1638</v>
@@ -15076,7 +15106,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15095,18 +15125,18 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>2670</v>
+        <v>2686</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>2277</v>
+        <v>2359</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -15127,7 +15157,7 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2687</v>
+        <v>2686</v>
       </c>
       <c r="M260" s="3" t="n">
         <v>3804</v>
@@ -15136,11 +15166,11 @@
         <v>3276</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15163,14 +15193,14 @@
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F261" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3666</v>
+        <v>3536</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15197,14 +15227,14 @@
         <v>7267</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O261" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15223,7 +15253,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15255,20 +15285,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O262" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15312,7 +15342,7 @@
         <v>819</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10940</v>
+        <v>10939</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1638</v>
@@ -15322,7 +15352,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15416,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15439,12 +15469,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15463,7 +15493,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15474,7 +15504,7 @@
         <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15501,14 +15531,14 @@
         <v>9983</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15527,18 +15557,18 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>1758</v>
+        <v>1455</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2229</v>
+        <v>2100</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15562,17 +15592,17 @@
         <v>2723</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>20149</v>
+        <v>20147</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>1933</v>
+        <v>1766</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15621,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15602,7 +15632,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15623,20 +15653,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8519</v>
+        <v>8518</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14757</v>
+        <v>14756</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="O268" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15679,12 +15709,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15725,20 +15755,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>25796</v>
+        <v>25793</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25796</v>
+        <v>25793</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15787,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>20969</v>
+        <v>20968</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15768,7 +15798,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>25456</v>
+        <v>25454</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15789,20 +15819,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24736</v>
+        <v>24734</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>53850</v>
+        <v>53846</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15846,7 +15876,7 @@
         <v>164</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>10054</v>
+        <v>10053</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>328</v>
@@ -15856,7 +15886,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15900,7 +15930,7 @@
         <v>164</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21697</v>
+        <v>21695</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>328</v>
@@ -15910,7 +15940,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -15964,7 +15994,7 @@
         <v>164</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>32873</v>
+        <v>32870</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>328</v>
@@ -15974,7 +16004,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16058,7 @@
         <v>164</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16464</v>
+        <v>16463</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>328</v>
@@ -16038,7 +16068,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16087,7 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>13868</v>
+        <v>13866</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -16068,7 +16098,7 @@
         <v>2</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16092,7 +16122,7 @@
         <v>164</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>163330</v>
+        <v>163317</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>328</v>
@@ -16102,7 +16132,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16148,11 +16178,11 @@
         <v>1638</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16209,14 +16239,14 @@
         <v>8838</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O278" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16270,7 +16300,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16311,20 +16341,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="M280" s="3" t="n">
         <v>8915</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10485</v>
+        <v>10484</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16367,12 +16397,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14416</v>
+        <v>14415</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16415,12 +16445,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16463,12 +16493,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16487,7 +16517,7 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>20969</v>
+        <v>20968</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -16498,7 +16528,7 @@
         <v>1</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>20969</v>
+        <v>20968</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -16519,20 +16549,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16551,18 +16581,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9754</v>
+        <v>10217</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>10265</v>
+        <v>10220</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16583,20 +16613,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10265</v>
+        <v>10218</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>11590</v>
+        <v>11085</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16690,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16720,7 @@
         <v>14</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5192</v>
+        <v>5191</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16707,20 +16737,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5814</v>
+        <v>5434</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5980</v>
+        <v>5979</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5814</v>
+        <v>5958</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16750,7 +16780,7 @@
         <v>28</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7053</v>
+        <v>7052</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16766,15 +16796,21 @@
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
-      <c r="L288" s="3" t="inlineStr"/>
-      <c r="M288" s="3" t="inlineStr"/>
+      <c r="L288" s="3" t="n">
+        <v>7661</v>
+      </c>
+      <c r="M288" s="3" t="n">
+        <v>7666</v>
+      </c>
       <c r="N288" s="3" t="n">
-        <v>7536</v>
-      </c>
-      <c r="O288" s="2" t="inlineStr"/>
+        <v>7514</v>
+      </c>
+      <c r="O288" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16829,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>10855</v>
+        <v>10854</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16804,7 +16840,7 @@
         <v>20</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9517</v>
+        <v>9516</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16821,20 +16857,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>11161</v>
+        <v>10191</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11648</v>
+        <v>11064</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11235</v>
+        <v>11234</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16864,7 +16900,7 @@
         <v>2</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>3195</v>
+        <v>3194</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -16898,7 +16934,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16917,18 +16953,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2642</v>
+        <v>2924</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2712</v>
+        <v>2765</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16949,7 +16985,7 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>2924</v>
+        <v>4259</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5242</v>
@@ -16958,11 +16994,11 @@
         <v>3276</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -16992,7 +17028,7 @@
         <v>7</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3949</v>
+        <v>3948</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17016,17 +17052,17 @@
         <v>4349</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5734</v>
+        <v>5733</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17053,10 +17089,10 @@
         </is>
       </c>
       <c r="F293" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G293" s="3" t="n">
-        <v>307</v>
+        <v>352</v>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
@@ -17090,7 +17126,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17109,18 +17145,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>8121</v>
+        <v>5245</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
         <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6829</v>
+        <v>6811</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17141,20 +17177,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>5246</v>
+        <v>5340</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>19556</v>
+        <v>19554</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>7526</v>
+        <v>7275</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17195,20 +17231,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>53247</v>
+        <v>53243</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>723672</v>
+        <v>723615</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17227,7 +17263,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17238,7 +17274,7 @@
         <v>10</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17259,20 +17295,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>71228</v>
+        <v>71223</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>40956</v>
+        <v>40952</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17291,18 +17327,18 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>65529</v>
+        <v>65524</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>65529</v>
+        <v>65524</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17323,20 +17359,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>65529</v>
+        <v>65524</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>81911</v>
+        <v>81905</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17391,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17363,10 +17399,10 @@
         </is>
       </c>
       <c r="F298" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17387,20 +17423,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>131058</v>
+        <v>131048</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>131061</v>
+        <v>131051</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>163823</v>
+        <v>163810</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17419,7 +17455,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>262116</v>
+        <v>262095</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17430,7 +17466,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>262116</v>
+        <v>262095</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17451,20 +17487,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>262116</v>
+        <v>262095</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>264641</v>
+        <v>264620</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>327645</v>
+        <v>327619</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17483,18 +17519,18 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>458703</v>
+        <v>458667</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F300" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>458703</v>
+        <v>458667</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17515,20 +17551,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>458703</v>
+        <v>458667</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>983770</v>
+        <v>906133</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>655291</v>
+        <v>655239</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17547,7 +17583,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>17141</v>
+        <v>17139</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17558,7 +17594,7 @@
         <v>6</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>18073</v>
+        <v>18071</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17579,20 +17615,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>19218</v>
+        <v>21353</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>34567</v>
+        <v>34564</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17615,14 +17651,14 @@
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1622</v>
+        <v>1563</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17643,20 +17679,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1147</v>
+        <v>1948</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4969</v>
+        <v>4968</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17675,18 +17711,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>3570</v>
+        <v>4236</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
         <v>12</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4328</v>
+        <v>4289</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17707,20 +17743,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4236</v>
+        <v>4076</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>16381</v>
+        <v>16379</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4161</v>
+        <v>4261</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17771,20 +17807,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2294</v>
+        <v>2793</v>
       </c>
       <c r="O304" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17848,7 +17884,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17902,17 +17938,17 @@
         <v>164</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N306" s="3" t="n">
-        <v>4038</v>
+        <v>328</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17437</v>
+        <v>17750</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -17939,10 +17975,10 @@
         </is>
       </c>
       <c r="F307" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G307" s="3" t="n">
-        <v>1488</v>
+        <v>1419</v>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
@@ -17966,7 +18002,7 @@
         <v>1412</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>328</v>
@@ -17976,7 +18012,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18030,17 +18066,17 @@
         <v>2130</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1310581</v>
+        <v>1310477</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>227</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18084,17 +18120,17 @@
         <v>4587</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>33125</v>
+        <v>33122</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>124</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18148,17 +18184,17 @@
         <v>1638</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6242</v>
+        <v>6241</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3276</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18215,14 +18251,14 @@
         <v>6251</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18265,12 +18301,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18324,17 +18360,17 @@
         <v>9829</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>27086</v>
+        <v>27084</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18375,20 +18411,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>16027</v>
+        <v>16026</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>16027</v>
+        <v>16026</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18407,7 +18443,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18415,10 +18451,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18439,20 +18475,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18507,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18479,10 +18515,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18503,20 +18539,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>39317</v>
+        <v>39314</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>78635</v>
+        <v>78629</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18534,13 +18570,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D317" s="3" t="inlineStr"/>
-      <c r="E317" s="2" t="inlineStr"/>
-      <c r="F317" s="2" t="inlineStr"/>
-      <c r="G317" s="3" t="inlineStr"/>
+      <c r="D317" s="3" t="n">
+        <v>106476</v>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G317" s="3" t="n">
+        <v>106476</v>
+      </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I317" s="2" t="n">
@@ -18557,20 +18603,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>106485</v>
+        <v>106476</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>106485</v>
+        <v>106476</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>212969</v>
+        <v>212953</v>
       </c>
       <c r="O317" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18680,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18652,13 +18698,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D319" s="3" t="inlineStr"/>
-      <c r="E319" s="2" t="inlineStr"/>
-      <c r="F319" s="2" t="inlineStr"/>
-      <c r="G319" s="3" t="inlineStr"/>
+      <c r="D319" s="3" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G319" s="3" t="n">
+        <v>1504</v>
+      </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I319" s="2" t="n">
@@ -18675,20 +18731,20 @@
         </is>
       </c>
       <c r="L319" s="3" t="n">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>16271</v>
+        <v>16270</v>
       </c>
       <c r="N319" s="3" t="n">
-        <v>328</v>
+        <v>1653</v>
       </c>
       <c r="O319" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18711,14 +18767,14 @@
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1474</v>
+        <v>1451</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18742,17 +18798,17 @@
         <v>1147</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>10178</v>
+        <v>10177</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O320" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18862,7 @@
         <v>3768</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>6093</v>
+        <v>6092</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>328</v>
@@ -18816,7 +18872,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18843,10 +18899,10 @@
         </is>
       </c>
       <c r="F322" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>426</v>
+        <v>514</v>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
@@ -18880,7 +18936,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18907,10 +18963,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>3120</v>
+        <v>3067</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18934,7 +18990,7 @@
         <v>2544</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>17092</v>
+        <v>17090</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>2583</v>
@@ -18944,7 +19000,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -18988,7 +19044,7 @@
         <v>328</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5793</v>
+        <v>5792</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>328</v>
@@ -18998,7 +19054,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19017,18 +19073,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2088</v>
+        <v>2041</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19049,20 +19105,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>1938</v>
+        <v>1951</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>16271</v>
+        <v>16270</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2156</v>
+        <v>2133</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19119,14 +19175,14 @@
         <v>2485</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O326" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19145,18 +19201,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>3396</v>
+        <v>2112</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>4883</v>
+        <v>4605</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19177,20 +19233,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2112</v>
+        <v>3394</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15902</v>
+        <v>15901</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>5681</v>
+        <v>3109</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19265,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>25720</v>
+        <v>25718</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19220,7 +19276,7 @@
         <v>27</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22436</v>
+        <v>22434</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19241,20 +19297,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>22809</v>
+        <v>21837</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>33765</v>
+        <v>1638097</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>26020</v>
+        <v>26080</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19273,18 +19329,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7284</v>
+        <v>7765</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
         <v>42</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7347</v>
+        <v>7348</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19305,20 +19361,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7765</v>
+        <v>7745</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9425</v>
+        <v>9424</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7257</v>
+        <v>7755</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19337,7 +19393,7 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5824</v>
+        <v>5871</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -19345,10 +19401,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>6074</v>
+        <v>6053</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19369,20 +19425,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5921</v>
+        <v>6066</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8964</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6310</v>
+        <v>6122</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19409,10 +19465,10 @@
         </is>
       </c>
       <c r="F331" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>1531</v>
+        <v>1474</v>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
@@ -19433,7 +19489,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3276</v>
@@ -19446,7 +19502,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19465,18 +19521,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>1076</v>
+        <v>1024</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1196</v>
+        <v>1180</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19497,20 +19553,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1270</v>
+        <v>1145</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19529,18 +19585,18 @@
         </is>
       </c>
       <c r="D333" s="3" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19561,7 +19617,7 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="M333" s="3" t="n">
         <v>5003</v>
@@ -19570,11 +19626,11 @@
         <v>328</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19597,14 +19653,14 @@
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>2057</v>
+        <v>1909</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19628,17 +19684,17 @@
         <v>437</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="O334" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19657,18 +19713,18 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>2294</v>
+        <v>1147</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1406</v>
+        <v>1348</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19689,20 +19745,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1147</v>
+        <v>1551</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>2957</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19725,14 +19781,14 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19766,7 +19822,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19876,7 @@
         <v>164</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>16040</v>
+        <v>16039</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>328</v>
@@ -19830,7 +19886,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19894,7 +19950,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -19913,18 +19969,18 @@
         </is>
       </c>
       <c r="D339" s="3" t="n">
-        <v>472</v>
+        <v>193</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F339" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G339" s="3" t="n">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
@@ -19948,7 +20004,7 @@
         <v>457</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4879</v>
+        <v>4878</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>328</v>
@@ -19958,7 +20014,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20022,7 +20078,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20049,10 +20105,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20079,14 +20135,14 @@
         <v>2475</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>916</v>
+        <v>975</v>
       </c>
       <c r="O341" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20137,20 +20193,20 @@
         </is>
       </c>
       <c r="L342" s="3" t="n">
-        <v>323</v>
+        <v>654</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>16382</v>
+        <v>16381</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>354</v>
       </c>
       <c r="O342" s="2" t="n">
-        <v>591</v>
+        <v>530</v>
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20270,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20265,20 +20321,20 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>1958</v>
+        <v>1638</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>17622</v>
+        <v>17621</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3276</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20332,17 +20388,17 @@
         <v>2130</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1638227</v>
+        <v>1638097</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>4096</v>
+        <v>4095</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20385,12 +20441,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4915</v>
+        <v>4914</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20444,17 +20500,17 @@
         <v>4587</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>8221</v>
+        <v>8441</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6553</v>
+        <v>6552</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20501,14 +20557,14 @@
         <v>9829</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>13106</v>
+        <v>13105</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20531,11 +20587,11 @@
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G349" s="3" t="n">
         <v>9829</v>
@@ -20562,17 +20618,17 @@
         <v>9829</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19659</v>
+        <v>19657</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20613,20 +20669,20 @@
         </is>
       </c>
       <c r="L350" s="3" t="n">
-        <v>16500</v>
+        <v>16014</v>
       </c>
       <c r="M350" s="3" t="n">
-        <v>19413</v>
+        <v>16014</v>
       </c>
       <c r="N350" s="3" t="n">
-        <v>26212</v>
+        <v>26210</v>
       </c>
       <c r="O350" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20645,18 +20701,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>18004</v>
+        <v>16381</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>17009</v>
+        <v>16961</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20677,20 +20733,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16987</v>
+        <v>16381</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>39181</v>
+        <v>39178</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>32765</v>
+        <v>32762</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20765,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>42235</v>
+        <v>42232</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20720,7 +20776,7 @@
         <v>6</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>46925</v>
+        <v>46922</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20741,20 +20797,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>48532</v>
+        <v>47364</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>48727</v>
+        <v>48724</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>78635</v>
+        <v>78629</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20773,7 +20829,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>195907</v>
+        <v>195892</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20784,7 +20840,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>195907</v>
+        <v>195892</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20805,20 +20861,20 @@
         </is>
       </c>
       <c r="L353" s="3" t="n">
-        <v>155309</v>
+        <v>155296</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>155309</v>
+        <v>155296</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>212969</v>
+        <v>212953</v>
       </c>
       <c r="O353" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20869,10 +20925,10 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9708</v>
+        <v>9707</v>
       </c>
       <c r="N354" s="3" t="n">
         <v>537</v>
@@ -20882,7 +20938,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20901,7 +20957,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20912,7 +20968,7 @@
         <v>1</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20933,20 +20989,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19618</v>
+        <v>19616</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>18348</v>
+        <v>18347</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -20965,7 +21021,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -20976,7 +21032,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -20997,20 +21053,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>9174</v>
+        <v>9173</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>22558</v>
+        <v>22557</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>18348</v>
+        <v>18347</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -21040,7 +21096,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>163.822652</v>
+        <v>163.809686</v>
       </c>
     </row>
     <row r="2">
@@ -21051,7 +21107,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 25 Jul 2026 00:02:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 26 Jul 2026 00:02:32 +0000)</t>
         </is>
       </c>
     </row>
@@ -21063,7 +21119,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3927</v>
+        <v>3928</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3768</v>
+        <v>3831</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3879</v>
+        <v>3880</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>181</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -660,20 +660,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>100059</v>
+        <v>100085</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -724,20 +724,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>24552</v>
+        <v>24558</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -767,7 +767,7 @@
         <v>2</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24552</v>
+        <v>24558</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -788,20 +788,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>24552</v>
+        <v>24558</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>24552</v>
+        <v>24558</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>49104</v>
+        <v>49117</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         <v>3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -852,20 +852,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>74939</v>
+        <v>74959</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>88387</v>
+        <v>88410</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -916,20 +916,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>147311</v>
+        <v>147350</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>147311</v>
+        <v>147350</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -970,20 +970,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>368278</v>
+        <v>368376</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>368278</v>
+        <v>368376</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>736557</v>
+        <v>736751</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1002,18 +1002,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6189</v>
+        <v>5799</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>36</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>6306</v>
+        <v>6289</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1034,20 +1034,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5798</v>
+        <v>6115</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>9002</v>
+        <v>9005</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1066,18 +1066,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8613</v>
+        <v>8731</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>9028</v>
+        <v>9056</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1098,20 +1098,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8736</v>
+        <v>8630</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>155453</v>
+        <v>155494</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>18005</v>
+        <v>18009</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14404</v>
+        <v>14408</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14923</v>
+        <v>14948</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1162,20 +1162,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14404</v>
+        <v>14408</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>43946</v>
+        <v>43958</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>36009</v>
+        <v>36019</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1216,20 +1216,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>26454</v>
+        <v>40929</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1270,20 +1270,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>97257</v>
+        <v>97282</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>97257</v>
+        <v>97282</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1324,20 +1324,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1378,20 +1378,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>35481</v>
+        <v>35490</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>66308</v>
+        <v>66326</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5565</v>
+        <v>5567</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14854</v>
+        <v>14691</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>66308</v>
+        <v>66326</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5565</v>
+        <v>5567</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1486,20 +1486,20 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1637</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
         <v>1637</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>235713</v>
+        <v>235775</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1607,17 +1607,17 @@
         <v>3274</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>278255</v>
+        <v>278328</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1658,20 +1658,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5892</v>
+        <v>5894</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11785</v>
+        <v>11788</v>
       </c>
       <c r="O20" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1712,20 +1712,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11458</v>
+        <v>11461</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>38252</v>
+        <v>38262</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1766,20 +1766,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>22097</v>
+        <v>22103</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>144480</v>
+        <v>144518</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1830,20 +1830,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>332819</v>
+        <v>332907</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>81840</v>
+        <v>81861</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
         <v>2</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1895,20 +1895,20 @@
         </is>
       </c>
       <c r="L24" s="3" t="n">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>41</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
         <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>327</v>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2013,20 +2013,20 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2077,20 +2077,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1632446</v>
+        <v>1632876</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1637</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2109,18 +2109,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1999</v>
+        <v>1842</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1672</v>
+        <v>1686</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2141,20 +2141,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1841</v>
+        <v>2428</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2208,17 +2208,17 @@
         <v>3274</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17635</v>
+        <v>17639</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2262,17 +2262,17 @@
         <v>655</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>381</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         <v>4</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2323,20 +2323,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11940</v>
+        <v>11944</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>1172</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>654717</v>
+        <v>654890</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1637</v>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
         <v>10</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2451,20 +2451,20 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2992</v>
+        <v>2940</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>13260</v>
+        <v>13263</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2487,14 +2487,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3462</v>
+        <v>3453</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2518,17 +2518,17 @@
         <v>3274</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21879</v>
+        <v>21885</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6595</v>
+        <v>6596</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2555,10 +2555,10 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6551</v>
+        <v>6553</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2579,20 +2579,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>31638</v>
+        <v>31646</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2639,10 +2639,10 @@
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6500</v>
+        <v>6501</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1637</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         <v>1763</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4301</v>
+        <v>4303</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3274</v>
@@ -2702,7 +2702,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2752,17 +2752,17 @@
         <v>3274</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>327359</v>
+        <v>327445</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2781,7 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
@@ -2813,20 +2813,20 @@
         </is>
       </c>
       <c r="L39" s="3" t="n">
-        <v>2891</v>
+        <v>2290</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>149843</v>
+        <v>149883</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2845,18 +2845,18 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4871</v>
+        <v>7670</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>4072</v>
+        <v>5272</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2877,20 +2877,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>7668</v>
+        <v>7672</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>18006</v>
+        <v>18011</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6547</v>
+        <v>6898</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2909,18 +2909,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>23</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6613</v>
+        <v>6592</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2941,20 +2941,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15659</v>
+        <v>15663</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -2973,18 +2973,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>3846</v>
+        <v>3882</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2883</v>
+        <v>3134</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3001,20 +3001,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>3994</v>
+        <v>3995</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6339</v>
+        <v>6341</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>4231</v>
+        <v>4250</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6462</v>
+        <v>6464</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>4</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>5298</v>
+        <v>5300</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3061,20 +3061,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>9199</v>
+        <v>9201</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3093,18 +3093,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9243</v>
+        <v>9872</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>10010</v>
+        <v>9973</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3121,20 +3121,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>10235</v>
+        <v>10671</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>10235</v>
+        <v>10671</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10505</v>
+        <v>10578</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
         <v>1637</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>9024</v>
+        <v>9026</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3274</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
         <v>3274</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3270,23 +3270,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>494</v>
-      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -3306,17 +3296,17 @@
         <v>802</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>6079</v>
+        <v>6081</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O47" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3367,7 +3357,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2711</v>
@@ -3380,7 +3370,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3389,7 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -3431,10 +3421,10 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2913</v>
+        <v>1455</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3274</v>
@@ -3444,7 +3434,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3453,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3474,7 +3464,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3491,20 +3481,20 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4292</v>
+        <v>4293</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>1616</v>
+        <v>819</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3513,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>3910</v>
+        <v>3911</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3534,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>3428</v>
+        <v>3429</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3551,20 +3541,20 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>3912</v>
+        <v>3913</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4516</v>
+        <v>4517</v>
       </c>
       <c r="N51" s="3" t="n">
-        <v>4300</v>
+        <v>4301</v>
       </c>
       <c r="O51" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3601,10 +3591,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3274</v>
@@ -3614,7 +3604,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3668,17 +3658,17 @@
         <v>686</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4991</v>
+        <v>4992</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3722,7 @@
         <v>1866</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11688</v>
+        <v>11691</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1637</v>
@@ -3742,7 +3732,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3751,7 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -3772,7 +3762,7 @@
         <v>1</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>3576</v>
+        <v>3577</v>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
@@ -3793,10 +3783,10 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>31660</v>
+        <v>31669</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3274</v>
@@ -3806,7 +3796,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3815,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>8770</v>
+        <v>8772</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3836,7 +3826,7 @@
         <v>9</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>11265</v>
+        <v>11268</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3857,20 +3847,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>8243</v>
+        <v>7765</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>11801</v>
+        <v>11804</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>9646</v>
+        <v>9648</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3879,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10957</v>
+        <v>10960</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -3897,10 +3887,10 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>14361</v>
+        <v>14392</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3921,20 +3911,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>12124</v>
+        <v>12111</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>31701</v>
+        <v>31710</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -3953,18 +3943,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4009</v>
+        <v>4851</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>4658</v>
+        <v>4693</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -3985,20 +3975,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>5053</v>
+        <v>5054</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10685</v>
+        <v>10688</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>3837</v>
+        <v>4129</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4017,7 +4007,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4025,10 +4015,10 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3685</v>
+        <v>3724</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4049,20 +4039,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>4408</v>
+        <v>3883</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11703</v>
+        <v>11706</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>3375</v>
+        <v>3209</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4106,17 +4096,17 @@
         <v>1151</v>
       </c>
       <c r="M60" s="3" t="n">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="N60" s="3" t="n">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="O60" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4157,20 +4147,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3583</v>
+        <v>3584</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4213,12 +4203,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>10148</v>
+        <v>10151</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4227,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4269,20 +4259,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>18478</v>
+        <v>18483</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4325,12 +4315,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4371,20 +4361,20 @@
         </is>
       </c>
       <c r="L65" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M65" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N65" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4425,20 +4415,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>52377</v>
+        <v>52391</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4479,20 +4469,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4535,12 +4525,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22915</v>
+        <v>22921</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4557,7 @@
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>327</v>
@@ -4594,7 +4584,7 @@
         <v>327</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3833</v>
+        <v>3834</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1637</v>
@@ -4604,7 +4594,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4638,7 @@
         <v>655</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5213</v>
+        <v>5215</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3274</v>
@@ -4658,7 +4648,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4702,17 +4692,17 @@
         <v>1390</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5205</v>
+        <v>5206</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4753,20 +4743,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1535380</v>
+        <v>1535786</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11785</v>
+        <v>11788</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4807,20 +4797,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4919</v>
+        <v>4920</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7737</v>
+        <v>7739</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4861,20 +4851,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>9002</v>
+        <v>9005</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21686</v>
+        <v>21692</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>18005</v>
+        <v>18009</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4915,20 +4905,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>18005</v>
+        <v>18009</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27992</v>
+        <v>28000</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -4947,18 +4937,18 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -4979,20 +4969,20 @@
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6596</v>
+        <v>6598</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5036,7 @@
         <v>1228</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5367</v>
+        <v>5368</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>655</v>
@@ -5056,7 +5046,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5065,7 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
@@ -5086,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
@@ -5109,12 +5099,12 @@
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="3" t="inlineStr"/>
       <c r="N78" s="3" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5155,20 +5145,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5892</v>
+        <v>5894</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5892</v>
+        <v>5894</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5211,12 +5201,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5257,20 +5247,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23940</v>
+        <v>23946</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23940</v>
+        <v>23946</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5303,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20951</v>
+        <v>20956</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5345,10 +5335,10 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5368,17 +5358,17 @@
         <v>290</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1636629</v>
+        <v>1637061</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5425,10 +5415,10 @@
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="3" t="n">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>35780</v>
+        <v>35790</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1637</v>
@@ -5438,7 +5428,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5478,7 @@
         <v>2331</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3264</v>
+        <v>3265</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3274</v>
@@ -5498,7 +5488,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5535,20 +5525,20 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5587,12 +5577,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5629,20 +5619,20 @@
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="n">
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>4889</v>
+        <v>4890</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5681,12 +5671,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>18005</v>
+        <v>18009</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5713,10 +5703,10 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5736,17 +5726,17 @@
         <v>512</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>88956</v>
+        <v>88980</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5786,7 @@
         <v>851</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5441</v>
+        <v>5442</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1637</v>
@@ -5806,7 +5796,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5843,10 +5833,10 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3274</v>
@@ -5856,7 +5846,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5895,12 +5885,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5939,12 +5929,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5973,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6027,12 +6017,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>18005</v>
+        <v>18009</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6073,20 +6063,20 @@
         </is>
       </c>
       <c r="L97" s="3" t="n">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3203</v>
+        <v>3204</v>
       </c>
       <c r="N97" s="3" t="n">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="O97" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6133,14 +6123,14 @@
         <v>2128</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6181,20 +6171,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4883</v>
+        <v>4884</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5357</v>
+        <v>5359</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>10148</v>
+        <v>10151</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6235,20 +6225,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6291,12 +6281,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6337,20 +6327,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18596</v>
+        <v>18601</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18596</v>
+        <v>18601</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6393,12 +6383,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>52377</v>
+        <v>52391</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6445,14 +6435,14 @@
         <v>2783</v>
       </c>
       <c r="N104" s="3" t="n">
-        <v>2946</v>
+        <v>2947</v>
       </c>
       <c r="O104" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6495,12 +6485,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6533,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>10148</v>
+        <v>10151</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6589,20 +6579,20 @@
         </is>
       </c>
       <c r="L107" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O107" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6635,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6693,12 +6683,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6731,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>52377</v>
+        <v>52391</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6786,21 +6776,15 @@
           <t>Vehicle / Transport Aircraft</t>
         </is>
       </c>
-      <c r="L111" s="3" t="n">
-        <v>76258</v>
-      </c>
-      <c r="M111" s="3" t="n">
-        <v>76258</v>
-      </c>
+      <c r="L111" s="3" t="inlineStr"/>
+      <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>81840</v>
-      </c>
-      <c r="O111" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>81861</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6819,7 +6803,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>90024</v>
+        <v>90047</v>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
@@ -6830,7 +6814,7 @@
         <v>1</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>90024</v>
+        <v>90047</v>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
@@ -6851,20 +6835,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>90024</v>
+        <v>90047</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>100489</v>
+        <v>100516</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>114576</v>
+        <v>114606</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6905,20 +6889,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>114576</v>
+        <v>114606</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>114576</v>
+        <v>114606</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>147311</v>
+        <v>147350</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6921,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
@@ -6948,7 +6932,7 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
@@ -6968,21 +6952,15 @@
           <t>Vehicle / Transport Aircraft</t>
         </is>
       </c>
-      <c r="L114" s="3" t="n">
-        <v>130943</v>
-      </c>
-      <c r="M114" s="3" t="n">
-        <v>130943</v>
-      </c>
+      <c r="L114" s="3" t="inlineStr"/>
+      <c r="M114" s="3" t="inlineStr"/>
       <c r="N114" s="3" t="n">
-        <v>163679</v>
-      </c>
-      <c r="O114" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>163722</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr"/>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7001,7 +6979,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -7012,7 +6990,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7033,20 +7011,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>196415</v>
+        <v>196467</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7087,20 +7065,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>220967</v>
+        <v>221025</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7132,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7195,20 +7173,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3925</v>
+        <v>3926</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7251,12 +7229,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7297,20 +7275,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7331,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23570</v>
+        <v>23576</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7399,20 +7377,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19681</v>
+        <v>19686</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7453,20 +7431,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>42494</v>
+        <v>42506</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7520,7 +7498,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7561,20 +7539,20 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5878</v>
+        <v>5879</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7615,20 +7593,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6685</v>
+        <v>6686</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6685</v>
+        <v>6686</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7669,20 +7647,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>12297</v>
+        <v>12300</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7725,12 +7703,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23570</v>
+        <v>23576</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7773,12 +7751,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7804,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7873,14 +7851,14 @@
         <v>3274</v>
       </c>
       <c r="N131" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O131" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7921,20 +7899,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -7975,20 +7953,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16458</v>
+        <v>16462</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8031,12 +8009,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8077,20 +8055,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>22097</v>
+        <v>22103</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>22097</v>
+        <v>22103</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>49104</v>
+        <v>49117</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8087,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8120,7 +8098,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8141,20 +8119,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>73656</v>
+        <v>73675</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8195,20 +8173,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8205,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8235,10 +8213,10 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8259,20 +8237,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>13188</v>
+        <v>13191</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8336,7 +8314,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8344,7 @@
         <v>7</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8390,7 +8368,7 @@
         <v>589</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5344</v>
+        <v>5346</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>637</v>
@@ -8400,7 +8378,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8442,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8496,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8559,10 +8537,10 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3274</v>
@@ -8572,7 +8550,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8591,18 +8569,18 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2128</v>
+        <v>2155</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2128</v>
+        <v>2141</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8623,20 +8601,20 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2154</v>
+        <v>3437</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>11111</v>
+        <v>11113</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O144" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8679,12 +8657,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8681,7 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -8714,7 +8692,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -8735,20 +8713,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>55353</v>
+        <v>55368</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8791,12 +8769,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8837,20 +8815,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17936</v>
+        <v>17941</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8893,12 +8871,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8917,15 +8895,15 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>16536</v>
@@ -8949,20 +8927,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -8981,7 +8959,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -8989,10 +8967,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9013,20 +8991,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>86979</v>
+        <v>87002</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>78566</v>
+        <v>78587</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9067,20 +9045,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>212783</v>
+        <v>212839</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9112,7 @@
         <v>164</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10708</v>
+        <v>10711</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>327</v>
@@ -9144,7 +9122,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9198,7 +9176,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9217,7 +9195,7 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
@@ -9228,7 +9206,7 @@
         <v>3</v>
       </c>
       <c r="G155" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
@@ -9245,20 +9223,20 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>16037</v>
+        <v>16042</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1637</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9286,7 @@
         <v>1637</v>
       </c>
       <c r="M156" s="3" t="n">
-        <v>3352</v>
+        <v>3353</v>
       </c>
       <c r="N156" s="3" t="n">
         <v>3274</v>
@@ -9318,7 +9296,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9368,17 +9346,17 @@
         <v>3274</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9419,20 +9397,20 @@
         </is>
       </c>
       <c r="L158" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>20010</v>
+        <v>20015</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1637</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9454,7 @@
         <v>1637</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19849</v>
+        <v>19855</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3274</v>
@@ -9486,7 +9464,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9540,17 +9518,17 @@
         <v>3274</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6847</v>
+        <v>6849</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9582,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9634,7 +9612,7 @@
         <v>6</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9655,20 +9633,20 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>31230</v>
+        <v>31238</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>2043</v>
+        <v>1637</v>
       </c>
       <c r="O162" s="2" t="n">
         <v>32</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9665,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9695,10 +9673,10 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3232</v>
+        <v>3329</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9719,20 +9697,20 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3928</v>
+        <v>3929</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3882</v>
+        <v>3883</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9751,18 +9729,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3995</v>
+        <v>3998</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>57</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3772</v>
+        <v>3774</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9783,20 +9761,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3997</v>
+        <v>3797</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9828,7 @@
         <v>193</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>5082</v>
+        <v>5084</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>327</v>
@@ -9860,7 +9838,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9924,7 +9902,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9921,7 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
@@ -9978,17 +9956,17 @@
         <v>1457</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>10060</v>
+        <v>10062</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="O167" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10010,7 @@
         <v>1637</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>327</v>
@@ -10042,7 +10020,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10093,10 +10071,10 @@
         </is>
       </c>
       <c r="L169" s="3" t="n">
-        <v>484</v>
+        <v>2913</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>327</v>
@@ -10106,7 +10084,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10147,20 +10125,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>98208</v>
+        <v>98233</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>98208</v>
+        <v>98233</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10203,12 +10181,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10258,7 +10236,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10298,17 +10276,17 @@
         <v>2128</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>4030</v>
+        <v>4031</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10347,12 +10325,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10389,20 +10367,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14700</v>
+        <v>14704</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10439,20 +10417,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11785</v>
+        <v>11788</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11785</v>
+        <v>11788</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23570</v>
+        <v>23576</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10489,20 +10467,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16450</v>
+        <v>16454</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10539,20 +10517,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19805</v>
+        <v>19810</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10592,15 +10570,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L179" s="3" t="inlineStr"/>
-      <c r="M179" s="3" t="inlineStr"/>
+      <c r="L179" s="3" t="n">
+        <v>3161</v>
+      </c>
+      <c r="M179" s="3" t="n">
+        <v>3161</v>
+      </c>
       <c r="N179" s="3" t="n">
         <v>3274</v>
       </c>
-      <c r="O179" s="2" t="inlineStr"/>
+      <c r="O179" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10641,20 +10625,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10697,12 +10681,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10743,20 +10727,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10799,12 +10783,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10845,20 +10829,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>22097</v>
+        <v>22103</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>22097</v>
+        <v>22103</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>44193</v>
+        <v>44205</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10899,20 +10883,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>29462</v>
+        <v>29470</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>58925</v>
+        <v>58940</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>24</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -10956,17 +10940,17 @@
         <v>164</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11010,17 +10994,17 @@
         <v>164</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11048,7 @@
         <v>164</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>106493</v>
+        <v>106521</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>327</v>
@@ -11074,7 +11058,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11122,7 +11106,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11150,7 @@
         <v>164</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>30189</v>
+        <v>30197</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>327</v>
@@ -11176,7 +11160,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11195,7 +11179,7 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
@@ -11206,7 +11190,7 @@
         <v>1</v>
       </c>
       <c r="G191" s="3" t="n">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
@@ -11230,17 +11214,17 @@
         <v>164</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>161605</v>
+        <v>161648</v>
       </c>
       <c r="N191" s="3" t="n">
-        <v>944</v>
+        <v>327</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11284,17 +11268,17 @@
         <v>164</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11326,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11386,17 +11370,17 @@
         <v>164</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11450,17 +11434,17 @@
         <v>164</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>163516</v>
+        <v>163559</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11504,17 +11488,17 @@
         <v>164</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11546,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11581,7 +11565,7 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
@@ -11613,10 +11597,10 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>1023</v>
@@ -11626,7 +11610,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11629,7 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
@@ -11656,7 +11640,7 @@
         <v>1</v>
       </c>
       <c r="G199" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
@@ -11677,20 +11661,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>21314</v>
+        <v>21320</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11709,7 +11693,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -11720,7 +11704,7 @@
         <v>1</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -11741,20 +11725,20 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6526</v>
+        <v>6528</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11795,20 +11779,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>11151</v>
+        <v>11154</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7857</v>
+        <v>7859</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11849,20 +11833,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10711</v>
+        <v>10714</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11903,20 +11887,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8511</v>
+        <v>8514</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>285735</v>
+        <v>285810</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14404</v>
+        <v>14408</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11957,20 +11941,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>16173</v>
+        <v>16177</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16600</v>
+        <v>16605</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11973,7 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>21964</v>
+        <v>21970</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
@@ -12000,7 +11984,7 @@
         <v>1</v>
       </c>
       <c r="G205" s="3" t="n">
-        <v>21964</v>
+        <v>21970</v>
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
@@ -12021,20 +12005,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>22408</v>
+        <v>22414</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>50493</v>
+        <v>50507</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12077,12 +12061,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23570</v>
+        <v>23576</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12136,7 +12120,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12200,7 +12184,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12241,7 +12225,7 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>3107</v>
@@ -12254,7 +12238,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12298,17 +12282,17 @@
         <v>2128</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4627</v>
+        <v>4628</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4256</v>
+        <v>4257</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12349,20 +12333,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12403,20 +12387,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12459,12 +12443,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23570</v>
+        <v>23576</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12505,20 +12489,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12556,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12616,17 +12600,17 @@
         <v>2128</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>12291</v>
+        <v>12294</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4256</v>
+        <v>4257</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12667,20 +12651,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>16116</v>
+        <v>16120</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>48534</v>
+        <v>48547</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12721,20 +12705,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>7956</v>
+        <v>7959</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12775,20 +12759,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7366</v>
+        <v>7368</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14731</v>
+        <v>14735</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12815,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12877,20 +12861,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -12954,7 +12938,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13008,17 +12992,17 @@
         <v>1637</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4189</v>
+        <v>4190</v>
       </c>
       <c r="N223" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13036,13 +13020,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D224" s="3" t="inlineStr"/>
-      <c r="E224" s="2" t="inlineStr"/>
-      <c r="F224" s="2" t="inlineStr"/>
-      <c r="G224" s="3" t="inlineStr"/>
+      <c r="D224" s="3" t="n">
+        <v>3274</v>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G224" s="3" t="n">
+        <v>3274</v>
+      </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I224" s="2" t="n">
@@ -13062,17 +13056,17 @@
         <v>3274</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7449</v>
+        <v>7451</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O224" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13113,10 +13107,10 @@
         </is>
       </c>
       <c r="L225" s="3" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1637</v>
@@ -13126,7 +13120,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13177,10 +13171,10 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3154</v>
+        <v>3155</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>3596</v>
+        <v>3597</v>
       </c>
       <c r="N226" s="3" t="n">
         <v>3274</v>
@@ -13190,7 +13184,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13244,17 +13238,17 @@
         <v>3274</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3914</v>
+        <v>3915</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13308,7 +13302,7 @@
         <v>164</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>327</v>
@@ -13318,7 +13312,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13362,17 +13356,17 @@
         <v>164</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13385,7 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -13426,17 +13420,17 @@
         <v>164</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N230" s="3" t="n">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13477,10 +13471,10 @@
         </is>
       </c>
       <c r="L231" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1637</v>
@@ -13490,7 +13484,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13554,7 +13548,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13608,17 +13602,17 @@
         <v>3274</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7457</v>
+        <v>7459</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13666,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13713,10 +13707,10 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4411</v>
+        <v>4412</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3274</v>
@@ -13726,7 +13720,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13739,7 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>5172</v>
+        <v>5174</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
@@ -13756,7 +13750,7 @@
         <v>1</v>
       </c>
       <c r="G236" s="3" t="n">
-        <v>5172</v>
+        <v>5174</v>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
@@ -13777,20 +13771,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>5187</v>
+        <v>5188</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6750</v>
+        <v>6752</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13833,12 +13827,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13857,7 +13851,7 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -13868,7 +13862,7 @@
         <v>1</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -13889,20 +13883,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>5817</v>
+        <v>5819</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11410</v>
+        <v>11413</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13945,12 +13939,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -13991,20 +13985,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10842</v>
+        <v>10845</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10842</v>
+        <v>10845</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14023,7 +14017,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>21856</v>
+        <v>21862</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14031,10 +14025,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>19139</v>
+        <v>19491</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14055,20 +14049,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>25344</v>
+        <v>23743</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>35996</v>
+        <v>36006</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14087,7 +14081,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14098,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14119,20 +14113,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>39324</v>
+        <v>39293</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>60646</v>
+        <v>60662</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>78566</v>
+        <v>78587</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14151,7 +14145,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14162,7 +14156,7 @@
         <v>14</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>18416</v>
+        <v>18421</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14179,20 +14173,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>18985</v>
+        <v>18990</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>32735858</v>
+        <v>32744498</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14235,12 +14229,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14284,7 +14278,7 @@
         <v>655</v>
       </c>
       <c r="M245" s="3" t="n">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="N245" s="3" t="n">
         <v>327</v>
@@ -14294,7 +14288,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14313,7 +14307,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -14324,7 +14318,7 @@
         <v>8</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14348,17 +14342,17 @@
         <v>2367</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14399,20 +14393,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>16073</v>
+        <v>9168</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>24133</v>
+        <v>24139</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>18332</v>
+        <v>18337</v>
       </c>
       <c r="O247" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14453,20 +14447,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>18332</v>
+        <v>18337</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14503,10 +14497,10 @@
       </c>
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9610</v>
+        <v>9612</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1637</v>
@@ -14516,7 +14510,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14553,10 +14547,10 @@
       </c>
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="3" t="n">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="M250" s="3" t="n">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="N250" s="3" t="n">
         <v>1637</v>
@@ -14566,7 +14560,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14579,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>32382</v>
+        <v>32391</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -14596,7 +14590,7 @@
         <v>1</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>32382</v>
+        <v>32391</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -14620,17 +14614,17 @@
         <v>164</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>100648</v>
+        <v>100675</v>
       </c>
       <c r="N251" s="3" t="n">
-        <v>35620</v>
+        <v>35629</v>
       </c>
       <c r="O251" s="2" t="n">
         <v>138</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14648,13 +14642,23 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D252" s="3" t="inlineStr"/>
-      <c r="E252" s="2" t="inlineStr"/>
-      <c r="F252" s="2" t="inlineStr"/>
-      <c r="G252" s="3" t="inlineStr"/>
+      <c r="D252" s="3" t="n">
+        <v>4584</v>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" s="3" t="n">
+        <v>4584</v>
+      </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I252" s="2" t="n">
@@ -14671,20 +14675,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>4583</v>
+        <v>52169</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>52155</v>
+        <v>52169</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O252" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14725,20 +14729,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>6893</v>
+        <v>6894</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>7804</v>
+        <v>7806</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7857</v>
+        <v>7859</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14757,7 +14761,7 @@
         </is>
       </c>
       <c r="D254" s="3" t="n">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
@@ -14768,7 +14772,7 @@
         <v>1</v>
       </c>
       <c r="G254" s="3" t="n">
-        <v>6915</v>
+        <v>6917</v>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
@@ -14789,20 +14793,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>8136</v>
+        <v>8139</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>196415</v>
+        <v>196467</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14825,7 @@
         </is>
       </c>
       <c r="D255" s="3" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
@@ -14832,7 +14836,7 @@
         <v>1</v>
       </c>
       <c r="G255" s="3" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
@@ -14853,7 +14857,7 @@
         </is>
       </c>
       <c r="L255" s="3" t="n">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="M255" s="3" t="n">
         <v>1637</v>
@@ -14866,7 +14870,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14924,7 +14928,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -14968,7 +14972,7 @@
         <v>301</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>8184</v>
+        <v>8186</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>327</v>
@@ -14978,7 +14982,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15001,7 +15005,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -15035,14 +15039,14 @@
         <v>997</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>1285</v>
+        <v>1393</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15061,7 +15065,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -15072,7 +15076,7 @@
         <v>1</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -15096,7 +15100,7 @@
         <v>1262</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>22134</v>
+        <v>22140</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1637</v>
@@ -15106,7 +15110,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15129,7 @@
         </is>
       </c>
       <c r="D260" s="3" t="n">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -15157,10 +15161,10 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2684</v>
+        <v>2685</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3801</v>
+        <v>3802</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3274</v>
@@ -15170,7 +15174,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15200,7 +15204,7 @@
         <v>3</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15224,17 +15228,17 @@
         <v>3274</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7261</v>
+        <v>7263</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15253,18 +15257,18 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15285,20 +15289,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15339,20 +15343,20 @@
         </is>
       </c>
       <c r="L263" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10931</v>
+        <v>10933</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1637</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15420,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15439,7 @@
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
@@ -15446,7 +15450,7 @@
         <v>1</v>
       </c>
       <c r="G265" s="3" t="n">
-        <v>3275</v>
+        <v>3276</v>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
@@ -15469,12 +15473,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15493,7 +15497,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15504,7 +15508,7 @@
         <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15525,20 +15529,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>9975</v>
+        <v>9977</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9975</v>
+        <v>9977</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15561,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15568,7 +15572,7 @@
         <v>6</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15589,20 +15593,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>20131</v>
+        <v>20136</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15621,7 +15625,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8511</v>
+        <v>8514</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15632,7 +15636,7 @@
         <v>2</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8511</v>
+        <v>8514</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15653,20 +15657,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8511</v>
+        <v>8514</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14744</v>
+        <v>14748</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14404</v>
+        <v>14408</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15709,12 +15713,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15755,20 +15759,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>25773</v>
+        <v>25780</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25773</v>
+        <v>25780</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15787,7 +15791,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>20951</v>
+        <v>20956</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15798,7 +15802,7 @@
         <v>3</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>25434</v>
+        <v>25441</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15819,20 +15823,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24714</v>
+        <v>24486</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>53803</v>
+        <v>53817</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15880,7 @@
         <v>164</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>10045</v>
+        <v>10048</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>327</v>
@@ -15886,7 +15890,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15930,7 +15934,7 @@
         <v>164</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21678</v>
+        <v>21683</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>327</v>
@@ -15940,7 +15944,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -15994,17 +15998,17 @@
         <v>164</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>32844</v>
+        <v>32853</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16058,17 +16062,17 @@
         <v>164</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16450</v>
+        <v>16454</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16087,7 +16091,7 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>13855</v>
+        <v>13859</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -16098,7 +16102,7 @@
         <v>2</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>7010</v>
+        <v>7011</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16122,17 +16126,17 @@
         <v>164</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>163187</v>
+        <v>163230</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>327</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16169,10 +16173,10 @@
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="3" t="n">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M277" s="3" t="n">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="N277" s="3" t="n">
         <v>1637</v>
@@ -16182,7 +16186,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16200,23 +16204,13 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D278" s="3" t="n">
-        <v>4583</v>
-      </c>
-      <c r="E278" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="F278" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G278" s="3" t="n">
-        <v>4583</v>
-      </c>
+      <c r="D278" s="3" t="inlineStr"/>
+      <c r="E278" s="2" t="inlineStr"/>
+      <c r="F278" s="2" t="inlineStr"/>
+      <c r="G278" s="3" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I278" s="2" t="n">
@@ -16233,20 +16227,20 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>8830</v>
+        <v>8833</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16287,20 +16281,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>10241</v>
+        <v>10244</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7857</v>
+        <v>7859</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16341,20 +16335,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8907</v>
+        <v>8910</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10475</v>
+        <v>10478</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16397,12 +16391,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14404</v>
+        <v>14408</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16445,12 +16439,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16493,12 +16487,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16517,7 +16511,7 @@
         </is>
       </c>
       <c r="D284" s="3" t="n">
-        <v>20951</v>
+        <v>20956</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
@@ -16528,7 +16522,7 @@
         <v>1</v>
       </c>
       <c r="G284" s="3" t="n">
-        <v>20951</v>
+        <v>20956</v>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
@@ -16549,20 +16543,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16581,18 +16575,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10569</v>
+        <v>9707</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>10202</v>
+        <v>10153</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16613,20 +16607,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>11268</v>
+        <v>11163</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>11214</v>
+        <v>11240</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16690,7 +16684,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16709,7 +16703,7 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5429</v>
+        <v>5431</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
@@ -16720,7 +16714,7 @@
         <v>13</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5286</v>
+        <v>5287</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16737,20 +16731,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5534</v>
+        <v>5535</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5974</v>
+        <v>5976</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>6007</v>
+        <v>6009</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16769,18 +16763,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7087</v>
+        <v>7646</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
         <v>29</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7048</v>
+        <v>7069</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16797,20 +16791,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>7644</v>
+        <v>7620</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8939</v>
+        <v>8941</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7878</v>
+        <v>8019</v>
       </c>
       <c r="O288" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16823,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9698</v>
+        <v>9701</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16840,7 +16834,7 @@
         <v>20</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9517</v>
+        <v>9520</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16857,20 +16851,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9621</v>
+        <v>9624</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11171</v>
+        <v>11058</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>11207</v>
+        <v>11511</v>
       </c>
       <c r="O289" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16900,7 +16894,7 @@
         <v>2</v>
       </c>
       <c r="G290" s="3" t="n">
-        <v>3192</v>
+        <v>3193</v>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
@@ -16934,7 +16928,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -16953,18 +16947,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>2922</v>
+        <v>2423</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2763</v>
+        <v>2696</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16988,7 +16982,7 @@
         <v>2904</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>5238</v>
+        <v>5239</v>
       </c>
       <c r="N291" s="3" t="n">
         <v>3274</v>
@@ -16998,7 +16992,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17022,7 @@
         <v>7</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17049,20 +17043,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4175</v>
+        <v>4177</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17126,7 +17120,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17139,7 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5346</v>
+        <v>5347</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -17153,10 +17147,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>6743</v>
+        <v>6734</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17177,20 +17171,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>4848</v>
+        <v>4849</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>19538</v>
+        <v>19544</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6834</v>
+        <v>6785</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17231,20 +17225,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>53201</v>
+        <v>53215</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>723039</v>
+        <v>723229</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17263,7 +17257,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17274,7 +17268,7 @@
         <v>9</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17295,20 +17289,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>71166</v>
+        <v>71185</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>40920</v>
+        <v>40931</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17321,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>65472</v>
+        <v>65489</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17338,7 +17332,7 @@
         <v>3</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>65472</v>
+        <v>65489</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17359,20 +17353,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>65472</v>
+        <v>65489</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>81840</v>
+        <v>81861</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17391,7 +17385,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17402,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17423,20 +17417,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>130943</v>
+        <v>130978</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>130947</v>
+        <v>130981</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>163679</v>
+        <v>163722</v>
       </c>
       <c r="O298" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17455,7 +17449,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17466,7 +17460,7 @@
         <v>2</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17487,20 +17481,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>261887</v>
+        <v>261956</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>264409</v>
+        <v>264479</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>327359</v>
+        <v>327445</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17513,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>458302</v>
+        <v>458423</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17530,7 +17524,7 @@
         <v>3</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>458302</v>
+        <v>458423</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17551,20 +17545,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>458302</v>
+        <v>458423</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>905412</v>
+        <v>905651</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>654717</v>
+        <v>654890</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17583,7 +17577,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>17126</v>
+        <v>17130</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17591,10 +17585,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>18057</v>
+        <v>17348</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17615,20 +17609,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>19921</v>
+        <v>19414</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>33250</v>
+        <v>33259</v>
       </c>
       <c r="N301" s="3" t="n">
         <v>2292</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17679,10 +17673,10 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4964</v>
+        <v>4966</v>
       </c>
       <c r="N302" s="3" t="n">
         <v>2292</v>
@@ -17692,7 +17686,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17711,7 +17705,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4233</v>
+        <v>4234</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17722,7 +17716,7 @@
         <v>12</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4285</v>
+        <v>4286</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17743,20 +17737,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>16366</v>
+        <v>16371</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4257</v>
+        <v>4258</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17775,7 +17769,7 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -17783,10 +17777,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1630</v>
+        <v>1727</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17807,20 +17801,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2791</v>
+        <v>2292</v>
       </c>
       <c r="O304" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17874,17 +17868,17 @@
         <v>488</v>
       </c>
       <c r="M305" s="3" t="n">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="N305" s="3" t="n">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="O305" s="2" t="n">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17911,10 +17905,10 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>3592</v>
+        <v>4165</v>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
@@ -17938,7 +17932,7 @@
         <v>164</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>327</v>
@@ -17948,7 +17942,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -17967,7 +17961,7 @@
         </is>
       </c>
       <c r="D307" s="3" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
@@ -17978,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="G307" s="3" t="n">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
@@ -18002,7 +17996,7 @@
         <v>1411</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>327</v>
@@ -18012,7 +18006,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18066,17 +18060,17 @@
         <v>2128</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1309434</v>
+        <v>1309780</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>226</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18117,20 +18111,20 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>33096</v>
+        <v>33105</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18178,7 @@
         <v>1637</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6236</v>
+        <v>6238</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3274</v>
@@ -18194,7 +18188,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18245,20 +18239,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>5012</v>
+        <v>5013</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6246</v>
+        <v>6248</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18301,12 +18295,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18325,7 +18319,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18336,7 +18330,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18357,20 +18351,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>27063</v>
+        <v>27070</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>41</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18411,20 +18405,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>16013</v>
+        <v>16017</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>16013</v>
+        <v>16017</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18443,7 +18437,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18451,10 +18445,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18475,20 +18469,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18507,7 +18501,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18515,10 +18509,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18539,20 +18533,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>39283</v>
+        <v>39293</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>78566</v>
+        <v>78587</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18571,7 +18565,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18582,7 +18576,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18603,20 +18597,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>106392</v>
+        <v>106420</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>212783</v>
+        <v>212839</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18680,7 +18674,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18734,7 +18728,7 @@
         <v>1233</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>16257</v>
+        <v>16261</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1652</v>
@@ -18744,7 +18738,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18771,10 +18765,10 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1473</v>
+        <v>1460</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18798,7 +18792,7 @@
         <v>1146</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>10169</v>
+        <v>10172</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2292</v>
@@ -18808,7 +18802,7 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18827,7 +18821,7 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
@@ -18838,7 +18832,7 @@
         <v>2</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18859,10 +18853,10 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3765</v>
+        <v>3766</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>327</v>
@@ -18872,7 +18866,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18936,7 +18930,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -18966,7 +18960,7 @@
         <v>7</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2834</v>
+        <v>2835</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18990,7 +18984,7 @@
         <v>1745</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>17077</v>
+        <v>17081</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>2292</v>
@@ -19000,7 +18994,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19044,7 +19038,7 @@
         <v>327</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5788</v>
+        <v>5789</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>327</v>
@@ -19054,7 +19048,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19073,7 +19067,7 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -19105,20 +19099,20 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>16257</v>
+        <v>16261</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="O325" s="2" t="n">
         <v>31</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19172,7 +19166,7 @@
         <v>1922</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>2292</v>
@@ -19182,7 +19176,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19201,7 +19195,7 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>3391</v>
+        <v>3582</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -19209,10 +19203,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>4492</v>
+        <v>4374</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19233,20 +19227,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>3773</v>
+        <v>3689</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15888</v>
+        <v>10554</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>3231</v>
+        <v>3484</v>
       </c>
       <c r="O327" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19265,18 +19259,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>25698</v>
+        <v>19403</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22416</v>
+        <v>22406</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19297,20 +19291,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>21378</v>
+        <v>21726</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>26185</v>
+        <v>25898</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19329,18 +19323,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7406</v>
+        <v>7066</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7342</v>
+        <v>7297</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19361,20 +19355,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7477</v>
+        <v>7183</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9416</v>
+        <v>9419</v>
       </c>
       <c r="N329" s="3" t="n">
         <v>7798</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19393,18 +19387,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5539</v>
+        <v>5691</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>6013</v>
+        <v>5973</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19425,20 +19419,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5534</v>
+        <v>6305</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8957</v>
+        <v>8959</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6149</v>
+        <v>6181</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19451,7 @@
         </is>
       </c>
       <c r="D331" s="3" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -19468,7 +19462,7 @@
         <v>1</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
@@ -19489,7 +19483,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3274</v>
@@ -19502,7 +19496,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19553,20 +19547,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1180</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19589,11 +19583,11 @@
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G333" s="3" t="n">
         <v>233</v>
@@ -19617,10 +19611,10 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="M333" s="3" t="n">
-        <v>4999</v>
+        <v>5000</v>
       </c>
       <c r="N333" s="3" t="n">
         <v>327</v>
@@ -19630,7 +19624,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19657,10 +19651,10 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>1908</v>
+        <v>2052</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19684,17 +19678,17 @@
         <v>427</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="O334" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19748,17 +19742,17 @@
         <v>1550</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>2954</v>
+        <v>2955</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2292</v>
       </c>
       <c r="O335" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19781,14 +19775,14 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G336" s="3" t="n">
-        <v>253</v>
+        <v>210</v>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
@@ -19822,7 +19816,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19870,7 @@
         <v>164</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>16026</v>
+        <v>16030</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>327</v>
@@ -19886,7 +19880,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -19909,11 +19903,11 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G338" s="3" t="n">
         <v>313</v>
@@ -19943,14 +19937,14 @@
         <v>1013</v>
       </c>
       <c r="N338" s="3" t="n">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="O338" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20004,7 +19998,7 @@
         <v>457</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4874</v>
+        <v>4876</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>327</v>
@@ -20014,7 +20008,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20033,7 +20027,7 @@
         </is>
       </c>
       <c r="D340" s="3" t="n">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
@@ -20044,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="G340" s="3" t="n">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
@@ -20065,7 +20059,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>1056</v>
+        <v>1023</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3274</v>
@@ -20074,11 +20068,11 @@
         <v>1177</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20102,7 @@
         <v>10</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20129,20 +20123,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="M341" s="3" t="n">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="N341" s="3" t="n">
         <v>974</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20161,7 +20155,7 @@
         </is>
       </c>
       <c r="D342" s="3" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
@@ -20196,7 +20190,7 @@
         <v>653</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>16368</v>
+        <v>16372</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>354</v>
@@ -20206,7 +20200,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20225,18 +20219,18 @@
         </is>
       </c>
       <c r="D343" s="3" t="n">
-        <v>419</v>
+        <v>473</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20257,20 +20251,20 @@
         </is>
       </c>
       <c r="L343" s="3" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M343" s="3" t="n">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N343" s="3" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20294,7 @@
         <v>13</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20324,17 +20318,17 @@
         <v>1637</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>17607</v>
+        <v>17612</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3274</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20388,17 +20382,17 @@
         <v>2128</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1636793</v>
+        <v>1637225</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="O345" s="2" t="n">
         <v>88</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20441,12 +20435,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4910</v>
+        <v>4912</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20465,7 +20459,7 @@
         </is>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -20476,7 +20470,7 @@
         <v>2</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
@@ -20497,20 +20491,20 @@
         </is>
       </c>
       <c r="L347" s="3" t="n">
-        <v>4583</v>
+        <v>4584</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>8434</v>
+        <v>8437</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6547</v>
+        <v>6549</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20551,20 +20545,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>13094</v>
+        <v>13098</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20583,7 +20577,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20594,7 +20588,7 @@
         <v>5</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20615,20 +20609,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9821</v>
+        <v>9823</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19642</v>
+        <v>19647</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20669,20 +20663,20 @@
         </is>
       </c>
       <c r="L350" s="3" t="n">
-        <v>13094</v>
+        <v>16968</v>
       </c>
       <c r="M350" s="3" t="n">
-        <v>13094</v>
+        <v>16968</v>
       </c>
       <c r="N350" s="3" t="n">
-        <v>26189</v>
+        <v>26196</v>
       </c>
       <c r="O350" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20701,18 +20695,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16368</v>
+        <v>17508</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16899</v>
+        <v>16914</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20733,20 +20727,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16368</v>
+        <v>17448</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>39147</v>
+        <v>39158</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>32736</v>
+        <v>32744</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20765,18 +20759,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>42198</v>
+        <v>43198</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>46884</v>
+        <v>46368</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20797,20 +20791,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>47326</v>
+        <v>47299</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>48685</v>
+        <v>47337</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>78566</v>
+        <v>78587</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20823,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>195736</v>
+        <v>195788</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20840,7 +20834,7 @@
         <v>1</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>195736</v>
+        <v>195788</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20861,20 +20855,20 @@
         </is>
       </c>
       <c r="L353" s="3" t="n">
-        <v>155173</v>
+        <v>145643</v>
       </c>
       <c r="M353" s="3" t="n">
-        <v>155173</v>
+        <v>145643</v>
       </c>
       <c r="N353" s="3" t="n">
-        <v>212783</v>
+        <v>212839</v>
       </c>
       <c r="O353" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20887,7 @@
         </is>
       </c>
       <c r="D354" s="3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
@@ -20904,7 +20898,7 @@
         <v>1</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
@@ -20925,20 +20919,20 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9700</v>
+        <v>9702</v>
       </c>
       <c r="N354" s="3" t="n">
         <v>537</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>337</v>
+        <v>490</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -20957,7 +20951,7 @@
         </is>
       </c>
       <c r="D355" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="E355" s="2" t="inlineStr">
         <is>
@@ -20968,7 +20962,7 @@
         <v>1</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="H355" s="2" t="inlineStr">
         <is>
@@ -20989,20 +20983,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19601</v>
+        <v>19606</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>18332</v>
+        <v>18337</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -21021,7 +21015,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -21032,7 +21026,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -21053,20 +21047,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>9166</v>
+        <v>9168</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>22539</v>
+        <v>22545</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>18332</v>
+        <v>18337</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21090,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>163.679291</v>
+        <v>163.722491</v>
       </c>
     </row>
     <row r="2">
@@ -21107,7 +21101,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Mon, 27 Jul 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Tue, 28 Jul 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21119,7 +21113,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3877</v>
+        <v>3186</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6372</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -679,11 +679,11 @@
         <v>12743</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>12743</v>
@@ -743,11 +743,11 @@
         <v>25487</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -811,7 +811,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -834,14 +834,14 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43632</v>
+        <v>43543</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
         <v>86017</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -932,14 +932,14 @@
         <v>143362</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>254866</v>
+        <v>254865</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>358406</v>
+        <v>358405</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>358406</v>
+        <v>358405</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>358406</v>
+        <v>358405</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>358406</v>
+        <v>358405</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>716812</v>
+        <v>716809</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1022,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5432</v>
+        <v>5287</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5811</v>
+        <v>5741</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1054,20 +1054,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5338</v>
+        <v>5335</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8761</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1086,18 +1086,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8231</v>
+        <v>8411</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8386</v>
+        <v>8391</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8307</v>
+        <v>8329</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>151286</v>
+        <v>151285</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>17522</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1154,11 +1154,11 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>14024</v>
@@ -1191,11 +1191,11 @@
         <v>35044</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N14" s="3" t="n">
         <v>19403</v>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34530</v>
+        <v>34529</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64531</v>
+        <v>64530</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5416</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1462,20 +1462,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22701</v>
+        <v>14717</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64531</v>
+        <v>64530</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5416</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1519,17 +1519,17 @@
         <v>796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1593</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
         <v>1593</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>229394</v>
+        <v>229393</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3186</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>3186</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>270796</v>
+        <v>270795</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6372</v>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         <v>21504</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>140607</v>
+        <v>140606</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>43009</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
         <v>39823</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>323897</v>
+        <v>323896</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79646</v>
+        <v>79645</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -1998,11 +1998,11 @@
         <v>319</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2120,17 +2120,17 @@
         <v>1359</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1588684</v>
+        <v>1588678</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1593</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
@@ -2181,20 +2181,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1593</v>
+        <v>1649</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3186</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2217,11 +2217,11 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3186</v>
@@ -2254,11 +2254,11 @@
         <v>6372</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2312,17 +2312,17 @@
         <v>637</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1274</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2382,11 +2382,11 @@
         <v>4779</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
         <v>1075</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>637166</v>
+        <v>637164</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1593</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2527</v>
+        <v>2551</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2533,18 +2533,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3186</v>
+        <v>3326</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3323</v>
+        <v>3329</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3664</v>
+        <v>3186</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>21292</v>
@@ -2574,11 +2574,11 @@
         <v>6372</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>6375</v>
@@ -2638,11 +2638,11 @@
         <v>12743</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2688,11 +2688,11 @@
         <v>1593</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2802,17 +2802,17 @@
         <v>3186</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>318583</v>
+        <v>318582</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6372</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
         <v>1593</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>145827</v>
+        <v>145826</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3186</v>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6372</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3171,20 +3171,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9239</v>
+        <v>8729</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>9723</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10024</v>
+        <v>9981</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3244,11 +3244,11 @@
         <v>3186</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3308,11 +3308,11 @@
         <v>6372</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9511</v>
+        <v>9514</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>11036</v>
+        <v>10825</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9513</v>
+        <v>8729</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30852</v>
+        <v>30851</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>12743</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4013,18 +4013,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3895</v>
+        <v>3887</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3968</v>
+        <v>3922</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3880</v>
+        <v>3895</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10399</v>
@@ -4054,11 +4054,11 @@
         <v>4221</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4077,18 +4077,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2136</v>
+        <v>3533</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3256</v>
+        <v>3175</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4115,14 +4115,14 @@
         <v>11389</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>2350</v>
+        <v>3117</v>
       </c>
       <c r="O59" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4230,7 +4230,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>31858</v>
+        <v>8920</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>31858</v>
@@ -4542,11 +4542,11 @@
         <v>22301</v>
       </c>
       <c r="O67" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4708,11 +4708,11 @@
         <v>3186</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4745</v>
+        <v>4431</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>5065</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
         <v>2549</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1494221</v>
+        <v>1494216</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11469</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
         <v>8761</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21105</v>
+        <v>21104</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>17522</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5324,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>282</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1592756</v>
+        <v>1592750</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>796</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5589,7 +5589,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>1274</v>
+        <v>2426</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>6372</v>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5646,7 +5646,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5740,7 +5740,7 @@
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
         <v>499</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86572</v>
+        <v>86571</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>796</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6086,7 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6800,7 +6800,7 @@
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6843,12 +6843,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79646</v>
+        <v>79645</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7003,14 +7003,14 @@
         <v>127433</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
@@ -7061,20 +7061,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>191150</v>
+        <v>191149</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7115,20 +7115,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>215044</v>
+        <v>215043</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>254866</v>
+        <v>254865</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>254866</v>
+        <v>254865</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7284,7 +7284,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7494,7 +7494,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7908,7 +7908,7 @@
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8461,11 +8461,11 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G141" s="3" t="n">
         <v>1593</v>
@@ -8498,11 +8498,11 @@
         <v>1752</v>
       </c>
       <c r="O141" s="2" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr"/>
-      <c r="E142" s="2" t="inlineStr"/>
-      <c r="F142" s="2" t="inlineStr"/>
-      <c r="G142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="n">
+        <v>1523</v>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>1523</v>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
@@ -8549,14 +8559,14 @@
         <v>1593</v>
       </c>
       <c r="N142" s="3" t="n">
-        <v>319</v>
+        <v>1676</v>
       </c>
       <c r="O142" s="2" t="n">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8620,7 +8630,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8694,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8732,7 +8742,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8806,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8854,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8898,7 +8908,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8946,7 +8956,7 @@
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8983,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>15929</v>
@@ -9010,7 +9020,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9047,7 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G151" s="3" t="n">
         <v>38230</v>
@@ -9064,17 +9074,17 @@
         <v>38230</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>84648</v>
+        <v>84647</v>
       </c>
       <c r="N151" s="3" t="n">
         <v>76460</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9121,14 +9131,14 @@
         <v>103539</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>207079</v>
+        <v>207078</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9151,11 +9161,11 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>159</v>
@@ -9188,11 +9198,11 @@
         <v>319</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9266,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9312,11 +9322,11 @@
         <v>1593</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9376,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9426,7 +9436,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9480,7 +9490,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9530,11 +9540,11 @@
         <v>3186</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9588,7 +9598,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9652,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9661,18 +9671,18 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1365</v>
+        <v>1633</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1580</v>
+        <v>1697</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9693,20 +9703,20 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1907</v>
+        <v>1927</v>
       </c>
       <c r="M162" s="3" t="n">
         <v>30393</v>
       </c>
       <c r="N162" s="3" t="n">
-        <v>1747</v>
+        <v>1771</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9780,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9789,18 +9799,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3587</v>
+        <v>3539</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3769</v>
+        <v>3762</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9821,7 +9831,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3697</v>
+        <v>3727</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10354</v>
@@ -9830,11 +9840,11 @@
         <v>6372</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9908,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9962,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10016,7 +10026,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10070,7 +10080,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10144,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10198,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10246,7 @@
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10286,7 +10296,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10346,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10380,7 +10390,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10440,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10490,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10540,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10580,7 +10590,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10628,7 +10638,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10682,7 +10692,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10730,7 +10740,7 @@
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10784,7 +10794,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10832,7 +10842,7 @@
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10886,7 +10896,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10940,7 +10950,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -10984,17 +10994,17 @@
         <v>159</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>319</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11038,17 +11048,17 @@
         <v>159</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>319</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11108,11 +11118,11 @@
         <v>319</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11170,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11210,11 +11220,11 @@
         <v>319</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11278,7 +11288,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11322,7 +11332,7 @@
         <v>159</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>319</v>
@@ -11332,7 +11342,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11380,7 +11390,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11424,17 +11434,17 @@
         <v>159</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>319</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11488,7 +11498,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11532,7 +11542,7 @@
         <v>159</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>319</v>
@@ -11542,7 +11552,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11600,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11617,10 +11627,10 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>778</v>
+        <v>906</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11654,7 +11664,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11708,7 +11718,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11769,7 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>6214</v>
+        <v>4460</v>
       </c>
       <c r="M200" s="3" t="n">
         <v>6351</v>
@@ -11768,11 +11778,11 @@
         <v>6372</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11826,7 +11836,7 @@
         <v>5097</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10853</v>
+        <v>10852</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7646</v>
@@ -11836,7 +11846,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11900,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11944,7 @@
         <v>8283</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>278075</v>
+        <v>278074</v>
       </c>
       <c r="N203" s="3" t="n">
         <v>14018</v>
@@ -11944,7 +11954,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -11998,7 +12008,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12052,7 +12062,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12110,7 @@
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12164,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12205,7 @@
         </is>
       </c>
       <c r="L208" s="3" t="n">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="M208" s="3" t="n">
         <v>1593</v>
@@ -12204,11 +12214,11 @@
         <v>319</v>
       </c>
       <c r="O208" s="2" t="n">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12272,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12326,7 +12336,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12390,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12434,7 +12444,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12492,7 @@
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12536,7 +12546,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12590,7 +12600,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12644,7 +12654,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12708,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12752,7 +12762,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12806,7 +12816,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12864,7 @@
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12908,7 +12918,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12982,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13036,7 +13046,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13100,7 +13110,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13154,7 +13164,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13228,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13241,11 +13251,11 @@
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G227" s="3" t="n">
         <v>3186</v>
@@ -13278,11 +13288,11 @@
         <v>6372</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13326,7 +13336,7 @@
         <v>159</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>319</v>
@@ -13336,7 +13346,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13380,7 +13390,7 @@
         <v>159</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>319</v>
@@ -13390,7 +13400,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13444,7 +13454,7 @@
         <v>159</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>319</v>
@@ -13454,7 +13464,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13498,7 +13508,7 @@
         <v>796</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1593</v>
@@ -13508,7 +13518,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13568,11 +13578,11 @@
         <v>3186</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13636,7 +13646,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13700,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13744,7 +13754,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13762,23 +13772,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D236" s="3" t="n">
-        <v>5034</v>
-      </c>
-      <c r="E236" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-14</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G236" s="3" t="n">
-        <v>5034</v>
-      </c>
+      <c r="D236" s="3" t="inlineStr"/>
+      <c r="E236" s="2" t="inlineStr"/>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="3" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I236" s="2" t="n">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13856,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14022,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14073,7 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>21778</v>
+        <v>21672</v>
       </c>
       <c r="M241" s="3" t="n">
         <v>35031</v>
@@ -14086,7 +14086,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14140,7 @@
         <v>53718</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>59021</v>
+        <v>59020</v>
       </c>
       <c r="N242" s="3" t="n">
         <v>76460</v>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14177,10 +14177,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>17461</v>
+        <v>17563</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14197,20 +14197,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17788</v>
+        <v>17678</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31858304</v>
+        <v>31858182</v>
       </c>
       <c r="N243" s="3" t="n">
         <v>31858</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14258,7 +14258,7 @@
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14312,7 +14312,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14339,10 +14339,10 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2328</v>
+        <v>2301</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2034</v>
+        <v>1919</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6372</v>
@@ -14372,11 +14372,11 @@
         <v>2168</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14417,7 +14417,7 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>15642</v>
+        <v>8920</v>
       </c>
       <c r="M247" s="3" t="n">
         <v>23486</v>
@@ -14426,11 +14426,11 @@
         <v>17841</v>
       </c>
       <c r="O247" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14480,11 +14480,11 @@
         <v>17841</v>
       </c>
       <c r="O248" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14654,11 +14654,11 @@
         <v>319</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14709,10 +14709,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50757</v>
+        <v>50756</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50757</v>
+        <v>50756</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6372</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14786,7 +14786,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
         <v>7918</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>191150</v>
+        <v>191149</v>
       </c>
       <c r="N254" s="3" t="n">
         <v>10195</v>
@@ -14850,7 +14850,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14914,7 +14914,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -14972,7 +14972,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15026,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15045,18 +15045,18 @@
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>448</v>
+        <v>319</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15083,14 +15083,14 @@
         <v>970</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>1023</v>
+        <v>957</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G262" s="3" t="n">
         <v>6372</v>
@@ -15342,11 +15342,11 @@
         <v>12743</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15460,11 +15460,11 @@
         <v>3186</v>
       </c>
       <c r="O264" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15572,11 +15572,11 @@
         <v>12743</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15633,14 +15633,14 @@
         <v>19591</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>1671</v>
+        <v>2698</v>
       </c>
       <c r="O267" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15924,7 +15924,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -15978,17 +15978,17 @@
         <v>159</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21097</v>
+        <v>21096</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>319</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16038,11 +16038,11 @@
         <v>319</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16092,11 +16092,11 @@
         <v>319</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16150,17 +16150,17 @@
         <v>159</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>158812</v>
+        <v>158811</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>2015</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16328,7 +16328,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16430,7 +16430,7 @@
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16478,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16590,7 +16590,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16641,20 +16641,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>10171</v>
+        <v>9694</v>
       </c>
       <c r="M285" s="3" t="n">
         <v>15929</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10867</v>
+        <v>10983</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16737,18 +16737,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5193</v>
+        <v>5327</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
         <v>15</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5095</v>
+        <v>5118</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16765,20 +16765,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>5327</v>
+        <v>5287</v>
       </c>
       <c r="M287" s="3" t="n">
         <v>5814</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5599</v>
+        <v>5650</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16797,18 +16797,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6835</v>
+        <v>6795</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6794</v>
+        <v>6785</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16825,20 +16825,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6415</v>
+        <v>6794</v>
       </c>
       <c r="M288" s="3" t="n">
         <v>8699</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7679</v>
+        <v>7318</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16885,10 +16885,10 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9914</v>
+        <v>9217</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>13720</v>
+        <v>11655</v>
       </c>
       <c r="N289" s="3" t="n">
         <v>9559</v>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -16939,7 +16939,7 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>3186</v>
+        <v>2913</v>
       </c>
       <c r="M290" s="3" t="n">
         <v>3186</v>
@@ -16948,11 +16948,11 @@
         <v>1593</v>
       </c>
       <c r="O290" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17003,20 +17003,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>4142</v>
+        <v>3884</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5097</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3457</v>
+        <v>3186</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17067,7 +17067,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4046</v>
+        <v>3394</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>5575</v>
@@ -17076,11 +17076,11 @@
         <v>6372</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17134,7 +17134,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17153,18 +17153,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5379</v>
+        <v>5876</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5765</v>
+        <v>5735</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17185,20 +17185,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>5392</v>
+        <v>5894</v>
       </c>
       <c r="M294" s="3" t="n">
         <v>28481</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6402</v>
+        <v>6360</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51775</v>
+        <v>51774</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>703656</v>
+        <v>703653</v>
       </c>
       <c r="N295" s="3" t="n">
         <v>39823</v>
@@ -17252,7 +17252,7 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17279,7 @@
         </is>
       </c>
       <c r="F296" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G296" s="3" t="n">
         <v>31858</v>
@@ -17312,11 +17312,11 @@
         <v>39823</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17335,18 +17335,18 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63717</v>
+        <v>63716</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F297" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63717</v>
+        <v>63716</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17367,20 +17367,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63717</v>
+        <v>63716</v>
       </c>
       <c r="M297" s="3" t="n">
         <v>127433</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79646</v>
+        <v>79645</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17434,17 +17434,17 @@
         <v>127433</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>127701</v>
+        <v>127700</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>159292</v>
+        <v>159291</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17485,20 +17485,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>254866</v>
+        <v>254865</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>257321</v>
+        <v>257320</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>318583</v>
+        <v>318582</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17517,7 +17517,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>446016</v>
+        <v>446015</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>446016</v>
+        <v>446015</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17549,20 +17549,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>446016</v>
+        <v>446015</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>802259</v>
+        <v>802256</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>637166</v>
+        <v>637164</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17581,18 +17581,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>9550</v>
+        <v>3973</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>10075</v>
+        <v>8152</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17613,20 +17613,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>9408</v>
+        <v>3979</v>
       </c>
       <c r="M301" s="3" t="n">
         <v>32358</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>8261</v>
+        <v>5279</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17645,18 +17645,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>2254</v>
+        <v>2084</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1728</v>
+        <v>1755</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17677,7 +17677,7 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1690</v>
+        <v>1940</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4831</v>
@@ -17686,11 +17686,11 @@
         <v>2230</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17717,10 +17717,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4365</v>
+        <v>4373</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17741,20 +17741,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4723</v>
+        <v>4713</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15928</v>
+        <v>15927</v>
       </c>
       <c r="N303" s="3" t="n">
         <v>4948</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17773,18 +17773,18 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1612</v>
+        <v>2221</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1690</v>
+        <v>1778</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>1115</v>
+        <v>2451</v>
       </c>
       <c r="M304" s="3" t="n">
         <v>15929</v>
@@ -17814,11 +17814,11 @@
         <v>2230</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -17905,14 +17905,14 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>2520</v>
+        <v>2338</v>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
@@ -17942,11 +17942,11 @@
         <v>319</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17716</v>
+        <v>18050</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18010,7 +18010,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18064,17 +18064,17 @@
         <v>2071</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1274332</v>
+        <v>1274327</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3982</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18134,11 +18134,11 @@
         <v>6372</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18202,7 +18202,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>4878</v>
+        <v>4877</v>
       </c>
       <c r="M311" s="3" t="n">
         <v>6079</v>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18314,7 +18314,7 @@
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18374,11 +18374,11 @@
         <v>19115</v>
       </c>
       <c r="O313" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18432,7 +18432,7 @@
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18486,17 +18486,17 @@
         <v>15929</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N315" s="3" t="n">
         <v>31858</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18560,7 +18560,7 @@
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18617,14 +18617,14 @@
         <v>103539</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>207079</v>
+        <v>207078</v>
       </c>
       <c r="O317" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18688,7 +18688,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18752,7 +18752,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18771,18 +18771,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>1782</v>
+        <v>2439</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1591</v>
+        <v>1618</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18803,7 +18803,7 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1115</v>
+        <v>2588</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>9897</v>
@@ -18812,11 +18812,11 @@
         <v>2230</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18867,7 +18867,7 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3625</v>
+        <v>3664</v>
       </c>
       <c r="M321" s="3" t="n">
         <v>9701</v>
@@ -18876,11 +18876,11 @@
         <v>319</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18944,7 +18944,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -18995,20 +18995,20 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>11150</v>
+        <v>9414</v>
       </c>
       <c r="M323" s="3" t="n">
         <v>16619</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>3017</v>
+        <v>4199</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19026,13 +19026,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D324" s="3" t="inlineStr"/>
-      <c r="E324" s="2" t="inlineStr"/>
-      <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="3" t="inlineStr"/>
+      <c r="D324" s="3" t="n">
+        <v>319</v>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G324" s="3" t="n">
+        <v>319</v>
+      </c>
       <c r="H324" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I324" s="2" t="n">
@@ -19055,14 +19065,14 @@
         <v>5633</v>
       </c>
       <c r="N324" s="3" t="n">
-        <v>319</v>
+        <v>350</v>
       </c>
       <c r="O324" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19119,14 +19129,14 @@
         <v>15821</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19145,18 +19155,18 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>3949</v>
+        <v>3186</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>1873</v>
+        <v>2037</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19183,14 +19193,14 @@
         <v>19115</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>4342</v>
+        <v>3923</v>
       </c>
       <c r="O326" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19251,7 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>3154</v>
+        <v>2899</v>
       </c>
       <c r="M327" s="3" t="n">
         <v>4801</v>
@@ -19250,11 +19260,11 @@
         <v>3775</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19273,7 +19283,7 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>20601</v>
+        <v>23097</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
@@ -19281,10 +19291,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22683</v>
+        <v>22700</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19305,20 +19315,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>23097</v>
+        <v>22313</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32832</v>
+        <v>32831</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>24748</v>
+        <v>24841</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19337,18 +19347,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7487</v>
+        <v>7407</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>6843</v>
+        <v>6870</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19369,20 +19379,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7487</v>
+        <v>6794</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9838</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7651</v>
+        <v>7984</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19401,18 +19411,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6053</v>
+        <v>5762</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
         <v>32</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5606</v>
+        <v>5600</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19433,20 +19443,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5763</v>
+        <v>5432</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8716</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>5832</v>
+        <v>5926</v>
       </c>
       <c r="O330" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19510,7 +19520,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19537,10 +19547,10 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19570,11 +19580,11 @@
         <v>1078</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19634,11 +19644,11 @@
         <v>319</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19657,18 +19667,18 @@
         </is>
       </c>
       <c r="D334" s="3" t="n">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
         <v>9</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19695,14 +19705,14 @@
         <v>15929</v>
       </c>
       <c r="N334" s="3" t="n">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="O334" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19721,18 +19731,18 @@
         </is>
       </c>
       <c r="D335" s="3" t="n">
-        <v>2401</v>
+        <v>2875</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1910</v>
+        <v>1892</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19753,20 +19763,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1115</v>
+        <v>2619</v>
       </c>
       <c r="M335" s="3" t="n">
         <v>15443</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2520</v>
+        <v>2343</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19789,11 +19799,11 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>163</v>
@@ -19826,11 +19836,11 @@
         <v>319</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19890,11 +19900,11 @@
         <v>319</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>492</v>
+        <v>526</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -19954,11 +19964,11 @@
         <v>319</v>
       </c>
       <c r="O338" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20018,11 +20028,11 @@
         <v>319</v>
       </c>
       <c r="O339" s="2" t="n">
-        <v>481</v>
+        <v>581</v>
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20096,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20105,15 +20115,15 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>586</v>
+        <v>667</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G341" s="3" t="n">
         <v>663</v>
@@ -20137,20 +20147,20 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2450</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>644</v>
+        <v>733</v>
       </c>
       <c r="O341" s="2" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20214,7 +20224,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20271,14 +20281,14 @@
         <v>2450</v>
       </c>
       <c r="N343" s="3" t="n">
-        <v>663</v>
+        <v>319</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20297,18 +20307,18 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>1939</v>
+        <v>1599</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20329,7 +20339,7 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>1599</v>
+        <v>2428</v>
       </c>
       <c r="M344" s="3" t="n">
         <v>17135</v>
@@ -20342,7 +20352,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20365,11 +20375,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2071</v>
@@ -20396,7 +20406,7 @@
         <v>2071</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1592915</v>
+        <v>1592909</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>3982</v>
@@ -20406,7 +20416,7 @@
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20425,18 +20435,18 @@
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>3186</v>
+        <v>4164</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F346" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>3186</v>
+        <v>3675</v>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
@@ -20456,21 +20466,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L346" s="3" t="n">
-        <v>4164</v>
-      </c>
-      <c r="M346" s="3" t="n">
-        <v>4164</v>
-      </c>
+      <c r="L346" s="3" t="inlineStr"/>
+      <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
         <v>4779</v>
       </c>
-      <c r="O346" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20530,11 +20534,11 @@
         <v>6372</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20588,7 +20592,7 @@
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20648,11 +20652,11 @@
         <v>19115</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20710,7 +20714,7 @@
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20729,18 +20733,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16977</v>
+        <v>15932</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16407</v>
+        <v>16393</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20774,7 +20778,7 @@
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20832,7 +20836,7 @@
       <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20862,7 +20866,7 @@
         <v>3</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>133409</v>
+        <v>133408</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20885,12 +20889,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>207079</v>
+        <v>207078</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -20954,7 +20958,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21014,11 +21018,11 @@
         <v>17841</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21078,11 +21082,11 @@
         <v>17841</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21133,7 +21137,7 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>919</v>
+        <v>534</v>
       </c>
       <c r="M357" s="3" t="n">
         <v>15929</v>
@@ -21146,7 +21150,7 @@
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -21176,7 +21180,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>159.291518</v>
+        <v>159.290909</v>
       </c>
     </row>
     <row r="2">
@@ -21187,7 +21191,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Tue, 11 Aug 2026 23:57:32 +0000)</t>
+          <t>open.er-api.com (取得日時: Thu, 13 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21199,7 +21203,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4220</v>
+        <v>3185</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3532</v>
+        <v>3554</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         <v>3185</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -673,17 +673,17 @@
         <v>6369</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>97343</v>
+        <v>97336</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>35</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23886</v>
+        <v>23884</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23886</v>
+        <v>23884</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -800,12 +800,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47771</v>
+        <v>47768</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43528</v>
+        <v>43525</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -856,20 +856,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>47137</v>
+        <v>47134</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85988</v>
+        <v>85982</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -920,20 +920,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>143313</v>
+        <v>143303</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>254779</v>
+        <v>254761</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>358284</v>
+        <v>358258</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>358284</v>
+        <v>358258</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -984,20 +984,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>358284</v>
+        <v>358258</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>358284</v>
+        <v>358258</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>716567</v>
+        <v>716516</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1016,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5452</v>
+        <v>5603</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5683</v>
+        <v>5666</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1048,20 +1048,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5627</v>
+        <v>5605</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8758</v>
+        <v>8757</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>123</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1080,18 +1080,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8454</v>
+        <v>7786</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8376</v>
+        <v>8366</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1112,20 +1112,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8355</v>
+        <v>8149</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>151234</v>
+        <v>151223</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17516</v>
+        <v>17515</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14019</v>
+        <v>14018</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1176,20 +1176,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42754</v>
+        <v>42751</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35032</v>
+        <v>35030</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39808</v>
+        <v>39805</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1284,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94617</v>
+        <v>94610</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94617</v>
+        <v>94610</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17634</v>
+        <v>17633</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>17634</v>
+        <v>17633</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1348,20 +1348,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1592372</v>
+        <v>318452</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>19397</v>
+        <v>15923</v>
       </c>
       <c r="O14" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34518</v>
+        <v>34515</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64509</v>
+        <v>64504</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5414</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14712</v>
+        <v>14711</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64509</v>
+        <v>64504</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>5414</v>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
         <v>796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1592</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         <v>1592</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>229316</v>
+        <v>229300</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3185</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1631,17 +1631,17 @@
         <v>3185</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>270703</v>
+        <v>270684</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1692,20 +1692,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11465</v>
+        <v>11464</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11147</v>
+        <v>11146</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37214</v>
+        <v>37211</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1800,20 +1800,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21497</v>
+        <v>21495</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>140559</v>
+        <v>140549</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1864,20 +1864,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>323787</v>
+        <v>323763</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79619</v>
+        <v>79613</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
         <v>1938</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>318</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
         <v>1417</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1459</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2060,7 @@
         <v>1274</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2548</v>
@@ -2070,7 +2070,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2089,18 +2089,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1164</v>
+        <v>1358</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>18</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1093</v>
+        <v>1118</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2121,20 +2121,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1358</v>
+        <v>1369</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1588142</v>
+        <v>1588029</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1653</v>
+        <v>1592</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>24</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2188,17 +2188,17 @@
         <v>1592</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2252,17 +2252,17 @@
         <v>3185</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17156</v>
+        <v>17155</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>637</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1274</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2345,18 +2345,18 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2389</v>
+        <v>2388</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>11616</v>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2409,18 +2409,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1075</v>
+        <v>1175</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1027</v>
+        <v>1051</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2441,20 +2441,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1175</v>
+        <v>1487</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>636949</v>
+        <v>636903</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
         <v>2912</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12900</v>
+        <v>12899</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3185</v>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3389</v>
+        <v>3388</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>3317</v>
@@ -2569,20 +2569,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3586</v>
+        <v>3185</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21285</v>
+        <v>21284</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6373</v>
+        <v>6372</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2636,17 +2636,17 @@
         <v>6369</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30779</v>
+        <v>30777</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2692,11 +2692,11 @@
         <v>1592</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
         <v>1903</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4185</v>
+        <v>4184</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3185</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2779,11 +2779,11 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>3185</v>
@@ -2806,17 +2806,17 @@
         <v>3185</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>318474</v>
+        <v>318452</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v>1592</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>145777</v>
+        <v>145766</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3185</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4803</v>
+        <v>4802</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2931,20 +2931,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4890</v>
+        <v>3185</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17518</v>
+        <v>17516</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6369</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -2998,17 +2998,17 @@
         <v>6369</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15234</v>
+        <v>15233</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O41" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>6369</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8949</v>
+        <v>8948</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>3981</v>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3147,18 +3147,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8854</v>
+        <v>8928</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9405</v>
+        <v>9335</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3175,20 +3175,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9170</v>
+        <v>9181</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>9720</v>
+        <v>9719</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>9863</v>
+        <v>9733</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3242,17 @@
         <v>1592</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8779</v>
+        <v>8778</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>3185</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>6369</v>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
         <v>3</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>3185</v>
+        <v>3105</v>
       </c>
       <c r="M49" s="3" t="n">
         <v>6369</v>
@@ -3504,11 +3504,11 @@
         <v>3185</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>3435</v>
+        <v>2522</v>
       </c>
       <c r="M51" s="3" t="n">
         <v>4393</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3646,13 +3646,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="3" t="inlineStr"/>
+      <c r="D52" s="3" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>2892</v>
+      </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -3668,7 +3678,7 @@
         <v>6369</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3185</v>
@@ -3678,7 +3688,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3752,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3806,7 @@
         <v>1799</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11371</v>
+        <v>11370</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1592</v>
@@ -3806,7 +3816,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3857,20 +3867,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>4777</v>
+        <v>2892</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30801</v>
+        <v>30799</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3921,20 +3931,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>6268</v>
+        <v>5821</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>6268</v>
+        <v>5821</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6787</v>
+        <v>6786</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -3953,18 +3963,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9819</v>
+        <v>8941</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>40</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>10552</v>
+        <v>10346</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3985,20 +3995,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9804</v>
+        <v>9211</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30841</v>
+        <v>30839</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4017,18 +4027,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3893</v>
+        <v>3876</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>29</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3829</v>
+        <v>3841</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4049,20 +4059,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3879</v>
+        <v>3877</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10395</v>
+        <v>10394</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4244</v>
+        <v>4245</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4089,10 +4099,10 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>3174</v>
+        <v>2909</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4126,7 +4136,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4190,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4221,20 +4231,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3486</v>
+        <v>3485</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4287,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9873</v>
+        <v>9872</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4301,7 +4311,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4312,7 +4322,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4333,20 +4343,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>17976</v>
+        <v>17975</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4399,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4447,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4483,20 +4493,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50956</v>
+        <v>50952</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4540,17 +4550,17 @@
         <v>8917</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4603,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22293</v>
+        <v>22292</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4662,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4716,7 @@
         <v>637</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5072</v>
+        <v>5071</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3185</v>
@@ -4716,7 +4726,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4780,7 @@
         <v>4430</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>5064</v>
+        <v>5063</v>
       </c>
       <c r="N71" s="3" t="n">
         <v>6369</v>
@@ -4780,7 +4790,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4844,17 @@
         <v>2548</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1493712</v>
+        <v>1493605</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11465</v>
+        <v>11464</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4908,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4939,20 +4949,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8758</v>
+        <v>8757</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21097</v>
+        <v>21096</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17516</v>
+        <v>17515</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -4993,20 +5003,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17516</v>
+        <v>17515</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27233</v>
+        <v>27231</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5080,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5134,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5182,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5213,10 +5223,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2548</v>
@@ -5226,7 +5236,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5279,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5315,20 +5325,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23290</v>
+        <v>23288</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23290</v>
+        <v>23288</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5381,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20382</v>
+        <v>20381</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5403,10 +5413,10 @@
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5426,7 +5436,7 @@
         <v>232</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1592213</v>
+        <v>1592099</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>796</v>
@@ -5436,7 +5446,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5496,7 @@
         <v>939</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34809</v>
+        <v>34807</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1592</v>
@@ -5496,7 +5506,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5533,7 +5543,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="n">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="M85" s="3" t="n">
         <v>3175</v>
@@ -5546,7 +5556,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5593,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="3" t="n">
-        <v>2425</v>
+        <v>1274</v>
       </c>
       <c r="M86" s="3" t="n">
         <v>6369</v>
@@ -5596,7 +5606,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5635,12 +5645,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5683,14 +5693,14 @@
         <v>3185</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5739,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17516</v>
+        <v>17515</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5761,10 +5771,10 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5784,7 +5794,7 @@
         <v>498</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86542</v>
+        <v>86536</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>796</v>
@@ -5794,7 +5804,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5854,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5914,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5958,7 @@
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -5987,12 +5997,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6041,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6085,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17516</v>
+        <v>17515</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6144,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6181,14 +6191,14 @@
         <v>2070</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6232,17 +6242,17 @@
         <v>4750</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5212</v>
+        <v>5211</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9873</v>
+        <v>9872</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6283,20 +6293,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6339,12 +6349,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6385,20 +6395,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18091</v>
+        <v>18090</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18091</v>
+        <v>18090</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6451,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50956</v>
+        <v>50952</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6510,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6553,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6601,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9873</v>
+        <v>9872</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6614,13 +6624,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="2" t="inlineStr"/>
-      <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
+      <c r="D107" s="3" t="n">
+        <v>7165</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>7165</v>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
@@ -6636,21 +6656,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L107" s="3" t="n">
-        <v>7166</v>
-      </c>
-      <c r="M107" s="3" t="n">
-        <v>7166</v>
-      </c>
+      <c r="L107" s="3" t="inlineStr"/>
+      <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>19108</v>
-      </c>
-      <c r="O107" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>19107</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6693,12 +6707,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6741,12 +6755,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6789,12 +6803,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50956</v>
+        <v>50952</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6837,12 +6851,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79619</v>
+        <v>79613</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6883,20 +6897,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87580</v>
+        <v>87574</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>111466</v>
+        <v>111458</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>111466</v>
+        <v>111458</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6937,20 +6951,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>111466</v>
+        <v>111458</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>111466</v>
+        <v>111458</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>143313</v>
+        <v>143303</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -6991,20 +7005,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="O114" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7045,20 +7059,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>191085</v>
+        <v>191071</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7099,20 +7113,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>214970</v>
+        <v>214955</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>254779</v>
+        <v>254761</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>254779</v>
+        <v>254761</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7180,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7207,10 +7221,10 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5889</v>
+        <v>5888</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>3981</v>
@@ -7220,7 +7234,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7263,12 +7277,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7309,20 +7323,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7379,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22930</v>
+        <v>22929</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7411,20 +7425,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19147</v>
+        <v>19145</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7465,20 +7479,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41341</v>
+        <v>41338</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7532,7 +7546,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7587,7 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>5718</v>
@@ -7586,7 +7600,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7633,14 +7647,14 @@
         <v>6503</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7681,20 +7695,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M127" s="3" t="n">
         <v>11963</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7737,12 +7751,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22930</v>
+        <v>22929</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7783,20 +7797,20 @@
         </is>
       </c>
       <c r="L129" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O129" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7858,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7906,7 @@
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -7949,14 +7963,14 @@
         <v>6369</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8024,17 @@
         <v>9554</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16011</v>
+        <v>16010</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8077,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8109,20 +8123,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21497</v>
+        <v>21495</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21497</v>
+        <v>21495</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47771</v>
+        <v>47768</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8140,13 +8154,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr"/>
-      <c r="E136" s="2" t="inlineStr"/>
-      <c r="F136" s="2" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="n">
+        <v>28661</v>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>28661</v>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
@@ -8163,20 +8187,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71657</v>
+        <v>71652</v>
       </c>
       <c r="O136" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8217,20 +8241,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8281,20 +8305,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6369</v>
+        <v>6824</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12830</v>
+        <v>12829</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8345,20 +8369,20 @@
         </is>
       </c>
       <c r="L139" s="3" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="N139" s="3" t="n">
-        <v>1164</v>
+        <v>318</v>
       </c>
       <c r="O139" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8377,18 +8401,18 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>314</v>
+        <v>562</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8409,20 +8433,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5199</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>346</v>
+        <v>436</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8479,14 +8503,14 @@
         <v>1592</v>
       </c>
       <c r="N141" s="3" t="n">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="O141" s="2" t="n">
         <v>239</v>
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8537,7 +8561,7 @@
         </is>
       </c>
       <c r="L142" s="3" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="M142" s="3" t="n">
         <v>1592</v>
@@ -8550,7 +8574,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8638,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8644,7 +8668,7 @@
         <v>3</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8668,7 +8692,7 @@
         <v>2158</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10809</v>
+        <v>10808</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>3981</v>
@@ -8678,7 +8702,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8726,7 +8750,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8769,7 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
@@ -8756,7 +8780,7 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
@@ -8777,10 +8801,10 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53851</v>
+        <v>53847</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6369</v>
@@ -8790,7 +8814,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8833,12 +8857,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8882,17 +8906,17 @@
         <v>9554</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17449</v>
+        <v>17448</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8959,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -8959,18 +8983,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8991,20 +9015,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9047,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9034,7 +9058,7 @@
         <v>13</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9055,20 +9079,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>84619</v>
+        <v>84613</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>76434</v>
+        <v>76428</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9109,20 +9133,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>207008</v>
+        <v>206994</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9145,11 +9169,11 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>159</v>
@@ -9182,11 +9206,11 @@
         <v>318</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9274,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9300,7 +9324,7 @@
         <v>796</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15602</v>
+        <v>15601</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1592</v>
@@ -9310,7 +9334,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9384,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9420,7 +9444,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9488,7 @@
         <v>796</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19467</v>
+        <v>19465</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1592</v>
@@ -9474,7 +9498,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9542,7 @@
         <v>1592</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19311</v>
+        <v>19309</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3185</v>
@@ -9528,7 +9552,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9572,7 +9596,7 @@
         <v>3185</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6661</v>
+        <v>6660</v>
       </c>
       <c r="N160" s="3" t="n">
         <v>6369</v>
@@ -9582,7 +9606,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9660,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9690,7 +9714,7 @@
         <v>1927</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30382</v>
+        <v>30380</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1796</v>
@@ -9700,7 +9724,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9719,7 +9743,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9751,10 +9775,10 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3822</v>
+        <v>3821</v>
       </c>
       <c r="N163" s="3" t="n">
         <v>3447</v>
@@ -9764,7 +9788,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9783,18 +9807,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3814</v>
+        <v>4606</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3779</v>
+        <v>3796</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9815,7 +9839,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3901</v>
+        <v>4633</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10350</v>
@@ -9824,11 +9848,11 @@
         <v>6369</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9916,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9946,7 +9970,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -9965,18 +9989,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>725</v>
+        <v>637</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1076</v>
+        <v>930</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -10000,7 +10024,7 @@
         <v>1409</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9787</v>
+        <v>9786</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1274</v>
@@ -10010,7 +10034,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10088,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10118,17 +10142,17 @@
         <v>314</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N169" s="3" t="n">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="O169" s="2" t="n">
         <v>49</v>
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10169,20 +10193,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>95542</v>
+        <v>95536</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>95542</v>
+        <v>95536</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10225,12 +10249,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10304,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10298,13 +10322,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D173" s="3" t="inlineStr"/>
-      <c r="E173" s="2" t="inlineStr"/>
-      <c r="F173" s="2" t="inlineStr"/>
-      <c r="G173" s="3" t="inlineStr"/>
+      <c r="D173" s="3" t="n">
+        <v>2070</v>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>2070</v>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
@@ -10317,7 +10351,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>2070</v>
+        <v>3344</v>
       </c>
       <c r="M173" s="3" t="n">
         <v>3920</v>
@@ -10326,11 +10360,11 @@
         <v>3981</v>
       </c>
       <c r="O173" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10369,12 +10403,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10411,20 +10445,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14301</v>
+        <v>14300</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10461,20 +10495,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11465</v>
+        <v>11464</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11465</v>
+        <v>11464</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22930</v>
+        <v>22929</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10511,20 +10545,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16003</v>
+        <v>16002</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10561,20 +10595,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19605</v>
+        <v>19604</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10656,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10710,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10719,12 +10753,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10771,14 +10805,14 @@
         <v>9554</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10821,12 +10855,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10867,20 +10901,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21497</v>
+        <v>21495</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21497</v>
+        <v>21495</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42994</v>
+        <v>42991</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10921,20 +10955,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28663</v>
+        <v>28661</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>57325</v>
+        <v>57321</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -10978,7 +11012,7 @@
         <v>159</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>318</v>
@@ -10988,7 +11022,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11032,17 +11066,17 @@
         <v>159</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11096,17 +11130,17 @@
         <v>159</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>103603</v>
+        <v>103596</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11154,7 +11188,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11198,17 +11232,17 @@
         <v>159</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29370</v>
+        <v>29368</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11262,17 +11296,17 @@
         <v>159</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>157220</v>
+        <v>157208</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11316,17 +11350,17 @@
         <v>159</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11408,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11418,17 +11452,17 @@
         <v>159</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11506,7 @@
         <v>159</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>159078</v>
+        <v>159067</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>318</v>
@@ -11482,7 +11516,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11526,17 +11560,17 @@
         <v>159</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11618,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11672,7 @@
         <v>1169</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>318</v>
@@ -11648,7 +11682,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11689,20 +11723,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20736</v>
+        <v>20734</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20736</v>
+        <v>20734</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11721,7 +11755,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -11732,7 +11766,7 @@
         <v>2</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -11753,10 +11787,10 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6349</v>
+        <v>6348</v>
       </c>
       <c r="N200" s="3" t="n">
         <v>6369</v>
@@ -11766,7 +11800,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11819,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -11796,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -11817,10 +11851,10 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10849</v>
+        <v>10848</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7643</v>
@@ -11830,7 +11864,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11877,14 +11911,14 @@
         <v>10420</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11928,17 +11962,17 @@
         <v>8280</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>277980</v>
+        <v>277961</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -11979,20 +12013,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15734</v>
+        <v>15733</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16150</v>
+        <v>16149</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12033,20 +12067,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20382</v>
+        <v>20381</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>49123</v>
+        <v>49120</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12089,12 +12123,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22930</v>
+        <v>22929</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12192,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12246,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12300,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12320,7 +12354,7 @@
         <v>2070</v>
       </c>
       <c r="M210" s="3" t="n">
-        <v>4502</v>
+        <v>4501</v>
       </c>
       <c r="N210" s="3" t="n">
         <v>4140</v>
@@ -12330,7 +12364,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12374,17 +12408,17 @@
         <v>3981</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="O211" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12425,20 +12459,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12481,12 +12515,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22930</v>
+        <v>22929</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12527,20 +12561,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12594,7 +12628,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12638,7 +12672,7 @@
         <v>2070</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11957</v>
+        <v>11956</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4140</v>
@@ -12648,7 +12682,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12667,7 +12701,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12678,7 +12712,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12699,20 +12733,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15678</v>
+        <v>15677</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37723</v>
+        <v>37721</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12756,17 +12790,17 @@
         <v>3981</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>6804</v>
+        <v>6793</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12807,20 +12841,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7166</v>
+        <v>7165</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14331</v>
+        <v>14330</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12863,12 +12897,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12909,20 +12943,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -12986,7 +13020,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13009,11 +13043,11 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>1592</v>
@@ -13046,11 +13080,11 @@
         <v>3185</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13138,7 @@
         <v>3185</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7247</v>
+        <v>7246</v>
       </c>
       <c r="N224" s="3" t="n">
         <v>6369</v>
@@ -13114,7 +13148,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13168,7 +13202,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13253,7 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="M226" s="3" t="n">
         <v>3498</v>
@@ -13232,7 +13266,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13330,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13340,17 +13374,17 @@
         <v>159</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13394,17 +13428,17 @@
         <v>159</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13492,7 @@
         <v>159</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>318</v>
@@ -13468,7 +13502,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13512,17 +13546,17 @@
         <v>796</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13586,7 +13620,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13604,23 +13638,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D233" s="3" t="n">
-        <v>3185</v>
-      </c>
-      <c r="E233" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F233" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G233" s="3" t="n">
-        <v>3185</v>
-      </c>
+      <c r="D233" s="3" t="inlineStr"/>
+      <c r="E233" s="2" t="inlineStr"/>
+      <c r="F233" s="2" t="inlineStr"/>
+      <c r="G233" s="3" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I233" s="2" t="n">
@@ -13640,7 +13664,7 @@
         <v>3185</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7255</v>
+        <v>7254</v>
       </c>
       <c r="N233" s="3" t="n">
         <v>6369</v>
@@ -13650,7 +13674,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13668,13 +13692,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D234" s="3" t="inlineStr"/>
-      <c r="E234" s="2" t="inlineStr"/>
-      <c r="F234" s="2" t="inlineStr"/>
-      <c r="G234" s="3" t="inlineStr"/>
+      <c r="D234" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G234" s="3" t="n">
+        <v>237</v>
+      </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I234" s="2" t="n">
@@ -13691,7 +13725,7 @@
         </is>
       </c>
       <c r="L234" s="3" t="n">
-        <v>237</v>
+        <v>377</v>
       </c>
       <c r="M234" s="3" t="n">
         <v>412</v>
@@ -13700,11 +13734,11 @@
         <v>318</v>
       </c>
       <c r="O234" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13745,7 +13779,7 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>2717</v>
+        <v>2716</v>
       </c>
       <c r="M235" s="3" t="n">
         <v>4291</v>
@@ -13758,7 +13792,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13802,7 +13836,7 @@
         <v>3981</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6567</v>
+        <v>6566</v>
       </c>
       <c r="N236" s="3" t="n">
         <v>3981</v>
@@ -13812,7 +13846,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13894,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13879,7 +13913,7 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -13890,7 +13924,7 @@
         <v>2</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
@@ -13911,7 +13945,7 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>4459</v>
+        <v>8757</v>
       </c>
       <c r="M238" s="3" t="n">
         <v>11100</v>
@@ -13920,11 +13954,11 @@
         <v>6369</v>
       </c>
       <c r="O238" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -13967,12 +14001,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14013,20 +14047,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10548</v>
+        <v>10547</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10548</v>
+        <v>10547</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14045,7 +14079,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>23042</v>
+        <v>23040</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14056,7 +14090,7 @@
         <v>7</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>21413</v>
+        <v>21412</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14077,20 +14111,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>20279</v>
+        <v>20276</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>35019</v>
+        <v>35017</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14143,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14120,7 +14154,7 @@
         <v>3</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38243</v>
+        <v>38241</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14141,20 +14175,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>53700</v>
+        <v>53696</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>59001</v>
+        <v>58996</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>76434</v>
+        <v>76428</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14207,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>16158</v>
+        <v>16157</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14181,10 +14215,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>17715</v>
+        <v>17521</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14201,20 +14235,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17671</v>
+        <v>17666</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31847436</v>
+        <v>31845169</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14257,12 +14291,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14350,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14369,7 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
@@ -14367,7 +14401,7 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2131</v>
+        <v>2025</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6369</v>
@@ -14380,7 +14414,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14424,17 +14458,17 @@
         <v>8917</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23478</v>
+        <v>23476</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17835</v>
+        <v>17833</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14481,14 +14515,14 @@
         <v>8917</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>17835</v>
+        <v>17833</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14538,7 +14572,7 @@
         <v>796</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9349</v>
+        <v>9348</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1592</v>
@@ -14548,7 +14582,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14585,20 +14619,20 @@
       </c>
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="3" t="n">
-        <v>2154</v>
+        <v>2380</v>
       </c>
       <c r="M250" s="3" t="n">
-        <v>2381</v>
+        <v>2380</v>
       </c>
       <c r="N250" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O250" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14617,7 +14651,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>31503</v>
+        <v>31501</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -14628,7 +14662,7 @@
         <v>1</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>31503</v>
+        <v>31501</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -14652,17 +14686,17 @@
         <v>159</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97917</v>
+        <v>97910</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14681,7 +14715,7 @@
         </is>
       </c>
       <c r="D252" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
@@ -14692,7 +14726,7 @@
         <v>1</v>
       </c>
       <c r="G252" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
@@ -14713,10 +14747,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50739</v>
+        <v>50736</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50739</v>
+        <v>50736</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6369</v>
@@ -14726,7 +14760,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14756,7 +14790,7 @@
         <v>2</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>5901</v>
+        <v>5900</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14777,7 +14811,7 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>5147</v>
+        <v>5146</v>
       </c>
       <c r="M253" s="3" t="n">
         <v>7592</v>
@@ -14790,7 +14824,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14808,23 +14842,13 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D254" s="3" t="n">
-        <v>6728</v>
-      </c>
-      <c r="E254" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G254" s="3" t="n">
-        <v>6728</v>
-      </c>
+      <c r="D254" s="3" t="inlineStr"/>
+      <c r="E254" s="2" t="inlineStr"/>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="3" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I254" s="2" t="n">
@@ -14841,20 +14865,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>7916</v>
+        <v>7915</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>191085</v>
+        <v>191071</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14872,23 +14896,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D255" s="3" t="n">
-        <v>1432</v>
-      </c>
-      <c r="E255" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G255" s="3" t="n">
-        <v>1432</v>
-      </c>
+      <c r="D255" s="3" t="inlineStr"/>
+      <c r="E255" s="2" t="inlineStr"/>
+      <c r="F255" s="2" t="inlineStr"/>
+      <c r="G255" s="3" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I255" s="2" t="n">
@@ -14905,7 +14919,7 @@
         </is>
       </c>
       <c r="L255" s="3" t="n">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="M255" s="3" t="n">
         <v>1592</v>
@@ -14918,7 +14932,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14990,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15034,7 @@
         <v>293</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7962</v>
+        <v>7961</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>318</v>
@@ -15030,7 +15044,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15053,14 +15067,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>873</v>
+        <v>992</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15087,14 +15101,14 @@
         <v>970</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>909</v>
+        <v>1146</v>
       </c>
       <c r="O258" s="2" t="n">
         <v>113</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15162,7 @@
         <v>1226</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21534</v>
+        <v>21532</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1592</v>
@@ -15158,7 +15172,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15185,10 +15199,10 @@
         </is>
       </c>
       <c r="F260" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G260" s="3" t="n">
-        <v>2102</v>
+        <v>2003</v>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
@@ -15222,7 +15236,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15290,7 @@
         <v>3185</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7064</v>
+        <v>7063</v>
       </c>
       <c r="N261" s="3" t="n">
         <v>6369</v>
@@ -15286,7 +15300,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15309,11 +15323,11 @@
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G262" s="3" t="n">
         <v>6369</v>
@@ -15340,17 +15354,17 @@
         <v>6369</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15408,7 @@
         <v>796</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10634</v>
+        <v>10633</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1592</v>
@@ -15404,7 +15418,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15482,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15530,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15570,17 +15584,17 @@
         <v>6369</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9704</v>
+        <v>9703</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15599,18 +15613,18 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2647</v>
+        <v>2723</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1712</v>
+        <v>1856</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15631,20 +15645,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2723</v>
+        <v>1842</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19585</v>
+        <v>19583</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2804</v>
+        <v>2952</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15698,17 +15712,17 @@
         <v>8280</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14344</v>
+        <v>14343</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15751,12 +15765,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15797,20 +15811,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>19593</v>
+        <v>19591</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25073</v>
+        <v>25072</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15843,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>20382</v>
+        <v>20381</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15840,7 +15854,7 @@
         <v>1</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>20382</v>
+        <v>20381</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15861,20 +15875,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24787</v>
+        <v>24785</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>38597</v>
+        <v>38595</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15924,11 +15938,11 @@
         <v>318</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -15982,17 +15996,17 @@
         <v>159</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21089</v>
+        <v>21088</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16036,7 +16050,7 @@
         <v>159</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31953</v>
+        <v>31950</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>318</v>
@@ -16046,7 +16060,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16090,17 +16104,17 @@
         <v>159</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16003</v>
+        <v>16002</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16144,7 @@
         <v>5</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>15091</v>
+        <v>15090</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16154,17 +16168,17 @@
         <v>159</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>158758</v>
+        <v>158747</v>
       </c>
       <c r="N276" s="3" t="n">
-        <v>2440</v>
+        <v>2439</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16220,11 +16234,11 @@
         <v>1592</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16265,10 +16279,10 @@
         </is>
       </c>
       <c r="L278" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>8591</v>
+        <v>8590</v>
       </c>
       <c r="N278" s="3" t="n">
         <v>6369</v>
@@ -16278,7 +16292,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16333,7 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="M279" s="3" t="n">
         <v>9963</v>
@@ -16332,7 +16346,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16376,17 +16390,17 @@
         <v>6369</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8666</v>
+        <v>8665</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10191</v>
+        <v>10190</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16429,12 +16443,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14013</v>
+        <v>14012</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16477,12 +16491,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16525,12 +16539,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16571,20 +16585,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>33440</v>
+        <v>33437</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33953</v>
+        <v>33950</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16603,18 +16617,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>10183</v>
+        <v>9323</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9955</v>
+        <v>9918</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16635,20 +16649,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>9323</v>
+        <v>9546</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10427</v>
+        <v>10391</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16712,7 +16726,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16731,18 +16745,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>5325</v>
+        <v>4366</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5107</v>
+        <v>5039</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16759,20 +16773,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>4803</v>
+        <v>4799</v>
       </c>
       <c r="M287" s="3" t="n">
         <v>5812</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5768</v>
+        <v>5517</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16791,18 +16805,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6791</v>
+        <v>6283</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6806</v>
+        <v>6792</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16819,20 +16833,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6288</v>
+        <v>6856</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8696</v>
+        <v>8695</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7341</v>
+        <v>7156</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16851,18 +16865,18 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>8938</v>
+        <v>8734</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F289" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9352</v>
+        <v>9290</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16879,20 +16893,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9123</v>
+        <v>9122</v>
       </c>
       <c r="M289" s="3" t="n">
         <v>11651</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>9741</v>
+        <v>9706</v>
       </c>
       <c r="O289" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16946,7 +16960,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -16973,10 +16987,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2761</v>
+        <v>2796</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -17000,7 +17014,7 @@
         <v>4140</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>5096</v>
+        <v>5095</v>
       </c>
       <c r="N291" s="3" t="n">
         <v>4269</v>
@@ -17010,7 +17024,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17061,7 +17075,7 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>4043</v>
+        <v>3880</v>
       </c>
       <c r="M292" s="3" t="n">
         <v>5573</v>
@@ -17070,11 +17084,11 @@
         <v>6369</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17142,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17147,18 +17161,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>5844</v>
+        <v>6113</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5731</v>
+        <v>5719</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17179,20 +17193,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6303</v>
+        <v>6302</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>28472</v>
+        <v>28470</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6362</v>
+        <v>6385</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17233,20 +17247,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51757</v>
+        <v>51753</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>703416</v>
+        <v>703366</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17265,18 +17279,18 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F296" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17297,20 +17311,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>69235</v>
+        <v>69230</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39809</v>
+        <v>39806</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17329,7 +17343,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63695</v>
+        <v>63690</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17340,7 +17354,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63695</v>
+        <v>63690</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17361,20 +17375,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63695</v>
+        <v>63690</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79619</v>
+        <v>79613</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17407,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17404,7 +17418,7 @@
         <v>2</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17425,20 +17439,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>127390</v>
+        <v>127381</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>127657</v>
+        <v>127648</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>159237</v>
+        <v>159226</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17456,13 +17470,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D299" s="3" t="inlineStr"/>
-      <c r="E299" s="2" t="inlineStr"/>
-      <c r="F299" s="2" t="inlineStr"/>
-      <c r="G299" s="3" t="inlineStr"/>
+      <c r="D299" s="3" t="n">
+        <v>254761</v>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G299" s="3" t="n">
+        <v>254761</v>
+      </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I299" s="2" t="n">
@@ -17479,20 +17503,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>254779</v>
+        <v>254761</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>257233</v>
+        <v>257215</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>318474</v>
+        <v>318452</v>
       </c>
       <c r="O299" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17535,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>445864</v>
+        <v>445832</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17522,7 +17546,7 @@
         <v>5</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>445864</v>
+        <v>445832</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17543,20 +17567,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>445864</v>
+        <v>445832</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>801985</v>
+        <v>949301</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>636949</v>
+        <v>636903</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17575,18 +17599,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3809</v>
+        <v>4170</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>5834</v>
+        <v>5504</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17607,20 +17631,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>3492</v>
+        <v>3105</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>32347</v>
+        <v>32345</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>5158</v>
+        <v>4758</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17639,18 +17663,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1940</v>
+        <v>2911</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1953</v>
+        <v>2021</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17674,17 +17698,17 @@
         <v>2842</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4830</v>
+        <v>4829</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2508</v>
+        <v>2586</v>
       </c>
       <c r="O302" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17703,18 +17727,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4363</v>
+        <v>4657</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4393</v>
+        <v>4408</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17738,17 +17762,17 @@
         <v>4713</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15922</v>
+        <v>15921</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5005</v>
+        <v>5035</v>
       </c>
       <c r="O303" s="2" t="n">
         <v>22</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17767,18 +17791,18 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>1573</v>
+        <v>2135</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1749</v>
+        <v>1797</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17799,20 +17823,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2135</v>
+        <v>2425</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N304" s="3" t="n">
-        <v>2299</v>
+        <v>2307</v>
       </c>
       <c r="O304" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17900,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17930,17 +17954,17 @@
         <v>159</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17817</v>
+        <v>17912</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17994,7 +18018,7 @@
         <v>1373</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>318</v>
@@ -18004,7 +18028,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18058,7 +18082,7 @@
         <v>2070</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1273897</v>
+        <v>1273807</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3981</v>
@@ -18068,7 +18092,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18087,7 +18111,7 @@
         </is>
       </c>
       <c r="D309" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
@@ -18098,7 +18122,7 @@
         <v>1</v>
       </c>
       <c r="G309" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
@@ -18119,10 +18143,10 @@
         </is>
       </c>
       <c r="L309" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32198</v>
+        <v>32195</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6369</v>
@@ -18132,7 +18156,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18210,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18227,7 +18251,7 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>4876</v>
+        <v>4875</v>
       </c>
       <c r="M311" s="3" t="n">
         <v>6076</v>
@@ -18240,7 +18264,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18283,12 +18307,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18342,17 +18366,17 @@
         <v>9554</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26328</v>
+        <v>26326</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>44</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18393,20 +18417,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15578</v>
+        <v>15577</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15578</v>
+        <v>15577</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18425,7 +18449,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18436,7 +18460,7 @@
         <v>14</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18457,20 +18481,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18513,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18497,10 +18521,10 @@
         </is>
       </c>
       <c r="F316" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18521,20 +18545,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38217</v>
+        <v>38214</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>76434</v>
+        <v>76428</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18553,7 +18577,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18564,7 +18588,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18585,20 +18609,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>207008</v>
+        <v>206994</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18617,18 +18641,18 @@
         </is>
       </c>
       <c r="D318" s="3" t="n">
-        <v>874</v>
+        <v>1186</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F318" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G318" s="3" t="n">
-        <v>805</v>
+        <v>932</v>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
@@ -18655,14 +18679,14 @@
         <v>2065</v>
       </c>
       <c r="N318" s="3" t="n">
-        <v>318</v>
+        <v>1304</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18740,7 @@
         <v>1355</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15815</v>
+        <v>15814</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>318</v>
@@ -18726,7 +18750,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18745,18 +18769,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>2438</v>
+        <v>3008</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1656</v>
+        <v>1765</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18777,20 +18801,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1940</v>
+        <v>2320</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>9893</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2229</v>
+        <v>2275</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18841,10 +18865,10 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>9698</v>
+        <v>9697</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>318</v>
@@ -18854,7 +18878,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18918,7 +18942,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -18969,10 +18993,10 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>5801</v>
+        <v>4366</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16613</v>
+        <v>16612</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>4197</v>
@@ -18982,7 +19006,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19036,7 +19060,7 @@
         <v>318</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5631</v>
+        <v>5630</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>350</v>
@@ -19046,7 +19070,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19065,7 +19089,7 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
@@ -19073,10 +19097,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19097,10 +19121,10 @@
         </is>
       </c>
       <c r="L325" s="3" t="n">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15815</v>
+        <v>15814</v>
       </c>
       <c r="N325" s="3" t="n">
         <v>2524</v>
@@ -19110,7 +19134,7 @@
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19188,7 @@
         <v>3185</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>19108</v>
+        <v>15923</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>3922</v>
@@ -19174,7 +19198,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19225,7 +19249,7 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2846</v>
+        <v>2845</v>
       </c>
       <c r="M327" s="3" t="n">
         <v>4799</v>
@@ -19238,7 +19262,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19257,18 +19281,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>22306</v>
+        <v>21462</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22696</v>
+        <v>22400</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19289,20 +19313,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>20860</v>
+        <v>21545</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32820</v>
+        <v>32818</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>24196</v>
+        <v>23733</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19329,10 +19353,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>6866</v>
+        <v>6881</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19353,20 +19377,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7193</v>
+        <v>7192</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9834</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7803</v>
+        <v>7799</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19385,18 +19409,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5244</v>
+        <v>5305</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5506</v>
+        <v>5472</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19417,20 +19441,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5433</v>
+        <v>5530</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8713</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6051</v>
+        <v>6017</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19481,7 +19505,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1387</v>
+        <v>1358</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3185</v>
@@ -19494,7 +19518,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19517,14 +19541,14 @@
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19548,17 +19572,17 @@
         <v>970</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1078</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19622,7 +19646,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19641,18 +19665,18 @@
         </is>
       </c>
       <c r="D334" s="3" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F334" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19676,7 +19700,7 @@
         <v>334</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>366</v>
@@ -19686,7 +19710,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19737,10 +19761,10 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1842</v>
+        <v>1650</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15438</v>
+        <v>15437</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2342</v>
@@ -19750,7 +19774,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19773,11 +19797,11 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>163</v>
@@ -19814,7 +19838,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19841,10 +19865,10 @@
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19868,17 +19892,17 @@
         <v>159</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15591</v>
+        <v>15590</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -19942,7 +19966,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20006,7 +20030,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20057,7 +20081,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3185</v>
@@ -20066,11 +20090,11 @@
         <v>318</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20093,11 +20117,11 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G341" s="3" t="n">
         <v>669</v>
@@ -20134,7 +20158,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20212,7 @@
         <v>631</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>318</v>
@@ -20198,7 +20222,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20217,7 +20241,7 @@
         </is>
       </c>
       <c r="D343" s="3" t="n">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
@@ -20262,7 +20286,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20289,10 +20313,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1646</v>
+        <v>1642</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20316,17 +20340,17 @@
         <v>2427</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>17129</v>
+        <v>17128</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20349,11 +20373,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2070</v>
@@ -20380,17 +20404,17 @@
         <v>2070</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1592372</v>
+        <v>1592258</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>3981</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20420,7 +20444,7 @@
         <v>2</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>3674</v>
+        <v>3673</v>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
@@ -20448,7 +20472,7 @@
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20467,7 +20491,7 @@
         </is>
       </c>
       <c r="D347" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
@@ -20478,7 +20502,7 @@
         <v>3</v>
       </c>
       <c r="G347" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
@@ -20499,7 +20523,7 @@
         </is>
       </c>
       <c r="L347" s="3" t="n">
-        <v>4459</v>
+        <v>4458</v>
       </c>
       <c r="M347" s="3" t="n">
         <v>8205</v>
@@ -20508,11 +20532,11 @@
         <v>6369</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20559,14 +20583,14 @@
         <v>9554</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12739</v>
+        <v>12738</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20593,7 +20617,7 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G349" s="3" t="n">
         <v>9554</v>
@@ -20620,17 +20644,17 @@
         <v>9554</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="O349" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20683,12 +20707,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25478</v>
+        <v>25476</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20707,18 +20731,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16212</v>
+        <v>15923</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>60</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16380</v>
+        <v>16374</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20739,20 +20763,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38085</v>
+        <v>38082</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31847</v>
+        <v>31845</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20771,7 +20795,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>46040</v>
+        <v>46037</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20779,10 +20803,10 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>43218</v>
+        <v>42966</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20802,15 +20826,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="inlineStr"/>
-      <c r="M352" s="3" t="inlineStr"/>
+      <c r="L352" s="3" t="n">
+        <v>46093</v>
+      </c>
+      <c r="M352" s="3" t="n">
+        <v>46093</v>
+      </c>
       <c r="N352" s="3" t="n">
-        <v>76434</v>
-      </c>
-      <c r="O352" s="2" t="inlineStr"/>
+        <v>76428</v>
+      </c>
+      <c r="O352" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20829,7 +20859,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>103504</v>
+        <v>103497</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20840,7 +20870,7 @@
         <v>3</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>133363</v>
+        <v>133354</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20863,12 +20893,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>207008</v>
+        <v>206994</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20932,7 +20962,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -20976,17 +21006,17 @@
         <v>8917</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19069</v>
+        <v>19067</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17835</v>
+        <v>17833</v>
       </c>
       <c r="O355" s="2" t="n">
         <v>79</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21004,23 +21034,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D356" s="3" t="n">
-        <v>8917</v>
-      </c>
-      <c r="E356" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="F356" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G356" s="3" t="n">
-        <v>8917</v>
-      </c>
+      <c r="D356" s="3" t="inlineStr"/>
+      <c r="E356" s="2" t="inlineStr"/>
+      <c r="F356" s="2" t="inlineStr"/>
+      <c r="G356" s="3" t="inlineStr"/>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I356" s="2" t="n">
@@ -21040,17 +21060,17 @@
         <v>8917</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55733</v>
+        <v>55729</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17835</v>
+        <v>17833</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>50</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21101,20 +21121,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>1455</v>
+        <v>533</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15924</v>
+        <v>15923</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>562</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -21144,7 +21164,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>159.237179</v>
+        <v>159.225847</v>
       </c>
     </row>
     <row r="2">
@@ -21155,7 +21175,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 15 Aug 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 16 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21167,7 +21187,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3554</v>
+        <v>3580</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3185</v>
+        <v>3206</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>183</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>97336</v>
+        <v>97323</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>35</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23884</v>
+        <v>23881</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23884</v>
+        <v>23881</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -800,12 +800,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47768</v>
+        <v>47761</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43525</v>
+        <v>43519</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -856,20 +856,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>47134</v>
+        <v>47128</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85982</v>
+        <v>85970</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -920,20 +920,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>143303</v>
+        <v>143284</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>358258</v>
+        <v>358210</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>358258</v>
+        <v>358210</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -984,20 +984,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>358258</v>
+        <v>358210</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>358258</v>
+        <v>358210</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>716516</v>
+        <v>716420</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1016,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5603</v>
+        <v>5290</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5666</v>
+        <v>5645</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1048,20 +1048,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5605</v>
+        <v>5827</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8757</v>
+        <v>8756</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>123</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1080,18 +1080,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>7786</v>
+        <v>7763</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8366</v>
+        <v>8349</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1112,20 +1112,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8149</v>
+        <v>7774</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>151223</v>
+        <v>151203</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17515</v>
+        <v>17512</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14018</v>
+        <v>14016</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1176,20 +1176,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42751</v>
+        <v>42745</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35030</v>
+        <v>35025</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39805</v>
+        <v>39800</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1284,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94610</v>
+        <v>94598</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94610</v>
+        <v>94598</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17633</v>
+        <v>17630</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>17633</v>
+        <v>17630</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1348,20 +1348,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>318452</v>
+        <v>318409</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1402,20 +1402,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34515</v>
+        <v>34511</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64504</v>
+        <v>64495</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1456,20 +1456,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14711</v>
+        <v>14709</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64504</v>
+        <v>64495</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5414</v>
+        <v>5413</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1513,17 +1513,17 @@
         <v>796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1577,17 +1577,17 @@
         <v>1592</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>229300</v>
+        <v>229269</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>118</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1628,20 +1628,20 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>270684</v>
+        <v>270648</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1692,20 +1692,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11464</v>
+        <v>11463</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11146</v>
+        <v>11144</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37211</v>
+        <v>37206</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1800,20 +1800,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21495</v>
+        <v>21493</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>140549</v>
+        <v>140530</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>1</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
@@ -1864,20 +1864,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>323763</v>
+        <v>323720</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79613</v>
+        <v>79602</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>1938</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>318</v>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -1969,10 +1969,10 @@
         </is>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1365</v>
+        <v>1326</v>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
@@ -1993,20 +1993,20 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1417</v>
+        <v>1358</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2060,17 +2060,17 @@
         <v>1274</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2097,10 +2097,10 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1118</v>
+        <v>1104</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2121,20 +2121,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1369</v>
+        <v>1258</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1588029</v>
+        <v>1587816</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2157,14 +2157,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2188,17 +2188,17 @@
         <v>1592</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2217,18 +2217,18 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2249,20 +2249,20 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17155</v>
+        <v>17153</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>637</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1274</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2380,17 +2380,17 @@
         <v>2388</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11616</v>
+        <v>11614</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>57</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2444,17 +2444,17 @@
         <v>1487</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>636903</v>
+        <v>636818</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>2579</v>
+        <v>2575</v>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
@@ -2508,17 +2508,17 @@
         <v>2912</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12899</v>
+        <v>12897</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2537,18 +2537,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3388</v>
+        <v>3184</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3317</v>
+        <v>3308</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2569,20 +2569,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21284</v>
+        <v>21281</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>15</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6372</v>
+        <v>6371</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2633,20 +2633,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30777</v>
+        <v>30773</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O35" s="2" t="n">
         <v>98</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2664,13 +2664,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="n">
+        <v>796</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>796</v>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -2686,17 +2696,17 @@
         <v>796</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6323</v>
+        <v>6322</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O36" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2743,20 +2753,20 @@
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="3" t="n">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="M37" s="3" t="n">
         <v>4184</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2785,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -2786,7 +2796,7 @@
         <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2803,20 +2813,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>318452</v>
+        <v>318409</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2846,7 +2856,7 @@
         <v>3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2870,17 +2880,17 @@
         <v>1592</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>145766</v>
+        <v>145747</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>49</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2920,7 @@
         <v>3</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>5667</v>
+        <v>5666</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2931,20 +2941,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>3185</v>
+        <v>4367</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17516</v>
+        <v>17514</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2973,7 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
@@ -2974,7 +2984,7 @@
         <v>19</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2995,20 +3005,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15233</v>
+        <v>15231</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3048,7 @@
         <v>4</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3748</v>
+        <v>3747</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3058,7 +3068,7 @@
         <v>4299</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6167</v>
+        <v>6166</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>2229</v>
@@ -3068,7 +3078,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3087,18 +3097,18 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3115,20 +3125,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6369</v>
+        <v>6395</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8948</v>
+        <v>8947</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>3981</v>
+        <v>7005</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3147,18 +3157,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>8928</v>
+        <v>9021</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>37</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9335</v>
+        <v>9313</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3175,20 +3185,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9181</v>
+        <v>8355</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>9719</v>
+        <v>9718</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>9733</v>
+        <v>9718</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3242,17 +3252,17 @@
         <v>1592</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8778</v>
+        <v>8777</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3281,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3282,7 +3292,7 @@
         <v>3</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3303,20 +3313,20 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O46" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3380,7 @@
         <v>780</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5914</v>
+        <v>5913</v>
       </c>
       <c r="N47" s="3" t="n">
         <v>796</v>
@@ -3380,7 +3390,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3409,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -3434,7 +3444,7 @@
         <v>1019</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2637</v>
+        <v>2636</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>1592</v>
@@ -3444,7 +3454,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3495,20 +3505,20 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>3105</v>
+        <v>3104</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O49" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3555,10 +3565,10 @@
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="3" t="n">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4175</v>
+        <v>4174</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>876</v>
@@ -3568,7 +3578,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3608,7 @@
         <v>2</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>2630</v>
+        <v>2629</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3618,7 +3628,7 @@
         <v>2522</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4393</v>
+        <v>4392</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1600</v>
@@ -3628,7 +3638,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3657,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3658,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2892</v>
+        <v>2891</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3675,20 +3685,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3742,7 +3752,7 @@
         <v>788</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4855</v>
+        <v>4854</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>796</v>
@@ -3752,7 +3762,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3816,7 @@
         <v>1799</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11370</v>
+        <v>11369</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1592</v>
@@ -3816,7 +3826,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3867,20 +3877,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>2892</v>
+        <v>4776</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30799</v>
+        <v>30795</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3909,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>6170</v>
+        <v>6169</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3910,7 +3920,7 @@
         <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6925</v>
+        <v>6924</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3937,14 +3947,14 @@
         <v>5821</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6786</v>
+        <v>6785</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -3963,18 +3973,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>8941</v>
+        <v>9022</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>10346</v>
+        <v>10141</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3995,20 +4005,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9211</v>
+        <v>9210</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30839</v>
+        <v>30835</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4037,7 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3876</v>
+        <v>3877</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -4035,10 +4045,10 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4059,20 +4069,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>3877</v>
+        <v>3883</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10394</v>
+        <v>10393</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4245</v>
+        <v>4249</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4101,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>3532</v>
+        <v>3531</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4126,7 +4136,7 @@
         <v>2635</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11385</v>
+        <v>11383</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>3116</v>
@@ -4136,7 +4146,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4200,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4254,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4297,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9872</v>
+        <v>9871</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4321,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4322,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4343,20 +4353,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>17975</v>
+        <v>17973</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4409,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4457,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4493,20 +4503,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50952</v>
+        <v>50945</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4547,20 +4557,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4613,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22292</v>
+        <v>22289</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4672,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4719,14 +4729,14 @@
         <v>5071</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>40</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4777,20 +4787,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4430</v>
+        <v>4429</v>
       </c>
       <c r="M71" s="3" t="n">
         <v>5063</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4819,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -4820,7 +4830,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4841,20 +4851,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1493605</v>
+        <v>1493405</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11464</v>
+        <v>11463</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4895,20 +4905,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4785</v>
+        <v>4784</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7527</v>
+        <v>7526</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -4949,20 +4959,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8757</v>
+        <v>8756</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21096</v>
+        <v>21093</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17515</v>
+        <v>17512</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5003,20 +5013,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17515</v>
+        <v>17512</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27231</v>
+        <v>27227</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5067,20 +5077,20 @@
         </is>
       </c>
       <c r="L76" s="3" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6417</v>
+        <v>6416</v>
       </c>
       <c r="N76" s="3" t="n">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="O76" s="2" t="n">
         <v>48</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5134,7 @@
         <v>1194</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5221</v>
+        <v>5220</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>637</v>
@@ -5134,7 +5144,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5192,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5223,20 +5233,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5732</v>
+        <v>5731</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2548</v>
+        <v>2547</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5284,7 +5294,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5325,20 +5335,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23288</v>
+        <v>23285</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23288</v>
+        <v>23285</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5391,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20381</v>
+        <v>20378</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5409,14 +5419,14 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5436,17 +5446,17 @@
         <v>232</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1592099</v>
+        <v>1591885</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>796</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5496,17 +5506,17 @@
         <v>939</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34807</v>
+        <v>34802</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O84" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5549,14 +5559,14 @@
         <v>3175</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5596,17 +5606,17 @@
         <v>1274</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5645,12 +5655,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5687,20 +5697,20 @@
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5749,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17515</v>
+        <v>17512</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5771,10 +5781,10 @@
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
@@ -5794,7 +5804,7 @@
         <v>498</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86536</v>
+        <v>86524</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>796</v>
@@ -5804,7 +5814,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5854,7 @@
         <v>828</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5293</v>
+        <v>5292</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1592</v>
@@ -5854,7 +5864,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5901,20 +5911,20 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5963,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5997,12 +6007,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6051,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6095,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17515</v>
+        <v>17512</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6154,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6208,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6239,20 +6249,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4750</v>
+        <v>4749</v>
       </c>
       <c r="M99" s="3" t="n">
         <v>5211</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9872</v>
+        <v>9871</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6293,20 +6303,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6359,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6395,20 +6405,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18090</v>
+        <v>18087</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18090</v>
+        <v>18087</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6461,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50952</v>
+        <v>50945</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6497,10 +6507,10 @@
         </is>
       </c>
       <c r="L104" s="3" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="M104" s="3" t="n">
-        <v>2707</v>
+        <v>2706</v>
       </c>
       <c r="N104" s="3" t="n">
         <v>2866</v>
@@ -6510,7 +6520,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6568,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6611,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9872</v>
+        <v>9871</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6635,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -6636,7 +6646,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -6659,12 +6669,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6717,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6765,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6813,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50952</v>
+        <v>50945</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6851,12 +6861,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79613</v>
+        <v>79602</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6897,20 +6907,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87574</v>
+        <v>87562</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>111458</v>
+        <v>111443</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>111458</v>
+        <v>111443</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -6951,20 +6961,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>111458</v>
+        <v>111443</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>111458</v>
+        <v>111443</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>143303</v>
+        <v>143284</v>
       </c>
       <c r="O113" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7015,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7059,20 +7069,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>191071</v>
+        <v>191045</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7113,20 +7123,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>214955</v>
+        <v>214926</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7180,7 @@
         <v>1697</v>
       </c>
       <c r="M117" s="3" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="N117" s="3" t="n">
         <v>2229</v>
@@ -7180,7 +7190,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7224,17 +7234,17 @@
         <v>3818</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5888</v>
+        <v>5887</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7277,12 +7287,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7323,20 +7333,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7389,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7425,20 +7435,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19145</v>
+        <v>19143</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7479,20 +7489,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41338</v>
+        <v>41333</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7546,7 +7556,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7590,17 +7600,17 @@
         <v>2251</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5718</v>
+        <v>5717</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7641,20 +7651,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6503</v>
+        <v>6502</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6503</v>
+        <v>6502</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7705,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11963</v>
+        <v>11961</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7751,12 +7761,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7797,20 +7807,20 @@
         </is>
       </c>
       <c r="L129" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O129" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7853,12 +7863,12 @@
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="3" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7911,12 @@
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7935,7 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -7936,7 +7946,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -7957,20 +7967,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7999,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -8000,7 +8010,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -8021,20 +8031,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16010</v>
+        <v>16008</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8087,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8123,20 +8133,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21495</v>
+        <v>21493</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21495</v>
+        <v>21493</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47768</v>
+        <v>47761</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8165,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8166,7 +8176,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8187,20 +8197,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71652</v>
+        <v>71642</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8241,20 +8251,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8283,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6406</v>
+        <v>6405</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8284,7 +8294,7 @@
         <v>14</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6372</v>
+        <v>6371</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8308,17 +8318,17 @@
         <v>6824</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12829</v>
+        <v>12827</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8382,7 +8392,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8446,7 @@
         <v>573</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5199</v>
+        <v>5198</v>
       </c>
       <c r="N140" s="3" t="n">
         <v>436</v>
@@ -8446,7 +8456,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8520,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8584,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8603,7 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -8604,7 +8614,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>2930</v>
+        <v>2929</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -8628,17 +8638,17 @@
         <v>2086</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8689,20 +8699,20 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10808</v>
+        <v>10807</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O144" s="2" t="n">
         <v>52</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8755,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8804,17 +8814,17 @@
         <v>4458</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53847</v>
+        <v>53840</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8867,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8903,20 +8913,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17448</v>
+        <v>17446</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8959,12 +8969,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -8983,18 +8993,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
         <v>36</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -9015,20 +9025,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9057,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9055,10 +9065,10 @@
         </is>
       </c>
       <c r="F151" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9079,20 +9089,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>84613</v>
+        <v>84601</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>76428</v>
+        <v>76418</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9133,20 +9143,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>206994</v>
+        <v>206966</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9200,7 +9210,7 @@
         <v>159</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10417</v>
+        <v>10415</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>318</v>
@@ -9210,7 +9220,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9284,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9292,23 +9302,13 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D155" s="3" t="n">
-        <v>796</v>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>796</v>
-      </c>
+      <c r="D155" s="3" t="inlineStr"/>
+      <c r="E155" s="2" t="inlineStr"/>
+      <c r="F155" s="2" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
@@ -9324,7 +9324,7 @@
         <v>796</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15601</v>
+        <v>15599</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1592</v>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9377,14 +9377,14 @@
         <v>3261</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O156" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="G157" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
@@ -9431,20 +9431,20 @@
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
         <v>796</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19465</v>
+        <v>19463</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1592</v>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9542,17 +9542,17 @@
         <v>1592</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19309</v>
+        <v>19307</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>40</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9593,20 +9593,20 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M160" s="3" t="n">
         <v>6660</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1696</v>
+        <v>1673</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9711,20 +9711,20 @@
         </is>
       </c>
       <c r="L162" s="3" t="n">
-        <v>1927</v>
+        <v>1746</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30380</v>
+        <v>30376</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1796</v>
       </c>
       <c r="O162" s="2" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9751,10 +9751,10 @@
         </is>
       </c>
       <c r="F163" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3232</v>
+        <v>3383</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9781,14 +9781,14 @@
         <v>3821</v>
       </c>
       <c r="N163" s="3" t="n">
-        <v>3447</v>
+        <v>4203</v>
       </c>
       <c r="O163" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9807,18 +9807,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4606</v>
+        <v>4271</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3796</v>
+        <v>3817</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9839,20 +9839,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4633</v>
+        <v>4267</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10350</v>
+        <v>10348</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9906,7 +9906,7 @@
         <v>280</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4944</v>
+        <v>4943</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>318</v>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -9970,7 +9970,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9786</v>
+        <v>9785</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1274</v>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
         <v>1592</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5430</v>
+        <v>5429</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>318</v>
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10142,7 +10142,7 @@
         <v>314</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>318</v>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10193,20 +10193,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>95536</v>
+        <v>95523</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>95536</v>
+        <v>95523</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10249,12 +10249,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10351,20 +10351,20 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>3344</v>
+        <v>3343</v>
       </c>
       <c r="M173" s="3" t="n">
         <v>3920</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10403,12 +10403,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10445,20 +10445,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14300</v>
+        <v>14298</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10495,20 +10495,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11464</v>
+        <v>11463</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11464</v>
+        <v>11463</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10545,20 +10545,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16002</v>
+        <v>16000</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10595,20 +10595,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19604</v>
+        <v>19601</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10651,12 +10651,12 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10697,20 +10697,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10799,20 +10799,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10901,20 +10901,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21495</v>
+        <v>21493</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21495</v>
+        <v>21493</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42991</v>
+        <v>42985</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -10955,20 +10955,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28661</v>
+        <v>28657</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>57321</v>
+        <v>57314</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11012,17 +11012,17 @@
         <v>159</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
         <v>159</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>318</v>
@@ -11076,7 +11076,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11130,7 +11130,7 @@
         <v>159</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>103596</v>
+        <v>103582</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>318</v>
@@ -11140,7 +11140,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
         <v>159</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29368</v>
+        <v>29364</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>318</v>
@@ -11242,7 +11242,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11296,7 @@
         <v>159</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>157208</v>
+        <v>157187</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>318</v>
@@ -11306,7 +11306,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11350,7 +11350,7 @@
         <v>159</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>318</v>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11408,7 +11408,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11452,17 +11452,17 @@
         <v>159</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
         <v>159</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>159067</v>
+        <v>159045</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>318</v>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11534,13 +11534,23 @@
           <t>チップ / チップ</t>
         </is>
       </c>
-      <c r="D196" s="3" t="inlineStr"/>
-      <c r="E196" s="2" t="inlineStr"/>
-      <c r="F196" s="2" t="inlineStr"/>
-      <c r="G196" s="3" t="inlineStr"/>
+      <c r="D196" s="3" t="n">
+        <v>833</v>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" s="3" t="n">
+        <v>833</v>
+      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I196" s="2" t="n">
@@ -11560,17 +11570,17 @@
         <v>159</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N196" s="3" t="n">
-        <v>318</v>
+        <v>915</v>
       </c>
       <c r="O196" s="2" t="n">
         <v>543</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11628,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11682,7 @@
         <v>1169</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>318</v>
@@ -11682,7 +11692,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11723,20 +11733,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20734</v>
+        <v>20732</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20734</v>
+        <v>20732</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11790,17 +11800,17 @@
         <v>4458</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6348</v>
+        <v>6347</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11854,17 +11864,17 @@
         <v>5095</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10848</v>
+        <v>10847</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7643</v>
+        <v>7642</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11905,20 +11915,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10420</v>
+        <v>10418</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -11959,20 +11969,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8280</v>
+        <v>8279</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>277961</v>
+        <v>277923</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12013,20 +12023,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15733</v>
+        <v>15731</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16149</v>
+        <v>16147</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12067,20 +12077,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20381</v>
+        <v>20378</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>49120</v>
+        <v>49113</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12123,12 +12133,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12202,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12246,7 +12256,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12310,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12357,14 +12367,14 @@
         <v>4501</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12405,20 +12415,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12459,20 +12469,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12515,12 +12525,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22929</v>
+        <v>22925</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12561,20 +12571,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12615,10 +12625,10 @@
         </is>
       </c>
       <c r="L215" s="3" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="M215" s="3" t="n">
-        <v>2750</v>
+        <v>2749</v>
       </c>
       <c r="N215" s="3" t="n">
         <v>2229</v>
@@ -12628,7 +12638,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12672,17 +12682,17 @@
         <v>2070</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11956</v>
+        <v>11955</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12701,7 +12711,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12712,7 +12722,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12733,20 +12743,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15677</v>
+        <v>15675</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37721</v>
+        <v>37716</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12787,20 +12797,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>6793</v>
+        <v>6792</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12841,20 +12851,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7165</v>
+        <v>7164</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14330</v>
+        <v>14328</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12897,12 +12907,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -12943,20 +12953,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13020,7 @@
         <v>887</v>
       </c>
       <c r="M222" s="3" t="n">
-        <v>2860</v>
+        <v>2859</v>
       </c>
       <c r="N222" s="3" t="n">
         <v>1592</v>
@@ -13020,7 +13030,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13074,17 +13084,17 @@
         <v>1592</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4075</v>
+        <v>4074</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O223" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13103,7 +13113,7 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
@@ -13114,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
@@ -13135,20 +13145,20 @@
         </is>
       </c>
       <c r="L224" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7246</v>
+        <v>7245</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13202,7 +13212,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13259,14 +13269,14 @@
         <v>3498</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O226" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13295,7 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -13293,10 +13303,10 @@
         </is>
       </c>
       <c r="F227" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -13317,20 +13327,20 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M227" s="3" t="n">
         <v>3807</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13374,7 +13384,7 @@
         <v>159</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>318</v>
@@ -13384,7 +13394,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13428,17 +13438,17 @@
         <v>159</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13492,17 +13502,17 @@
         <v>159</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13546,17 +13556,17 @@
         <v>796</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13610,17 +13620,17 @@
         <v>1592</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3925</v>
+        <v>3924</v>
       </c>
       <c r="N232" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O232" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13661,20 +13671,20 @@
         </is>
       </c>
       <c r="L233" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7254</v>
+        <v>7253</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13738,7 +13748,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13785,14 +13795,14 @@
         <v>4291</v>
       </c>
       <c r="N235" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O235" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13833,20 +13843,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="M236" s="3" t="n">
         <v>6566</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13899,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -13945,20 +13955,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8757</v>
+        <v>8756</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11100</v>
+        <v>11098</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14001,12 +14011,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14047,20 +14057,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10547</v>
+        <v>10546</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10547</v>
+        <v>10546</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14089,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>23040</v>
+        <v>23037</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14087,10 +14097,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>21412</v>
+        <v>21647</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14111,20 +14121,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>20276</v>
+        <v>20193</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>35017</v>
+        <v>35012</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14153,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14154,7 +14164,7 @@
         <v>3</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38241</v>
+        <v>38236</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14175,20 +14185,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>53696</v>
+        <v>43683</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58996</v>
+        <v>58988</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>76428</v>
+        <v>76418</v>
       </c>
       <c r="O242" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14217,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>16157</v>
+        <v>16154</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14215,10 +14225,10 @@
         </is>
       </c>
       <c r="F243" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>17521</v>
+        <v>17245</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14235,20 +14245,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17666</v>
+        <v>17664</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31845169</v>
+        <v>31840892</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14291,12 +14301,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14360,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14390,7 @@
         <v>9</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14404,17 +14414,17 @@
         <v>2025</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2072</v>
+        <v>2296</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14455,20 +14465,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23476</v>
+        <v>23473</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17833</v>
+        <v>17831</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14509,20 +14519,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>17833</v>
+        <v>17831</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14572,17 +14582,17 @@
         <v>796</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9348</v>
+        <v>9347</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O249" s="2" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14632,7 +14642,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14651,7 +14661,7 @@
         </is>
       </c>
       <c r="D251" s="3" t="n">
-        <v>31501</v>
+        <v>31497</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
@@ -14662,7 +14672,7 @@
         <v>1</v>
       </c>
       <c r="G251" s="3" t="n">
-        <v>31501</v>
+        <v>31497</v>
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
@@ -14686,17 +14696,17 @@
         <v>159</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97910</v>
+        <v>97896</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14747,20 +14757,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50736</v>
+        <v>50729</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50736</v>
+        <v>50729</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14779,7 +14789,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>6705</v>
+        <v>6704</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -14790,7 +14800,7 @@
         <v>2</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>5900</v>
+        <v>5899</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14811,20 +14821,20 @@
         </is>
       </c>
       <c r="L253" s="3" t="n">
-        <v>5146</v>
+        <v>7580</v>
       </c>
       <c r="M253" s="3" t="n">
-        <v>7592</v>
+        <v>7591</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>7643</v>
+        <v>7642</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14865,20 +14875,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>7915</v>
+        <v>7914</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>191071</v>
+        <v>191045</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14942,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -14990,7 +15000,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15044,7 @@
         <v>293</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7961</v>
+        <v>7960</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>318</v>
@@ -15044,7 +15054,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15067,14 +15077,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15101,14 +15111,14 @@
         <v>970</v>
       </c>
       <c r="N258" s="3" t="n">
-        <v>1146</v>
+        <v>1078</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15162,7 +15172,7 @@
         <v>1226</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21532</v>
+        <v>21529</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1592</v>
@@ -15172,7 +15182,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15229,14 +15239,14 @@
         <v>3697</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15255,7 +15265,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15266,7 +15276,7 @@
         <v>3</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15287,20 +15297,20 @@
         </is>
       </c>
       <c r="L261" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7063</v>
+        <v>7062</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15319,7 +15329,7 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
@@ -15330,7 +15340,7 @@
         <v>13</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15351,20 +15361,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O262" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15408,17 +15418,17 @@
         <v>796</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10633</v>
+        <v>10632</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O263" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15475,14 +15485,14 @@
         <v>1624</v>
       </c>
       <c r="N264" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O264" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15525,12 +15535,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15549,7 +15559,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15560,7 +15570,7 @@
         <v>1</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15581,20 +15591,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9703</v>
+        <v>9702</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O266" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15623,7 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2723</v>
+        <v>2722</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
@@ -15648,17 +15658,17 @@
         <v>1842</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19583</v>
+        <v>19581</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>2952</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15677,7 +15687,7 @@
         </is>
       </c>
       <c r="D268" s="3" t="n">
-        <v>8280</v>
+        <v>8279</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
@@ -15688,7 +15698,7 @@
         <v>1</v>
       </c>
       <c r="G268" s="3" t="n">
-        <v>8280</v>
+        <v>8279</v>
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
@@ -15709,20 +15719,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8280</v>
+        <v>8279</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14343</v>
+        <v>14341</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15765,12 +15775,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15811,20 +15821,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>19591</v>
+        <v>14010</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>25072</v>
+        <v>25068</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15843,7 +15853,7 @@
         </is>
       </c>
       <c r="D271" s="3" t="n">
-        <v>20381</v>
+        <v>20378</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
@@ -15854,7 +15864,7 @@
         <v>1</v>
       </c>
       <c r="G271" s="3" t="n">
-        <v>20381</v>
+        <v>20378</v>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
@@ -15875,20 +15885,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24785</v>
+        <v>24782</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>38595</v>
+        <v>38590</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15932,7 +15942,7 @@
         <v>159</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>9772</v>
+        <v>9770</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>318</v>
@@ -15942,7 +15952,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -15961,18 +15971,18 @@
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>159</v>
+        <v>941</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F273" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G273" s="3" t="n">
-        <v>914</v>
+        <v>923</v>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
@@ -15996,17 +16006,17 @@
         <v>159</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21088</v>
+        <v>21085</v>
       </c>
       <c r="N273" s="3" t="n">
-        <v>318</v>
+        <v>1035</v>
       </c>
       <c r="O273" s="2" t="n">
         <v>187</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16060,7 @@
         <v>159</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31950</v>
+        <v>31946</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>318</v>
@@ -16060,7 +16070,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16104,7 +16114,7 @@
         <v>159</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16002</v>
+        <v>16000</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>318</v>
@@ -16114,7 +16124,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16143,7 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -16144,7 +16154,7 @@
         <v>5</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>15090</v>
+        <v>15088</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16168,17 +16178,17 @@
         <v>159</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>158747</v>
+        <v>158725</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>2439</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16228,17 +16238,17 @@
         <v>796</v>
       </c>
       <c r="M277" s="3" t="n">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="N277" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16282,17 +16292,17 @@
         <v>4458</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>8590</v>
+        <v>8589</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16336,17 +16346,17 @@
         <v>5095</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9963</v>
+        <v>9961</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7643</v>
+        <v>7642</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16387,20 +16397,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8665</v>
+        <v>8664</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10190</v>
+        <v>10189</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16443,12 +16453,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14012</v>
+        <v>14010</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16491,12 +16501,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16539,12 +16549,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16585,20 +16595,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>33437</v>
+        <v>33433</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33950</v>
+        <v>33946</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16617,18 +16627,18 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9323</v>
+        <v>8998</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9918</v>
+        <v>9865</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16649,20 +16659,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>9546</v>
+        <v>9863</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10391</v>
+        <v>10382</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16726,7 +16736,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16745,18 +16755,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>4366</v>
+        <v>4657</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>5039</v>
+        <v>5016</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16773,20 +16783,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>4799</v>
+        <v>4797</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5812</v>
+        <v>5811</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5517</v>
+        <v>5438</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16805,18 +16815,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>6283</v>
+        <v>6510</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6792</v>
+        <v>6779</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16833,20 +16843,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>6856</v>
+        <v>6706</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8695</v>
+        <v>8694</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7156</v>
+        <v>7174</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16865,7 +16875,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>8734</v>
+        <v>9121</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16873,10 +16883,10 @@
         </is>
       </c>
       <c r="F289" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9290</v>
+        <v>9277</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16893,20 +16903,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9122</v>
+        <v>9492</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11651</v>
+        <v>11649</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>9706</v>
+        <v>9770</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16950,7 +16960,7 @@
         <v>2912</v>
       </c>
       <c r="M290" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="N290" s="3" t="n">
         <v>1592</v>
@@ -16960,7 +16970,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -16979,7 +16989,7 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>3882</v>
+        <v>3881</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -16987,10 +16997,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2796</v>
+        <v>2823</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -17011,20 +17021,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>4140</v>
+        <v>4139</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5095</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>4269</v>
+        <v>4268</v>
       </c>
       <c r="O291" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17043,18 +17053,18 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>3393</v>
+        <v>4044</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F292" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3619</v>
+        <v>3600</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17075,20 +17085,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>3880</v>
+        <v>4042</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5573</v>
+        <v>5572</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O292" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17152,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17161,7 +17171,7 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6113</v>
+        <v>6301</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -17169,10 +17179,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5719</v>
+        <v>5712</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17193,20 +17203,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>6302</v>
+        <v>6800</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>28470</v>
+        <v>28466</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6385</v>
+        <v>6427</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17247,20 +17257,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51753</v>
+        <v>51746</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>703366</v>
+        <v>703271</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17279,7 +17289,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17290,7 +17300,7 @@
         <v>5</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17311,20 +17321,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>69230</v>
+        <v>69221</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39806</v>
+        <v>39801</v>
       </c>
       <c r="O296" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17343,7 +17353,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63690</v>
+        <v>63682</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17354,7 +17364,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63690</v>
+        <v>63682</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17375,20 +17385,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63690</v>
+        <v>63682</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79613</v>
+        <v>79602</v>
       </c>
       <c r="O297" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17407,7 +17417,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17418,7 +17428,7 @@
         <v>2</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17439,20 +17449,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>127381</v>
+        <v>127364</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>127648</v>
+        <v>127631</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>159226</v>
+        <v>159204</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17471,7 +17481,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17482,7 +17492,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17503,20 +17513,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>254761</v>
+        <v>254727</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>257215</v>
+        <v>257180</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>318452</v>
+        <v>318409</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17545,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>445832</v>
+        <v>445772</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17546,7 +17556,7 @@
         <v>5</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>445832</v>
+        <v>445772</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17567,20 +17577,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>445832</v>
+        <v>445772</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>949301</v>
+        <v>949174</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>636903</v>
+        <v>636818</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17599,18 +17609,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>4170</v>
+        <v>2996</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>5504</v>
+        <v>5310</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17631,20 +17641,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>3105</v>
+        <v>2874</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>32345</v>
+        <v>32341</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>4758</v>
+        <v>4725</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17673,7 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>2911</v>
+        <v>2910</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
@@ -17695,20 +17705,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2842</v>
+        <v>2622</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4829</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17748,7 @@
         <v>17</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4408</v>
+        <v>4407</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17759,20 +17769,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4713</v>
+        <v>4649</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15921</v>
+        <v>15919</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>5035</v>
+        <v>5034</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17823,20 +17833,20 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2425</v>
+        <v>2307</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2307</v>
       </c>
       <c r="O304" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17863,10 +17873,10 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G305" s="3" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
@@ -17900,7 +17910,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17954,17 +17964,17 @@
         <v>159</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17912</v>
+        <v>17935</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -17982,23 +17992,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D307" s="3" t="n">
-        <v>1379</v>
-      </c>
-      <c r="E307" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-18</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G307" s="3" t="n">
-        <v>1379</v>
-      </c>
+      <c r="D307" s="3" t="inlineStr"/>
+      <c r="E307" s="2" t="inlineStr"/>
+      <c r="F307" s="2" t="inlineStr"/>
+      <c r="G307" s="3" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I307" s="2" t="n">
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="L307" s="3" t="n">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>318</v>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18082,17 +18082,17 @@
         <v>2070</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1273807</v>
+        <v>1273636</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>229</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18146,17 +18146,17 @@
         <v>4458</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32195</v>
+        <v>32191</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>126</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18200,17 +18200,17 @@
         <v>1592</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6067</v>
+        <v>6066</v>
       </c>
       <c r="N310" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O310" s="2" t="n">
         <v>68</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18254,17 +18254,17 @@
         <v>4875</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6076</v>
+        <v>6075</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18307,12 +18307,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18363,20 +18363,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26326</v>
+        <v>26323</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>44</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18417,20 +18417,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15577</v>
+        <v>15575</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15577</v>
+        <v>15575</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18449,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18457,10 +18457,10 @@
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18481,20 +18481,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18513,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18545,20 +18545,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38214</v>
+        <v>38209</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>76428</v>
+        <v>76418</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18577,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18609,20 +18609,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>206994</v>
+        <v>206966</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18705,7 +18705,7 @@
         </is>
       </c>
       <c r="D319" s="3" t="n">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>2</v>
       </c>
       <c r="G319" s="3" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
         <v>1355</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15814</v>
+        <v>15812</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>318</v>
@@ -18750,7 +18750,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18769,7 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>3008</v>
+        <v>2585</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
@@ -18777,10 +18777,10 @@
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>1765</v>
+        <v>1900</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18801,20 +18801,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>2320</v>
+        <v>3768</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9893</v>
+        <v>9891</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2275</v>
+        <v>2500</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18868,7 +18868,7 @@
         <v>3501</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>9697</v>
+        <v>9696</v>
       </c>
       <c r="N321" s="3" t="n">
         <v>318</v>
@@ -18878,7 +18878,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>3817</v>
+        <v>3816</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>8</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18993,20 +18993,20 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>4366</v>
+        <v>3496</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16612</v>
+        <v>16610</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>4197</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19060,7 @@
         <v>318</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5630</v>
+        <v>5629</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>350</v>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19097,10 +19097,10 @@
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>1985</v>
+        <v>1972</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19124,17 +19124,17 @@
         <v>2087</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15814</v>
+        <v>15812</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2524</v>
+        <v>2523</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19153,7 +19153,7 @@
         </is>
       </c>
       <c r="D326" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
@@ -19185,20 +19185,20 @@
         </is>
       </c>
       <c r="L326" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>3922</v>
+        <v>3502</v>
       </c>
       <c r="O326" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19228,7 +19228,7 @@
         <v>8</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>4117</v>
+        <v>4116</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19249,20 +19249,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2845</v>
+        <v>2428</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>4799</v>
+        <v>4798</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>3202</v>
       </c>
       <c r="O327" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19281,18 +19281,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>21462</v>
+        <v>19170</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22400</v>
+        <v>22179</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19313,20 +19313,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>21545</v>
+        <v>20373</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32818</v>
+        <v>32814</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>23733</v>
+        <v>23142</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19345,18 +19345,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>6793</v>
+        <v>6306</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>6881</v>
+        <v>6816</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19377,20 +19377,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7192</v>
+        <v>7191</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>9834</v>
+        <v>9832</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>7799</v>
+        <v>7691</v>
       </c>
       <c r="O329" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19409,18 +19409,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5305</v>
+        <v>5821</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
         <v>31</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5472</v>
+        <v>5461</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19441,20 +19441,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5530</v>
+        <v>5827</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8713</v>
+        <v>8712</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6017</v>
+        <v>6059</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19473,7 +19473,7 @@
         </is>
       </c>
       <c r="D331" s="3" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>1</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H331" s="2" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>1358</v>
       </c>
       <c r="M331" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="N331" s="3" t="n">
         <v>318</v>
@@ -19518,7 +19518,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19545,10 +19545,10 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19569,20 +19569,20 @@
         </is>
       </c>
       <c r="L332" s="3" t="n">
-        <v>970</v>
+        <v>922</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1078</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19633,7 +19633,7 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M333" s="3" t="n">
         <v>2917</v>
@@ -19642,11 +19642,11 @@
         <v>318</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19700,7 +19700,7 @@
         <v>334</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>366</v>
@@ -19710,7 +19710,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>1650</v>
+        <v>1358</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15437</v>
+        <v>15435</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2342</v>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19838,7 +19838,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19861,14 +19861,14 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19892,17 +19892,17 @@
         <v>159</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15590</v>
+        <v>15588</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -19925,14 +19925,14 @@
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19953,10 +19953,10 @@
         </is>
       </c>
       <c r="L338" s="3" t="n">
-        <v>287</v>
+        <v>242</v>
       </c>
       <c r="M338" s="3" t="n">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="N338" s="3" t="n">
         <v>318</v>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20017,10 +20017,10 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4742</v>
+        <v>4741</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>580</v>
@@ -20030,7 +20030,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20081,10 +20081,10 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>898</v>
+        <v>871</v>
       </c>
       <c r="M340" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="N340" s="3" t="n">
         <v>318</v>
@@ -20094,7 +20094,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20113,7 +20113,7 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -20121,10 +20121,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         </is>
       </c>
       <c r="L341" s="3" t="n">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M341" s="3" t="n">
         <v>2449</v>
@@ -20158,7 +20158,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20209,10 +20209,10 @@
         </is>
       </c>
       <c r="L342" s="3" t="n">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="M342" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N342" s="3" t="n">
         <v>318</v>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20249,10 +20249,10 @@
         </is>
       </c>
       <c r="F343" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20313,10 +20313,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1642</v>
+        <v>1646</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20337,20 +20337,20 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>17128</v>
+        <v>17126</v>
       </c>
       <c r="N344" s="3" t="n">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20377,7 +20377,7 @@
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2070</v>
@@ -20404,17 +20404,17 @@
         <v>2070</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1592258</v>
+        <v>1592045</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3981</v>
+        <v>3980</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20467,12 +20467,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4777</v>
+        <v>4776</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20526,17 +20526,17 @@
         <v>4458</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>8205</v>
+        <v>8204</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6369</v>
+        <v>6368</v>
       </c>
       <c r="O347" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20577,20 +20577,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12738</v>
+        <v>12736</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20609,7 +20609,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20617,10 +20617,10 @@
         </is>
       </c>
       <c r="F349" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20641,20 +20641,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9554</v>
+        <v>9552</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19107</v>
+        <v>19105</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20673,7 +20673,7 @@
         </is>
       </c>
       <c r="D350" s="3" t="n">
-        <v>12764</v>
+        <v>12762</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>1</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>12764</v>
+        <v>12762</v>
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
@@ -20707,12 +20707,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25476</v>
+        <v>25473</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20731,18 +20731,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16374</v>
+        <v>16384</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20763,20 +20763,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38082</v>
+        <v>38077</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31845</v>
+        <v>31841</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20795,7 +20795,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>10</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>42966</v>
+        <v>42961</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20827,20 +20827,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>46093</v>
+        <v>43683</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>46093</v>
+        <v>46087</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>76428</v>
+        <v>76418</v>
       </c>
       <c r="O352" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>103497</v>
+        <v>103483</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20867,10 +20867,10 @@
         </is>
       </c>
       <c r="F353" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>133354</v>
+        <v>104811</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20893,12 +20893,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>206994</v>
+        <v>206966</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -20952,7 +20952,7 @@
         <v>387</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9436</v>
+        <v>9434</v>
       </c>
       <c r="N354" s="3" t="n">
         <v>318</v>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -21003,20 +21003,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19067</v>
+        <v>19065</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17833</v>
+        <v>17831</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -21057,20 +21057,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8917</v>
+        <v>8915</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55729</v>
+        <v>55722</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17833</v>
+        <v>17831</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>50</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -21121,20 +21121,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15923</v>
+        <v>15920</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>562</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21164,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>159.225847</v>
+        <v>159.20446</v>
       </c>
     </row>
     <row r="2">
@@ -21175,7 +21175,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sun, 16 Aug 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Mon, 17 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21187,7 +21187,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -578,14 +578,14 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3627</v>
+        <v>3595</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3178</v>
+        <v>3297</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>97124</v>
+        <v>97141</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24150</v>
+        <v>24154</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -800,12 +800,12 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="n">
-        <v>47664</v>
+        <v>47672</v>
       </c>
       <c r="O5" s="2" t="inlineStr"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43430</v>
+        <v>43438</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -856,20 +856,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>47031</v>
+        <v>47039</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85795</v>
+        <v>85809</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -920,20 +920,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>142991</v>
+        <v>143016</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>357478</v>
+        <v>357539</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>357478</v>
+        <v>357539</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -984,20 +984,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>357478</v>
+        <v>357539</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>357478</v>
+        <v>357539</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>714956</v>
+        <v>715078</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1016,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6255</v>
+        <v>6291</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5661</v>
+        <v>5692</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1048,20 +1048,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6288</v>
+        <v>6396</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8738</v>
+        <v>8740</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1080,18 +1080,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8473</v>
+        <v>8630</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8307</v>
+        <v>8321</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1112,20 +1112,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8715</v>
+        <v>8235</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>150894</v>
+        <v>150920</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17477</v>
+        <v>17480</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1144,18 +1144,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>20</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13982</v>
+        <v>13984</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1176,20 +1176,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42657</v>
+        <v>42665</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34953</v>
+        <v>34959</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1230,20 +1230,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39718</v>
+        <v>39725</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39720</v>
+        <v>39727</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1284,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94404</v>
+        <v>94421</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94404</v>
+        <v>94421</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17594</v>
+        <v>17597</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>17594</v>
+        <v>17597</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1348,20 +1348,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>317758</v>
+        <v>317813</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1402,20 +1402,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34440</v>
+        <v>34446</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64363</v>
+        <v>64375</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1456,20 +1456,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14671</v>
+        <v>14673</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64363</v>
+        <v>64375</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5402</v>
+        <v>5403</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1510,20 +1510,20 @@
         </is>
       </c>
       <c r="L17" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1589</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1577,17 +1577,17 @@
         <v>1589</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>228800</v>
+        <v>228839</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3178</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1631,17 +1631,17 @@
         <v>3178</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>270094</v>
+        <v>270141</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1692,20 +1692,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11439</v>
+        <v>11441</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1746,20 +1746,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11122</v>
+        <v>11123</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37130</v>
+        <v>37136</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1800,20 +1800,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21449</v>
+        <v>21452</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>140243</v>
+        <v>140267</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1854,20 +1854,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39720</v>
+        <v>39727</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>323058</v>
+        <v>323114</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79440</v>
+        <v>79453</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>1934</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>318</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -1986,17 +1986,17 @@
         <v>1355</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2050,17 @@
         <v>1271</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>27</v>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2111,20 +2111,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1255</v>
+        <v>842</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1584571</v>
+        <v>1584843</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1589</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1785</v>
+        <v>1779</v>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
@@ -2178,17 +2178,17 @@
         <v>2328</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3178</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3178</v>
@@ -2242,17 +2242,17 @@
         <v>3178</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17118</v>
+        <v>17121</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2306,17 +2306,17 @@
         <v>636</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1271</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2367,20 +2367,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11590</v>
+        <v>11592</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="O31" s="2" t="n">
         <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2431,20 +2431,20 @@
         </is>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1066</v>
+        <v>795</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>635516</v>
+        <v>635625</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>194</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
@@ -2495,20 +2495,20 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2720</v>
+        <v>2450</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12871</v>
+        <v>12873</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3178</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2527,18 +2527,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3519</v>
+        <v>3819</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3309</v>
+        <v>3316</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2559,20 +2559,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3438</v>
+        <v>3178</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21237</v>
+        <v>21241</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2591,18 +2591,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2623,20 +2623,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30710</v>
+        <v>30715</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
@@ -2683,10 +2683,10 @@
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6309</v>
+        <v>6310</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1589</v>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
         <v>1899</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>4175</v>
+        <v>4176</v>
       </c>
       <c r="N37" s="3" t="n">
         <v>3178</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2803,20 +2803,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>317758</v>
+        <v>317813</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2870,7 +2870,7 @@
         <v>1589</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>145449</v>
+        <v>145474</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3178</v>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>4792</v>
+        <v>4793</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
@@ -2931,20 +2931,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4366</v>
+        <v>4367</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17478</v>
+        <v>17481</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -2963,18 +2963,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -2995,20 +2995,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15200</v>
+        <v>15203</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
         <v>4290</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6153</v>
+        <v>6154</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3115,20 +3115,20 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6382</v>
+        <v>6383</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8929</v>
+        <v>8931</v>
       </c>
       <c r="N43" s="3" t="n">
-        <v>6991</v>
+        <v>3973</v>
       </c>
       <c r="O43" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9121</v>
+        <v>9123</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9226</v>
+        <v>9215</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3175,20 +3175,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>16495</v>
+        <v>9690</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>17270</v>
+        <v>14557</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>9900</v>
+        <v>9901</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3242,7 @@
         <v>1589</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8759</v>
+        <v>8761</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3178</v>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
         <v>3178</v>
@@ -3306,17 +3306,17 @@
         <v>3178</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3367,20 +3367,20 @@
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>779</v>
+        <v>315</v>
       </c>
       <c r="M47" s="3" t="n">
-        <v>5901</v>
+        <v>5902</v>
       </c>
       <c r="N47" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3495,10 +3495,10 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3178</v>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
@@ -3538,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
@@ -3558,17 +3558,17 @@
         <v>2148</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4166</v>
+        <v>4167</v>
       </c>
       <c r="N50" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3615,10 +3615,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4383</v>
+        <v>4384</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1589</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>1</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3675,10 +3675,10 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="N52" s="3" t="n">
         <v>3178</v>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3739,20 +3739,20 @@
         </is>
       </c>
       <c r="L53" s="3" t="n">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4844</v>
+        <v>4845</v>
       </c>
       <c r="N53" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O53" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="L54" s="3" t="n">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11346</v>
+        <v>11348</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1589</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3867,20 +3867,20 @@
         </is>
       </c>
       <c r="L55" s="3" t="n">
-        <v>2695</v>
+        <v>4767</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30732</v>
+        <v>30737</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3178</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>5807</v>
+        <v>5808</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="F56" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>6634</v>
+        <v>6009</v>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
@@ -3931,20 +3931,20 @@
         </is>
       </c>
       <c r="L56" s="3" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="M56" s="3" t="n">
-        <v>5809</v>
+        <v>5810</v>
       </c>
       <c r="N56" s="3" t="n">
-        <v>6387</v>
+        <v>6388</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -3963,18 +3963,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9604</v>
+        <v>8991</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9659</v>
+        <v>9607</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3995,20 +3995,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9491</v>
+        <v>9223</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30772</v>
+        <v>30777</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4027,18 +4027,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3883</v>
+        <v>3784</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4059,20 +4059,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>4832</v>
+        <v>4214</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10372</v>
+        <v>10373</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4129</v>
+        <v>4116</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11360</v>
+        <v>11362</v>
       </c>
       <c r="N59" s="3" t="n">
         <v>2892</v>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4237,14 +4237,14 @@
         <v>3478</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4287,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9851</v>
+        <v>9852</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>2</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4343,20 +4343,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>17936</v>
+        <v>17939</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4447,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4493,20 +4493,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50841</v>
+        <v>50850</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4547,20 +4547,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22243</v>
+        <v>22247</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>318</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3721</v>
+        <v>3722</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1589</v>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
         <v>636</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>5060</v>
+        <v>5061</v>
       </c>
       <c r="N70" s="3" t="n">
         <v>3178</v>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4777,20 +4777,20 @@
         </is>
       </c>
       <c r="L71" s="3" t="n">
-        <v>4215</v>
+        <v>4216</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>2</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
@@ -4841,20 +4841,20 @@
         </is>
       </c>
       <c r="L72" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1490352</v>
+        <v>1490608</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11439</v>
+        <v>11441</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4895,20 +4895,20 @@
         </is>
       </c>
       <c r="L73" s="3" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7510</v>
+        <v>7512</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -4949,20 +4949,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8738</v>
+        <v>8740</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21050</v>
+        <v>21053</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17477</v>
+        <v>17480</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5003,20 +5003,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17477</v>
+        <v>17480</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27171</v>
+        <v>27176</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5070,7 @@
         <v>159</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6403</v>
+        <v>6404</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>318</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
         <v>1192</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5210</v>
+        <v>5211</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>636</v>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5182,7 +5182,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5223,20 +5223,20 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5720</v>
+        <v>5721</v>
       </c>
       <c r="N79" s="3" t="n">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="O79" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5279,12 +5279,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5325,20 +5325,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23238</v>
+        <v>23242</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23238</v>
+        <v>23242</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20337</v>
+        <v>20340</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5405,18 +5405,18 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
@@ -5433,20 +5433,20 @@
       </c>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="3" t="n">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1588632</v>
+        <v>1588904</v>
       </c>
       <c r="N83" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
         <v>775</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34731</v>
+        <v>34737</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1589</v>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5543,10 +5543,10 @@
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="3" t="n">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>3168</v>
+        <v>3169</v>
       </c>
       <c r="N85" s="3" t="n">
         <v>3178</v>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5596,17 +5596,17 @@
         <v>1271</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5645,12 +5645,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5693,14 +5693,14 @@
         <v>3178</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17477</v>
+        <v>17480</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5794,17 +5794,17 @@
         <v>497</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86348</v>
+        <v>86362</v>
       </c>
       <c r="N90" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O90" s="2" t="n">
         <v>60</v>
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
         <v>826</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>5281</v>
+        <v>5282</v>
       </c>
       <c r="N91" s="3" t="n">
         <v>1589</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5901,10 +5901,10 @@
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="N92" s="3" t="n">
         <v>3178</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5953,12 +5953,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -5997,12 +5997,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6041,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17477</v>
+        <v>17480</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6134,7 @@
         <v>1608</v>
       </c>
       <c r="M97" s="3" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="N97" s="3" t="n">
         <v>2860</v>
@@ -6144,7 +6144,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6185,20 +6185,20 @@
         </is>
       </c>
       <c r="L98" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="M98" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6239,20 +6239,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4739</v>
+        <v>4740</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5200</v>
+        <v>5201</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9851</v>
+        <v>9852</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6293,20 +6293,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6349,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6395,20 +6395,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18050</v>
+        <v>18053</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18050</v>
+        <v>18053</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6451,12 +6451,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50841</v>
+        <v>50850</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6553,12 +6553,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6601,12 +6601,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9851</v>
+        <v>9852</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -6659,12 +6659,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6707,12 +6707,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50841</v>
+        <v>50850</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6851,12 +6851,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79440</v>
+        <v>79453</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6897,20 +6897,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87383</v>
+        <v>87398</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>111215</v>
+        <v>111234</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>111215</v>
+        <v>111234</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -6951,20 +6951,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>111215</v>
+        <v>111234</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>111215</v>
+        <v>111234</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>142991</v>
+        <v>143016</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>14</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7005,20 +7005,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7059,20 +7059,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>190655</v>
+        <v>190688</v>
       </c>
       <c r="O115" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7113,20 +7113,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>214487</v>
+        <v>214524</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7173,14 +7173,14 @@
         <v>2277</v>
       </c>
       <c r="N117" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O117" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7221,20 +7221,20 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>5875</v>
+        <v>5876</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O118" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7277,12 +7277,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7323,20 +7323,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22879</v>
+        <v>22883</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7425,20 +7425,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19104</v>
+        <v>19107</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7479,20 +7479,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41248</v>
+        <v>41255</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7539,14 +7539,14 @@
         <v>1934</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O124" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7590,17 +7590,17 @@
         <v>2247</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5705</v>
+        <v>5706</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O125" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7641,20 +7641,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6489</v>
+        <v>6490</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6489</v>
+        <v>6490</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7695,20 +7695,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11937</v>
+        <v>11939</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7751,12 +7751,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22879</v>
+        <v>22883</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7797,20 +7797,20 @@
         </is>
       </c>
       <c r="L129" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O129" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7858,7 +7858,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -7936,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -7957,20 +7957,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -8021,20 +8021,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15975</v>
+        <v>15978</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8077,12 +8077,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8123,20 +8123,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21449</v>
+        <v>21452</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21449</v>
+        <v>21452</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47664</v>
+        <v>47672</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8155,7 +8155,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8187,20 +8187,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71496</v>
+        <v>71508</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8241,20 +8241,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8273,18 +8273,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F138" s="2" t="n">
         <v>10</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8305,20 +8305,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6355</v>
+        <v>6811</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12801</v>
+        <v>12803</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8345,10 +8345,10 @@
         </is>
       </c>
       <c r="F139" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>1058</v>
       </c>
       <c r="M139" s="3" t="n">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="N139" s="3" t="n">
         <v>318</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>6</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8433,20 +8433,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="M140" s="3" t="n">
-        <v>5187</v>
+        <v>5188</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8510,7 +8510,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
         </is>
       </c>
       <c r="L142" s="3" t="n">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="M142" s="3" t="n">
         <v>1589</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8593,7 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="G143" s="3" t="n">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="L143" s="3" t="n">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3178</v>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8692,17 +8692,17 @@
         <v>2153</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10785</v>
+        <v>10787</v>
       </c>
       <c r="N144" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O144" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8745,12 +8745,12 @@
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="3" t="inlineStr"/>
       <c r="N145" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8804,17 +8804,17 @@
         <v>4449</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53730</v>
+        <v>53739</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8857,12 +8857,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8903,20 +8903,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>17410</v>
+        <v>17413</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8959,12 +8959,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -8991,10 +8991,10 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -9015,20 +9015,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39720</v>
+        <v>39727</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9047,7 +9047,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9079,20 +9079,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>115891</v>
+        <v>115911</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>76262</v>
+        <v>76275</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9110,13 +9110,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D152" s="3" t="inlineStr"/>
-      <c r="E152" s="2" t="inlineStr"/>
-      <c r="F152" s="2" t="inlineStr"/>
-      <c r="G152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="n">
+        <v>103289</v>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>103289</v>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I152" s="2" t="n">
@@ -9133,20 +9143,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>206543</v>
+        <v>206578</v>
       </c>
       <c r="O152" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9169,11 +9179,11 @@
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F153" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G153" s="3" t="n">
         <v>159</v>
@@ -9200,17 +9210,17 @@
         <v>159</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10394</v>
+        <v>10396</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O153" s="2" t="n">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9284,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9311,10 +9321,10 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15567</v>
+        <v>15570</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1589</v>
@@ -9324,7 +9334,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9374,7 +9384,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9424,17 +9434,17 @@
         <v>3178</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O157" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9475,20 +9485,20 @@
         </is>
       </c>
       <c r="L158" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19423</v>
+        <v>19426</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1589</v>
       </c>
       <c r="O158" s="2" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9542,17 +9552,17 @@
         <v>1589</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19267</v>
+        <v>19271</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3178</v>
       </c>
       <c r="O159" s="2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9596,17 +9606,17 @@
         <v>3178</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6646</v>
+        <v>6647</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9670,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9714,7 +9724,7 @@
         <v>1743</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30314</v>
+        <v>30319</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1589</v>
@@ -9724,7 +9734,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9753,7 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
@@ -9754,7 +9764,7 @@
         <v>3</v>
       </c>
       <c r="G163" s="3" t="n">
-        <v>3342</v>
+        <v>3343</v>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
@@ -9775,10 +9785,10 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>2807</v>
+        <v>2808</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3813</v>
+        <v>3814</v>
       </c>
       <c r="N163" s="3" t="n">
         <v>3178</v>
@@ -9788,7 +9798,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9807,11 +9817,11 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3444</v>
+        <v>3648</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
@@ -9842,17 +9852,17 @@
         <v>3178</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>14555</v>
+        <v>14557</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9871,18 +9881,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9903,20 +9913,20 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4933</v>
+        <v>4934</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9990,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10034,7 +10044,7 @@
         <v>1398</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9765</v>
+        <v>9766</v>
       </c>
       <c r="N167" s="3" t="n">
         <v>1271</v>
@@ -10044,7 +10054,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10088,7 +10098,7 @@
         <v>1589</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5418</v>
+        <v>5419</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>318</v>
@@ -10098,7 +10108,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10162,7 @@
         <v>313</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>318</v>
@@ -10162,7 +10172,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10203,20 +10213,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>95327</v>
+        <v>95344</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>95327</v>
+        <v>95344</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10269,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10301,20 +10311,20 @@
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="M172" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="N172" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O172" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10333,7 +10343,7 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
@@ -10344,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="G173" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
@@ -10364,17 +10374,17 @@
         <v>2717</v>
       </c>
       <c r="M173" s="3" t="n">
-        <v>3384</v>
+        <v>3385</v>
       </c>
       <c r="N173" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O173" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10413,12 +10423,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10455,20 +10465,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14269</v>
+        <v>14271</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10505,20 +10515,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11439</v>
+        <v>11441</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11439</v>
+        <v>11441</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22879</v>
+        <v>22883</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10555,20 +10565,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15967</v>
+        <v>15970</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10605,20 +10615,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19224</v>
+        <v>19228</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10676,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10707,20 +10717,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10763,12 +10773,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10809,20 +10819,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10865,12 +10875,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10911,20 +10921,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21449</v>
+        <v>21452</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21449</v>
+        <v>21452</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42897</v>
+        <v>42905</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -10965,20 +10975,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28598</v>
+        <v>28603</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>57196</v>
+        <v>57206</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11022,7 +11032,7 @@
         <v>159</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>318</v>
@@ -11032,7 +11042,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11076,7 +11086,7 @@
         <v>159</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>318</v>
@@ -11086,7 +11096,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11140,7 +11150,7 @@
         <v>159</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>103370</v>
+        <v>103388</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>318</v>
@@ -11150,7 +11160,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11198,7 +11208,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11252,7 @@
         <v>159</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29304</v>
+        <v>29309</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>318</v>
@@ -11252,7 +11262,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11306,17 +11316,17 @@
         <v>159</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>156866</v>
+        <v>156893</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11360,7 +11370,7 @@
         <v>159</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>318</v>
@@ -11370,7 +11380,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11418,7 +11428,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11472,7 @@
         <v>159</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>318</v>
@@ -11472,7 +11482,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11516,7 +11526,7 @@
         <v>159</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>158720</v>
+        <v>158747</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>318</v>
@@ -11526,7 +11536,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11580,17 +11590,17 @@
         <v>159</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N196" s="3" t="n">
-        <v>914</v>
+        <v>318</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11648,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11657,18 +11667,18 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>904</v>
+        <v>1166</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>904</v>
+        <v>992</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11689,20 +11699,20 @@
         </is>
       </c>
       <c r="L198" s="3" t="n">
-        <v>1166</v>
+        <v>1271</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N198" s="3" t="n">
-        <v>318</v>
+        <v>1282</v>
       </c>
       <c r="O198" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11743,20 +11753,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20689</v>
+        <v>20693</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20689</v>
+        <v>20693</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11810,17 +11820,17 @@
         <v>4449</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6335</v>
+        <v>6336</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11849,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -11850,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -11871,20 +11881,20 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10824</v>
+        <v>10826</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7626</v>
+        <v>7628</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11925,20 +11935,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10397</v>
+        <v>10399</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -11979,20 +11989,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8262</v>
+        <v>8263</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>277355</v>
+        <v>277403</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12033,20 +12043,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15699</v>
+        <v>15702</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16114</v>
+        <v>16116</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12087,20 +12097,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20337</v>
+        <v>20340</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>49013</v>
+        <v>49021</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12143,12 +12153,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22879</v>
+        <v>22883</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12222,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12276,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12313,14 +12323,14 @@
         <v>3016</v>
       </c>
       <c r="N209" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O209" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12349,7 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
@@ -12350,7 +12360,7 @@
         <v>1</v>
       </c>
       <c r="G210" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
@@ -12371,20 +12381,20 @@
         </is>
       </c>
       <c r="L210" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="M210" s="3" t="n">
         <v>4492</v>
       </c>
       <c r="N210" s="3" t="n">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="O210" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12425,20 +12435,20 @@
         </is>
       </c>
       <c r="L211" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12479,20 +12489,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12535,12 +12545,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22879</v>
+        <v>22883</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12581,20 +12591,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12641,14 +12651,14 @@
         <v>2744</v>
       </c>
       <c r="N215" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O215" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12689,20 +12699,20 @@
         </is>
       </c>
       <c r="L216" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11930</v>
+        <v>11932</v>
       </c>
       <c r="N216" s="3" t="n">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="O216" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12721,7 +12731,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12732,7 +12742,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12753,20 +12763,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15643</v>
+        <v>15646</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37638</v>
+        <v>37645</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12807,20 +12817,20 @@
         </is>
       </c>
       <c r="L218" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>6778</v>
+        <v>6779</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12861,20 +12871,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7150</v>
+        <v>7151</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14299</v>
+        <v>14302</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12917,12 +12927,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -12963,20 +12973,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13030,7 +13040,7 @@
         <v>885</v>
       </c>
       <c r="M222" s="3" t="n">
-        <v>2853</v>
+        <v>2854</v>
       </c>
       <c r="N222" s="3" t="n">
         <v>1589</v>
@@ -13040,7 +13050,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13100,11 +13110,11 @@
         <v>3178</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13158,17 +13168,17 @@
         <v>3178</v>
       </c>
       <c r="M224" s="3" t="n">
-        <v>7231</v>
+        <v>7232</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13219,7 +13229,7 @@
         </is>
       </c>
       <c r="L225" s="3" t="n">
-        <v>1552</v>
+        <v>795</v>
       </c>
       <c r="M225" s="3" t="n">
         <v>1824</v>
@@ -13228,11 +13238,11 @@
         <v>1589</v>
       </c>
       <c r="O225" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13250,23 +13260,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D226" s="3" t="n">
-        <v>1891</v>
-      </c>
-      <c r="E226" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G226" s="3" t="n">
-        <v>1891</v>
-      </c>
+      <c r="D226" s="3" t="inlineStr"/>
+      <c r="E226" s="2" t="inlineStr"/>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="3" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I226" s="2" t="n">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13353,14 +13353,14 @@
         <v>3799</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13404,7 +13404,7 @@
         <v>159</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>318</v>
@@ -13414,7 +13414,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13458,7 @@
         <v>159</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>318</v>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13522,17 +13522,17 @@
         <v>159</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13573,20 +13573,20 @@
         </is>
       </c>
       <c r="L231" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1589</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13640,7 +13640,7 @@
         <v>1589</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3916</v>
+        <v>3917</v>
       </c>
       <c r="N232" s="3" t="n">
         <v>3178</v>
@@ -13650,7 +13650,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13694,17 +13694,17 @@
         <v>3178</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7239</v>
+        <v>7240</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O233" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>377</v>
       </c>
       <c r="M234" s="3" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N234" s="3" t="n">
         <v>318</v>
@@ -13768,7 +13768,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13809,10 +13809,10 @@
         </is>
       </c>
       <c r="L235" s="3" t="n">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4282</v>
+        <v>4283</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3178</v>
@@ -13822,7 +13822,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13863,20 +13863,20 @@
         </is>
       </c>
       <c r="L236" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6552</v>
+        <v>6553</v>
       </c>
       <c r="N236" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O236" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13919,12 +13919,12 @@
       <c r="L237" s="3" t="inlineStr"/>
       <c r="M237" s="3" t="inlineStr"/>
       <c r="N237" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -13975,20 +13975,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8738</v>
+        <v>8740</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11075</v>
+        <v>11077</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14031,12 +14031,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14077,20 +14077,20 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10524</v>
+        <v>10526</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10524</v>
+        <v>10526</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14109,7 +14109,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>18436</v>
+        <v>18439</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14117,10 +14117,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>21150</v>
+        <v>21514</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14141,20 +14141,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>18325</v>
+        <v>17953</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>34941</v>
+        <v>34947</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14173,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14184,7 +14184,7 @@
         <v>3</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38157</v>
+        <v>38164</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14205,20 +14205,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>58868</v>
+        <v>58878</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>76262</v>
+        <v>76275</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>17111</v>
+        <v>17114</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
         <v>9</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>17047</v>
+        <v>17050</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14265,20 +14265,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>16816</v>
+        <v>16498</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31775810</v>
+        <v>31781265</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O243" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14321,12 +14321,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14399,18 +14399,18 @@
         </is>
       </c>
       <c r="D246" s="3" t="n">
-        <v>2019</v>
+        <v>2188</v>
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2138</v>
+        <v>2143</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14431,20 +14431,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2210</v>
+        <v>2183</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2193</v>
+        <v>2279</v>
       </c>
       <c r="O246" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14485,20 +14485,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23425</v>
+        <v>23429</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17794</v>
+        <v>17798</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14517,7 +14517,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14528,7 +14528,7 @@
         <v>1</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -14549,20 +14549,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>17794</v>
+        <v>17798</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14581,7 +14581,7 @@
         </is>
       </c>
       <c r="D249" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>1</v>
       </c>
       <c r="G249" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
@@ -14609,10 +14609,10 @@
       </c>
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M249" s="3" t="n">
-        <v>9328</v>
+        <v>9329</v>
       </c>
       <c r="N249" s="3" t="n">
         <v>1589</v>
@@ -14622,7 +14622,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14659,10 +14659,10 @@
       </c>
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="3" t="n">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="M250" s="3" t="n">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="N250" s="3" t="n">
         <v>1589</v>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14716,7 +14716,7 @@
         <v>159</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97696</v>
+        <v>97713</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>318</v>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14777,20 +14777,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50625</v>
+        <v>50634</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50625</v>
+        <v>50634</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14809,18 +14809,18 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>6690</v>
+        <v>7577</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F253" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>5887</v>
+        <v>6451</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14840,21 +14840,15 @@
           <t>Outfit / Set</t>
         </is>
       </c>
-      <c r="L253" s="3" t="n">
-        <v>7575</v>
-      </c>
-      <c r="M253" s="3" t="n">
-        <v>7575</v>
-      </c>
+      <c r="L253" s="3" t="inlineStr"/>
+      <c r="M253" s="3" t="inlineStr"/>
       <c r="N253" s="3" t="n">
-        <v>7626</v>
-      </c>
-      <c r="O253" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>8333</v>
+      </c>
+      <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14895,20 +14889,20 @@
         </is>
       </c>
       <c r="L254" s="3" t="n">
-        <v>7898</v>
+        <v>7899</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>190655</v>
+        <v>190688</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14943,7 @@
         </is>
       </c>
       <c r="L255" s="3" t="n">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="M255" s="3" t="n">
         <v>1589</v>
@@ -14962,7 +14956,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -14980,23 +14974,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D256" s="3" t="n">
-        <v>451</v>
-      </c>
-      <c r="E256" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="F256" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G256" s="3" t="n">
-        <v>451</v>
-      </c>
+      <c r="D256" s="3" t="inlineStr"/>
+      <c r="E256" s="2" t="inlineStr"/>
+      <c r="F256" s="2" t="inlineStr"/>
+      <c r="G256" s="3" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I256" s="2" t="n">
@@ -15020,7 +15004,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15064,7 +15048,7 @@
         <v>292</v>
       </c>
       <c r="M257" s="3" t="n">
-        <v>7944</v>
+        <v>7945</v>
       </c>
       <c r="N257" s="3" t="n">
         <v>318</v>
@@ -15074,7 +15058,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15097,14 +15081,14 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>1015</v>
+        <v>1043</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15134,11 +15118,11 @@
         <v>636</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15157,7 +15141,7 @@
         </is>
       </c>
       <c r="D259" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -15168,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="G259" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
@@ -15189,10 +15173,10 @@
         </is>
       </c>
       <c r="L259" s="3" t="n">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21485</v>
+        <v>21489</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1589</v>
@@ -15202,7 +15186,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15256,7 +15240,7 @@
         <v>1589</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3689</v>
+        <v>3690</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3178</v>
@@ -15266,7 +15250,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15320,17 +15304,17 @@
         <v>3178</v>
       </c>
       <c r="M261" s="3" t="n">
-        <v>7048</v>
+        <v>7049</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15349,18 +15333,18 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6355</v>
+        <v>7829</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G262" s="3" t="n">
-        <v>6355</v>
+        <v>6461</v>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
@@ -15381,20 +15365,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15435,10 +15419,10 @@
         </is>
       </c>
       <c r="L263" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M263" s="3" t="n">
-        <v>10610</v>
+        <v>10612</v>
       </c>
       <c r="N263" s="3" t="n">
         <v>1589</v>
@@ -15448,7 +15432,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15496,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15555,12 +15539,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15578,23 +15562,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D266" s="3" t="n">
-        <v>6355</v>
-      </c>
-      <c r="E266" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G266" s="3" t="n">
-        <v>6355</v>
-      </c>
+      <c r="D266" s="3" t="inlineStr"/>
+      <c r="E266" s="2" t="inlineStr"/>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="3" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
@@ -15611,20 +15585,20 @@
         </is>
       </c>
       <c r="L266" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>9682</v>
+        <v>9684</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15643,18 +15617,18 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>1838</v>
+        <v>3178</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>1871</v>
+        <v>2035</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15678,17 +15652,17 @@
         <v>2717</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19541</v>
+        <v>19544</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2021</v>
+        <v>2759</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15729,20 +15703,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8262</v>
+        <v>8263</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14312</v>
+        <v>14314</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15785,12 +15759,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15831,20 +15805,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15885,20 +15859,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24731</v>
+        <v>24735</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>38511</v>
+        <v>38517</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15942,7 +15916,7 @@
         <v>159</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>9750</v>
+        <v>9752</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>318</v>
@@ -15952,7 +15926,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -15971,7 +15945,7 @@
         </is>
       </c>
       <c r="D273" s="3" t="n">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
@@ -16006,17 +15980,17 @@
         <v>159</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21042</v>
+        <v>21046</v>
       </c>
       <c r="N273" s="3" t="n">
-        <v>1155</v>
+        <v>1278</v>
       </c>
       <c r="O273" s="2" t="n">
         <v>190</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16060,17 +16034,17 @@
         <v>159</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31881</v>
+        <v>31886</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16088,7 @@
         <v>159</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>15967</v>
+        <v>15970</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>318</v>
@@ -16124,7 +16098,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16143,7 +16117,7 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>2966</v>
+        <v>2967</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
@@ -16154,7 +16128,7 @@
         <v>5</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>15057</v>
+        <v>15060</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16178,17 +16152,17 @@
         <v>159</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>158401</v>
+        <v>158428</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16181,7 @@
         </is>
       </c>
       <c r="D277" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
@@ -16218,7 +16192,7 @@
         <v>2</v>
       </c>
       <c r="G277" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
@@ -16235,7 +16209,7 @@
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="3" t="n">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M277" s="3" t="n">
         <v>2121</v>
@@ -16244,11 +16218,11 @@
         <v>1589</v>
       </c>
       <c r="O277" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16292,17 +16266,17 @@
         <v>4449</v>
       </c>
       <c r="M278" s="3" t="n">
-        <v>6908</v>
+        <v>6909</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>25</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16343,20 +16317,20 @@
         </is>
       </c>
       <c r="L279" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9941</v>
+        <v>9943</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7626</v>
+        <v>7628</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16397,20 +16371,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="M280" s="3" t="n">
-        <v>8646</v>
+        <v>8648</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10168</v>
+        <v>10170</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16453,12 +16427,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>13981</v>
+        <v>13984</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16501,12 +16475,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16549,12 +16523,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16595,20 +16569,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>33365</v>
+        <v>33370</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33876</v>
+        <v>33882</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16627,7 +16601,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>8980</v>
+        <v>8981</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -16635,10 +16609,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9927</v>
+        <v>9962</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16659,20 +16633,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>8942</v>
+        <v>8943</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>9878</v>
+        <v>318</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16699,7 +16673,7 @@
         </is>
       </c>
       <c r="F286" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G286" s="3" t="n">
         <v>159</v>
@@ -16736,7 +16710,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16783,20 +16757,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>4787</v>
+        <v>4788</v>
       </c>
       <c r="M287" s="3" t="n">
-        <v>5799</v>
+        <v>5800</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5137</v>
+        <v>5150</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16789,7 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>7367</v>
+        <v>7368</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
@@ -16826,7 +16800,7 @@
         <v>24</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6833</v>
+        <v>6834</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16843,20 +16817,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>8675</v>
+        <v>8676</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8676</v>
+        <v>8678</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>7688</v>
+        <v>7758</v>
       </c>
       <c r="O288" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16849,7 @@
         </is>
       </c>
       <c r="D289" s="3" t="n">
-        <v>9472</v>
+        <v>9474</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
@@ -16886,7 +16860,7 @@
         <v>14</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9141</v>
+        <v>9142</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16903,20 +16877,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>9606</v>
+        <v>9607</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11625</v>
+        <v>11627</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>10049</v>
+        <v>10059</v>
       </c>
       <c r="O289" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -16970,7 +16944,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17021,20 +16995,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>3398</v>
+        <v>3399</v>
       </c>
       <c r="M291" s="3" t="n">
-        <v>5084</v>
+        <v>5085</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3724</v>
+        <v>3725</v>
       </c>
       <c r="O291" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17027,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -17064,7 +17038,7 @@
         <v>6</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17085,20 +17059,20 @@
         </is>
       </c>
       <c r="L292" s="3" t="n">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5561</v>
+        <v>5562</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17142,7 +17116,7 @@
         <v>254</v>
       </c>
       <c r="M293" s="3" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N293" s="3" t="n">
         <v>318</v>
@@ -17152,7 +17126,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17171,18 +17145,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>6288</v>
+        <v>8625</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5578</v>
+        <v>5688</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17203,20 +17177,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>8730</v>
+        <v>8443</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>28408</v>
+        <v>28412</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6376</v>
+        <v>6744</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17257,20 +17231,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51640</v>
+        <v>51649</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>701834</v>
+        <v>701954</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39720</v>
+        <v>39727</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17289,7 +17263,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17300,7 +17274,7 @@
         <v>4</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17321,20 +17295,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>69079</v>
+        <v>69091</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39720</v>
+        <v>39727</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17353,7 +17327,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63552</v>
+        <v>63563</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17364,7 +17338,7 @@
         <v>6</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63552</v>
+        <v>63563</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17385,20 +17359,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63552</v>
+        <v>63563</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79440</v>
+        <v>79453</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17417,7 +17391,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17428,7 +17402,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17449,20 +17423,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>127103</v>
+        <v>127125</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>127370</v>
+        <v>127392</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>158879</v>
+        <v>158906</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17455,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17492,7 +17466,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17513,20 +17487,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>254206</v>
+        <v>254250</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>256655</v>
+        <v>256699</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>317758</v>
+        <v>317813</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17545,7 +17519,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>444861</v>
+        <v>444938</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17556,7 +17530,7 @@
         <v>5</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>444861</v>
+        <v>444938</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17577,20 +17551,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>444861</v>
+        <v>444938</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>947234</v>
+        <v>947396</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>635516</v>
+        <v>635625</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17609,18 +17583,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3159</v>
+        <v>2406</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>4674</v>
+        <v>4572</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17644,17 +17618,17 @@
         <v>2231</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>32275</v>
+        <v>32280</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>4530</v>
+        <v>4497</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17673,18 +17647,18 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>1165</v>
+        <v>1732</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1960</v>
+        <v>1946</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17705,20 +17679,20 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>2065</v>
+        <v>1843</v>
       </c>
       <c r="M302" s="3" t="n">
-        <v>4819</v>
+        <v>4820</v>
       </c>
       <c r="N302" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O302" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17737,7 +17711,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17745,10 +17719,10 @@
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4396</v>
+        <v>4451</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17769,20 +17743,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4528</v>
+        <v>3880</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15886</v>
+        <v>15889</v>
       </c>
       <c r="N303" s="3" t="n">
         <v>4646</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17801,7 +17775,7 @@
         </is>
       </c>
       <c r="D304" s="3" t="n">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
@@ -17812,7 +17786,7 @@
         <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17836,7 +17810,7 @@
         <v>2420</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2531</v>
@@ -17846,7 +17820,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17903,14 +17877,14 @@
         <v>1468</v>
       </c>
       <c r="N305" s="3" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O305" s="2" t="n">
         <v>664</v>
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -17937,10 +17911,10 @@
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>1285</v>
+        <v>1379</v>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
@@ -17964,17 +17938,17 @@
         <v>159</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>17986</v>
+        <v>17732</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18018,7 +17992,7 @@
         <v>1370</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>318</v>
@@ -18028,7 +18002,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18047,7 +18021,7 @@
         </is>
       </c>
       <c r="D308" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
@@ -18058,7 +18032,7 @@
         <v>1</v>
       </c>
       <c r="G308" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
@@ -18079,20 +18053,20 @@
         </is>
       </c>
       <c r="L308" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1271032</v>
+        <v>1271251</v>
       </c>
       <c r="N308" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O308" s="2" t="n">
         <v>231</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18146,17 +18120,17 @@
         <v>4449</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32125</v>
+        <v>32131</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O309" s="2" t="n">
         <v>125</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18174,7 @@
         <v>1589</v>
       </c>
       <c r="M310" s="3" t="n">
-        <v>6053</v>
+        <v>6054</v>
       </c>
       <c r="N310" s="3" t="n">
         <v>3178</v>
@@ -18210,7 +18184,7 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18251,20 +18225,20 @@
         </is>
       </c>
       <c r="L311" s="3" t="n">
-        <v>4865</v>
+        <v>4866</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6063</v>
+        <v>6064</v>
       </c>
       <c r="N311" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="O311" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18307,12 +18281,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18331,7 +18305,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18342,7 +18316,7 @@
         <v>1</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18363,20 +18337,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26269</v>
+        <v>26274</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>45</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18417,20 +18391,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15543</v>
+        <v>15546</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15543</v>
+        <v>15546</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18449,7 +18423,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18460,7 +18434,7 @@
         <v>11</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18481,20 +18455,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18513,7 +18487,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18524,7 +18498,7 @@
         <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18545,20 +18519,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38131</v>
+        <v>38138</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>76262</v>
+        <v>76275</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18577,7 +18551,7 @@
         </is>
       </c>
       <c r="D317" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
@@ -18588,7 +18562,7 @@
         <v>1</v>
       </c>
       <c r="G317" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="H317" s="2" t="inlineStr">
         <is>
@@ -18609,20 +18583,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>206543</v>
+        <v>206578</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18686,7 +18660,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18714,7 @@
         <v>1352</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15780</v>
+        <v>15783</v>
       </c>
       <c r="N319" s="3" t="n">
         <v>1487</v>
@@ -18750,7 +18724,7 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18769,7 +18743,7 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>2998</v>
+        <v>2999</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
@@ -18801,20 +18775,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9871</v>
+        <v>9873</v>
       </c>
       <c r="N320" s="3" t="n">
-        <v>2920</v>
+        <v>3054</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18833,18 +18807,18 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>3654</v>
+        <v>291</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>3729</v>
+        <v>2583</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18868,17 +18842,17 @@
         <v>3494</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>9676</v>
+        <v>9677</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O321" s="2" t="n">
         <v>29</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18929,7 +18903,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1041</v>
@@ -18942,7 +18916,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -18961,7 +18935,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>3808</v>
+        <v>3809</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18993,20 +18967,20 @@
         </is>
       </c>
       <c r="L323" s="3" t="n">
-        <v>3109</v>
+        <v>3010</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16576</v>
+        <v>16579</v>
       </c>
       <c r="N323" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O323" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19034,7 @@
         <v>318</v>
       </c>
       <c r="M324" s="3" t="n">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="N324" s="3" t="n">
         <v>318</v>
@@ -19070,7 +19044,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19089,18 +19063,18 @@
         </is>
       </c>
       <c r="D325" s="3" t="n">
-        <v>3178</v>
+        <v>2830</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2078</v>
+        <v>2167</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19124,17 +19098,17 @@
         <v>2326</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15780</v>
+        <v>15783</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2690</v>
+        <v>2860</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19138,7 @@
         <v>8</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19188,17 +19162,17 @@
         <v>2137</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O326" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19217,18 +19191,18 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>1449</v>
+        <v>1935</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F327" s="2" t="n">
         <v>7</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2911</v>
+        <v>2718</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19249,20 +19223,20 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>1935</v>
+        <v>2628</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N327" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O327" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19281,18 +19255,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>23015</v>
+        <v>19409</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22084</v>
+        <v>21728</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19313,20 +19287,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>19405</v>
+        <v>22288</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32747</v>
+        <v>32752</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>23147</v>
+        <v>23552</v>
       </c>
       <c r="O328" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19345,18 +19319,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7672</v>
+        <v>6860</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7055</v>
+        <v>7073</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19377,20 +19351,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7469</v>
+        <v>6299</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>19405</v>
+        <v>19409</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8157</v>
+        <v>8215</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19383,7 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
@@ -19417,10 +19391,10 @@
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5506</v>
+        <v>5514</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19444,17 +19418,17 @@
         <v>5539</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8694</v>
+        <v>8695</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6342</v>
+        <v>6390</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19505,7 +19479,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3178</v>
@@ -19514,11 +19488,11 @@
         <v>318</v>
       </c>
       <c r="O331" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19537,18 +19511,18 @@
         </is>
       </c>
       <c r="D332" s="3" t="n">
-        <v>979</v>
+        <v>968</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F332" s="2" t="n">
         <v>14</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19572,17 +19546,17 @@
         <v>968</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="O332" s="2" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19609,10 +19583,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19646,7 +19620,7 @@
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19673,10 +19647,10 @@
         </is>
       </c>
       <c r="F334" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
@@ -19700,7 +19674,7 @@
         <v>329</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9463</v>
+        <v>9464</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>367</v>
@@ -19710,7 +19684,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19714,7 @@
         <v>9</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19761,20 +19735,20 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="N335" s="3" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="O335" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19771,7 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
@@ -19825,7 +19799,7 @@
         </is>
       </c>
       <c r="L336" s="3" t="n">
-        <v>159</v>
+        <v>316</v>
       </c>
       <c r="M336" s="3" t="n">
         <v>2911</v>
@@ -19834,11 +19808,11 @@
         <v>318</v>
       </c>
       <c r="O336" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19861,14 +19835,14 @@
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="F337" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19892,17 +19866,17 @@
         <v>159</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15556</v>
+        <v>15559</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -19956,7 +19930,7 @@
         <v>240</v>
       </c>
       <c r="M338" s="3" t="n">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="N338" s="3" t="n">
         <v>318</v>
@@ -19966,7 +19940,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20017,10 +19991,10 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="M339" s="3" t="n">
-        <v>4731</v>
+        <v>4732</v>
       </c>
       <c r="N339" s="3" t="n">
         <v>318</v>
@@ -20030,7 +20004,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20045,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>680</v>
+        <v>869</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3178</v>
@@ -20080,11 +20054,11 @@
         <v>318</v>
       </c>
       <c r="O340" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20111,10 +20085,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20148,7 +20122,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20212,7 +20186,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20276,7 +20250,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20306,7 +20280,7 @@
         <v>16</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20327,10 +20301,10 @@
         </is>
       </c>
       <c r="L344" s="3" t="n">
-        <v>2823</v>
+        <v>2824</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>57953</v>
+        <v>57963</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3178</v>
@@ -20340,7 +20314,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20359,7 +20333,7 @@
         </is>
       </c>
       <c r="D345" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
@@ -20391,20 +20365,20 @@
         </is>
       </c>
       <c r="L345" s="3" t="n">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1588791</v>
+        <v>1589063</v>
       </c>
       <c r="N345" s="3" t="n">
-        <v>3972</v>
+        <v>3973</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20423,7 +20397,7 @@
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>4153</v>
+        <v>4154</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -20434,7 +20408,7 @@
         <v>2</v>
       </c>
       <c r="G346" s="3" t="n">
-        <v>3665</v>
+        <v>3666</v>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
@@ -20457,12 +20431,12 @@
       <c r="L346" s="3" t="inlineStr"/>
       <c r="M346" s="3" t="inlineStr"/>
       <c r="N346" s="3" t="n">
-        <v>4766</v>
+        <v>4767</v>
       </c>
       <c r="O346" s="2" t="inlineStr"/>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20516,17 +20490,17 @@
         <v>4449</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>8187</v>
+        <v>8188</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6355</v>
+        <v>6356</v>
       </c>
       <c r="O347" s="2" t="n">
         <v>61</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20567,20 +20541,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12710</v>
+        <v>12713</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20599,7 +20573,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20610,7 +20584,7 @@
         <v>2</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20631,20 +20605,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9533</v>
+        <v>9534</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19065</v>
+        <v>19069</v>
       </c>
       <c r="O349" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20663,7 +20637,7 @@
         </is>
       </c>
       <c r="D350" s="3" t="n">
-        <v>12736</v>
+        <v>12738</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -20674,7 +20648,7 @@
         <v>1</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>12736</v>
+        <v>12738</v>
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
@@ -20697,12 +20671,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25421</v>
+        <v>25425</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20721,18 +20695,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16272</v>
+        <v>16172</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20753,20 +20727,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>15888</v>
+        <v>15891</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>37999</v>
+        <v>38006</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31776</v>
+        <v>31781</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20785,7 +20759,7 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>44914</v>
+        <v>44921</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
@@ -20793,10 +20767,10 @@
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>42273</v>
+        <v>42412</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20817,20 +20791,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>45992</v>
+        <v>46000</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>76262</v>
+        <v>76275</v>
       </c>
       <c r="O352" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20849,7 +20823,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>103271</v>
+        <v>103289</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20860,7 +20834,7 @@
         <v>2</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>104597</v>
+        <v>104615</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20883,12 +20857,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>206543</v>
+        <v>206578</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20907,18 +20881,18 @@
         </is>
       </c>
       <c r="D354" s="3" t="n">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="E354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F354" s="2" t="n">
         <v>3</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
@@ -20942,17 +20916,17 @@
         <v>386</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9415</v>
+        <v>9417</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="O354" s="2" t="n">
         <v>272</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -20993,20 +20967,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19026</v>
+        <v>19029</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17794</v>
+        <v>17798</v>
       </c>
       <c r="O355" s="2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -21025,7 +20999,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -21036,7 +21010,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -21057,20 +21031,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8897</v>
+        <v>8899</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55608</v>
+        <v>55617</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17794</v>
+        <v>17798</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>51</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21098,7 @@
         <v>478</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>4887</v>
+        <v>4888</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>532</v>
@@ -21134,7 +21108,7 @@
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21138,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>158.879052</v>
+        <v>158.906325</v>
       </c>
     </row>
     <row r="2">
@@ -21175,7 +21149,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sun, 23 Aug 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Mon, 24 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21187,7 +21161,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3304</v>
+        <v>3877</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3566</v>
+        <v>3587</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3878</v>
+        <v>4454</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>97349</v>
+        <v>97342</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23887</v>
+        <v>23885</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24152</v>
+        <v>24151</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -797,15 +797,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="n">
+        <v>23885</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>23885</v>
+      </c>
       <c r="N5" s="3" t="n">
-        <v>47774</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
+        <v>47770</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -824,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -835,7 +841,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43531</v>
+        <v>43528</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -856,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>47140</v>
+        <v>47137</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>85993</v>
+        <v>85987</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -888,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -899,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -920,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>143322</v>
+        <v>143311</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -952,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>358305</v>
+        <v>358279</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -963,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>358305</v>
+        <v>358279</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -984,20 +990,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>358305</v>
+        <v>358279</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>358305</v>
+        <v>358279</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>716610</v>
+        <v>716557</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1016,18 +1022,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5824</v>
+        <v>6326</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5702</v>
+        <v>5732</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1048,20 +1054,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6808</v>
+        <v>6333</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8759</v>
+        <v>8758</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1080,18 +1086,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8931</v>
+        <v>9494</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8350</v>
+        <v>8368</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1112,20 +1118,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>9606</v>
+        <v>9019</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>151243</v>
+        <v>151232</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17517</v>
+        <v>17516</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1150,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -1155,7 +1161,7 @@
         <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1176,20 +1182,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42756</v>
+        <v>42753</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35034</v>
+        <v>35032</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1230,20 +1236,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39810</v>
+        <v>21594</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39812</v>
+        <v>39809</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="O12" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1284,20 +1290,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>94623</v>
+        <v>94616</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>94623</v>
+        <v>94616</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1322,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17635</v>
+        <v>17634</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1327,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>17635</v>
+        <v>17634</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1348,20 +1354,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>318493</v>
+        <v>318470</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1402,10 +1408,10 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34520</v>
+        <v>34517</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64512</v>
+        <v>64508</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>5414</v>
@@ -1415,7 +1421,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1439,23 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="n">
+        <v>14704</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>14704</v>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1456,20 +1472,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>14705</v>
+        <v>22693</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64512</v>
+        <v>64508</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5414</v>
+        <v>16173</v>
       </c>
       <c r="O16" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1529,7 @@
         <v>796</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1592</v>
@@ -1523,7 +1539,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1577,17 +1593,17 @@
         <v>1592</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>229329</v>
+        <v>229313</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O18" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1631,17 +1647,17 @@
         <v>3185</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>270719</v>
+        <v>270699</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1676,7 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -1671,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
@@ -1692,20 +1708,20 @@
         </is>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11466</v>
+        <v>11465</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1740,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>11147</v>
+        <v>11146</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1735,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>11147</v>
+        <v>11146</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1756,20 +1772,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>11147</v>
+        <v>11146</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37216</v>
+        <v>37213</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1810,20 +1826,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21498</v>
+        <v>21497</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>140567</v>
+        <v>140557</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1864,20 +1880,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39812</v>
+        <v>39809</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>323806</v>
+        <v>323782</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79623</v>
+        <v>79617</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1896,23 +1912,13 @@
           <t>お宝 / 宝箱</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>2430</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>2430</v>
-      </c>
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -1932,7 +1938,7 @@
         <v>1936</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>318</v>
@@ -1942,7 +1948,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2002,7 @@
         <v>1358</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>1494</v>
@@ -2006,7 +2012,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2076,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2089,18 +2095,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1358</v>
+        <v>1258</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1086</v>
+        <v>1096</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2121,10 +2127,10 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>1258</v>
+        <v>1263</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1588236</v>
+        <v>1588120</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1592</v>
@@ -2134,7 +2140,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2167,7 @@
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>1797</v>
@@ -2185,20 +2191,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2430</v>
+        <v>1592</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2221,11 +2227,11 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>3185</v>
@@ -2252,17 +2258,17 @@
         <v>3185</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17157</v>
+        <v>17156</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2316,17 +2322,17 @@
         <v>637</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1274</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2380,17 +2386,17 @@
         <v>2389</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11617</v>
+        <v>11616</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4777</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2413,14 +2419,14 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1054</v>
+        <v>1017</v>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
@@ -2444,17 +2450,17 @@
         <v>796</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>636986</v>
+        <v>636940</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2505,10 +2511,10 @@
         </is>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2159</v>
+        <v>1900</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12901</v>
+        <v>12900</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3185</v>
@@ -2518,7 +2524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2537,18 +2543,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3752</v>
+        <v>3881</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>53</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3333</v>
+        <v>3360</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2569,20 +2575,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3782</v>
+        <v>3691</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21286</v>
+        <v>21285</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2601,18 +2607,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2633,20 +2639,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30781</v>
+        <v>30779</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2702,7 @@
         <v>796</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6324</v>
+        <v>6323</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1592</v>
@@ -2706,7 +2712,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2772,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2816,17 +2822,17 @@
         <v>3631</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>318493</v>
+        <v>318470</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2886,7 @@
         <v>1592</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>145785</v>
+        <v>145775</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3185</v>
@@ -2890,7 +2896,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2917,10 +2923,10 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>6132</v>
+        <v>4803</v>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
@@ -2941,20 +2947,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4375</v>
+        <v>4374</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17519</v>
+        <v>17517</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2973,18 +2979,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -3005,20 +3011,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>15235</v>
+        <v>15234</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3045,10 +3051,10 @@
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>3298</v>
+        <v>3139</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3065,10 +3071,10 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>4300</v>
+        <v>4299</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6168</v>
+        <v>6167</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>2229</v>
@@ -3078,7 +3084,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3097,7 +3103,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3108,7 +3114,7 @@
         <v>2</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -3125,10 +3131,10 @@
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="3" t="n">
-        <v>6397</v>
+        <v>6396</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8950</v>
+        <v>8949</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>3981</v>
@@ -3138,7 +3144,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3157,7 +3163,7 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>11649</v>
+        <v>11648</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -3165,10 +3171,10 @@
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9330</v>
+        <v>9331</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3185,20 +3191,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>13026</v>
+        <v>10086</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>14589</v>
+        <v>14588</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10338</v>
+        <v>10427</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3268,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3316,17 +3322,17 @@
         <v>3185</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3383,7 @@
         </is>
       </c>
       <c r="L47" s="3" t="n">
-        <v>210</v>
+        <v>780</v>
       </c>
       <c r="M47" s="3" t="n">
         <v>5914</v>
@@ -3386,11 +3392,11 @@
         <v>796</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3447,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2637</v>
@@ -3454,7 +3460,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3505,20 +3511,20 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>1456</v>
+        <v>3105</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3584,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3597,7 +3603,7 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -3608,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
@@ -3628,7 +3634,7 @@
         <v>2516</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4394</v>
+        <v>4393</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1592</v>
@@ -3638,7 +3644,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3663,7 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -3691,14 +3697,14 @@
         <v>7166</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3768,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3780,23 +3786,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>659</v>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>659</v>
-      </c>
+      <c r="D54" s="3" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -3816,7 +3812,7 @@
         <v>1799</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11372</v>
+        <v>11371</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1592</v>
@@ -3826,7 +3822,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3876,7 @@
         <v>4777</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30803</v>
+        <v>30801</v>
       </c>
       <c r="N55" s="3" t="n">
         <v>3185</v>
@@ -3890,7 +3886,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3905,7 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>5340</v>
+        <v>5339</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -3943,12 +3939,12 @@
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -3967,18 +3963,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9069</v>
+        <v>10088</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9465</v>
+        <v>9458</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3999,20 +3995,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>9510</v>
+        <v>9595</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30843</v>
+        <v>30841</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4031,18 +4027,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>4169</v>
+        <v>3201</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3892</v>
+        <v>3873</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4063,20 +4059,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>5340</v>
+        <v>4075</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10396</v>
+        <v>10395</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4222</v>
+        <v>4533</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4095,18 +4091,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>2636</v>
+        <v>1941</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2784</v>
+        <v>2615</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4127,20 +4123,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>2236</v>
+        <v>4290</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>11386</v>
+        <v>11385</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>1592</v>
+        <v>2134</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4177,7 @@
         </is>
       </c>
       <c r="L60" s="3" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="M60" s="3" t="n">
         <v>2866</v>
@@ -4194,7 +4190,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4244,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4292,7 @@
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4347,20 +4343,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>17977</v>
+        <v>17976</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O63" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4403,12 +4399,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4451,12 +4447,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4497,20 +4493,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>50959</v>
+        <v>50955</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4551,20 +4547,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4603,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22295</v>
+        <v>22293</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4652,7 @@
         <v>318</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3730</v>
+        <v>3729</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1592</v>
@@ -4666,7 +4662,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4726,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4787,14 +4783,14 @@
         <v>6346</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4848,17 +4844,17 @@
         <v>2548</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1493800</v>
+        <v>1493691</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11466</v>
+        <v>11465</v>
       </c>
       <c r="O72" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4902,17 +4898,17 @@
         <v>4785</v>
       </c>
       <c r="M73" s="3" t="n">
-        <v>7528</v>
+        <v>7527</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -4953,20 +4949,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8759</v>
+        <v>8758</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21099</v>
+        <v>21097</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17517</v>
+        <v>17516</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5007,20 +5003,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17517</v>
+        <v>17516</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27234</v>
+        <v>27232</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5047,10 +5043,10 @@
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
@@ -5074,7 +5070,7 @@
         <v>159</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6418</v>
+        <v>6417</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>318</v>
@@ -5084,7 +5080,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5128,7 +5124,7 @@
         <v>1194</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5222</v>
+        <v>5221</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>637</v>
@@ -5138,7 +5134,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5182,7 @@
       <c r="O78" s="2" t="inlineStr"/>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5227,10 +5223,10 @@
         </is>
       </c>
       <c r="L79" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>5733</v>
+        <v>5732</v>
       </c>
       <c r="N79" s="3" t="n">
         <v>2548</v>
@@ -5240,7 +5236,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5288,7 +5284,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5329,20 +5325,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>23291</v>
+        <v>23290</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>23291</v>
+        <v>23290</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5385,12 +5381,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20384</v>
+        <v>20382</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5440,17 +5436,17 @@
         <v>159</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1592306</v>
+        <v>1592190</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>796</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5496,7 @@
         <v>779</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34811</v>
+        <v>34809</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1592</v>
@@ -5510,7 +5506,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5556,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5600,17 +5596,17 @@
         <v>1274</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5649,12 +5645,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5697,14 +5693,14 @@
         <v>3185</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5739,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17517</v>
+        <v>17516</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5794,7 @@
         <v>498</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86547</v>
+        <v>86541</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>796</v>
@@ -5808,7 +5804,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5858,7 +5854,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5914,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5953,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6001,12 +5997,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6045,12 +6041,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6089,12 +6085,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17517</v>
+        <v>17516</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6131,7 @@
         </is>
       </c>
       <c r="L97" s="3" t="n">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="M97" s="3" t="n">
         <v>3116</v>
@@ -6148,7 +6144,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6198,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6252,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6303,14 +6299,14 @@
         <v>7166</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6353,12 +6349,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6399,20 +6395,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>18092</v>
+        <v>18091</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>18092</v>
+        <v>18091</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6455,12 +6451,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>50959</v>
+        <v>50955</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6510,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6558,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6610,7 +6606,7 @@
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6663,12 +6659,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6711,12 +6707,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6755,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6807,12 +6803,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>50959</v>
+        <v>50955</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6855,12 +6851,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79623</v>
+        <v>79617</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6901,20 +6897,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87586</v>
+        <v>87579</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>111473</v>
+        <v>97761</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>111473</v>
+        <v>111464</v>
       </c>
       <c r="O112" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -6955,20 +6951,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>111473</v>
+        <v>111464</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>111473</v>
+        <v>111464</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>143322</v>
+        <v>143311</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7009,20 +7005,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7063,20 +7059,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>191096</v>
+        <v>191082</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7117,20 +7113,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>214983</v>
+        <v>214967</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7167,7 @@
         </is>
       </c>
       <c r="L117" s="3" t="n">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="M117" s="3" t="n">
         <v>2282</v>
@@ -7184,7 +7180,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7221,7 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>3819</v>
+        <v>3818</v>
       </c>
       <c r="M118" s="3" t="n">
         <v>5889</v>
@@ -7238,7 +7234,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7282,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7330,17 +7326,17 @@
         <v>7166</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7383,12 +7379,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7429,20 +7425,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19148</v>
+        <v>19146</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7483,20 +7479,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41344</v>
+        <v>41341</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7546,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7590,7 @@
         <v>2252</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>5719</v>
+        <v>5718</v>
       </c>
       <c r="N125" s="3" t="n">
         <v>3981</v>
@@ -7604,7 +7600,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7645,10 +7641,10 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6504</v>
+        <v>6503</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6504</v>
+        <v>6503</v>
       </c>
       <c r="N126" s="3" t="n">
         <v>7962</v>
@@ -7658,7 +7654,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7702,17 +7698,17 @@
         <v>7166</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11964</v>
+        <v>11963</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7755,12 +7751,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7801,20 +7797,20 @@
         </is>
       </c>
       <c r="L129" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M129" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N129" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O129" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7858,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7905,12 +7901,12 @@
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7925,7 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
@@ -7940,7 +7936,7 @@
         <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
@@ -7961,20 +7957,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7989,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -8004,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -8025,20 +8021,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16012</v>
+        <v>16011</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8081,12 +8077,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8127,20 +8123,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21498</v>
+        <v>21497</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21498</v>
+        <v>21497</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47774</v>
+        <v>47770</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8155,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8170,7 +8166,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8191,20 +8187,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71661</v>
+        <v>71656</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8245,20 +8241,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8273,7 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
@@ -8288,7 +8284,7 @@
         <v>10</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6374</v>
+        <v>6373</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8315,14 +8311,14 @@
         <v>12830</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O138" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8382,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8433,7 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>584</v>
+        <v>484</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5199</v>
@@ -8446,11 +8442,11 @@
         <v>562</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8514,7 +8510,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8561,7 @@
         </is>
       </c>
       <c r="L142" s="3" t="n">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="M142" s="3" t="n">
         <v>1592</v>
@@ -8578,7 +8574,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8628,7 @@
         <v>2086</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3185</v>
@@ -8642,7 +8638,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8669,10 +8665,10 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G144" s="3" t="n">
-        <v>2083</v>
+        <v>2070</v>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
@@ -8696,7 +8692,7 @@
         <v>2134</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10810</v>
+        <v>10809</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>3981</v>
@@ -8706,7 +8702,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8754,7 +8750,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8808,17 +8804,17 @@
         <v>4459</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>53854</v>
+        <v>53850</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8857,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8907,20 +8903,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>18446</v>
+        <v>18444</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O148" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8963,12 +8959,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8983,7 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15925</v>
+        <v>15982</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
@@ -8995,7 +8991,7 @@
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G150" s="3" t="n">
         <v>15925</v>
@@ -9019,20 +9015,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39812</v>
+        <v>39809</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9051,7 +9047,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9062,7 +9058,7 @@
         <v>17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9083,20 +9079,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>116159</v>
+        <v>116151</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>76438</v>
+        <v>76433</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9115,7 +9111,7 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -9126,7 +9122,7 @@
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -9147,20 +9143,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>207021</v>
+        <v>207005</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9214,7 +9210,7 @@
         <v>159</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10418</v>
+        <v>10417</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>318</v>
@@ -9224,7 +9220,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9284,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9306,13 +9302,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D155" s="3" t="inlineStr"/>
-      <c r="E155" s="2" t="inlineStr"/>
-      <c r="F155" s="2" t="inlineStr"/>
-      <c r="G155" s="3" t="inlineStr"/>
+      <c r="D155" s="3" t="n">
+        <v>796</v>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>796</v>
+      </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I155" s="2" t="n">
@@ -9325,10 +9331,10 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>796</v>
+        <v>822</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15603</v>
+        <v>15602</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1592</v>
@@ -9338,7 +9344,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9356,13 +9362,23 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr"/>
-      <c r="E156" s="2" t="inlineStr"/>
-      <c r="F156" s="2" t="inlineStr"/>
-      <c r="G156" s="3" t="inlineStr"/>
+      <c r="D156" s="3" t="n">
+        <v>1592</v>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>1592</v>
+      </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
@@ -9375,7 +9391,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="3" t="n">
-        <v>1592</v>
+        <v>1627</v>
       </c>
       <c r="M156" s="3" t="n">
         <v>3261</v>
@@ -9384,11 +9400,11 @@
         <v>3185</v>
       </c>
       <c r="O156" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9438,17 +9454,17 @@
         <v>3185</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9508,7 @@
         <v>796</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>19468</v>
+        <v>19466</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1592</v>
@@ -9502,7 +9518,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9556,7 +9572,7 @@
         <v>1592</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19312</v>
+        <v>19310</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3185</v>
@@ -9566,7 +9582,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9613,14 +9629,14 @@
         <v>6661</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O160" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9690,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9744,7 @@
         <v>1747</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>30384</v>
+        <v>30382</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1592</v>
@@ -9738,7 +9754,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9802,7 +9818,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9821,18 +9837,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4325</v>
+        <v>4610</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3861</v>
+        <v>3886</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9853,20 +9869,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>4634</v>
+        <v>4309</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>14589</v>
+        <v>14588</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O164" s="2" t="n">
         <v>32</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9920,17 +9936,17 @@
         <v>280</v>
       </c>
       <c r="M165" s="3" t="n">
-        <v>4945</v>
+        <v>4944</v>
       </c>
       <c r="N165" s="3" t="n">
         <v>328</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -9994,7 +10010,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10013,18 +10029,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>637</v>
+        <v>1551</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>681</v>
+        <v>971</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -10051,14 +10067,14 @@
         <v>9787</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1274</v>
+        <v>1705</v>
       </c>
       <c r="O167" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10128,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10166,7 +10182,7 @@
         <v>314</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>318</v>
@@ -10176,7 +10192,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10217,20 +10233,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>95548</v>
+        <v>95541</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>95548</v>
+        <v>95541</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10273,12 +10289,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10328,7 +10344,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10404,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10432,7 +10448,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10472,17 +10488,17 @@
         <v>7166</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14302</v>
+        <v>14301</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10519,20 +10535,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11466</v>
+        <v>11465</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11466</v>
+        <v>11465</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10569,20 +10585,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16004</v>
+        <v>16003</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10619,20 +10635,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>19269</v>
+        <v>19267</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10696,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10721,20 +10737,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10777,12 +10793,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10823,20 +10839,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10879,12 +10895,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10925,20 +10941,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21498</v>
+        <v>21497</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21498</v>
+        <v>21497</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42997</v>
+        <v>42993</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -10979,20 +10995,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28664</v>
+        <v>28662</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>57329</v>
+        <v>57325</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11036,17 +11052,17 @@
         <v>159</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11090,17 +11106,17 @@
         <v>159</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11154,17 +11170,17 @@
         <v>159</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>103609</v>
+        <v>103601</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11228,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11256,17 +11272,17 @@
         <v>159</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>29371</v>
+        <v>29369</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11320,17 +11336,17 @@
         <v>159</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>157229</v>
+        <v>157217</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11374,17 +11390,17 @@
         <v>159</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11432,7 +11448,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11476,17 +11492,17 @@
         <v>159</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O194" s="2" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11530,17 +11546,17 @@
         <v>159</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>159087</v>
+        <v>159076</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11594,17 +11610,17 @@
         <v>159</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11652,7 +11668,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11722,7 @@
         <v>1274</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>1285</v>
@@ -11716,7 +11732,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11757,20 +11773,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20737</v>
+        <v>20736</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20737</v>
+        <v>20736</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11827,14 +11843,14 @@
         <v>6349</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11891,14 +11907,14 @@
         <v>10849</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7644</v>
+        <v>7643</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11939,20 +11955,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10421</v>
+        <v>10420</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -11993,20 +12009,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8281</v>
+        <v>8280</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>277997</v>
+        <v>277976</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12047,20 +12063,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15735</v>
+        <v>15734</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>16151</v>
+        <v>16150</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12101,20 +12117,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20384</v>
+        <v>20382</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>49126</v>
+        <v>49122</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12157,12 +12173,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12222,11 +12238,11 @@
         <v>318</v>
       </c>
       <c r="O207" s="2" t="n">
-        <v>708</v>
+        <v>665</v>
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12296,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12350,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12414,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12468,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12499,14 +12515,14 @@
         <v>7166</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12549,12 +12565,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22932</v>
+        <v>22930</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12595,20 +12611,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12662,7 +12678,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12722,7 @@
         <v>2070</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11958</v>
+        <v>11957</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4140</v>
@@ -12716,7 +12732,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12751,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12746,7 +12762,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12767,20 +12783,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15679</v>
+        <v>15678</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37726</v>
+        <v>37723</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12834,7 +12850,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12881,14 +12897,14 @@
         <v>7166</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12931,12 +12947,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -12977,20 +12993,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13070,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13114,11 +13130,11 @@
         <v>3185</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13136,23 +13152,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D224" s="3" t="n">
-        <v>3185</v>
-      </c>
-      <c r="E224" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="F224" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G224" s="3" t="n">
-        <v>3185</v>
-      </c>
+      <c r="D224" s="3" t="inlineStr"/>
+      <c r="E224" s="2" t="inlineStr"/>
+      <c r="F224" s="2" t="inlineStr"/>
+      <c r="G224" s="3" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I224" s="2" t="n">
@@ -13175,14 +13181,14 @@
         <v>7247</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13236,17 +13242,17 @@
         <v>796</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>1828</v>
+        <v>7761</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1592</v>
       </c>
       <c r="O225" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13287,20 +13293,20 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3069</v>
+        <v>1892</v>
       </c>
       <c r="M226" s="3" t="n">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="N226" s="3" t="n">
         <v>3185</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13354,17 +13360,17 @@
         <v>3185</v>
       </c>
       <c r="M227" s="3" t="n">
-        <v>3808</v>
+        <v>3807</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O227" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13408,17 +13414,17 @@
         <v>159</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O228" s="2" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13462,17 +13468,17 @@
         <v>159</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13499,10 +13505,10 @@
         </is>
       </c>
       <c r="F230" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>903</v>
+        <v>197</v>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
@@ -13526,17 +13532,17 @@
         <v>159</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13586,7 @@
         <v>796</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1592</v>
@@ -13590,7 +13596,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13654,7 +13660,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13701,14 +13707,14 @@
         <v>7255</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>33</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13772,7 +13778,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13816,7 +13822,7 @@
         <v>2717</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4292</v>
+        <v>4291</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3185</v>
@@ -13826,7 +13832,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13880,7 +13886,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13928,7 +13934,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -13979,20 +13985,20 @@
         </is>
       </c>
       <c r="L238" s="3" t="n">
-        <v>8759</v>
+        <v>8758</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11101</v>
+        <v>11100</v>
       </c>
       <c r="N238" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O238" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14035,12 +14041,12 @@
       <c r="L239" s="3" t="inlineStr"/>
       <c r="M239" s="3" t="inlineStr"/>
       <c r="N239" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14087,14 +14093,14 @@
         <v>10548</v>
       </c>
       <c r="N240" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O240" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14119,7 @@
         </is>
       </c>
       <c r="D241" s="3" t="n">
-        <v>18708</v>
+        <v>18707</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
@@ -14121,10 +14127,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>20690</v>
+        <v>20593</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14145,20 +14151,20 @@
         </is>
       </c>
       <c r="L241" s="3" t="n">
-        <v>18710</v>
+        <v>18688</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30852</v>
+        <v>30850</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O241" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14177,7 +14183,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14188,7 +14194,7 @@
         <v>3</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38246</v>
+        <v>38243</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14209,20 +14215,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>59004</v>
+        <v>59000</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>76438</v>
+        <v>76433</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14241,7 +14247,7 @@
         </is>
       </c>
       <c r="D243" s="3" t="n">
-        <v>17049</v>
+        <v>17048</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
@@ -14252,7 +14258,7 @@
         <v>10</v>
       </c>
       <c r="G243" s="3" t="n">
-        <v>17144</v>
+        <v>17142</v>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
@@ -14269,20 +14275,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17406</v>
+        <v>17404</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31849313</v>
+        <v>31846989</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14325,12 +14331,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14390,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14435,20 +14441,20 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2421</v>
+        <v>2326</v>
       </c>
       <c r="M246" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="N246" s="3" t="n">
-        <v>2368</v>
+        <v>2424</v>
       </c>
       <c r="O246" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14489,20 +14495,20 @@
         </is>
       </c>
       <c r="L247" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23479</v>
+        <v>23478</v>
       </c>
       <c r="N247" s="3" t="n">
-        <v>17836</v>
+        <v>17834</v>
       </c>
       <c r="O247" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14521,7 +14527,7 @@
         </is>
       </c>
       <c r="D248" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -14532,7 +14538,7 @@
         <v>1</v>
       </c>
       <c r="G248" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
@@ -14553,20 +14559,20 @@
         </is>
       </c>
       <c r="L248" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="M248" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="N248" s="3" t="n">
-        <v>17836</v>
+        <v>17834</v>
       </c>
       <c r="O248" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14632,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14686,7 @@
       <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14724,17 +14730,17 @@
         <v>159</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>97922</v>
+        <v>97915</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14752,23 +14758,13 @@
           <t>衣装 / セット</t>
         </is>
       </c>
-      <c r="D252" s="3" t="n">
-        <v>4459</v>
-      </c>
-      <c r="E252" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G252" s="3" t="n">
-        <v>4459</v>
-      </c>
+      <c r="D252" s="3" t="inlineStr"/>
+      <c r="E252" s="2" t="inlineStr"/>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="3" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I252" s="2" t="n">
@@ -14785,20 +14781,20 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50742</v>
+        <v>50739</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50742</v>
+        <v>50739</v>
       </c>
       <c r="N252" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O252" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14817,7 +14813,7 @@
         </is>
       </c>
       <c r="D253" s="3" t="n">
-        <v>7593</v>
+        <v>7592</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
@@ -14828,7 +14824,7 @@
         <v>3</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>6465</v>
+        <v>6464</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14855,14 +14851,14 @@
         <v>5096</v>
       </c>
       <c r="N253" s="3" t="n">
-        <v>8351</v>
+        <v>8350</v>
       </c>
       <c r="O253" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14906,17 +14902,17 @@
         <v>7916</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>191096</v>
+        <v>191082</v>
       </c>
       <c r="N254" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O254" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14966,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15018,7 +15014,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15072,7 +15068,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15099,10 +15095,10 @@
         </is>
       </c>
       <c r="F258" s="2" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G258" s="3" t="n">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
@@ -15136,7 +15132,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15187,10 +15183,10 @@
         </is>
       </c>
       <c r="L259" s="3" t="n">
-        <v>1118</v>
+        <v>1226</v>
       </c>
       <c r="M259" s="3" t="n">
-        <v>21535</v>
+        <v>21533</v>
       </c>
       <c r="N259" s="3" t="n">
         <v>1592</v>
@@ -15200,7 +15196,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15254,7 +15250,7 @@
         <v>2535</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3698</v>
+        <v>3697</v>
       </c>
       <c r="N260" s="3" t="n">
         <v>3185</v>
@@ -15264,7 +15260,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15321,14 +15317,14 @@
         <v>7064</v>
       </c>
       <c r="N261" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O261" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15347,11 +15343,11 @@
         </is>
       </c>
       <c r="D262" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F262" s="2" t="n">
@@ -15379,20 +15375,20 @@
         </is>
       </c>
       <c r="L262" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M262" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="N262" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15446,7 +15442,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15506,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15553,12 +15549,12 @@
       <c r="L265" s="3" t="inlineStr"/>
       <c r="M265" s="3" t="inlineStr"/>
       <c r="N265" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15577,7 +15573,7 @@
         </is>
       </c>
       <c r="D266" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
@@ -15588,7 +15584,7 @@
         <v>2</v>
       </c>
       <c r="G266" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
@@ -15615,14 +15611,14 @@
         <v>9704</v>
       </c>
       <c r="N266" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O266" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15641,18 +15637,18 @@
         </is>
       </c>
       <c r="D267" s="3" t="n">
-        <v>2723</v>
+        <v>2771</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F267" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G267" s="3" t="n">
-        <v>2203</v>
+        <v>2266</v>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
@@ -15673,20 +15669,20 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>2771</v>
+        <v>2804</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19586</v>
+        <v>19584</v>
       </c>
       <c r="N267" s="3" t="n">
-        <v>2841</v>
+        <v>3182</v>
       </c>
       <c r="O267" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15727,20 +15723,20 @@
         </is>
       </c>
       <c r="L268" s="3" t="n">
-        <v>8281</v>
+        <v>8280</v>
       </c>
       <c r="M268" s="3" t="n">
-        <v>14345</v>
+        <v>14344</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15783,12 +15779,12 @@
       <c r="L269" s="3" t="inlineStr"/>
       <c r="M269" s="3" t="inlineStr"/>
       <c r="N269" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15829,20 +15825,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15883,20 +15879,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24307</v>
+        <v>24306</v>
       </c>
       <c r="M271" s="3" t="n">
-        <v>24788</v>
+        <v>24787</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -15940,17 +15936,17 @@
         <v>159</v>
       </c>
       <c r="M272" s="3" t="n">
-        <v>9773</v>
+        <v>9772</v>
       </c>
       <c r="N272" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16004,17 +16000,17 @@
         <v>159</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21091</v>
+        <v>21089</v>
       </c>
       <c r="N273" s="3" t="n">
-        <v>1280</v>
+        <v>318</v>
       </c>
       <c r="O273" s="2" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16058,17 +16054,17 @@
         <v>159</v>
       </c>
       <c r="M274" s="3" t="n">
-        <v>31954</v>
+        <v>31952</v>
       </c>
       <c r="N274" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O274" s="2" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16112,17 +16108,17 @@
         <v>159</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16004</v>
+        <v>16003</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O275" s="2" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16141,18 +16137,18 @@
         </is>
       </c>
       <c r="D276" s="3" t="n">
-        <v>3255</v>
+        <v>374</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>13119</v>
+        <v>11297</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16176,17 +16172,17 @@
         <v>159</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>158767</v>
+        <v>158756</v>
       </c>
       <c r="N276" s="3" t="n">
-        <v>3580</v>
+        <v>1995</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16242,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16293,14 +16289,14 @@
         <v>6924</v>
       </c>
       <c r="N278" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O278" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16344,17 +16340,17 @@
         <v>5096</v>
       </c>
       <c r="M279" s="3" t="n">
-        <v>9964</v>
+        <v>9963</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7644</v>
+        <v>7643</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16395,20 +16391,20 @@
         </is>
       </c>
       <c r="L280" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="M280" s="3" t="n">
         <v>8666</v>
       </c>
       <c r="N280" s="3" t="n">
-        <v>10192</v>
+        <v>10191</v>
       </c>
       <c r="O280" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16451,12 +16447,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14014</v>
+        <v>14013</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16499,12 +16495,12 @@
       <c r="L282" s="3" t="inlineStr"/>
       <c r="M282" s="3" t="inlineStr"/>
       <c r="N282" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16547,12 +16543,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16593,20 +16589,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>33442</v>
+        <v>33439</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>33955</v>
+        <v>33952</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16625,7 +16621,7 @@
         </is>
       </c>
       <c r="D285" s="3" t="n">
-        <v>9396</v>
+        <v>9395</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
@@ -16633,10 +16629,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9834</v>
+        <v>9808</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16657,20 +16653,20 @@
         </is>
       </c>
       <c r="L285" s="3" t="n">
-        <v>9517</v>
+        <v>8242</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N285" s="3" t="n">
-        <v>10332</v>
+        <v>10861</v>
       </c>
       <c r="O285" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16734,7 +16730,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16753,18 +16749,18 @@
         </is>
       </c>
       <c r="D287" s="3" t="n">
-        <v>4437</v>
+        <v>5049</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F287" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G287" s="3" t="n">
-        <v>4885</v>
+        <v>4867</v>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
@@ -16781,20 +16777,20 @@
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="3" t="n">
-        <v>4567</v>
+        <v>5812</v>
       </c>
       <c r="M287" s="3" t="n">
         <v>5812</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5067</v>
+        <v>5153</v>
       </c>
       <c r="O287" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16813,18 +16809,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>8695</v>
+        <v>8250</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>6922</v>
+        <v>6957</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16841,20 +16837,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>8251</v>
+        <v>8048</v>
       </c>
       <c r="M288" s="3" t="n">
         <v>8696</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>8061</v>
+        <v>8363</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16880,7 @@
         <v>15</v>
       </c>
       <c r="G289" s="3" t="n">
-        <v>9145</v>
+        <v>9144</v>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
@@ -16901,20 +16897,20 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>11652</v>
+        <v>11635</v>
       </c>
       <c r="M289" s="3" t="n">
-        <v>11652</v>
+        <v>11651</v>
       </c>
       <c r="N289" s="3" t="n">
-        <v>9964</v>
+        <v>10204</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16964,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16983,7 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>3394</v>
+        <v>3393</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
@@ -16995,10 +16991,10 @@
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>2916</v>
+        <v>3027</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -17032,7 +17028,7 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17051,7 +17047,7 @@
         </is>
       </c>
       <c r="D292" s="3" t="n">
-        <v>3706</v>
+        <v>3705</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
@@ -17062,7 +17058,7 @@
         <v>6</v>
       </c>
       <c r="G292" s="3" t="n">
-        <v>3688</v>
+        <v>3687</v>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
@@ -17086,17 +17082,17 @@
         <v>3879</v>
       </c>
       <c r="M292" s="3" t="n">
-        <v>5574</v>
+        <v>5573</v>
       </c>
       <c r="N292" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O292" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17146,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17169,7 +17165,7 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>7942</v>
+        <v>7941</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
@@ -17177,10 +17173,10 @@
         </is>
       </c>
       <c r="F294" s="2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5833</v>
+        <v>5857</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17204,17 +17200,17 @@
         <v>6798</v>
       </c>
       <c r="M294" s="3" t="n">
-        <v>28473</v>
+        <v>28471</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>6972</v>
+        <v>7139</v>
       </c>
       <c r="O294" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17255,20 +17251,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51760</v>
+        <v>51756</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>703457</v>
+        <v>703406</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39812</v>
+        <v>39809</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17287,7 +17283,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17298,7 +17294,7 @@
         <v>4</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17319,20 +17315,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>69239</v>
+        <v>69234</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39812</v>
+        <v>39809</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17351,7 +17347,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63699</v>
+        <v>63694</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17362,7 +17358,7 @@
         <v>5</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63699</v>
+        <v>63694</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17383,20 +17379,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63699</v>
+        <v>63694</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79623</v>
+        <v>79617</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17415,7 +17411,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17426,7 +17422,7 @@
         <v>1</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17447,20 +17443,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>127397</v>
+        <v>127388</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>127665</v>
+        <v>127655</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>159247</v>
+        <v>159235</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17479,7 +17475,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17490,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17511,20 +17507,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>254795</v>
+        <v>254776</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>257248</v>
+        <v>257230</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>318493</v>
+        <v>318470</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17543,7 +17539,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>445890</v>
+        <v>445858</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17554,7 +17550,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>445890</v>
+        <v>445858</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17575,20 +17571,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>445890</v>
+        <v>445858</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>949425</v>
+        <v>949356</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>636986</v>
+        <v>636940</v>
       </c>
       <c r="O300" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17607,7 +17603,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3981</v>
+        <v>2624</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
@@ -17615,10 +17611,10 @@
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>4386</v>
+        <v>4318</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17642,17 +17638,17 @@
         <v>2236</v>
       </c>
       <c r="M301" s="3" t="n">
-        <v>32349</v>
+        <v>32347</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>4266</v>
+        <v>2893</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17682,7 +17678,7 @@
         <v>15</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17703,7 +17699,7 @@
         </is>
       </c>
       <c r="L302" s="3" t="n">
-        <v>1847</v>
+        <v>1115</v>
       </c>
       <c r="M302" s="3" t="n">
         <v>4830</v>
@@ -17712,11 +17708,11 @@
         <v>2229</v>
       </c>
       <c r="O302" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17735,7 +17731,7 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4539</v>
+        <v>4538</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
@@ -17746,7 +17742,7 @@
         <v>18</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4489</v>
+        <v>4488</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17767,20 +17763,20 @@
         </is>
       </c>
       <c r="L303" s="3" t="n">
-        <v>4639</v>
+        <v>4318</v>
       </c>
       <c r="M303" s="3" t="n">
-        <v>15923</v>
+        <v>15922</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4790</v>
+        <v>4718</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17810,7 +17806,7 @@
         <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17831,10 +17827,10 @@
         </is>
       </c>
       <c r="L304" s="3" t="n">
-        <v>2231</v>
+        <v>2040</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2229</v>
@@ -17844,7 +17840,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17871,10 +17867,10 @@
         </is>
       </c>
       <c r="F305" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G305" s="3" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
@@ -17895,7 +17891,7 @@
         </is>
       </c>
       <c r="L305" s="3" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="M305" s="3" t="n">
         <v>1471</v>
@@ -17908,7 +17904,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -17931,14 +17927,14 @@
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F306" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G306" s="3" t="n">
-        <v>1208</v>
+        <v>1076</v>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
@@ -17962,17 +17958,17 @@
         <v>159</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>18064</v>
+        <v>18066</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18012,7 @@
         <v>1373</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>318</v>
@@ -18026,7 +18022,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18080,17 +18076,17 @@
         <v>2070</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1273973</v>
+        <v>1273880</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3981</v>
       </c>
       <c r="O308" s="2" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18144,17 +18140,17 @@
         <v>4459</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32200</v>
+        <v>32197</v>
       </c>
       <c r="N309" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O309" s="2" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18204,11 +18200,11 @@
         <v>3185</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18248,7 @@
         <v>4876</v>
       </c>
       <c r="M311" s="3" t="n">
-        <v>6077</v>
+        <v>6076</v>
       </c>
       <c r="N311" s="3" t="n">
         <v>4777</v>
@@ -18262,7 +18258,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18305,12 +18301,12 @@
       <c r="L312" s="3" t="inlineStr"/>
       <c r="M312" s="3" t="inlineStr"/>
       <c r="N312" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18329,7 +18325,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18340,7 +18336,7 @@
         <v>2</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18361,20 +18357,20 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26330</v>
+        <v>26328</v>
       </c>
       <c r="N313" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O313" s="2" t="n">
         <v>46</v>
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18415,20 +18411,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15579</v>
+        <v>15578</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15579</v>
+        <v>15578</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18447,18 +18443,18 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F315" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18479,20 +18475,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18511,7 +18507,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18522,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18543,20 +18539,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38219</v>
+        <v>38216</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>76438</v>
+        <v>76433</v>
       </c>
       <c r="O316" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18597,20 +18593,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>207021</v>
+        <v>207005</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18661,7 +18657,7 @@
         </is>
       </c>
       <c r="L318" s="3" t="n">
-        <v>753</v>
+        <v>954</v>
       </c>
       <c r="M318" s="3" t="n">
         <v>2065</v>
@@ -18670,11 +18666,11 @@
         <v>828</v>
       </c>
       <c r="O318" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18725,20 +18721,20 @@
         </is>
       </c>
       <c r="L319" s="3" t="n">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="M319" s="3" t="n">
-        <v>15816</v>
+        <v>15815</v>
       </c>
       <c r="N319" s="3" t="n">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="O319" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18789,20 +18785,20 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>2908</v>
+        <v>2406</v>
       </c>
       <c r="M320" s="3" t="n">
-        <v>9894</v>
+        <v>9893</v>
       </c>
       <c r="N320" s="3" t="n">
         <v>2922</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18853,7 +18849,7 @@
         </is>
       </c>
       <c r="L321" s="3" t="n">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="M321" s="3" t="n">
         <v>9717</v>
@@ -18866,7 +18862,7 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18917,7 +18913,7 @@
         </is>
       </c>
       <c r="L322" s="3" t="n">
-        <v>459</v>
+        <v>635</v>
       </c>
       <c r="M322" s="3" t="n">
         <v>1043</v>
@@ -18926,11 +18922,11 @@
         <v>490</v>
       </c>
       <c r="O322" s="2" t="n">
-        <v>350</v>
+        <v>287</v>
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -18949,7 +18945,7 @@
         </is>
       </c>
       <c r="D323" s="3" t="n">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
@@ -18957,10 +18953,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2129</v>
+        <v>2231</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18984,7 +18980,7 @@
         <v>3016</v>
       </c>
       <c r="M323" s="3" t="n">
-        <v>16614</v>
+        <v>16613</v>
       </c>
       <c r="N323" s="3" t="n">
         <v>3516</v>
@@ -18994,7 +18990,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19058,7 +19054,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19081,14 +19077,14 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F325" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G325" s="3" t="n">
-        <v>2232</v>
+        <v>2342</v>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
@@ -19112,17 +19108,17 @@
         <v>2331</v>
       </c>
       <c r="M325" s="3" t="n">
-        <v>15816</v>
+        <v>15815</v>
       </c>
       <c r="N325" s="3" t="n">
-        <v>2919</v>
+        <v>2960</v>
       </c>
       <c r="O325" s="2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19152,7 +19148,7 @@
         <v>6</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2673</v>
+        <v>2672</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19176,17 +19172,17 @@
         <v>2142</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N326" s="3" t="n">
-        <v>3854</v>
+        <v>3853</v>
       </c>
       <c r="O326" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19205,7 +19201,7 @@
         </is>
       </c>
       <c r="D327" s="3" t="n">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
@@ -19213,10 +19209,10 @@
         </is>
       </c>
       <c r="F327" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G327" s="3" t="n">
-        <v>2835</v>
+        <v>2705</v>
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
@@ -19237,10 +19233,10 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2421</v>
+        <v>2037</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>3929</v>
+        <v>3928</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>2229</v>
@@ -19250,7 +19246,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19269,18 +19265,18 @@
         </is>
       </c>
       <c r="D328" s="3" t="n">
-        <v>20417</v>
+        <v>26210</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>21869</v>
+        <v>22353</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19301,20 +19297,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>24253</v>
+        <v>25705</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32822</v>
+        <v>32820</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>24233</v>
+        <v>25094</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19333,18 +19329,18 @@
         </is>
       </c>
       <c r="D329" s="3" t="n">
-        <v>7512</v>
+        <v>7525</v>
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7053</v>
+        <v>7067</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19365,20 +19361,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7692</v>
+        <v>7557</v>
       </c>
       <c r="M329" s="3" t="n">
-        <v>19450</v>
+        <v>19449</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8152</v>
+        <v>8188</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19397,18 +19393,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>6093</v>
+        <v>6467</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5568</v>
+        <v>5635</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19429,20 +19425,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>6464</v>
+        <v>6014</v>
       </c>
       <c r="M330" s="3" t="n">
-        <v>8714</v>
+        <v>8713</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6513</v>
+        <v>6653</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19493,7 +19489,7 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1336</v>
+        <v>1306</v>
       </c>
       <c r="M331" s="3" t="n">
         <v>3185</v>
@@ -19506,7 +19502,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19533,10 +19529,10 @@
         </is>
       </c>
       <c r="F332" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>997</v>
+        <v>981</v>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
@@ -19560,17 +19556,17 @@
         <v>989</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N332" s="3" t="n">
-        <v>1081</v>
+        <v>1097</v>
       </c>
       <c r="O332" s="2" t="n">
         <v>160</v>
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19597,10 +19593,10 @@
         </is>
       </c>
       <c r="F333" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
@@ -19621,7 +19617,7 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M333" s="3" t="n">
         <v>2917</v>
@@ -19630,11 +19626,11 @@
         <v>318</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19688,7 +19684,7 @@
         <v>330</v>
       </c>
       <c r="M334" s="3" t="n">
-        <v>9485</v>
+        <v>9484</v>
       </c>
       <c r="N334" s="3" t="n">
         <v>318</v>
@@ -19698,7 +19694,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19749,10 +19745,10 @@
         </is>
       </c>
       <c r="L335" s="3" t="n">
-        <v>2897</v>
+        <v>2861</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15925</v>
+        <v>15923</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2229</v>
@@ -19762,7 +19758,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19785,11 +19781,11 @@
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F336" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G336" s="3" t="n">
         <v>160</v>
@@ -19826,7 +19822,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19856,7 +19852,7 @@
         <v>15</v>
       </c>
       <c r="G337" s="3" t="n">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
@@ -19880,17 +19876,17 @@
         <v>159</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15592</v>
+        <v>15591</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O337" s="2" t="n">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -19917,10 +19913,10 @@
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19954,7 +19950,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20005,7 +20001,7 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M339" s="3" t="n">
         <v>4742</v>
@@ -20018,7 +20014,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20059,7 +20055,7 @@
         </is>
       </c>
       <c r="L340" s="3" t="n">
-        <v>863</v>
+        <v>853</v>
       </c>
       <c r="M340" s="3" t="n">
         <v>3185</v>
@@ -20072,7 +20068,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20091,7 +20087,7 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>624</v>
+        <v>666</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -20099,10 +20095,10 @@
         </is>
       </c>
       <c r="F341" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="H341" s="2" t="inlineStr">
         <is>
@@ -20129,14 +20125,14 @@
         <v>2449</v>
       </c>
       <c r="N341" s="3" t="n">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="O341" s="2" t="n">
         <v>66</v>
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20190,7 +20186,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20209,18 +20205,18 @@
         </is>
       </c>
       <c r="D343" s="3" t="n">
-        <v>604</v>
+        <v>465</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F343" s="2" t="n">
         <v>2</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
@@ -20247,14 +20243,14 @@
         <v>2449</v>
       </c>
       <c r="N343" s="3" t="n">
-        <v>318</v>
+        <v>511</v>
       </c>
       <c r="O343" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20308,7 +20304,7 @@
         <v>2830</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>58087</v>
+        <v>58083</v>
       </c>
       <c r="N344" s="3" t="n">
         <v>3185</v>
@@ -20318,7 +20314,7 @@
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20341,11 +20337,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2070</v>
@@ -20372,17 +20368,17 @@
         <v>2070</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1592466</v>
+        <v>1592349</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>3981</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20401,7 +20397,7 @@
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>3397</v>
+        <v>3396</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
@@ -20432,15 +20428,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L346" s="3" t="inlineStr"/>
-      <c r="M346" s="3" t="inlineStr"/>
+      <c r="L346" s="3" t="n">
+        <v>5357</v>
+      </c>
+      <c r="M346" s="3" t="n">
+        <v>5357</v>
+      </c>
       <c r="N346" s="3" t="n">
         <v>4777</v>
       </c>
-      <c r="O346" s="2" t="inlineStr"/>
+      <c r="O346" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20494,17 +20496,17 @@
         <v>4459</v>
       </c>
       <c r="M347" s="3" t="n">
-        <v>8206</v>
+        <v>8205</v>
       </c>
       <c r="N347" s="3" t="n">
-        <v>6370</v>
+        <v>6369</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20545,20 +20547,20 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="N348" s="3" t="n">
-        <v>12740</v>
+        <v>12739</v>
       </c>
       <c r="O348" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20577,7 +20579,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20588,7 +20590,7 @@
         <v>1</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20609,20 +20611,20 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9555</v>
+        <v>9554</v>
       </c>
       <c r="M349" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="N349" s="3" t="n">
-        <v>19110</v>
+        <v>19108</v>
       </c>
       <c r="O349" s="2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20641,7 +20643,7 @@
         </is>
       </c>
       <c r="D350" s="3" t="n">
-        <v>12765</v>
+        <v>12764</v>
       </c>
       <c r="E350" s="2" t="inlineStr">
         <is>
@@ -20652,7 +20654,7 @@
         <v>1</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>12765</v>
+        <v>12764</v>
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
@@ -20675,12 +20677,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25479</v>
+        <v>25478</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20699,18 +20701,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>15925</v>
+        <v>16920</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>58</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16197</v>
+        <v>16191</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20731,20 +20733,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>15925</v>
+        <v>17352</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38087</v>
+        <v>38084</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31849</v>
+        <v>31847</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20763,18 +20765,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>43826</v>
+        <v>46049</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
         <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>42623</v>
+        <v>42987</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20795,20 +20797,20 @@
         </is>
       </c>
       <c r="L352" s="3" t="n">
-        <v>46099</v>
+        <v>43664</v>
       </c>
       <c r="M352" s="3" t="n">
-        <v>46215</v>
+        <v>43664</v>
       </c>
       <c r="N352" s="3" t="n">
-        <v>76438</v>
+        <v>76433</v>
       </c>
       <c r="O352" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20827,7 +20829,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>103510</v>
+        <v>103503</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20838,7 +20840,7 @@
         <v>2</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>104839</v>
+        <v>104832</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20861,12 +20863,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>207021</v>
+        <v>207005</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20917,20 +20919,20 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>387</v>
+        <v>631</v>
       </c>
       <c r="M354" s="3" t="n">
-        <v>9437</v>
+        <v>9436</v>
       </c>
       <c r="N354" s="3" t="n">
-        <v>454</v>
+        <v>427</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>272</v>
+        <v>110</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -20971,20 +20973,20 @@
         </is>
       </c>
       <c r="L355" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="M355" s="3" t="n">
-        <v>19070</v>
+        <v>19068</v>
       </c>
       <c r="N355" s="3" t="n">
-        <v>17836</v>
+        <v>17834</v>
       </c>
       <c r="O355" s="2" t="n">
         <v>79</v>
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -21003,7 +21005,7 @@
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="E356" s="2" t="inlineStr">
         <is>
@@ -21014,7 +21016,7 @@
         <v>1</v>
       </c>
       <c r="G356" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
@@ -21035,20 +21037,20 @@
         </is>
       </c>
       <c r="L356" s="3" t="n">
-        <v>8918</v>
+        <v>8917</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55736</v>
+        <v>55732</v>
       </c>
       <c r="N356" s="3" t="n">
-        <v>17836</v>
+        <v>17834</v>
       </c>
       <c r="O356" s="2" t="n">
         <v>50</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -21099,20 +21101,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>4898</v>
+        <v>15923</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>318</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -21142,7 +21144,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>159.246565</v>
+        <v>159.234947</v>
       </c>
     </row>
     <row r="2">
@@ -21153,7 +21155,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Wed, 26 Aug 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Thu, 27 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21165,7 +21167,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>3587</v>
+        <v>3513</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3878</v>
+        <v>3200</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>6397</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -642,11 +642,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>6397</v>
@@ -673,17 +673,17 @@
         <v>6397</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>97764</v>
+        <v>97766</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>12794</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -740,14 +740,14 @@
         <v>12794</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>24255</v>
+        <v>24256</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
         <v>23989</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>47977</v>
+        <v>47978</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>47341</v>
+        <v>47342</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>86359</v>
+        <v>86361</v>
       </c>
       <c r="O6" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -926,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>143932</v>
+        <v>143935</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>359831</v>
+        <v>359839</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>359831</v>
+        <v>359839</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>359831</v>
+        <v>359839</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>359831</v>
+        <v>359839</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>719662</v>
+        <v>719677</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1022,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>6427</v>
+        <v>6491</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5811</v>
+        <v>5840</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1054,20 +1054,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>6491</v>
+        <v>6789</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>8796</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1086,18 +1086,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>9698</v>
+        <v>8806</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
         <v>55</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8462</v>
+        <v>8455</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>8244</v>
+        <v>8804</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>151887</v>
+        <v>151890</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>17592</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1150,18 +1150,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>21</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1182,20 +1182,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>42938</v>
+        <v>42939</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>35183</v>
+        <v>35184</v>
       </c>
       <c r="O11" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1236,20 +1236,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>21687</v>
+        <v>21688</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39981</v>
+        <v>39982</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1290,20 +1290,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>95026</v>
+        <v>95028</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>95026</v>
+        <v>95028</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1354,20 +1354,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>319850</v>
+        <v>319857</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1408,20 +1408,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>34667</v>
+        <v>34668</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>64787</v>
+        <v>64789</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5437</v>
+        <v>5438</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14767</v>
+        <v>14768</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14767</v>
+        <v>14768</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>22791</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>64787</v>
+        <v>64789</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>16244</v>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         <v>800</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1599</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1593,17 +1593,17 @@
         <v>1599</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>230306</v>
+        <v>230311</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>118</v>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="L19" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>271872</v>
+        <v>271878</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>6397</v>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
         <v>5757</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>11515</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1775,17 +1775,17 @@
         <v>11195</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>37374</v>
+        <v>37375</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1829,17 +1829,17 @@
         <v>21590</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>141166</v>
+        <v>141169</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1880,20 +1880,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39981</v>
+        <v>39982</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>325185</v>
+        <v>325192</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>79962</v>
+        <v>79964</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1938,7 @@
         <v>1895</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>320</v>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2002,17 +2002,17 @@
         <v>1315</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1500</v>
+        <v>320</v>
       </c>
       <c r="O25" s="2" t="n">
         <v>26</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2030,23 +2030,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>1279</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>1279</v>
-      </c>
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
@@ -2076,7 +2066,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2095,18 +2085,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>884</v>
+        <v>800</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
         <v>13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1081</v>
+        <v>1055</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2127,20 +2117,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>948</v>
+        <v>1268</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1595001</v>
+        <v>1595035</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1599</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2194,17 +2184,17 @@
         <v>2695</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O28" s="2" t="n">
         <v>82</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2223,18 +2213,18 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
@@ -2255,10 +2245,10 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>17230</v>
+        <v>17231</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>6397</v>
@@ -2268,7 +2258,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2285,7 @@
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>640</v>
@@ -2322,7 +2312,7 @@
         <v>640</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1279</v>
@@ -2332,7 +2322,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2392,11 +2382,11 @@
         <v>4798</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2450,17 +2440,17 @@
         <v>800</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>639700</v>
+        <v>639713</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1599</v>
       </c>
       <c r="O32" s="2" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2517,14 +2507,14 @@
         <v>12956</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O33" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2543,18 +2533,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3784</v>
+        <v>3199</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3400</v>
+        <v>3399</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2575,20 +2565,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3198</v>
+        <v>3635</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>21377</v>
+        <v>21378</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>6397</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2601,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2642,7 +2632,7 @@
         <v>6397</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30912</v>
+        <v>30913</v>
       </c>
       <c r="N35" s="3" t="n">
         <v>12794</v>
@@ -2652,7 +2642,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2702,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2765,14 +2755,14 @@
         <v>4203</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O37" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2781,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
@@ -2799,10 +2789,10 @@
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
@@ -2822,7 +2812,7 @@
         <v>3600</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>319850</v>
+        <v>319857</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>6397</v>
@@ -2832,7 +2822,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2886,17 +2876,17 @@
         <v>1599</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>146406</v>
+        <v>146410</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O39" s="2" t="n">
         <v>49</v>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2947,20 +2937,20 @@
         </is>
       </c>
       <c r="L40" s="3" t="n">
-        <v>4911</v>
+        <v>4910</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17593</v>
+        <v>17594</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>6397</v>
       </c>
       <c r="O40" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -2983,11 +2973,11 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>6397</v>
@@ -3020,11 +3010,11 @@
         <v>12794</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3043,18 +3033,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1951</v>
+        <v>4318</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>2927</v>
+        <v>3390</v>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
@@ -3071,20 +3061,20 @@
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="3" t="n">
-        <v>4318</v>
+        <v>4638</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>6194</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>2239</v>
+        <v>3448</v>
       </c>
       <c r="O42" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3101,7 @@
         </is>
       </c>
       <c r="F43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>6397</v>
@@ -3144,7 +3134,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3163,18 +3153,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>9711</v>
+        <v>8049</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9319</v>
+        <v>9276</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3191,20 +3181,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>9698</v>
+        <v>11201</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>14651</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>11068</v>
+        <v>10720</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3261,14 +3251,14 @@
         <v>8817</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O45" s="2" t="n">
         <v>43</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3277,7 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -3298,7 +3288,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
@@ -3319,7 +3309,7 @@
         </is>
       </c>
       <c r="L46" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M46" s="3" t="n">
         <v>12794</v>
@@ -3332,7 +3322,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3386,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3450,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3507,14 +3497,14 @@
         <v>6397</v>
       </c>
       <c r="N49" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O49" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3574,7 +3564,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3624,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3684,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3758,7 +3748,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3802,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3866,17 +3856,17 @@
         <v>4798</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30934</v>
+        <v>30935</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3934,7 +3924,7 @@
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -3953,18 +3943,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>9699</v>
+        <v>9816</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>41</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9424</v>
+        <v>9432</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3985,20 +3975,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>8729</v>
+        <v>10335</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30974</v>
+        <v>30975</v>
       </c>
       <c r="N57" s="3" t="n">
         <v>12794</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4025,10 +4015,10 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3853</v>
+        <v>3850</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4049,20 +4039,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>4363</v>
+        <v>4353</v>
       </c>
       <c r="M58" s="3" t="n">
         <v>10440</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4574</v>
+        <v>4603</v>
       </c>
       <c r="O58" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4071,7 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
@@ -4089,10 +4079,10 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2627</v>
+        <v>2572</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4126,7 +4116,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4170,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4224,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4277,12 +4267,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9915</v>
+        <v>9916</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4336,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4379,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4437,12 +4427,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4489,14 +4479,14 @@
         <v>19191</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>51176</v>
+        <v>51177</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4540,17 +4530,17 @@
         <v>8956</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4583,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>22389</v>
+        <v>22390</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4632,7 @@
         <v>320</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3745</v>
+        <v>3746</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1599</v>
@@ -4652,7 +4642,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4709,14 +4699,14 @@
         <v>5094</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O70" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4770,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4824,7 @@
         <v>2559</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1500163</v>
+        <v>1500195</v>
       </c>
       <c r="N72" s="3" t="n">
         <v>11515</v>
@@ -4844,7 +4834,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4891,14 +4881,14 @@
         <v>7560</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4932,7 @@
         <v>8796</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>21188</v>
+        <v>21189</v>
       </c>
       <c r="N74" s="3" t="n">
         <v>17592</v>
@@ -4952,7 +4942,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -4996,17 +4986,17 @@
         <v>17592</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>27350</v>
+        <v>27351</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5066,11 +5056,11 @@
         <v>320</v>
       </c>
       <c r="O76" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5114,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5164,15 +5154,21 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L78" s="3" t="inlineStr"/>
-      <c r="M78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="n">
+        <v>640</v>
+      </c>
+      <c r="M78" s="3" t="n">
+        <v>640</v>
+      </c>
       <c r="N78" s="3" t="n">
         <v>1279</v>
       </c>
-      <c r="O78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5222,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5270,7 @@
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5324,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5371,12 +5367,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>20470</v>
+        <v>20471</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5426,17 +5422,17 @@
         <v>160</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1599089</v>
+        <v>1599123</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>800</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5459,11 +5455,11 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>320</v>
@@ -5496,7 +5492,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5539,14 +5535,14 @@
         <v>3189</v>
       </c>
       <c r="N85" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O85" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5592,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5636,7 @@
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5677,20 +5673,20 @@
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="N88" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5726,15 +5722,21 @@
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
-      <c r="L89" s="3" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="n">
+        <v>10669</v>
+      </c>
+      <c r="M89" s="3" t="n">
+        <v>10669</v>
+      </c>
       <c r="N89" s="3" t="n">
         <v>17592</v>
       </c>
-      <c r="O89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5786,7 @@
         <v>501</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>86916</v>
+        <v>86918</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>800</v>
@@ -5794,7 +5796,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5846,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5897,14 +5899,14 @@
         <v>4798</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O92" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5950,7 @@
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5994,7 @@
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6033,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6082,7 @@
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6136,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6190,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6235,14 +6237,14 @@
         <v>5234</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9915</v>
+        <v>9916</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6298,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6339,12 +6341,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6391,14 +6393,14 @@
         <v>18169</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6443,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>51176</v>
+        <v>51177</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6502,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6548,7 +6550,7 @@
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6593,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9915</v>
+        <v>9916</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6656,7 @@
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6697,12 +6699,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6747,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6795,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>51176</v>
+        <v>51177</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6841,12 +6843,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>79962</v>
+        <v>79964</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6887,20 +6889,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>87959</v>
+        <v>87961</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>98184</v>
+        <v>98186</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>111947</v>
+        <v>111950</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6941,20 +6943,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>111947</v>
+        <v>111950</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>111947</v>
+        <v>111950</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>143932</v>
+        <v>143935</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>16</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -6995,20 +6997,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7049,20 +7051,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>191910</v>
+        <v>191914</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7103,20 +7105,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>215899</v>
+        <v>215903</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7172,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7226,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7274,7 @@
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7316,17 +7318,17 @@
         <v>7197</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7369,12 +7371,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>23029</v>
+        <v>23030</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7415,20 +7417,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>19229</v>
+        <v>19230</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7472,17 +7474,17 @@
         <v>19191</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>41520</v>
+        <v>41521</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7538,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7592,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7646,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7691,14 +7693,14 @@
         <v>12015</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7743,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>23029</v>
+        <v>23030</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7791,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7837,12 +7839,12 @@
       <c r="L130" s="3" t="inlineStr"/>
       <c r="M130" s="3" t="inlineStr"/>
       <c r="N130" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7892,7 @@
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7954,7 +7956,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7975,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -7984,7 +7986,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -8005,10 +8007,10 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>16080</v>
+        <v>16081</v>
       </c>
       <c r="N133" s="3" t="n">
         <v>19191</v>
@@ -8018,7 +8020,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8063,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8113,14 +8115,14 @@
         <v>21590</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>47977</v>
+        <v>47978</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8139,7 +8141,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8150,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8171,20 +8173,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>71966</v>
+        <v>71968</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8231,14 +8233,14 @@
         <v>19191</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8298,11 +8300,11 @@
         <v>12794</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8368,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8385,18 +8387,18 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>438</v>
+        <v>486</v>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F140" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
@@ -8417,20 +8419,20 @@
         </is>
       </c>
       <c r="L140" s="3" t="n">
-        <v>486</v>
+        <v>587</v>
       </c>
       <c r="M140" s="3" t="n">
         <v>5222</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>544</v>
+        <v>520</v>
       </c>
       <c r="O140" s="2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8494,7 +8496,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8558,7 +8560,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8615,14 +8617,14 @@
         <v>6397</v>
       </c>
       <c r="N143" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O143" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8688,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8734,7 +8736,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8790,7 @@
         <v>4478</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>54083</v>
+        <v>54085</v>
       </c>
       <c r="N146" s="3" t="n">
         <v>6397</v>
@@ -8798,7 +8800,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8848,7 @@
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8889,7 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M148" s="3" t="n">
         <v>18524</v>
@@ -8900,7 +8902,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8943,12 +8945,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -8967,18 +8969,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15994</v>
+        <v>15995</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8999,20 +9001,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39981</v>
+        <v>39982</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9033,7 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
@@ -9042,7 +9044,7 @@
         <v>16</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9063,20 +9065,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>116654</v>
+        <v>116656</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>76764</v>
+        <v>76766</v>
       </c>
       <c r="O151" s="2" t="n">
         <v>20</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9097,7 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -9106,7 +9108,7 @@
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -9127,20 +9129,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>207902</v>
+        <v>207907</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9194,7 +9196,7 @@
         <v>160</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10462</v>
+        <v>10463</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>320</v>
@@ -9204,7 +9206,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9261,14 +9263,14 @@
         <v>1599</v>
       </c>
       <c r="N154" s="3" t="n">
-        <v>1759</v>
+        <v>320</v>
       </c>
       <c r="O154" s="2" t="n">
         <v>338</v>
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9315,20 +9317,20 @@
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="3" t="n">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15669</v>
+        <v>15670</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1599</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9381,14 +9383,14 @@
         <v>3275</v>
       </c>
       <c r="N156" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O156" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9425,7 +9427,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M157" s="3" t="n">
         <v>6397</v>
@@ -9438,7 +9440,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9494,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9546,17 +9548,17 @@
         <v>1599</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>19394</v>
+        <v>19395</v>
       </c>
       <c r="N159" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O159" s="2" t="n">
         <v>39</v>
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9599,7 @@
         </is>
       </c>
       <c r="L160" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M160" s="3" t="n">
         <v>6690</v>
@@ -9610,7 +9612,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9666,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9730,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9781,7 @@
         </is>
       </c>
       <c r="L163" s="3" t="n">
-        <v>3704</v>
+        <v>2716</v>
       </c>
       <c r="M163" s="3" t="n">
         <v>3838</v>
@@ -9788,11 +9790,11 @@
         <v>3664</v>
       </c>
       <c r="O163" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9811,18 +9813,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>3880</v>
+        <v>4751</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3904</v>
+        <v>3915</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9843,7 +9845,7 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3200</v>
+        <v>4766</v>
       </c>
       <c r="M164" s="3" t="n">
         <v>10395</v>
@@ -9852,11 +9854,11 @@
         <v>6397</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9907,20 +9909,20 @@
         </is>
       </c>
       <c r="L165" s="3" t="n">
-        <v>194</v>
+        <v>160</v>
       </c>
       <c r="M165" s="3" t="n">
         <v>4966</v>
       </c>
       <c r="N165" s="3" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="O165" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -9977,14 +9979,14 @@
         <v>1167</v>
       </c>
       <c r="N166" s="3" t="n">
-        <v>830</v>
+        <v>640</v>
       </c>
       <c r="O166" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10003,18 +10005,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>1407</v>
+        <v>1415</v>
       </c>
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F167" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G167" s="3" t="n">
-        <v>1083</v>
+        <v>1150</v>
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
@@ -10035,20 +10037,20 @@
         </is>
       </c>
       <c r="L167" s="3" t="n">
-        <v>1415</v>
+        <v>1423</v>
       </c>
       <c r="M167" s="3" t="n">
         <v>9829</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1630</v>
+        <v>1606</v>
       </c>
       <c r="O167" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10094,7 @@
         <v>1599</v>
       </c>
       <c r="M168" s="3" t="n">
-        <v>5453</v>
+        <v>5454</v>
       </c>
       <c r="N168" s="3" t="n">
         <v>320</v>
@@ -10102,7 +10104,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10156,7 +10158,7 @@
         <v>315</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>320</v>
@@ -10166,7 +10168,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10207,20 +10209,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>95955</v>
+        <v>95957</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>95955</v>
+        <v>95957</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10263,12 +10265,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10318,7 +10320,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10378,7 +10380,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10424,7 @@
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10465,14 +10467,14 @@
         <v>14363</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10515,14 +10517,14 @@
         <v>11515</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>23029</v>
+        <v>23030</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10559,20 +10561,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>16072</v>
+        <v>16073</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10615,14 +10617,14 @@
         <v>19351</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O178" s="2" t="n">
         <v>28</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10665,12 +10667,12 @@
       <c r="L179" s="3" t="inlineStr"/>
       <c r="M179" s="3" t="inlineStr"/>
       <c r="N179" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10726,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10774,7 @@
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10813,10 +10815,10 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="N182" s="3" t="n">
         <v>19191</v>
@@ -10826,7 +10828,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10869,12 +10871,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10921,14 +10923,14 @@
         <v>21590</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>43180</v>
+        <v>43181</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -10969,20 +10971,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28786</v>
+        <v>28787</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>57573</v>
+        <v>57574</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11028,7 @@
         <v>160</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>320</v>
@@ -11036,7 +11038,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11082,7 @@
         <v>160</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>320</v>
@@ -11090,7 +11092,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11146,7 @@
         <v>160</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>104050</v>
+        <v>104053</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>320</v>
@@ -11154,7 +11156,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11204,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11252,11 +11254,11 @@
         <v>320</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11312,7 @@
         <v>160</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>157899</v>
+        <v>157902</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>320</v>
@@ -11320,7 +11322,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11366,7 @@
         <v>160</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>320</v>
@@ -11374,7 +11376,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11422,7 +11424,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11468,7 @@
         <v>160</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>320</v>
@@ -11476,7 +11478,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11522,7 @@
         <v>160</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>159765</v>
+        <v>159768</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>320</v>
@@ -11530,7 +11532,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11584,7 +11586,7 @@
         <v>160</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>320</v>
@@ -11594,7 +11596,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11642,7 +11644,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11669,10 +11671,10 @@
         </is>
       </c>
       <c r="F198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G198" s="3" t="n">
-        <v>1042</v>
+        <v>1174</v>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
@@ -11696,7 +11698,7 @@
         <v>1279</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>1291</v>
@@ -11706,7 +11708,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11747,20 +11749,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>20825</v>
+        <v>20826</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20825</v>
+        <v>20826</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11783,11 +11785,11 @@
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F200" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G200" s="3" t="n">
         <v>4478</v>
@@ -11811,7 +11813,7 @@
         </is>
       </c>
       <c r="L200" s="3" t="n">
-        <v>4478</v>
+        <v>6239</v>
       </c>
       <c r="M200" s="3" t="n">
         <v>6376</v>
@@ -11820,11 +11822,11 @@
         <v>6397</v>
       </c>
       <c r="O200" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11881,14 +11883,14 @@
         <v>10896</v>
       </c>
       <c r="N201" s="3" t="n">
-        <v>7676</v>
+        <v>7677</v>
       </c>
       <c r="O201" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11934,7 @@
         <v>6397</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10465</v>
+        <v>10466</v>
       </c>
       <c r="N202" s="3" t="n">
         <v>10235</v>
@@ -11942,7 +11944,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -11986,17 +11988,17 @@
         <v>8316</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>279181</v>
+        <v>279187</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12039,7 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15802</v>
+        <v>15803</v>
       </c>
       <c r="M204" s="3" t="n">
         <v>16220</v>
@@ -12050,7 +12052,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12091,20 +12093,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>20470</v>
+        <v>20471</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>49335</v>
+        <v>49336</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12147,12 +12149,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>23029</v>
+        <v>23030</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12218,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12272,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12326,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12390,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12442,7 +12444,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12486,17 +12488,17 @@
         <v>7197</v>
       </c>
       <c r="M212" s="3" t="n">
-        <v>7197</v>
+        <v>7275</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12539,12 +12541,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>23029</v>
+        <v>23030</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12585,20 +12587,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O214" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12652,7 +12654,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12708,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12727,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12736,7 +12738,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12757,20 +12759,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15746</v>
+        <v>15747</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>37886</v>
+        <v>37887</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12816,7 @@
         <v>3998</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>6822</v>
+        <v>6823</v>
       </c>
       <c r="N218" s="3" t="n">
         <v>7996</v>
@@ -12824,7 +12826,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12871,14 +12873,14 @@
         <v>7197</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14393</v>
+        <v>14394</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12921,12 +12923,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -12973,14 +12975,14 @@
         <v>19191</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13046,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13067,11 +13069,11 @@
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F223" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G223" s="3" t="n">
         <v>1599</v>
@@ -13098,17 +13100,17 @@
         <v>1599</v>
       </c>
       <c r="M223" s="3" t="n">
-        <v>4092</v>
+        <v>4093</v>
       </c>
       <c r="N223" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13149,7 +13151,7 @@
         </is>
       </c>
       <c r="L224" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M224" s="3" t="n">
         <v>7278</v>
@@ -13162,7 +13164,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13226,7 +13228,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13273,14 +13275,14 @@
         <v>3514</v>
       </c>
       <c r="N226" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O226" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13299,7 +13301,7 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
@@ -13310,7 +13312,7 @@
         <v>1</v>
       </c>
       <c r="G227" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
@@ -13331,7 +13333,7 @@
         </is>
       </c>
       <c r="L227" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M227" s="3" t="n">
         <v>3824</v>
@@ -13344,7 +13346,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13388,7 +13390,7 @@
         <v>160</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>320</v>
@@ -13398,7 +13400,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13444,7 @@
         <v>160</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>320</v>
@@ -13452,7 +13454,7 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13506,17 +13508,17 @@
         <v>160</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>320</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13560,7 +13562,7 @@
         <v>800</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1599</v>
@@ -13570,7 +13572,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13627,14 +13629,14 @@
         <v>3942</v>
       </c>
       <c r="N232" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O232" s="2" t="n">
         <v>60</v>
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13675,7 +13677,7 @@
         </is>
       </c>
       <c r="L233" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M233" s="3" t="n">
         <v>7286</v>
@@ -13688,7 +13690,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13754,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13799,14 +13801,14 @@
         <v>4310</v>
       </c>
       <c r="N235" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O235" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13862,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13908,7 +13910,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13964,7 @@
         <v>8796</v>
       </c>
       <c r="M238" s="3" t="n">
-        <v>11148</v>
+        <v>11149</v>
       </c>
       <c r="N238" s="3" t="n">
         <v>6397</v>
@@ -13972,7 +13974,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14020,7 +14022,7 @@
       <c r="O239" s="2" t="inlineStr"/>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14061,10 +14063,10 @@
         </is>
       </c>
       <c r="L240" s="3" t="n">
-        <v>10593</v>
+        <v>10594</v>
       </c>
       <c r="M240" s="3" t="n">
-        <v>10593</v>
+        <v>10594</v>
       </c>
       <c r="N240" s="3" t="n">
         <v>19191</v>
@@ -14074,7 +14076,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14101,10 +14103,10 @@
         </is>
       </c>
       <c r="F241" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G241" s="3" t="n">
-        <v>20682</v>
+        <v>20455</v>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
@@ -14128,17 +14130,17 @@
         <v>18486</v>
       </c>
       <c r="M241" s="3" t="n">
-        <v>30984</v>
+        <v>30985</v>
       </c>
       <c r="N241" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O241" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14157,7 +14159,7 @@
         </is>
       </c>
       <c r="D242" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
@@ -14165,10 +14167,10 @@
         </is>
       </c>
       <c r="F242" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G242" s="3" t="n">
-        <v>38409</v>
+        <v>38423</v>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
@@ -14189,20 +14191,20 @@
         </is>
       </c>
       <c r="L242" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="M242" s="3" t="n">
-        <v>59255</v>
+        <v>59257</v>
       </c>
       <c r="N242" s="3" t="n">
-        <v>76764</v>
+        <v>76766</v>
       </c>
       <c r="O242" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14249,20 +14251,20 @@
       </c>
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="3" t="n">
-        <v>17744</v>
+        <v>17741</v>
       </c>
       <c r="M243" s="3" t="n">
-        <v>31984978</v>
+        <v>31985660</v>
       </c>
       <c r="N243" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O243" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14305,12 +14307,12 @@
       <c r="L244" s="3" t="inlineStr"/>
       <c r="M244" s="3" t="inlineStr"/>
       <c r="N244" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O244" s="2" t="inlineStr"/>
       <c r="P244" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14366,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14391,10 +14393,10 @@
         </is>
       </c>
       <c r="F246" s="2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G246" s="3" t="n">
-        <v>2175</v>
+        <v>2099</v>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
@@ -14415,7 +14417,7 @@
         </is>
       </c>
       <c r="L246" s="3" t="n">
-        <v>2269</v>
+        <v>2229</v>
       </c>
       <c r="M246" s="3" t="n">
         <v>6397</v>
@@ -14428,7 +14430,7 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14474,7 @@
         <v>8956</v>
       </c>
       <c r="M247" s="3" t="n">
-        <v>23579</v>
+        <v>23580</v>
       </c>
       <c r="N247" s="3" t="n">
         <v>17912</v>
@@ -14482,7 +14484,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14546,7 +14548,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14606,7 +14608,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14660,7 +14662,7 @@
       <c r="O250" s="2" t="inlineStr"/>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14704,17 +14706,17 @@
         <v>160</v>
       </c>
       <c r="M251" s="3" t="n">
-        <v>98339</v>
+        <v>98342</v>
       </c>
       <c r="N251" s="3" t="n">
         <v>320</v>
       </c>
       <c r="O251" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14755,10 +14757,10 @@
         </is>
       </c>
       <c r="L252" s="3" t="n">
-        <v>50958</v>
+        <v>50960</v>
       </c>
       <c r="M252" s="3" t="n">
-        <v>50958</v>
+        <v>50960</v>
       </c>
       <c r="N252" s="3" t="n">
         <v>6397</v>
@@ -14768,7 +14770,7 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14800,7 @@
         <v>3</v>
       </c>
       <c r="G253" s="3" t="n">
-        <v>6492</v>
+        <v>6493</v>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
@@ -14818,21 +14820,15 @@
           <t>Outfit / Set</t>
         </is>
       </c>
-      <c r="L253" s="3" t="n">
-        <v>5118</v>
-      </c>
-      <c r="M253" s="3" t="n">
-        <v>5118</v>
-      </c>
+      <c r="L253" s="3" t="inlineStr"/>
+      <c r="M253" s="3" t="inlineStr"/>
       <c r="N253" s="3" t="n">
-        <v>8386</v>
-      </c>
-      <c r="O253" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>8387</v>
+      </c>
+      <c r="O253" s="2" t="inlineStr"/>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14872,7 @@
         <v>7950</v>
       </c>
       <c r="M254" s="3" t="n">
-        <v>191910</v>
+        <v>191914</v>
       </c>
       <c r="N254" s="3" t="n">
         <v>10235</v>
@@ -14886,7 +14882,7 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14940,7 +14936,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -14988,7 +14984,7 @@
       <c r="O256" s="2" t="inlineStr"/>
       <c r="P256" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15042,7 +15038,7 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15061,7 @@
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F258" s="2" t="n">
@@ -15102,11 +15098,11 @@
         <v>640</v>
       </c>
       <c r="O258" s="2" t="n">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15170,7 +15166,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15221,20 +15217,20 @@
         </is>
       </c>
       <c r="L260" s="3" t="n">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="M260" s="3" t="n">
-        <v>3713</v>
+        <v>3714</v>
       </c>
       <c r="N260" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O260" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15253,7 +15249,7 @@
         </is>
       </c>
       <c r="D261" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -15264,7 +15260,7 @@
         <v>3</v>
       </c>
       <c r="G261" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
@@ -15285,7 +15281,7 @@
         </is>
       </c>
       <c r="L261" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M261" s="3" t="n">
         <v>7094</v>
@@ -15294,11 +15290,11 @@
         <v>6397</v>
       </c>
       <c r="O261" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15358,11 +15354,11 @@
         <v>12794</v>
       </c>
       <c r="O262" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15426,7 +15422,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15483,14 +15479,14 @@
         <v>1631</v>
       </c>
       <c r="N264" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O264" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15534,7 @@
       <c r="O265" s="2" t="inlineStr"/>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15592,7 +15588,7 @@
         <v>9746</v>
       </c>
       <c r="M266" s="3" t="n">
-        <v>12608</v>
+        <v>12609</v>
       </c>
       <c r="N266" s="3" t="n">
         <v>12794</v>
@@ -15602,7 +15598,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15653,10 +15649,10 @@
         </is>
       </c>
       <c r="L267" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M267" s="3" t="n">
-        <v>19669</v>
+        <v>19670</v>
       </c>
       <c r="N267" s="3" t="n">
         <v>3171</v>
@@ -15666,7 +15662,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15713,14 +15709,14 @@
         <v>14406</v>
       </c>
       <c r="N268" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="O268" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15764,7 @@
       <c r="O269" s="2" t="inlineStr"/>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15809,20 +15805,20 @@
         </is>
       </c>
       <c r="L270" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="M270" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="N270" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O270" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15863,20 +15859,20 @@
         </is>
       </c>
       <c r="L271" s="3" t="n">
-        <v>24345</v>
+        <v>24346</v>
       </c>
       <c r="M271" s="3" t="n">
         <v>24411</v>
       </c>
       <c r="N271" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O271" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15926,11 +15922,11 @@
         <v>320</v>
       </c>
       <c r="O272" s="2" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15980,7 @@
         <v>160</v>
       </c>
       <c r="M273" s="3" t="n">
-        <v>21180</v>
+        <v>21181</v>
       </c>
       <c r="N273" s="3" t="n">
         <v>320</v>
@@ -15994,7 +15990,7 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16044,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16088,7 @@
         <v>160</v>
       </c>
       <c r="M275" s="3" t="n">
-        <v>16072</v>
+        <v>16073</v>
       </c>
       <c r="N275" s="3" t="n">
         <v>320</v>
@@ -16102,7 +16098,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16129,10 +16125,10 @@
         </is>
       </c>
       <c r="F276" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G276" s="3" t="n">
-        <v>11346</v>
+        <v>1686</v>
       </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
@@ -16156,17 +16152,17 @@
         <v>160</v>
       </c>
       <c r="M276" s="3" t="n">
-        <v>159444</v>
+        <v>159447</v>
       </c>
       <c r="N276" s="3" t="n">
         <v>2004</v>
       </c>
       <c r="O276" s="2" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16226,7 +16222,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16276,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16327,14 +16323,14 @@
         <v>10007</v>
       </c>
       <c r="N279" s="3" t="n">
-        <v>7676</v>
+        <v>7677</v>
       </c>
       <c r="O279" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16388,7 +16384,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16431,12 +16427,12 @@
       <c r="L281" s="3" t="inlineStr"/>
       <c r="M281" s="3" t="inlineStr"/>
       <c r="N281" s="3" t="n">
-        <v>14073</v>
+        <v>14074</v>
       </c>
       <c r="O281" s="2" t="inlineStr"/>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16484,7 +16480,7 @@
       <c r="O282" s="2" t="inlineStr"/>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16527,12 +16523,12 @@
       <c r="L283" s="3" t="inlineStr"/>
       <c r="M283" s="3" t="inlineStr"/>
       <c r="N283" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O283" s="2" t="inlineStr"/>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16573,20 +16569,20 @@
         </is>
       </c>
       <c r="L284" s="3" t="n">
-        <v>33584</v>
+        <v>33585</v>
       </c>
       <c r="M284" s="3" t="n">
-        <v>34099</v>
+        <v>34100</v>
       </c>
       <c r="N284" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="O284" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16613,10 +16609,10 @@
         </is>
       </c>
       <c r="F285" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G285" s="3" t="n">
-        <v>9609</v>
+        <v>9533</v>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
@@ -16640,17 +16636,17 @@
         <v>9215</v>
       </c>
       <c r="M285" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N285" s="3" t="n">
         <v>10515</v>
       </c>
       <c r="O285" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16710,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16767,14 +16763,14 @@
         <v>5837</v>
       </c>
       <c r="N287" s="3" t="n">
-        <v>5188</v>
+        <v>5172</v>
       </c>
       <c r="O287" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16793,18 +16789,18 @@
         </is>
       </c>
       <c r="D288" s="3" t="n">
-        <v>8083</v>
+        <v>7856</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F288" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G288" s="3" t="n">
-        <v>7023</v>
+        <v>7102</v>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
@@ -16821,20 +16817,20 @@
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="3" t="n">
-        <v>8228</v>
+        <v>7467</v>
       </c>
       <c r="M288" s="3" t="n">
-        <v>8733</v>
+        <v>8734</v>
       </c>
       <c r="N288" s="3" t="n">
-        <v>8949</v>
+        <v>9060</v>
       </c>
       <c r="O288" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16877,7 @@
       </c>
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="3" t="n">
-        <v>11686</v>
+        <v>11443</v>
       </c>
       <c r="M289" s="3" t="n">
         <v>11686</v>
@@ -16890,11 +16886,11 @@
         <v>11043</v>
       </c>
       <c r="O289" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16935,10 +16931,10 @@
         </is>
       </c>
       <c r="L290" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="M290" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="N290" s="3" t="n">
         <v>1599</v>
@@ -16948,7 +16944,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -16967,18 +16963,18 @@
         </is>
       </c>
       <c r="D291" s="3" t="n">
-        <v>3408</v>
+        <v>2727</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F291" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G291" s="3" t="n">
-        <v>3207</v>
+        <v>3111</v>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
@@ -16999,20 +16995,20 @@
         </is>
       </c>
       <c r="L291" s="3" t="n">
-        <v>2727</v>
+        <v>3421</v>
       </c>
       <c r="M291" s="3" t="n">
         <v>5118</v>
       </c>
       <c r="N291" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O291" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17076,7 +17072,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17130,7 +17126,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17149,18 +17145,18 @@
         </is>
       </c>
       <c r="D294" s="3" t="n">
-        <v>7975</v>
+        <v>7310</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F294" s="2" t="n">
         <v>24</v>
       </c>
       <c r="G294" s="3" t="n">
-        <v>5881</v>
+        <v>5839</v>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
@@ -17181,20 +17177,20 @@
         </is>
       </c>
       <c r="L294" s="3" t="n">
-        <v>7312</v>
+        <v>10640</v>
       </c>
       <c r="M294" s="3" t="n">
         <v>28595</v>
       </c>
       <c r="N294" s="3" t="n">
-        <v>8428</v>
+        <v>8786</v>
       </c>
       <c r="O294" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17235,20 +17231,20 @@
         </is>
       </c>
       <c r="L295" s="3" t="n">
-        <v>51980</v>
+        <v>51981</v>
       </c>
       <c r="M295" s="3" t="n">
-        <v>706454</v>
+        <v>706469</v>
       </c>
       <c r="N295" s="3" t="n">
-        <v>39981</v>
+        <v>39982</v>
       </c>
       <c r="O295" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17267,7 +17263,7 @@
         </is>
       </c>
       <c r="D296" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -17278,7 +17274,7 @@
         <v>3</v>
       </c>
       <c r="G296" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
@@ -17299,20 +17295,20 @@
         </is>
       </c>
       <c r="L296" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="M296" s="3" t="n">
-        <v>69534</v>
+        <v>69535</v>
       </c>
       <c r="N296" s="3" t="n">
-        <v>39981</v>
+        <v>39982</v>
       </c>
       <c r="O296" s="2" t="n">
         <v>18</v>
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17331,7 +17327,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>63970</v>
+        <v>63971</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -17342,7 +17338,7 @@
         <v>4</v>
       </c>
       <c r="G297" s="3" t="n">
-        <v>63970</v>
+        <v>63971</v>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
@@ -17363,20 +17359,20 @@
         </is>
       </c>
       <c r="L297" s="3" t="n">
-        <v>63970</v>
+        <v>63971</v>
       </c>
       <c r="M297" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="N297" s="3" t="n">
-        <v>79962</v>
+        <v>79964</v>
       </c>
       <c r="O297" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17391,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
@@ -17406,7 +17402,7 @@
         <v>2</v>
       </c>
       <c r="G298" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
@@ -17427,20 +17423,20 @@
         </is>
       </c>
       <c r="L298" s="3" t="n">
-        <v>127940</v>
+        <v>127943</v>
       </c>
       <c r="M298" s="3" t="n">
-        <v>128209</v>
+        <v>128211</v>
       </c>
       <c r="N298" s="3" t="n">
-        <v>159925</v>
+        <v>159928</v>
       </c>
       <c r="O298" s="2" t="n">
         <v>10</v>
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17455,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
@@ -17470,7 +17466,7 @@
         <v>1</v>
       </c>
       <c r="G299" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
@@ -17491,20 +17487,20 @@
         </is>
       </c>
       <c r="L299" s="3" t="n">
-        <v>255880</v>
+        <v>255885</v>
       </c>
       <c r="M299" s="3" t="n">
-        <v>258344</v>
+        <v>258350</v>
       </c>
       <c r="N299" s="3" t="n">
-        <v>319850</v>
+        <v>319857</v>
       </c>
       <c r="O299" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17523,7 +17519,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>447790</v>
+        <v>447799</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
@@ -17534,7 +17530,7 @@
         <v>4</v>
       </c>
       <c r="G300" s="3" t="n">
-        <v>447790</v>
+        <v>447799</v>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
@@ -17555,20 +17551,20 @@
         </is>
       </c>
       <c r="L300" s="3" t="n">
-        <v>447790</v>
+        <v>447799</v>
       </c>
       <c r="M300" s="3" t="n">
-        <v>953469</v>
+        <v>447799</v>
       </c>
       <c r="N300" s="3" t="n">
-        <v>639700</v>
+        <v>639713</v>
       </c>
       <c r="O300" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17587,18 +17583,18 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>3069</v>
+        <v>2279</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F301" s="2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G301" s="3" t="n">
-        <v>4097</v>
+        <v>3995</v>
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
@@ -17619,20 +17615,20 @@
         </is>
       </c>
       <c r="L301" s="3" t="n">
-        <v>2237</v>
+        <v>2338</v>
       </c>
       <c r="M301" s="3" t="n">
         <v>16527</v>
       </c>
       <c r="N301" s="3" t="n">
-        <v>2768</v>
+        <v>2879</v>
       </c>
       <c r="O301" s="2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17659,10 +17655,10 @@
         </is>
       </c>
       <c r="F302" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G302" s="3" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
@@ -17696,7 +17692,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17715,18 +17711,18 @@
         </is>
       </c>
       <c r="D303" s="3" t="n">
-        <v>4337</v>
+        <v>4588</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F303" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G303" s="3" t="n">
-        <v>4557</v>
+        <v>4548</v>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
@@ -17753,14 +17749,14 @@
         <v>15991</v>
       </c>
       <c r="N303" s="3" t="n">
-        <v>4828</v>
+        <v>4961</v>
       </c>
       <c r="O303" s="2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17787,10 +17783,10 @@
         </is>
       </c>
       <c r="F304" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G304" s="3" t="n">
-        <v>1828</v>
+        <v>1782</v>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
@@ -17814,7 +17810,7 @@
         <v>2436</v>
       </c>
       <c r="M304" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N304" s="3" t="n">
         <v>2239</v>
@@ -17824,7 +17820,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17871,7 @@
         </is>
       </c>
       <c r="L305" s="3" t="n">
-        <v>649</v>
+        <v>581</v>
       </c>
       <c r="M305" s="3" t="n">
         <v>1478</v>
@@ -17884,11 +17880,11 @@
         <v>320</v>
       </c>
       <c r="O305" s="2" t="n">
-        <v>669</v>
+        <v>679</v>
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17942,17 +17938,17 @@
         <v>160</v>
       </c>
       <c r="M306" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N306" s="3" t="n">
         <v>320</v>
       </c>
       <c r="O306" s="2" t="n">
-        <v>18299</v>
+        <v>18301</v>
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17992,7 @@
         <v>1379</v>
       </c>
       <c r="M307" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N307" s="3" t="n">
         <v>320</v>
@@ -18006,7 +18002,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18056,7 @@
         <v>2079</v>
       </c>
       <c r="M308" s="3" t="n">
-        <v>1279399</v>
+        <v>1279426</v>
       </c>
       <c r="N308" s="3" t="n">
         <v>3998</v>
@@ -18070,7 +18066,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18097,7 +18093,7 @@
         </is>
       </c>
       <c r="F309" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G309" s="3" t="n">
         <v>4478</v>
@@ -18124,7 +18120,7 @@
         <v>4478</v>
       </c>
       <c r="M309" s="3" t="n">
-        <v>32337</v>
+        <v>32338</v>
       </c>
       <c r="N309" s="3" t="n">
         <v>6397</v>
@@ -18134,7 +18130,7 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18181,14 +18177,14 @@
         <v>6093</v>
       </c>
       <c r="N310" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O310" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18242,7 +18238,7 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18290,7 +18286,7 @@
       <c r="O312" s="2" t="inlineStr"/>
       <c r="P312" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18309,7 +18305,7 @@
         </is>
       </c>
       <c r="D313" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
@@ -18320,7 +18316,7 @@
         <v>2</v>
       </c>
       <c r="G313" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
@@ -18341,10 +18337,10 @@
         </is>
       </c>
       <c r="L313" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M313" s="3" t="n">
-        <v>26442</v>
+        <v>26443</v>
       </c>
       <c r="N313" s="3" t="n">
         <v>19191</v>
@@ -18354,7 +18350,7 @@
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18395,20 +18391,20 @@
         </is>
       </c>
       <c r="L314" s="3" t="n">
-        <v>15645</v>
+        <v>15646</v>
       </c>
       <c r="M314" s="3" t="n">
-        <v>15645</v>
+        <v>15646</v>
       </c>
       <c r="N314" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O314" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18427,7 +18423,7 @@
         </is>
       </c>
       <c r="D315" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
@@ -18438,7 +18434,7 @@
         <v>13</v>
       </c>
       <c r="G315" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
@@ -18459,20 +18455,20 @@
         </is>
       </c>
       <c r="L315" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="M315" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N315" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O315" s="2" t="n">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18491,7 +18487,7 @@
         </is>
       </c>
       <c r="D316" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
@@ -18502,7 +18498,7 @@
         <v>2</v>
       </c>
       <c r="G316" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
@@ -18523,20 +18519,20 @@
         </is>
       </c>
       <c r="L316" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="M316" s="3" t="n">
-        <v>38382</v>
+        <v>38383</v>
       </c>
       <c r="N316" s="3" t="n">
-        <v>76764</v>
+        <v>76766</v>
       </c>
       <c r="O316" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18577,20 +18573,20 @@
         </is>
       </c>
       <c r="L317" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="M317" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="N317" s="3" t="n">
-        <v>207902</v>
+        <v>207907</v>
       </c>
       <c r="O317" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18650,7 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18714,11 +18710,11 @@
         <v>1497</v>
       </c>
       <c r="O319" s="2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18737,18 +18733,18 @@
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>1119</v>
+        <v>2327</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F320" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G320" s="3" t="n">
-        <v>2135</v>
+        <v>2147</v>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
@@ -18769,7 +18765,7 @@
         </is>
       </c>
       <c r="L320" s="3" t="n">
-        <v>1463</v>
+        <v>1929</v>
       </c>
       <c r="M320" s="3" t="n">
         <v>9936</v>
@@ -18778,11 +18774,11 @@
         <v>2239</v>
       </c>
       <c r="O320" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18801,18 +18797,18 @@
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>293</v>
+        <v>3514</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F321" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G321" s="3" t="n">
-        <v>2600</v>
+        <v>2828</v>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
@@ -18836,17 +18832,17 @@
         <v>3514</v>
       </c>
       <c r="M321" s="3" t="n">
-        <v>9759</v>
+        <v>5948</v>
       </c>
       <c r="N321" s="3" t="n">
-        <v>321</v>
+        <v>2093</v>
       </c>
       <c r="O321" s="2" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18906,7 @@
       </c>
       <c r="P322" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -18937,10 +18933,10 @@
         </is>
       </c>
       <c r="F323" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>2241</v>
+        <v>2285</v>
       </c>
       <c r="H323" s="2" t="inlineStr">
         <is>
@@ -18974,7 +18970,7 @@
       </c>
       <c r="P323" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19038,7 +19034,7 @@
       </c>
       <c r="P324" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19102,7 +19098,7 @@
       </c>
       <c r="P325" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19129,10 +19125,10 @@
         </is>
       </c>
       <c r="F326" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G326" s="3" t="n">
-        <v>2684</v>
+        <v>2845</v>
       </c>
       <c r="H326" s="2" t="inlineStr">
         <is>
@@ -19156,7 +19152,7 @@
         <v>2151</v>
       </c>
       <c r="M326" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N326" s="3" t="n">
         <v>3870</v>
@@ -19166,7 +19162,7 @@
       </c>
       <c r="P326" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19217,10 +19213,10 @@
         </is>
       </c>
       <c r="L327" s="3" t="n">
-        <v>2045</v>
+        <v>1940</v>
       </c>
       <c r="M327" s="3" t="n">
-        <v>3945</v>
+        <v>15993</v>
       </c>
       <c r="N327" s="3" t="n">
         <v>2389</v>
@@ -19230,7 +19226,7 @@
       </c>
       <c r="P327" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19257,10 +19253,10 @@
         </is>
       </c>
       <c r="F328" s="2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G328" s="3" t="n">
-        <v>22685</v>
+        <v>22791</v>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
@@ -19281,20 +19277,20 @@
         </is>
       </c>
       <c r="L328" s="3" t="n">
-        <v>26548</v>
+        <v>25800</v>
       </c>
       <c r="M328" s="3" t="n">
-        <v>32962</v>
+        <v>32963</v>
       </c>
       <c r="N328" s="3" t="n">
-        <v>25813</v>
+        <v>26175</v>
       </c>
       <c r="O328" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P328" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19321,10 +19317,10 @@
         </is>
       </c>
       <c r="F329" s="2" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G329" s="3" t="n">
-        <v>7141</v>
+        <v>7155</v>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
@@ -19345,20 +19341,20 @@
         </is>
       </c>
       <c r="L329" s="3" t="n">
-        <v>7588</v>
+        <v>7557</v>
       </c>
       <c r="M329" s="3" t="n">
         <v>9877</v>
       </c>
       <c r="N329" s="3" t="n">
-        <v>8183</v>
+        <v>8164</v>
       </c>
       <c r="O329" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P329" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19377,18 +19373,18 @@
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>5936</v>
+        <v>5916</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F330" s="2" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G330" s="3" t="n">
-        <v>5667</v>
+        <v>5658</v>
       </c>
       <c r="H330" s="2" t="inlineStr">
         <is>
@@ -19409,20 +19405,20 @@
         </is>
       </c>
       <c r="L330" s="3" t="n">
-        <v>5916</v>
+        <v>6029</v>
       </c>
       <c r="M330" s="3" t="n">
         <v>8751</v>
       </c>
       <c r="N330" s="3" t="n">
-        <v>6621</v>
+        <v>6642</v>
       </c>
       <c r="O330" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P330" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19473,10 +19469,10 @@
         </is>
       </c>
       <c r="L331" s="3" t="n">
-        <v>1259</v>
+        <v>1161</v>
       </c>
       <c r="M331" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="N331" s="3" t="n">
         <v>320</v>
@@ -19486,7 +19482,7 @@
       </c>
       <c r="P331" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19540,7 +19536,7 @@
         <v>969</v>
       </c>
       <c r="M332" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N332" s="3" t="n">
         <v>1092</v>
@@ -19550,7 +19546,7 @@
       </c>
       <c r="P332" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19601,7 +19597,7 @@
         </is>
       </c>
       <c r="L333" s="3" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="M333" s="3" t="n">
         <v>2930</v>
@@ -19610,11 +19606,11 @@
         <v>320</v>
       </c>
       <c r="O333" s="2" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P333" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19674,7 @@
       </c>
       <c r="P334" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19705,10 +19701,10 @@
         </is>
       </c>
       <c r="F335" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G335" s="3" t="n">
-        <v>2022</v>
+        <v>2106</v>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
@@ -19732,7 +19728,7 @@
         <v>1119</v>
       </c>
       <c r="M335" s="3" t="n">
-        <v>15992</v>
+        <v>15993</v>
       </c>
       <c r="N335" s="3" t="n">
         <v>2239</v>
@@ -19742,7 +19738,7 @@
       </c>
       <c r="P335" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19806,7 +19802,7 @@
       </c>
       <c r="P336" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19860,7 +19856,7 @@
         <v>160</v>
       </c>
       <c r="M337" s="3" t="n">
-        <v>15658</v>
+        <v>15659</v>
       </c>
       <c r="N337" s="3" t="n">
         <v>320</v>
@@ -19870,7 +19866,7 @@
       </c>
       <c r="P337" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19889,18 +19885,18 @@
         </is>
       </c>
       <c r="D338" s="3" t="n">
-        <v>320</v>
+        <v>160</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F338" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G338" s="3" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="H338" s="2" t="inlineStr">
         <is>
@@ -19934,7 +19930,7 @@
       </c>
       <c r="P338" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -19985,7 +19981,7 @@
         </is>
       </c>
       <c r="L339" s="3" t="n">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="M339" s="3" t="n">
         <v>4763</v>
@@ -19998,7 +19994,7 @@
       </c>
       <c r="P339" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20042,7 +20038,7 @@
         <v>857</v>
       </c>
       <c r="M340" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="N340" s="3" t="n">
         <v>320</v>
@@ -20052,7 +20048,7 @@
       </c>
       <c r="P340" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20067,7 @@
         </is>
       </c>
       <c r="D341" s="3" t="n">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
@@ -20116,7 +20112,7 @@
       </c>
       <c r="P341" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20170,7 +20166,7 @@
       </c>
       <c r="P342" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20234,7 +20230,7 @@
       </c>
       <c r="P343" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20253,7 +20249,7 @@
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
@@ -20261,10 +20257,10 @@
         </is>
       </c>
       <c r="F344" s="2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G344" s="3" t="n">
-        <v>1726</v>
+        <v>1747</v>
       </c>
       <c r="H344" s="2" t="inlineStr">
         <is>
@@ -20288,17 +20284,17 @@
         <v>2842</v>
       </c>
       <c r="M344" s="3" t="n">
-        <v>58334</v>
+        <v>58335</v>
       </c>
       <c r="N344" s="3" t="n">
-        <v>3198</v>
+        <v>3199</v>
       </c>
       <c r="O344" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P344" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20321,11 +20317,11 @@
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F345" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G345" s="3" t="n">
         <v>2079</v>
@@ -20352,17 +20348,17 @@
         <v>2079</v>
       </c>
       <c r="M345" s="3" t="n">
-        <v>1599249</v>
+        <v>1599283</v>
       </c>
       <c r="N345" s="3" t="n">
         <v>3998</v>
       </c>
       <c r="O345" s="2" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P345" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20422,7 @@
       </c>
       <c r="P346" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20486,11 +20482,11 @@
         <v>6397</v>
       </c>
       <c r="O347" s="2" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P347" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20531,10 +20527,10 @@
         </is>
       </c>
       <c r="L348" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M348" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="N348" s="3" t="n">
         <v>12794</v>
@@ -20544,7 +20540,7 @@
       </c>
       <c r="P348" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20559,7 @@
         </is>
       </c>
       <c r="D349" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="E349" s="2" t="inlineStr">
         <is>
@@ -20574,7 +20570,7 @@
         <v>1</v>
       </c>
       <c r="G349" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
@@ -20595,7 +20591,7 @@
         </is>
       </c>
       <c r="L349" s="3" t="n">
-        <v>9595</v>
+        <v>9596</v>
       </c>
       <c r="M349" s="3" t="n">
         <v>19191</v>
@@ -20608,7 +20604,7 @@
       </c>
       <c r="P349" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20661,12 +20657,12 @@
       <c r="L350" s="3" t="inlineStr"/>
       <c r="M350" s="3" t="inlineStr"/>
       <c r="N350" s="3" t="n">
-        <v>25588</v>
+        <v>25589</v>
       </c>
       <c r="O350" s="2" t="inlineStr"/>
       <c r="P350" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20685,18 +20681,18 @@
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>16002</v>
+        <v>16986</v>
       </c>
       <c r="E351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F351" s="2" t="n">
         <v>59</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>16274</v>
+        <v>16290</v>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
@@ -20717,20 +20713,20 @@
         </is>
       </c>
       <c r="L351" s="3" t="n">
-        <v>16485</v>
+        <v>17595</v>
       </c>
       <c r="M351" s="3" t="n">
-        <v>38249</v>
+        <v>38250</v>
       </c>
       <c r="N351" s="3" t="n">
-        <v>31985</v>
+        <v>31986</v>
       </c>
       <c r="O351" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P351" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20749,18 +20745,18 @@
         </is>
       </c>
       <c r="D352" s="3" t="n">
-        <v>46249</v>
+        <v>43854</v>
       </c>
       <c r="E352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="F352" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>43652</v>
+        <v>43769</v>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
@@ -20780,21 +20776,15 @@
           <t>Weapon</t>
         </is>
       </c>
-      <c r="L352" s="3" t="n">
-        <v>43853</v>
-      </c>
-      <c r="M352" s="3" t="n">
-        <v>43853</v>
-      </c>
+      <c r="L352" s="3" t="inlineStr"/>
+      <c r="M352" s="3" t="inlineStr"/>
       <c r="N352" s="3" t="n">
-        <v>76764</v>
-      </c>
-      <c r="O352" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>76766</v>
+      </c>
+      <c r="O352" s="2" t="inlineStr"/>
       <c r="P352" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20813,7 +20803,7 @@
         </is>
       </c>
       <c r="D353" s="3" t="n">
-        <v>103951</v>
+        <v>103953</v>
       </c>
       <c r="E353" s="2" t="inlineStr">
         <is>
@@ -20824,7 +20814,7 @@
         <v>2</v>
       </c>
       <c r="G353" s="3" t="n">
-        <v>105286</v>
+        <v>105288</v>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
@@ -20847,12 +20837,12 @@
       <c r="L353" s="3" t="inlineStr"/>
       <c r="M353" s="3" t="inlineStr"/>
       <c r="N353" s="3" t="n">
-        <v>207902</v>
+        <v>207907</v>
       </c>
       <c r="O353" s="2" t="inlineStr"/>
       <c r="P353" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20903,7 +20893,7 @@
         </is>
       </c>
       <c r="L354" s="3" t="n">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="M354" s="3" t="n">
         <v>9477</v>
@@ -20912,11 +20902,11 @@
         <v>429</v>
       </c>
       <c r="O354" s="2" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="P354" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20960,7 @@
       </c>
       <c r="P355" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -21024,17 +21014,17 @@
         <v>8956</v>
       </c>
       <c r="M356" s="3" t="n">
-        <v>55974</v>
+        <v>55975</v>
       </c>
       <c r="N356" s="3" t="n">
         <v>17912</v>
       </c>
       <c r="O356" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P356" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -21085,20 +21075,20 @@
         </is>
       </c>
       <c r="L357" s="3" t="n">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="M357" s="3" t="n">
-        <v>15992</v>
+        <v>4919</v>
       </c>
       <c r="N357" s="3" t="n">
         <v>475</v>
       </c>
       <c r="O357" s="2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P357" s="2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -21128,7 +21118,7 @@
         </is>
       </c>
       <c r="B1" t="n">
-        <v>159.924891</v>
+        <v>159.928299</v>
       </c>
     </row>
     <row r="2">
@@ -21139,7 +21129,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>open.er-api.com (取得日時: Sat, 29 Aug 2026 00:02:31 +0000)</t>
+          <t>open.er-api.com (取得日時: Sun, 30 Aug 2026 00:02:31 +0000)</t>
         </is>
       </c>
     </row>
@@ -21151,7 +21141,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/output/lootbar_knivesout_market_list.xlsx
+++ b/output/lootbar_knivesout_market_list.xlsx
@@ -606,20 +606,20 @@
         </is>
       </c>
       <c r="L2" s="3" t="n">
-        <v>3884</v>
+        <v>3123</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
@@ -649,7 +649,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
@@ -670,20 +670,20 @@
         </is>
       </c>
       <c r="L3" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M3" s="3" t="n">
-        <v>95460</v>
+        <v>95470</v>
       </c>
       <c r="N3" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -734,20 +734,20 @@
         </is>
       </c>
       <c r="L4" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>24985</v>
+        <v>24988</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>23423</v>
+        <v>23426</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>23684</v>
+        <v>23738</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
@@ -798,20 +798,20 @@
         </is>
       </c>
       <c r="L5" s="3" t="n">
-        <v>23423</v>
+        <v>23426</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>23423</v>
+        <v>23426</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>46847</v>
+        <v>46852</v>
       </c>
       <c r="O5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -862,20 +862,20 @@
         </is>
       </c>
       <c r="L6" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>84325</v>
+        <v>84333</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
@@ -926,20 +926,20 @@
         </is>
       </c>
       <c r="L7" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>140541</v>
+        <v>140556</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>249851</v>
+        <v>249877</v>
       </c>
       <c r="O7" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>351352</v>
+        <v>351389</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>351352</v>
+        <v>351389</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -990,20 +990,20 @@
         </is>
       </c>
       <c r="L8" s="3" t="n">
-        <v>351352</v>
+        <v>351389</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>351352</v>
+        <v>351389</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>702705</v>
+        <v>702778</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1022,18 +1022,18 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5864</v>
+        <v>5819</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5757</v>
+        <v>5768</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
@@ -1054,20 +1054,20 @@
         </is>
       </c>
       <c r="L9" s="3" t="n">
-        <v>5870</v>
+        <v>5817</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>8589</v>
+        <v>8590</v>
       </c>
       <c r="O9" s="2" t="n">
         <v>132</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1086,18 +1086,18 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8084</v>
+        <v>8518</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8282</v>
+        <v>8278</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -1118,20 +1118,20 @@
         </is>
       </c>
       <c r="L10" s="3" t="n">
-        <v>7761</v>
+        <v>8694</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>148308</v>
+        <v>148324</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>17177</v>
+        <v>17179</v>
       </c>
       <c r="O10" s="2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1150,18 +1150,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
@@ -1182,20 +1182,20 @@
         </is>
       </c>
       <c r="L11" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>41926</v>
+        <v>41931</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>34354</v>
+        <v>34358</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1236,20 +1236,20 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>39038</v>
+        <v>39042</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>39039</v>
+        <v>39043</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1290,20 +1290,20 @@
         </is>
       </c>
       <c r="L13" s="3" t="n">
-        <v>92787</v>
+        <v>92796</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>92787</v>
+        <v>92796</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="O13" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>17293</v>
+        <v>17295</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>17293</v>
+        <v>17295</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
@@ -1354,20 +1354,20 @@
         </is>
       </c>
       <c r="L14" s="3" t="n">
-        <v>312157</v>
+        <v>312190</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1408,20 +1408,20 @@
         </is>
       </c>
       <c r="L15" s="3" t="n">
-        <v>33850</v>
+        <v>33854</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>63261</v>
+        <v>63267</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="O15" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>14420</v>
+        <v>14421</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>14420</v>
+        <v>14421</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
@@ -1472,20 +1472,20 @@
         </is>
       </c>
       <c r="L16" s="3" t="n">
-        <v>22254</v>
+        <v>22256</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>63261</v>
+        <v>63267</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5309</v>
+        <v>5310</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
         <v>781</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>1562</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1593,7 @@
         <v>1562</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>224880</v>
+        <v>224903</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>3123</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
         <v>3123</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>265466</v>
+        <v>265494</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O19" s="2" t="n">
         <v>17</v>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1711,17 +1711,17 @@
         <v>5622</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>11243</v>
+        <v>11244</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>10931</v>
+        <v>10932</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>10931</v>
+        <v>10932</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
@@ -1772,20 +1772,20 @@
         </is>
       </c>
       <c r="L21" s="3" t="n">
-        <v>10931</v>
+        <v>10932</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>36494</v>
+        <v>36498</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="O21" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1826,20 +1826,20 @@
         </is>
       </c>
       <c r="L22" s="3" t="n">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>137839</v>
+        <v>137854</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1880,20 +1880,20 @@
         </is>
       </c>
       <c r="L23" s="3" t="n">
-        <v>39039</v>
+        <v>39043</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>317523</v>
+        <v>317556</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>78078</v>
+        <v>78086</v>
       </c>
       <c r="O23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1948,17 +1948,17 @@
         <v>1796</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>47</v>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2009,20 +2009,20 @@
         </is>
       </c>
       <c r="L25" s="3" t="n">
-        <v>2909</v>
+        <v>2418</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
         <v>1249</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>2499</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2095,18 +2095,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1238</v>
+        <v>979</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1091</v>
+        <v>1081</v>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
@@ -2127,20 +2127,20 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>967</v>
+        <v>1343</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>1557419</v>
+        <v>1557581</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>1562</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
@@ -2191,20 +2191,20 @@
         </is>
       </c>
       <c r="L28" s="3" t="n">
-        <v>2812</v>
+        <v>1562</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>3123</v>
       </c>
       <c r="O28" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2258,17 +2258,17 @@
         <v>3123</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>16824</v>
+        <v>16826</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O29" s="2" t="n">
         <v>46</v>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2286,23 +2286,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>625</v>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>625</v>
-      </c>
+      <c r="D30" s="3" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -2322,17 +2312,17 @@
         <v>625</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>1249</v>
       </c>
       <c r="O30" s="2" t="n">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2341,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
@@ -2383,20 +2373,20 @@
         </is>
       </c>
       <c r="L31" s="3" t="n">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>11392</v>
+        <v>11393</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>4685</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2440,7 @@
         <v>781</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>624626</v>
+        <v>624692</v>
       </c>
       <c r="N32" s="3" t="n">
         <v>1562</v>
@@ -2460,7 +2450,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2504,7 @@
         <v>2775</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>12650</v>
+        <v>12652</v>
       </c>
       <c r="N33" s="3" t="n">
         <v>3123</v>
@@ -2524,7 +2514,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2543,18 +2533,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>3785</v>
+        <v>3576</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>3405</v>
+        <v>3427</v>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
@@ -2575,20 +2565,20 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>3782</v>
+        <v>3775</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>20873</v>
+        <v>20876</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O34" s="2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2597,7 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
@@ -2618,7 +2608,7 @@
         <v>18</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
@@ -2639,20 +2629,20 @@
         </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>30184</v>
+        <v>30187</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2692,7 @@
         <v>781</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>6201</v>
+        <v>6202</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1562</v>
@@ -2712,7 +2702,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2762,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2819,20 +2809,20 @@
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="3" t="n">
-        <v>3560</v>
+        <v>3123</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>312313</v>
+        <v>312346</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O38" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2859,10 +2849,10 @@
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1633</v>
+        <v>1562</v>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
@@ -2886,7 +2876,7 @@
         <v>1562</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>142957</v>
+        <v>142972</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>3123</v>
@@ -2896,7 +2886,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2950,17 +2940,17 @@
         <v>4796</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>17179</v>
+        <v>17181</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -2979,18 +2969,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
@@ -3011,20 +3001,20 @@
         </is>
       </c>
       <c r="L41" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>14940</v>
+        <v>14941</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3043,7 +3033,7 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>4216</v>
+        <v>4217</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
@@ -3074,17 +3064,17 @@
         <v>4529</v>
       </c>
       <c r="M42" s="3" t="n">
-        <v>6048</v>
+        <v>6049</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>4638</v>
+        <v>2186</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3093,7 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>6151</v>
+        <v>6152</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
@@ -3134,7 +3124,7 @@
         <v>6273</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>8776</v>
+        <v>8777</v>
       </c>
       <c r="N43" s="3" t="n">
         <v>6765</v>
@@ -3144,7 +3134,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3163,18 +3153,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>11643</v>
+        <v>10649</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9280</v>
+        <v>9343</v>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
@@ -3191,20 +3181,20 @@
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="n">
-        <v>11637</v>
+        <v>11134</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>13598</v>
+        <v>13600</v>
       </c>
       <c r="N44" s="3" t="n">
-        <v>10833</v>
+        <v>11296</v>
       </c>
       <c r="O44" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3222,23 +3212,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>1562</v>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>1562</v>
-      </c>
+      <c r="D45" s="3" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3258,17 +3238,17 @@
         <v>1562</v>
       </c>
       <c r="M45" s="3" t="n">
-        <v>8609</v>
+        <v>8610</v>
       </c>
       <c r="N45" s="3" t="n">
         <v>3123</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3322,17 +3302,17 @@
         <v>3123</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3350,23 +3330,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>765</v>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>765</v>
-      </c>
+      <c r="D47" s="3" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -3396,7 +3366,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3415,7 +3385,7 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
@@ -3447,7 +3417,7 @@
         </is>
       </c>
       <c r="L48" s="3" t="n">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>2586</v>
@@ -3460,7 +3430,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3501,10 +3471,10 @@
         </is>
       </c>
       <c r="L49" s="3" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="M49" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N49" s="3" t="n">
         <v>3123</v>
@@ -3514,7 +3484,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3534,7 @@
         <v>2111</v>
       </c>
       <c r="M50" s="3" t="n">
-        <v>4094</v>
+        <v>4095</v>
       </c>
       <c r="N50" s="3" t="n">
         <v>781</v>
@@ -3574,7 +3544,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3621,10 +3591,10 @@
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="3" t="n">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="M51" s="3" t="n">
-        <v>4308</v>
+        <v>4309</v>
       </c>
       <c r="N51" s="3" t="n">
         <v>1562</v>
@@ -3634,7 +3604,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3653,18 +3623,18 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>6246</v>
+        <v>6403</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>4541</v>
+        <v>5162</v>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -3681,20 +3651,20 @@
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="3" t="n">
-        <v>6402</v>
+        <v>6559</v>
       </c>
       <c r="M52" s="3" t="n">
-        <v>7183</v>
+        <v>7184</v>
       </c>
       <c r="N52" s="3" t="n">
-        <v>3123</v>
+        <v>7043</v>
       </c>
       <c r="O52" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3718,7 @@
         <v>773</v>
       </c>
       <c r="M53" s="3" t="n">
-        <v>4761</v>
+        <v>4762</v>
       </c>
       <c r="N53" s="3" t="n">
         <v>781</v>
@@ -3758,7 +3728,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3782,7 @@
         <v>1780</v>
       </c>
       <c r="M54" s="3" t="n">
-        <v>11151</v>
+        <v>11152</v>
       </c>
       <c r="N54" s="3" t="n">
         <v>1941</v>
@@ -3822,7 +3792,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3876,17 +3846,17 @@
         <v>3392</v>
       </c>
       <c r="M55" s="3" t="n">
-        <v>30205</v>
+        <v>30209</v>
       </c>
       <c r="N55" s="3" t="n">
-        <v>5153</v>
+        <v>5154</v>
       </c>
       <c r="O55" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3909,12 @@
       <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="n">
-        <v>8122</v>
+        <v>8123</v>
       </c>
       <c r="O56" s="2" t="inlineStr"/>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -3963,18 +3933,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>10714</v>
+        <v>9934</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>9320</v>
+        <v>9397</v>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
@@ -3995,20 +3965,20 @@
         </is>
       </c>
       <c r="L57" s="3" t="n">
-        <v>10186</v>
+        <v>10562</v>
       </c>
       <c r="M57" s="3" t="n">
-        <v>30244</v>
+        <v>30248</v>
       </c>
       <c r="N57" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4027,18 +3997,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>3884</v>
+        <v>3851</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>3841</v>
+        <v>3842</v>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
@@ -4059,20 +4029,20 @@
         </is>
       </c>
       <c r="L58" s="3" t="n">
-        <v>4016</v>
+        <v>3870</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>10194</v>
+        <v>10195</v>
       </c>
       <c r="N58" s="3" t="n">
-        <v>4346</v>
+        <v>4289</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4091,18 +4061,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1904</v>
+        <v>2444</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>2511</v>
+        <v>2498</v>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
@@ -4123,20 +4093,20 @@
         </is>
       </c>
       <c r="L59" s="3" t="n">
-        <v>2525</v>
+        <v>2314</v>
       </c>
       <c r="M59" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N59" s="3" t="n">
-        <v>1562</v>
+        <v>2688</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4160,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4231,20 +4201,20 @@
         </is>
       </c>
       <c r="L61" s="3" t="n">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>3418</v>
+        <v>3419</v>
       </c>
       <c r="N61" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="O61" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4287,12 +4257,12 @@
       <c r="L62" s="3" t="inlineStr"/>
       <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="n">
-        <v>9682</v>
+        <v>9683</v>
       </c>
       <c r="O62" s="2" t="inlineStr"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4281,7 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
@@ -4322,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
@@ -4343,20 +4313,20 @@
         </is>
       </c>
       <c r="L63" s="3" t="n">
-        <v>17629</v>
+        <v>7028</v>
       </c>
       <c r="M63" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="N63" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4369,12 @@
       <c r="L64" s="3" t="inlineStr"/>
       <c r="M64" s="3" t="inlineStr"/>
       <c r="N64" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O64" s="2" t="inlineStr"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4447,12 +4417,12 @@
       <c r="L65" s="3" t="inlineStr"/>
       <c r="M65" s="3" t="inlineStr"/>
       <c r="N65" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O65" s="2" t="inlineStr"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4493,20 +4463,20 @@
         </is>
       </c>
       <c r="L66" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M66" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="N66" s="3" t="n">
-        <v>49970</v>
+        <v>49975</v>
       </c>
       <c r="O66" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4547,20 +4517,20 @@
         </is>
       </c>
       <c r="L67" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="O67" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4573,12 @@
       <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="3" t="inlineStr"/>
       <c r="N68" s="3" t="n">
-        <v>21862</v>
+        <v>21864</v>
       </c>
       <c r="O68" s="2" t="inlineStr"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4622,7 @@
         <v>312</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>3657</v>
+        <v>3658</v>
       </c>
       <c r="N69" s="3" t="n">
         <v>1562</v>
@@ -4662,7 +4632,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4680,23 +4650,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n">
-        <v>625</v>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>625</v>
-      </c>
+      <c r="D70" s="3" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -4722,11 +4682,11 @@
         <v>3123</v>
       </c>
       <c r="O70" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4773,14 +4733,14 @@
         <v>4966</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O71" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4794,17 @@
         <v>2499</v>
       </c>
       <c r="M72" s="3" t="n">
-        <v>1464815</v>
+        <v>1464967</v>
       </c>
       <c r="N72" s="3" t="n">
-        <v>11243</v>
+        <v>11244</v>
       </c>
       <c r="O72" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4891,14 +4851,14 @@
         <v>7382</v>
       </c>
       <c r="N73" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="O73" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4939,20 +4899,20 @@
         </is>
       </c>
       <c r="L74" s="3" t="n">
-        <v>8589</v>
+        <v>8590</v>
       </c>
       <c r="M74" s="3" t="n">
-        <v>20689</v>
+        <v>20691</v>
       </c>
       <c r="N74" s="3" t="n">
-        <v>17177</v>
+        <v>17179</v>
       </c>
       <c r="O74" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -4993,20 +4953,20 @@
         </is>
       </c>
       <c r="L75" s="3" t="n">
-        <v>17177</v>
+        <v>17179</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>26706</v>
+        <v>26709</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O75" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5020,7 @@
         <v>297</v>
       </c>
       <c r="M76" s="3" t="n">
-        <v>6293</v>
+        <v>6294</v>
       </c>
       <c r="N76" s="3" t="n">
         <v>312</v>
@@ -5070,7 +5030,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5114,7 +5074,7 @@
         <v>1171</v>
       </c>
       <c r="M77" s="3" t="n">
-        <v>5120</v>
+        <v>5121</v>
       </c>
       <c r="N77" s="3" t="n">
         <v>625</v>
@@ -5124,7 +5084,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5138,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5192,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5235,12 @@
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="3" t="inlineStr"/>
       <c r="N80" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="O80" s="2" t="inlineStr"/>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5321,20 +5281,20 @@
         </is>
       </c>
       <c r="L81" s="3" t="n">
-        <v>22839</v>
+        <v>22842</v>
       </c>
       <c r="M81" s="3" t="n">
-        <v>22839</v>
+        <v>22842</v>
       </c>
       <c r="N81" s="3" t="n">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="O81" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5377,12 +5337,12 @@
       <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="3" t="inlineStr"/>
       <c r="N82" s="3" t="n">
-        <v>19988</v>
+        <v>19990</v>
       </c>
       <c r="O82" s="2" t="inlineStr"/>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5432,17 +5392,17 @@
         <v>156</v>
       </c>
       <c r="M83" s="3" t="n">
-        <v>1561410</v>
+        <v>1561573</v>
       </c>
       <c r="N83" s="3" t="n">
         <v>781</v>
       </c>
       <c r="O83" s="2" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5429,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>312</v>
@@ -5492,7 +5452,7 @@
         <v>718</v>
       </c>
       <c r="M84" s="3" t="n">
-        <v>34136</v>
+        <v>34139</v>
       </c>
       <c r="N84" s="3" t="n">
         <v>1562</v>
@@ -5502,7 +5462,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5512,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5592,17 +5552,17 @@
         <v>1249</v>
       </c>
       <c r="M86" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N86" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O86" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5601,12 @@
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="3" t="n">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="O87" s="2" t="inlineStr"/>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5685,12 +5645,12 @@
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O88" s="2" t="inlineStr"/>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5689,12 @@
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="3" t="n">
-        <v>17177</v>
+        <v>17179</v>
       </c>
       <c r="O89" s="2" t="inlineStr"/>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5744,7 @@
         <v>489</v>
       </c>
       <c r="M90" s="3" t="n">
-        <v>84868</v>
+        <v>84877</v>
       </c>
       <c r="N90" s="3" t="n">
         <v>781</v>
@@ -5794,7 +5754,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5804,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5862,23 +5822,13 @@
           <t>不明（カテゴリタグなし）</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>740</v>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>740</v>
-      </c>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
@@ -5904,7 +5854,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5943,12 +5893,12 @@
       <c r="L93" s="3" t="inlineStr"/>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O93" s="2" t="inlineStr"/>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5987,12 +5937,12 @@
       <c r="L94" s="3" t="inlineStr"/>
       <c r="M94" s="3" t="inlineStr"/>
       <c r="N94" s="3" t="n">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="O94" s="2" t="inlineStr"/>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6031,12 +5981,12 @@
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="3" t="inlineStr"/>
       <c r="N95" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O95" s="2" t="inlineStr"/>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6075,12 +6025,12 @@
       <c r="L96" s="3" t="inlineStr"/>
       <c r="M96" s="3" t="inlineStr"/>
       <c r="N96" s="3" t="n">
-        <v>17177</v>
+        <v>17179</v>
       </c>
       <c r="O96" s="2" t="inlineStr"/>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6084,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6181,14 +6131,14 @@
         <v>2030</v>
       </c>
       <c r="N98" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="O98" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6229,20 +6179,20 @@
         </is>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4658</v>
+        <v>4659</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>5111</v>
+        <v>5112</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>9682</v>
+        <v>9683</v>
       </c>
       <c r="O99" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6283,20 +6233,20 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O100" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6339,12 +6289,12 @@
       <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="3" t="inlineStr"/>
       <c r="N101" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O101" s="2" t="inlineStr"/>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6385,20 +6335,20 @@
         </is>
       </c>
       <c r="L102" s="3" t="n">
-        <v>17741</v>
+        <v>17743</v>
       </c>
       <c r="M102" s="3" t="n">
-        <v>17741</v>
+        <v>17743</v>
       </c>
       <c r="N102" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O102" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6391,12 @@
       <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="3" t="inlineStr"/>
       <c r="N103" s="3" t="n">
-        <v>49970</v>
+        <v>49975</v>
       </c>
       <c r="O103" s="2" t="inlineStr"/>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6450,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6543,12 +6493,12 @@
       <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="3" t="inlineStr"/>
       <c r="N105" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="O105" s="2" t="inlineStr"/>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6591,12 +6541,12 @@
       <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="3" t="inlineStr"/>
       <c r="N106" s="3" t="n">
-        <v>9682</v>
+        <v>9683</v>
       </c>
       <c r="O106" s="2" t="inlineStr"/>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6565,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
@@ -6626,7 +6576,7 @@
         <v>1</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
@@ -6649,12 +6599,12 @@
       <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="3" t="inlineStr"/>
       <c r="N107" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O107" s="2" t="inlineStr"/>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6697,12 +6647,12 @@
       <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="3" t="inlineStr"/>
       <c r="N108" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O108" s="2" t="inlineStr"/>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6745,12 +6695,12 @@
       <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="3" t="inlineStr"/>
       <c r="N109" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O109" s="2" t="inlineStr"/>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6793,12 +6743,12 @@
       <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="3" t="inlineStr"/>
       <c r="N110" s="3" t="n">
-        <v>49970</v>
+        <v>49975</v>
       </c>
       <c r="O110" s="2" t="inlineStr"/>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6841,12 +6791,12 @@
       <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="3" t="inlineStr"/>
       <c r="N111" s="3" t="n">
-        <v>78078</v>
+        <v>78086</v>
       </c>
       <c r="O111" s="2" t="inlineStr"/>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6887,20 +6837,20 @@
         </is>
       </c>
       <c r="L112" s="3" t="n">
-        <v>85886</v>
+        <v>85895</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>95871</v>
+        <v>95881</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>109310</v>
+        <v>109321</v>
       </c>
       <c r="O112" s="2" t="n">
         <v>11</v>
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6941,20 +6891,20 @@
         </is>
       </c>
       <c r="L113" s="3" t="n">
-        <v>109310</v>
+        <v>109321</v>
       </c>
       <c r="M113" s="3" t="n">
-        <v>109310</v>
+        <v>109321</v>
       </c>
       <c r="N113" s="3" t="n">
-        <v>140541</v>
+        <v>140556</v>
       </c>
       <c r="O113" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -6995,20 +6945,20 @@
         </is>
       </c>
       <c r="L114" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="N114" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="O114" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7049,20 +6999,20 @@
         </is>
       </c>
       <c r="L115" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>187388</v>
+        <v>187407</v>
       </c>
       <c r="O115" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7103,20 +7053,20 @@
         </is>
       </c>
       <c r="L116" s="3" t="n">
-        <v>210811</v>
+        <v>210833</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>249851</v>
+        <v>249877</v>
       </c>
       <c r="N116" s="3" t="n">
-        <v>249851</v>
+        <v>249877</v>
       </c>
       <c r="O116" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7170,7 +7120,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7174,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7267,12 +7217,12 @@
       <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="3" t="inlineStr"/>
       <c r="N119" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="O119" s="2" t="inlineStr"/>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7313,20 +7263,20 @@
         </is>
       </c>
       <c r="L120" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M120" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="N120" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O120" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7369,12 +7319,12 @@
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="3" t="inlineStr"/>
       <c r="N121" s="3" t="n">
-        <v>22487</v>
+        <v>22489</v>
       </c>
       <c r="O121" s="2" t="inlineStr"/>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7415,20 +7365,20 @@
         </is>
       </c>
       <c r="L122" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="M122" s="3" t="n">
-        <v>18776</v>
+        <v>18778</v>
       </c>
       <c r="N122" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O122" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7469,20 +7419,20 @@
         </is>
       </c>
       <c r="L123" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M123" s="3" t="n">
-        <v>40541</v>
+        <v>40546</v>
       </c>
       <c r="N123" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O123" s="2" t="n">
         <v>7</v>
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7526,7 +7476,7 @@
         <v>1093</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="N124" s="3" t="n">
         <v>2186</v>
@@ -7536,7 +7486,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7590,7 +7540,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7631,20 +7581,20 @@
         </is>
       </c>
       <c r="L126" s="3" t="n">
-        <v>6377</v>
+        <v>6378</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>6377</v>
+        <v>6378</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="O126" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7685,20 +7635,20 @@
         </is>
       </c>
       <c r="L127" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M127" s="3" t="n">
-        <v>11732</v>
+        <v>11733</v>
       </c>
       <c r="N127" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O127" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7741,12 +7691,12 @@
       <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="3" t="inlineStr"/>
       <c r="N128" s="3" t="n">
-        <v>22487</v>
+        <v>22489</v>
       </c>
       <c r="O128" s="2" t="inlineStr"/>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7789,12 +7739,12 @@
       <c r="L129" s="3" t="inlineStr"/>
       <c r="M129" s="3" t="inlineStr"/>
       <c r="N129" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O129" s="2" t="inlineStr"/>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7792,7 @@
       <c r="O130" s="2" t="inlineStr"/>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7835,12 @@
       <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="3" t="inlineStr"/>
       <c r="N131" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O131" s="2" t="inlineStr"/>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7931,20 +7881,20 @@
         </is>
       </c>
       <c r="L132" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M132" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N132" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O132" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -7963,7 +7913,7 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
@@ -7974,7 +7924,7 @@
         <v>1</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
@@ -7995,20 +7945,20 @@
         </is>
       </c>
       <c r="L133" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="M133" s="3" t="n">
-        <v>15702</v>
+        <v>15703</v>
       </c>
       <c r="N133" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O133" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8051,12 +8001,12 @@
       <c r="L134" s="3" t="inlineStr"/>
       <c r="M134" s="3" t="inlineStr"/>
       <c r="N134" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="O134" s="2" t="inlineStr"/>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8097,20 +8047,20 @@
         </is>
       </c>
       <c r="L135" s="3" t="n">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>46847</v>
+        <v>46852</v>
       </c>
       <c r="O135" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8079,7 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
@@ -8140,7 +8090,7 @@
         <v>1</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
@@ -8161,20 +8111,20 @@
         </is>
       </c>
       <c r="L136" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="N136" s="3" t="n">
-        <v>70270</v>
+        <v>70278</v>
       </c>
       <c r="O136" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8215,20 +8165,20 @@
         </is>
       </c>
       <c r="L137" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M137" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="N137" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O137" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8255,10 +8205,10 @@
         </is>
       </c>
       <c r="F138" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>6319</v>
+        <v>6326</v>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
@@ -8279,20 +8229,20 @@
         </is>
       </c>
       <c r="L138" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M138" s="3" t="n">
-        <v>12582</v>
+        <v>12583</v>
       </c>
       <c r="N138" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O138" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8261,7 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
@@ -8322,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="G139" s="3" t="n">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
@@ -8356,7 +8306,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8413,14 +8363,14 @@
         <v>5099</v>
       </c>
       <c r="N140" s="3" t="n">
-        <v>522</v>
+        <v>312</v>
       </c>
       <c r="O140" s="2" t="n">
         <v>21</v>
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8434,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8548,7 +8498,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8592,7 +8542,7 @@
         <v>2046</v>
       </c>
       <c r="M143" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N143" s="3" t="n">
         <v>3123</v>
@@ -8602,7 +8552,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8643,10 +8593,10 @@
         </is>
       </c>
       <c r="L144" s="3" t="n">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="M144" s="3" t="n">
-        <v>10600</v>
+        <v>10601</v>
       </c>
       <c r="N144" s="3" t="n">
         <v>3904</v>
@@ -8656,7 +8606,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8654,7 @@
       <c r="O145" s="2" t="inlineStr"/>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8745,20 +8695,20 @@
         </is>
       </c>
       <c r="L146" s="3" t="n">
-        <v>4372</v>
+        <v>4373</v>
       </c>
       <c r="M146" s="3" t="n">
-        <v>52809</v>
+        <v>52815</v>
       </c>
       <c r="N146" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O146" s="2" t="n">
         <v>19</v>
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8801,12 +8751,12 @@
       <c r="L147" s="3" t="inlineStr"/>
       <c r="M147" s="3" t="inlineStr"/>
       <c r="N147" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O147" s="2" t="inlineStr"/>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8824,13 +8774,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr"/>
-      <c r="E148" s="2" t="inlineStr"/>
-      <c r="F148" s="2" t="inlineStr"/>
-      <c r="G148" s="3" t="inlineStr"/>
+      <c r="D148" s="3" t="n">
+        <v>9370</v>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>9370</v>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I148" s="2" t="n">
@@ -8847,20 +8807,20 @@
         </is>
       </c>
       <c r="L148" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="M148" s="3" t="n">
-        <v>18088</v>
+        <v>18090</v>
       </c>
       <c r="N148" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O148" s="2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8903,12 +8863,12 @@
       <c r="L149" s="3" t="inlineStr"/>
       <c r="M149" s="3" t="inlineStr"/>
       <c r="N149" s="3" t="n">
-        <v>24985</v>
+        <v>24988</v>
       </c>
       <c r="O149" s="2" t="inlineStr"/>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8927,18 +8887,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15617</v>
+        <v>15619</v>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
@@ -8959,20 +8919,20 @@
         </is>
       </c>
       <c r="L150" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="M150" s="3" t="n">
-        <v>39039</v>
+        <v>39043</v>
       </c>
       <c r="N150" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O150" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8991,18 +8951,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
         <v>17</v>
       </c>
       <c r="G151" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
@@ -9023,20 +8983,20 @@
         </is>
       </c>
       <c r="L151" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="M151" s="3" t="n">
-        <v>113905</v>
+        <v>113917</v>
       </c>
       <c r="N151" s="3" t="n">
-        <v>74955</v>
+        <v>74963</v>
       </c>
       <c r="O151" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9015,7 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>101502</v>
+        <v>101512</v>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
@@ -9066,7 +9026,7 @@
         <v>1</v>
       </c>
       <c r="G152" s="3" t="n">
-        <v>101502</v>
+        <v>101512</v>
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
@@ -9087,20 +9047,20 @@
         </is>
       </c>
       <c r="L152" s="3" t="n">
-        <v>101502</v>
+        <v>101512</v>
       </c>
       <c r="M152" s="3" t="n">
-        <v>101502</v>
+        <v>101512</v>
       </c>
       <c r="N152" s="3" t="n">
-        <v>203004</v>
+        <v>203025</v>
       </c>
       <c r="O152" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9114,7 @@
         <v>156</v>
       </c>
       <c r="M153" s="3" t="n">
-        <v>10216</v>
+        <v>10217</v>
       </c>
       <c r="N153" s="3" t="n">
         <v>312</v>
@@ -9164,7 +9124,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9188,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9278,17 +9238,17 @@
         <v>781</v>
       </c>
       <c r="M155" s="3" t="n">
-        <v>15300</v>
+        <v>15302</v>
       </c>
       <c r="N155" s="3" t="n">
         <v>1562</v>
       </c>
       <c r="O155" s="2" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9348,7 +9308,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9388,17 +9348,17 @@
         <v>3123</v>
       </c>
       <c r="M157" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N157" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O157" s="2" t="n">
         <v>13</v>
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9402,7 @@
         <v>781</v>
       </c>
       <c r="M158" s="3" t="n">
-        <v>1561566</v>
+        <v>1561729</v>
       </c>
       <c r="N158" s="3" t="n">
         <v>1562</v>
@@ -9452,7 +9412,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9466,7 @@
         <v>1562</v>
       </c>
       <c r="M159" s="3" t="n">
-        <v>18937</v>
+        <v>18939</v>
       </c>
       <c r="N159" s="3" t="n">
         <v>3123</v>
@@ -9516,7 +9476,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9534,13 +9494,23 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D160" s="3" t="inlineStr"/>
-      <c r="E160" s="2" t="inlineStr"/>
-      <c r="F160" s="2" t="inlineStr"/>
-      <c r="G160" s="3" t="inlineStr"/>
+      <c r="D160" s="3" t="n">
+        <v>3123</v>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>3123</v>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>直近30日間の取引データなし</t>
+          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
         </is>
       </c>
       <c r="I160" s="2" t="n">
@@ -9560,17 +9530,17 @@
         <v>3123</v>
       </c>
       <c r="M160" s="3" t="n">
-        <v>6532</v>
+        <v>6533</v>
       </c>
       <c r="N160" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O160" s="2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9594,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9643,7 +9613,7 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
@@ -9651,10 +9621,10 @@
         </is>
       </c>
       <c r="F162" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G162" s="3" t="n">
-        <v>1546</v>
+        <v>1507</v>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
@@ -9678,7 +9648,7 @@
         <v>2297</v>
       </c>
       <c r="M162" s="3" t="n">
-        <v>29795</v>
+        <v>29798</v>
       </c>
       <c r="N162" s="3" t="n">
         <v>1933</v>
@@ -9688,7 +9658,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9742,7 +9712,7 @@
         <v>3617</v>
       </c>
       <c r="M163" s="3" t="n">
-        <v>3799</v>
+        <v>3800</v>
       </c>
       <c r="N163" s="3" t="n">
         <v>3123</v>
@@ -9752,7 +9722,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9771,18 +9741,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>4265</v>
+        <v>3515</v>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="F164" s="2" t="n">
         <v>56</v>
       </c>
       <c r="G164" s="3" t="n">
-        <v>3922</v>
+        <v>3923</v>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
@@ -9803,20 +9773,20 @@
         </is>
       </c>
       <c r="L164" s="3" t="n">
-        <v>3968</v>
+        <v>3909</v>
       </c>
       <c r="M164" s="3" t="n">
-        <v>10150</v>
+        <v>10151</v>
       </c>
       <c r="N164" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O164" s="2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9843,10 +9813,10 @@
         </is>
       </c>
       <c r="F165" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G165" s="3" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
@@ -9880,7 +9850,7 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9914,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -9998,17 +9968,17 @@
         <v>1404</v>
       </c>
       <c r="M167" s="3" t="n">
-        <v>9597</v>
+        <v>9598</v>
       </c>
       <c r="N167" s="3" t="n">
-        <v>1524</v>
+        <v>1529</v>
       </c>
       <c r="O167" s="2" t="n">
         <v>15</v>
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10032,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10086,7 @@
         <v>308</v>
       </c>
       <c r="M169" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="N169" s="3" t="n">
         <v>312</v>
@@ -10126,7 +10096,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10167,20 +10137,20 @@
         </is>
       </c>
       <c r="L170" s="3" t="n">
-        <v>93694</v>
+        <v>93704</v>
       </c>
       <c r="M170" s="3" t="n">
-        <v>93694</v>
+        <v>93704</v>
       </c>
       <c r="N170" s="3" t="n">
-        <v>124925</v>
+        <v>124938</v>
       </c>
       <c r="O170" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10223,12 +10193,12 @@
       <c r="L171" s="3" t="inlineStr"/>
       <c r="M171" s="3" t="inlineStr"/>
       <c r="N171" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O171" s="2" t="inlineStr"/>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10278,7 +10248,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10325,7 +10295,7 @@
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="3" t="n">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="M173" s="3" t="n">
         <v>3326</v>
@@ -10338,7 +10308,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10377,12 +10347,12 @@
       <c r="L174" s="3" t="inlineStr"/>
       <c r="M174" s="3" t="inlineStr"/>
       <c r="N174" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="O174" s="2" t="inlineStr"/>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10419,20 +10389,20 @@
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M175" s="3" t="n">
-        <v>14024</v>
+        <v>14026</v>
       </c>
       <c r="N175" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O175" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10469,20 +10439,20 @@
       </c>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="3" t="n">
-        <v>11243</v>
+        <v>11244</v>
       </c>
       <c r="M176" s="3" t="n">
-        <v>11243</v>
+        <v>11244</v>
       </c>
       <c r="N176" s="3" t="n">
-        <v>22487</v>
+        <v>22489</v>
       </c>
       <c r="O176" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10519,20 +10489,20 @@
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="M177" s="3" t="n">
-        <v>15694</v>
+        <v>15695</v>
       </c>
       <c r="N177" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O177" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10569,20 +10539,20 @@
       </c>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M178" s="3" t="n">
-        <v>18895</v>
+        <v>18897</v>
       </c>
       <c r="N178" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O178" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10600,7 @@
       <c r="O179" s="2" t="inlineStr"/>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10671,20 +10641,20 @@
         </is>
       </c>
       <c r="L180" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M180" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="N180" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O180" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10727,12 +10697,12 @@
       <c r="L181" s="3" t="inlineStr"/>
       <c r="M181" s="3" t="inlineStr"/>
       <c r="N181" s="3" t="n">
-        <v>12493</v>
+        <v>12494</v>
       </c>
       <c r="O181" s="2" t="inlineStr"/>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10773,20 +10743,20 @@
         </is>
       </c>
       <c r="L182" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="M182" s="3" t="n">
-        <v>9369</v>
+        <v>9370</v>
       </c>
       <c r="N182" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O182" s="2" t="n">
         <v>8</v>
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10829,12 +10799,12 @@
       <c r="L183" s="3" t="inlineStr"/>
       <c r="M183" s="3" t="inlineStr"/>
       <c r="N183" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="O183" s="2" t="inlineStr"/>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10875,20 +10845,20 @@
         </is>
       </c>
       <c r="L184" s="3" t="n">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="M184" s="3" t="n">
-        <v>21081</v>
+        <v>21083</v>
       </c>
       <c r="N184" s="3" t="n">
-        <v>42162</v>
+        <v>42167</v>
       </c>
       <c r="O184" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10929,20 +10899,20 @@
         </is>
       </c>
       <c r="L185" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="M185" s="3" t="n">
-        <v>28108</v>
+        <v>28111</v>
       </c>
       <c r="N185" s="3" t="n">
-        <v>56216</v>
+        <v>56222</v>
       </c>
       <c r="O185" s="2" t="n">
         <v>23</v>
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -10986,17 +10956,17 @@
         <v>156</v>
       </c>
       <c r="M186" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N186" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O186" s="2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11040,17 +11010,17 @@
         <v>156</v>
       </c>
       <c r="M187" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N187" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O187" s="2" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11094,17 +11064,17 @@
         <v>156</v>
       </c>
       <c r="M188" s="3" t="n">
-        <v>101599</v>
+        <v>101609</v>
       </c>
       <c r="N188" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O188" s="2" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11152,7 +11122,7 @@
       <c r="O189" s="2" t="inlineStr"/>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11196,17 +11166,17 @@
         <v>156</v>
       </c>
       <c r="M190" s="3" t="n">
-        <v>28802</v>
+        <v>28805</v>
       </c>
       <c r="N190" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O190" s="2" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11250,17 +11220,17 @@
         <v>156</v>
       </c>
       <c r="M191" s="3" t="n">
-        <v>154178</v>
+        <v>154194</v>
       </c>
       <c r="N191" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O191" s="2" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11304,17 +11274,17 @@
         <v>156</v>
       </c>
       <c r="M192" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N192" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O192" s="2" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11332,7 @@
       <c r="O193" s="2" t="inlineStr"/>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11376,7 @@
         <v>156</v>
       </c>
       <c r="M194" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N194" s="3" t="n">
         <v>312</v>
@@ -11416,7 +11386,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11460,17 +11430,17 @@
         <v>156</v>
       </c>
       <c r="M195" s="3" t="n">
-        <v>156000</v>
+        <v>156017</v>
       </c>
       <c r="N195" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O195" s="2" t="n">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11524,17 +11494,17 @@
         <v>156</v>
       </c>
       <c r="M196" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N196" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O196" s="2" t="n">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11582,7 +11552,7 @@
       <c r="O197" s="2" t="inlineStr"/>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11606,7 @@
         <v>1249</v>
       </c>
       <c r="M198" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="N198" s="3" t="n">
         <v>312</v>
@@ -11646,7 +11616,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11687,20 +11657,20 @@
         </is>
       </c>
       <c r="L199" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M199" s="3" t="n">
-        <v>20335</v>
+        <v>20337</v>
       </c>
       <c r="N199" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O199" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11719,7 +11689,7 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>4372</v>
+        <v>4373</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
@@ -11730,7 +11700,7 @@
         <v>2</v>
       </c>
       <c r="G200" s="3" t="n">
-        <v>4372</v>
+        <v>4373</v>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
@@ -11754,17 +11724,17 @@
         <v>6092</v>
       </c>
       <c r="M200" s="3" t="n">
-        <v>6226</v>
+        <v>6227</v>
       </c>
       <c r="N200" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O200" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11783,7 +11753,7 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
@@ -11794,7 +11764,7 @@
         <v>2</v>
       </c>
       <c r="G201" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
@@ -11815,10 +11785,10 @@
         </is>
       </c>
       <c r="L201" s="3" t="n">
-        <v>4997</v>
+        <v>4998</v>
       </c>
       <c r="M201" s="3" t="n">
-        <v>10639</v>
+        <v>10640</v>
       </c>
       <c r="N201" s="3" t="n">
         <v>7496</v>
@@ -11828,7 +11798,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11869,20 +11839,20 @@
         </is>
       </c>
       <c r="L202" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="M202" s="3" t="n">
-        <v>10219</v>
+        <v>10220</v>
       </c>
       <c r="N202" s="3" t="n">
-        <v>9994</v>
+        <v>9995</v>
       </c>
       <c r="O202" s="2" t="n">
         <v>9</v>
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11923,20 +11893,20 @@
         </is>
       </c>
       <c r="L203" s="3" t="n">
-        <v>8120</v>
+        <v>8121</v>
       </c>
       <c r="M203" s="3" t="n">
-        <v>272603</v>
+        <v>272631</v>
       </c>
       <c r="N203" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="O203" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -11977,20 +11947,20 @@
         </is>
       </c>
       <c r="L204" s="3" t="n">
-        <v>15430</v>
+        <v>15431</v>
       </c>
       <c r="M204" s="3" t="n">
-        <v>15837</v>
+        <v>15839</v>
       </c>
       <c r="N204" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="O204" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12031,20 +12001,20 @@
         </is>
       </c>
       <c r="L205" s="3" t="n">
-        <v>19988</v>
+        <v>19990</v>
       </c>
       <c r="M205" s="3" t="n">
-        <v>48173</v>
+        <v>48178</v>
       </c>
       <c r="N205" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O205" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12087,12 +12057,12 @@
       <c r="L206" s="3" t="inlineStr"/>
       <c r="M206" s="3" t="inlineStr"/>
       <c r="N206" s="3" t="n">
-        <v>22487</v>
+        <v>22489</v>
       </c>
       <c r="O206" s="2" t="inlineStr"/>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12156,7 +12126,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12206,11 +12176,11 @@
         <v>312</v>
       </c>
       <c r="O208" s="2" t="n">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12221,7 @@
         </is>
       </c>
       <c r="L209" s="3" t="n">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="M209" s="3" t="n">
         <v>2964</v>
@@ -12264,7 +12234,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12282,23 +12252,13 @@
           <t>銃器</t>
         </is>
       </c>
-      <c r="D210" s="3" t="n">
-        <v>2030</v>
-      </c>
-      <c r="E210" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="F210" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G210" s="3" t="n">
-        <v>2030</v>
-      </c>
+      <c r="D210" s="3" t="inlineStr"/>
+      <c r="E210" s="2" t="inlineStr"/>
+      <c r="F210" s="2" t="inlineStr"/>
+      <c r="G210" s="3" t="inlineStr"/>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>※価格トレンドAPI(日次データ)に基づく近似値</t>
+          <t>直近30日間の取引データなし</t>
         </is>
       </c>
       <c r="I210" s="2" t="n">
@@ -12328,7 +12288,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12372,17 +12332,17 @@
         <v>3904</v>
       </c>
       <c r="M211" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="N211" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="O211" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12423,20 +12383,20 @@
         </is>
       </c>
       <c r="L212" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M212" s="3" t="n">
         <v>7104</v>
       </c>
       <c r="N212" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O212" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12479,12 +12439,12 @@
       <c r="L213" s="3" t="inlineStr"/>
       <c r="M213" s="3" t="inlineStr"/>
       <c r="N213" s="3" t="n">
-        <v>22487</v>
+        <v>22489</v>
       </c>
       <c r="O213" s="2" t="inlineStr"/>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12525,20 +12485,20 @@
         </is>
       </c>
       <c r="L214" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="M214" s="3" t="n">
-        <v>15616</v>
+        <v>15617</v>
       </c>
       <c r="N214" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O214" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12592,7 +12552,7 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12596,7 @@
         <v>2030</v>
       </c>
       <c r="M216" s="3" t="n">
-        <v>11726</v>
+        <v>11727</v>
       </c>
       <c r="N216" s="3" t="n">
         <v>4060</v>
@@ -12646,7 +12606,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12665,7 +12625,7 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
@@ -12676,7 +12636,7 @@
         <v>1</v>
       </c>
       <c r="G217" s="3" t="n">
-        <v>13742</v>
+        <v>13743</v>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
@@ -12697,20 +12657,20 @@
         </is>
       </c>
       <c r="L217" s="3" t="n">
-        <v>15375</v>
+        <v>15377</v>
       </c>
       <c r="M217" s="3" t="n">
-        <v>36994</v>
+        <v>36997</v>
       </c>
       <c r="N217" s="3" t="n">
-        <v>24985</v>
+        <v>24988</v>
       </c>
       <c r="O217" s="2" t="n">
         <v>3</v>
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12754,17 +12714,17 @@
         <v>3904</v>
       </c>
       <c r="M218" s="3" t="n">
-        <v>5729</v>
+        <v>5730</v>
       </c>
       <c r="N218" s="3" t="n">
-        <v>7808</v>
+        <v>7809</v>
       </c>
       <c r="O218" s="2" t="n">
         <v>2</v>
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12805,20 +12765,20 @@
         </is>
       </c>
       <c r="L219" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="M219" s="3" t="n">
-        <v>7027</v>
+        <v>7028</v>
       </c>
       <c r="N219" s="3" t="n">
-        <v>14054</v>
+        <v>14056</v>
       </c>
       <c r="O219" s="2" t="n">
         <v>6</v>
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12861,12 +12821,12 @@
       <c r="L220" s="3" t="inlineStr"/>
       <c r="M220" s="3" t="inlineStr"/>
       <c r="N220" s="3" t="n">
-        <v>31231</v>
+        <v>31235</v>
       </c>
       <c r="O220" s="2" t="inlineStr"/>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12907,20 +12867,20 @@
         </is>
       </c>
       <c r="L221" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="M221" s="3" t="n">
-        <v>18739</v>
+        <v>18741</v>
       </c>
       <c r="N221" s="3" t="n">
-        <v>37478</v>
+        <v>37481</v>
       </c>
       <c r="O221" s="2" t="n">
         <v>1</v>
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -12984,7 +12944,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13044,11 +13004,11 @@
         <v>3123</v>
       </c>
       <c r="O223" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13095,14 +13055,14 @@
         <v>7107</v>
       </c>
       <c r="N224" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O224" s="2" t="n">
         <v>12</v>
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13156,7 +13116,7 @@
         <v>781</v>
       </c>
       <c r="M225" s="3" t="n">
-        <v>7611</v>
+        <v>7612</v>
       </c>
       <c r="N225" s="3" t="n">
         <v>1562</v>
@@ -13166,7 +13126,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13217,7 +13177,7 @@
         </is>
       </c>
       <c r="L226" s="3" t="n">
-        <v>3009</v>
+        <v>1562</v>
       </c>
       <c r="M226" s="3" t="n">
         <v>3431</v>
@@ -13226,11 +13186,11 @@
         <v>3123</v>
       </c>
       <c r="O226" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13287,14 +13247,14 @@
         <v>3734</v>
       </c>
       <c r="N227" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O227" s="2" t="n">
         <v>4</v>
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13298,7 @@
         <v>156</v>
       </c>
       <c r="M228" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N228" s="3" t="n">
         <v>312</v>
@@ -13348,7 +13308,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13392,17 +13352,17 @@
         <v>156</v>
       </c>
       <c r="M229" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N229" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O229" s="2" t="n">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13456,17 +13416,17 @@
         <v>156</v>
       </c>
       <c r="M230" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N230" s="3" t="n">
         <v>312</v>
       </c>
       <c r="O230" s="2" t="n">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13510,17 +13470,17 @@
         <v>781</v>
       </c>
       <c r="M231" s="3" t="n">
-        <v>156157</v>
+        <v>156173</v>
       </c>
       <c r="N231" s="3" t="n">
         <v>1562</v>
       </c>
       <c r="O231" s="2" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13534,7 @@
         <v>1562</v>
       </c>
       <c r="M232" s="3" t="n">
-        <v>3849</v>
+        <v>3850</v>
       </c>
       <c r="N232" s="3" t="n">
         <v>3123</v>
@@ -13584,7 +13544,7 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13628,17 +13588,17 @@
         <v>3123</v>
       </c>
       <c r="M233" s="3" t="n">
-        <v>7114</v>
+        <v>7115</v>
       </c>
       <c r="N233" s="3" t="n">
-        <v>6246</v>
+        <v>6247</v>
       </c>
       <c r="O233" s="2" t="n">
         <v>34</v>
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13702,7 +13662,7 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13706,7 @@
         <v>2664</v>
       </c>
       <c r="M235" s="3" t="n">
-        <v>4208</v>
+        <v>4209</v>
       </c>
       <c r="N235" s="3" t="n">
         <v>3123</v>
@@ -13756,7 +13716,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13800,7 +13760,7 @@
         <v>3904</v>
       </c>
       <c r="M236" s="3" t="n">
-        <v>6440</v>
+        <v>6441</v>
       </c>
       <c r="N236" s="3" t="n">
         <v>3904</v>
@@ -13810,7 +13770,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -13858,7 +13818,7 @@
       <c r="O237" s="2" t="inlineStr"/>
       <c r="P237" s="2